--- a/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
+++ b/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="7"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -484,15 +484,6 @@
     <t xml:space="preserve">Idade - ano(s)</t>
   </si>
   <si>
-    <t xml:space="preserve">data('IDADEANO')&lt;6 || data('DOB')!="D:NS,M:NS,Y:NS"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The child must be younger than 6 years old:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança deve ter menos de 6 anos de idade:</t>
-  </si>
-  <si>
     <t>IDADEMES</t>
   </si>
   <si>
@@ -502,15 +493,6 @@
     <t xml:space="preserve">Idade - mes(es)</t>
   </si>
   <si>
-    <t xml:space="preserve">data('IDADEMES')&lt;13 || data('DOB')!="D:NS,M:NS,Y:NS"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be less than 13:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve ser menor que 13:</t>
-  </si>
-  <si>
     <t>sim/não</t>
   </si>
   <si>
@@ -985,7 +967,7 @@
     <t xml:space="preserve">data('JAINC') != null || data('CONSENT') == '2'</t>
   </si>
   <si>
-    <t xml:space="preserve">data('PODEVAC')=='2'|| data('PODEINC')=='2'  || data('JAINC') == '1' || data('BRACOCRI') &lt;110 || data('TEMPERATURA')&gt;37.9 || data('VENAOVAS') == '2' || data('SARVAC') == '1'</t>
+    <t xml:space="preserve">data('PODEVAC')=='2'|| data('PODEINC')=='2'  || data('JAINC') == '1' || data('BRACOCRI') &lt;110 || data('TEMPERATURA')&gt;37.9 || data('VENAOVAS') == '2' ||  data('VENAOVAS2') == '2' || data('SARVAC') != '1' || data('SARVAC2') == '1'</t>
   </si>
   <si>
     <t>INC</t>
@@ -1039,22 +1021,40 @@
     <t xml:space="preserve">A temperatura é mais alta do que 37,9 ({{data.TEMPERATURA}})</t>
   </si>
   <si>
+    <t xml:space="preserve">data('VENAOVAS2') == '2'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mother/guardian could not confirm that the child did not receive the first measles vaccine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mãe/tutor não pôde confirmar que a criança não recebeu a primeira vacina do sarampo</t>
+  </si>
+  <si>
     <t xml:space="preserve">data('VENAOVAS') == '2'</t>
   </si>
   <si>
-    <t xml:space="preserve">Mother/guardian could not confirm that the child did not receive measles vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mãe/tutor não pôde confirmar que a criança não recebeu a vacina do sarampo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('SARVAC') == '1'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The child has previously received the measles vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança recebeu a vacina do sarampo</t>
+    <t xml:space="preserve">Mother/guardian could not confirm that the child did not receive the second measles vaccine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mãe/tutor não pôde confirmar que a criança não recebeu a segunda vacina do sarampo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data('SARVAC') != '1'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The child has not previously received the first measles vaccine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A criança não recebeu a primeira vacina do sarampo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data('SARVAC2') == '1'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The child has previously received the second measles vaccine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A criança recebeu a segunda vacina do sarampo</t>
   </si>
   <si>
     <t>RANDOM1</t>
@@ -3153,38 +3153,22 @@
       <c r="H70" t="s">
         <v>152</v>
       </c>
-      <c r="K70" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="L70" t="s">
-        <v>154</v>
-      </c>
-      <c r="M70" t="s">
-        <v>155</v>
-      </c>
+      <c r="K70" s="4"/>
     </row>
     <row r="71">
       <c r="D71" t="s">
         <v>78</v>
       </c>
       <c r="F71" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G71" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H71" t="s">
-        <v>158</v>
-      </c>
-      <c r="K71" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="L71" t="s">
-        <v>160</v>
-      </c>
-      <c r="M71" t="s">
-        <v>161</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="K71" s="4"/>
     </row>
     <row r="72">
       <c r="B72" t="s">
@@ -3206,16 +3190,16 @@
         <v>98</v>
       </c>
       <c r="E75" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G75" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="H75" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="R75" t="b">
         <v>1</v>
@@ -3226,7 +3210,7 @@
         <v>55</v>
       </c>
       <c r="C76" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F76" s="4"/>
     </row>
@@ -3235,16 +3219,16 @@
         <v>98</v>
       </c>
       <c r="E77" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G77" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="H77" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="78">
@@ -3252,7 +3236,7 @@
         <v>55</v>
       </c>
       <c r="C78" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F78" s="4"/>
     </row>
@@ -3261,25 +3245,25 @@
         <v>98</v>
       </c>
       <c r="E79" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="K79" t="s">
+        <v>170</v>
+      </c>
+      <c r="L79" t="s">
+        <v>171</v>
+      </c>
+      <c r="M79" t="s">
         <v>172</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="K79" t="s">
-        <v>176</v>
-      </c>
-      <c r="L79" t="s">
-        <v>177</v>
-      </c>
-      <c r="M79" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="80">
@@ -3305,7 +3289,7 @@
         <v>55</v>
       </c>
       <c r="C83" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="84">
@@ -3318,22 +3302,22 @@
         <v>78</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="H85" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K85" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="L85" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="M85" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="86">
@@ -3341,10 +3325,10 @@
         <v>106</v>
       </c>
       <c r="E86" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="87">
@@ -3352,22 +3336,22 @@
         <v>78</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G87" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="H87" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="K87" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="L87" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="M87" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="88">
@@ -3375,10 +3359,10 @@
         <v>106</v>
       </c>
       <c r="E88" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="89">
@@ -3386,22 +3370,22 @@
         <v>78</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G89" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H89" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="K89" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="L89" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="M89" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="90">
@@ -3409,10 +3393,10 @@
         <v>106</v>
       </c>
       <c r="E90" t="s">
+        <v>185</v>
+      </c>
+      <c r="F90" s="4" t="s">
         <v>191</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="91">
@@ -3420,7 +3404,7 @@
         <v>55</v>
       </c>
       <c r="C91" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F91" s="4"/>
     </row>
@@ -3429,7 +3413,7 @@
         <v>41</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="I92">
         <v>999999999</v>
@@ -3446,7 +3430,7 @@
         <v>55</v>
       </c>
       <c r="C94" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F94" s="4"/>
     </row>
@@ -3455,7 +3439,7 @@
         <v>41</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="I95">
         <v>999999999</v>
@@ -3483,25 +3467,25 @@
         <v>98</v>
       </c>
       <c r="E99" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F99" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="G99" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="H99" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="K99" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="L99" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="M99" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="100">
@@ -3509,7 +3493,7 @@
         <v>55</v>
       </c>
       <c r="C100" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="101">
@@ -3517,25 +3501,25 @@
         <v>98</v>
       </c>
       <c r="E101" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G101" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="H101" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="K101" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="L101" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="M101" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="102">
@@ -3548,7 +3532,7 @@
         <v>55</v>
       </c>
       <c r="C103" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="104">
@@ -3556,25 +3540,25 @@
         <v>98</v>
       </c>
       <c r="E104" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F104" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="G104" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="H104" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="K104" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="L104" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="M104" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="105">
@@ -3588,7 +3572,7 @@
         <v>55</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D106" s="8"/>
       <c r="E106" s="8"/>
@@ -3609,27 +3593,27 @@
         <v>98</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="I107" s="8"/>
       <c r="J107" s="8"/>
       <c r="K107" s="11" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="L107" s="8" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="M107" s="8" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="108">
@@ -3655,7 +3639,7 @@
         <v>55</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="8"/>
@@ -3676,27 +3660,27 @@
         <v>98</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G110" s="11" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="H110" s="11" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="I110" s="8"/>
       <c r="J110" s="8"/>
       <c r="K110" s="8" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="L110" s="8" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="M110" s="8" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="111">
@@ -3726,21 +3710,21 @@
         <v>55</v>
       </c>
       <c r="C113" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="114">
       <c r="D114" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G114" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="H114" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="115">
@@ -3758,28 +3742,28 @@
         <v>63</v>
       </c>
       <c r="F117" t="s">
+        <v>220</v>
+      </c>
+      <c r="G117" t="s">
+        <v>221</v>
+      </c>
+      <c r="H117" t="s">
+        <v>222</v>
+      </c>
+      <c r="K117" t="s">
+        <v>223</v>
+      </c>
+      <c r="L117" t="s">
+        <v>224</v>
+      </c>
+      <c r="M117" t="s">
+        <v>225</v>
+      </c>
+      <c r="N117" t="s">
         <v>226</v>
       </c>
-      <c r="G117" t="s">
+      <c r="O117" t="s">
         <v>227</v>
-      </c>
-      <c r="H117" t="s">
-        <v>228</v>
-      </c>
-      <c r="K117" t="s">
-        <v>229</v>
-      </c>
-      <c r="L117" t="s">
-        <v>230</v>
-      </c>
-      <c r="M117" t="s">
-        <v>231</v>
-      </c>
-      <c r="N117" t="s">
-        <v>232</v>
-      </c>
-      <c r="O117" t="s">
-        <v>233</v>
       </c>
       <c r="P117" t="s">
         <v>92</v>
@@ -3790,22 +3774,22 @@
         <v>78</v>
       </c>
       <c r="F118" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="G118" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="H118" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="K118" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L118" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M118" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="119">
@@ -3823,16 +3807,16 @@
         <v>98</v>
       </c>
       <c r="E121" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F121" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G121" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H121" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="122">
@@ -3840,7 +3824,7 @@
         <v>55</v>
       </c>
       <c r="C122" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="123">
@@ -3849,17 +3833,17 @@
       </c>
       <c r="E123" s="4"/>
       <c r="F123" s="4" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I123" s="4"/>
       <c r="K123" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="L123" t="s">
         <v>143</v>
@@ -3888,16 +3872,16 @@
         <v>98</v>
       </c>
       <c r="E127" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F127" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="G127" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="128">
@@ -3905,16 +3889,16 @@
         <v>98</v>
       </c>
       <c r="E128" t="s">
+        <v>243</v>
+      </c>
+      <c r="F128" t="s">
+        <v>247</v>
+      </c>
+      <c r="G128" t="s">
+        <v>248</v>
+      </c>
+      <c r="H128" s="4" t="s">
         <v>249</v>
-      </c>
-      <c r="F128" t="s">
-        <v>253</v>
-      </c>
-      <c r="G128" t="s">
-        <v>254</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="129">
@@ -3922,16 +3906,16 @@
         <v>98</v>
       </c>
       <c r="E129" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F129" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="G129" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="130">
@@ -3939,7 +3923,7 @@
         <v>55</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D130" s="12"/>
       <c r="E130" s="12"/>
@@ -3956,12 +3940,12 @@
       </c>
       <c r="E131" s="12"/>
       <c r="F131" s="12" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="G131" s="12"/>
       <c r="H131" s="12"/>
       <c r="I131" s="12" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="132">
@@ -3984,12 +3968,12 @@
       </c>
       <c r="E133" s="12"/>
       <c r="F133" s="12" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="G133" s="12"/>
       <c r="H133" s="12"/>
       <c r="I133" s="12" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="134">
@@ -4019,16 +4003,16 @@
         <v>98</v>
       </c>
       <c r="E137" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F137" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="G137" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="H137" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="138">
@@ -4036,16 +4020,16 @@
         <v>98</v>
       </c>
       <c r="E138" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F138" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="G138" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="H138" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="139">
@@ -4053,16 +4037,16 @@
         <v>98</v>
       </c>
       <c r="E139" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F139" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="G139" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="H139" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="140">
@@ -4080,16 +4064,16 @@
         <v>98</v>
       </c>
       <c r="E142" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F142" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="G142" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H142" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="143">
@@ -4097,13 +4081,13 @@
         <v>63</v>
       </c>
       <c r="F143" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="G143" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="H143" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="144">
@@ -4121,16 +4105,16 @@
         <v>98</v>
       </c>
       <c r="E146" s="13" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F146" s="13" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="G146" s="13" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="H146" s="13" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="147" s="13" customFormat="1">
@@ -4138,7 +4122,7 @@
         <v>55</v>
       </c>
       <c r="C147" s="13" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="148" s="13" customFormat="1">
@@ -4146,16 +4130,16 @@
         <v>82</v>
       </c>
       <c r="E148" s="13" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="F148" s="13" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G148" s="13" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="H148" s="13" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="149" s="13" customFormat="1">
@@ -4163,7 +4147,7 @@
         <v>55</v>
       </c>
       <c r="C149" s="13" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="150" s="13" customFormat="1">
@@ -4171,13 +4155,13 @@
         <v>63</v>
       </c>
       <c r="F150" s="13" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="G150" s="13" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="H150" s="13" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="151" s="13" customFormat="1">
@@ -4205,16 +4189,16 @@
         <v>98</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="G155" s="6" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="156" s="6" customFormat="1">
@@ -4222,7 +4206,7 @@
         <v>55</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="157" s="6" customFormat="1">
@@ -4230,16 +4214,16 @@
         <v>82</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="F157" s="6" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="G157" s="6" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="H157" s="6" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="158" s="6" customFormat="1">
@@ -4247,7 +4231,7 @@
         <v>55</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="159" s="6" customFormat="1">
@@ -4255,13 +4239,13 @@
         <v>63</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="G159" s="6" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="H159" s="6" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="160" s="6" customFormat="1">
@@ -4286,16 +4270,16 @@
     </row>
     <row r="164">
       <c r="D164" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F164" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G164" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="H164" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="165">
@@ -4313,25 +4297,25 @@
         <v>98</v>
       </c>
       <c r="E167" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F167" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="G167" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="H167" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="K167" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="L167" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="M167" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="168">
@@ -4339,7 +4323,7 @@
         <v>55</v>
       </c>
       <c r="C168" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="169">
@@ -4347,13 +4331,13 @@
         <v>63</v>
       </c>
       <c r="F169" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="G169" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="H169" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="170">
@@ -4366,25 +4350,25 @@
         <v>98</v>
       </c>
       <c r="E171" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F171" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="G171" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="H171" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="K171" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="L171" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="M171" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="172">
@@ -4392,7 +4376,7 @@
         <v>55</v>
       </c>
       <c r="C172" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="173">
@@ -4400,13 +4384,13 @@
         <v>63</v>
       </c>
       <c r="F173" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="G173" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="H173" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="174">
@@ -4419,25 +4403,25 @@
         <v>98</v>
       </c>
       <c r="E175" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F175" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="G175" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="H175" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="K175" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="L175" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="M175" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="176">
@@ -4450,7 +4434,7 @@
         <v>55</v>
       </c>
       <c r="C177" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="178">
@@ -4463,7 +4447,7 @@
         <v>41</v>
       </c>
       <c r="F179" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="I179">
         <v>2</v>
@@ -4471,13 +4455,13 @@
     </row>
     <row r="180">
       <c r="D180" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="H180" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="181">
@@ -4485,19 +4469,19 @@
         <v>55</v>
       </c>
       <c r="C181" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="G181" s="4"/>
     </row>
     <row r="182">
       <c r="D182" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="H182" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="183">
@@ -4511,19 +4495,19 @@
         <v>55</v>
       </c>
       <c r="C184" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="G184" s="4"/>
     </row>
     <row r="185">
       <c r="D185" t="s">
+        <v>316</v>
+      </c>
+      <c r="G185" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="H185" t="s">
         <v>322</v>
-      </c>
-      <c r="G185" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="H185" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="186">
@@ -4537,19 +4521,19 @@
         <v>55</v>
       </c>
       <c r="C187" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="G187" s="4"/>
     </row>
     <row r="188">
       <c r="D188" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="G188" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="H188" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="189">
@@ -4563,19 +4547,19 @@
         <v>55</v>
       </c>
       <c r="C190" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="G190" s="4"/>
     </row>
     <row r="191">
       <c r="D191" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="G191" s="4" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="H191" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="192">
@@ -4589,19 +4573,19 @@
         <v>55</v>
       </c>
       <c r="C193" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="G193" s="4"/>
     </row>
     <row r="194">
       <c r="D194" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="G194" s="4" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="H194" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="195">
@@ -4611,209 +4595,221 @@
       <c r="G195" s="4"/>
     </row>
     <row r="196">
-      <c r="B196" t="s">
+      <c r="A196" s="8"/>
+      <c r="B196" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C196" t="s">
-        <v>338</v>
-      </c>
-      <c r="G196" s="4"/>
+      <c r="C196" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="D196" s="8"/>
+      <c r="E196" s="8"/>
+      <c r="F196" s="8"/>
+      <c r="G196"/>
+      <c r="H196" s="8"/>
     </row>
     <row r="197">
-      <c r="D197" t="s">
-        <v>322</v>
-      </c>
-      <c r="G197" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="H197" t="s">
-        <v>340</v>
+      <c r="A197" s="8"/>
+      <c r="B197" s="9"/>
+      <c r="C197" s="8"/>
+      <c r="D197" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="E197" s="8"/>
+      <c r="F197" s="8"/>
+      <c r="G197" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="H197" s="11" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="198">
-      <c r="B198" t="s">
+      <c r="A198" s="8"/>
+      <c r="B198" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G198" s="4"/>
+      <c r="C198" s="8"/>
+      <c r="D198" s="8"/>
+      <c r="E198" s="8"/>
+      <c r="F198" s="8"/>
+      <c r="G198"/>
+      <c r="H198" s="8"/>
     </row>
     <row r="199">
       <c r="B199" t="s">
         <v>55</v>
       </c>
       <c r="C199" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="G199" s="4"/>
     </row>
     <row r="200">
       <c r="D200" t="s">
-        <v>322</v>
-      </c>
-      <c r="G200" s="4" t="s">
-        <v>342</v>
+        <v>316</v>
+      </c>
+      <c r="G200" s="10" t="s">
+        <v>336</v>
       </c>
       <c r="H200" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="201">
       <c r="B201" t="s">
         <v>73</v>
       </c>
+      <c r="G201" s="4"/>
     </row>
     <row r="202">
-      <c r="B202" t="s">
-        <v>49</v>
-      </c>
+      <c r="A202" s="8"/>
+      <c r="B202" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C202" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="D202" s="8"/>
+      <c r="E202" s="8"/>
+      <c r="F202" s="8"/>
+      <c r="G202"/>
+      <c r="H202" s="8"/>
     </row>
     <row r="203">
-      <c r="B203" t="s">
-        <v>67</v>
+      <c r="A203" s="8"/>
+      <c r="B203" s="9"/>
+      <c r="C203" s="8"/>
+      <c r="D203" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="E203" s="8"/>
+      <c r="F203" s="8"/>
+      <c r="G203" t="s">
+        <v>339</v>
+      </c>
+      <c r="H203" s="10" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="204">
-      <c r="B204" t="s">
-        <v>40</v>
-      </c>
+      <c r="A204" s="8"/>
+      <c r="B204" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C204" s="8"/>
+      <c r="D204" s="8"/>
+      <c r="E204" s="8"/>
+      <c r="F204" s="8"/>
+      <c r="G204" s="8"/>
+      <c r="H204" s="8"/>
     </row>
     <row r="205">
-      <c r="D205" t="s">
-        <v>78</v>
-      </c>
-      <c r="F205" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G205" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="H205" t="s">
-        <v>346</v>
-      </c>
-      <c r="K205" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="L205" t="s">
-        <v>348</v>
-      </c>
-      <c r="M205" t="s">
-        <v>349</v>
-      </c>
+      <c r="B205" t="s">
+        <v>55</v>
+      </c>
+      <c r="C205" t="s">
+        <v>341</v>
+      </c>
+      <c r="G205" s="4"/>
     </row>
     <row r="206">
       <c r="D206" t="s">
-        <v>78</v>
-      </c>
-      <c r="F206" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="G206" s="4" t="s">
-        <v>351</v>
+        <v>316</v>
+      </c>
+      <c r="G206" s="10" t="s">
+        <v>342</v>
       </c>
       <c r="H206" t="s">
-        <v>352</v>
-      </c>
-      <c r="K206" t="s">
-        <v>353</v>
-      </c>
-      <c r="L206" t="s">
-        <v>354</v>
-      </c>
-      <c r="M206" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
     </row>
     <row r="207">
-      <c r="D207" t="s">
-        <v>41</v>
-      </c>
-      <c r="F207" t="s">
-        <v>356</v>
-      </c>
-      <c r="I207" t="s">
-        <v>357</v>
+      <c r="B207" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="208">
-      <c r="D208" t="s">
-        <v>322</v>
-      </c>
-      <c r="G208" t="s">
-        <v>358</v>
-      </c>
-      <c r="H208" t="s">
-        <v>359</v>
+      <c r="B208" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="209">
-      <c r="D209" t="s">
-        <v>41</v>
-      </c>
-      <c r="F209" t="s">
-        <v>321</v>
-      </c>
-      <c r="I209">
-        <v>1</v>
+      <c r="B209" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="210">
       <c r="B210" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="211">
-      <c r="B211" t="s">
-        <v>40</v>
+      <c r="D211" t="s">
+        <v>78</v>
+      </c>
+      <c r="F211" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="G211" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="H211" t="s">
+        <v>346</v>
+      </c>
+      <c r="K211" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="L211" t="s">
+        <v>348</v>
+      </c>
+      <c r="M211" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="212">
       <c r="D212" t="s">
-        <v>41</v>
-      </c>
-      <c r="F212" t="s">
-        <v>360</v>
-      </c>
-      <c r="I212" t="s">
-        <v>361</v>
+        <v>78</v>
+      </c>
+      <c r="F212" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="G212" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="H212" t="s">
+        <v>352</v>
+      </c>
+      <c r="K212" t="s">
+        <v>353</v>
+      </c>
+      <c r="L212" t="s">
+        <v>354</v>
+      </c>
+      <c r="M212" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="213">
       <c r="D213" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F213" t="s">
-        <v>360</v>
-      </c>
-      <c r="G213" t="s">
-        <v>362</v>
-      </c>
-      <c r="H213" t="s">
-        <v>363</v>
-      </c>
-      <c r="Q213" t="b">
-        <v>0</v>
+        <v>356</v>
+      </c>
+      <c r="I213" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="214">
       <c r="D214" t="s">
-        <v>364</v>
-      </c>
-      <c r="F214" t="s">
-        <v>365</v>
+        <v>316</v>
       </c>
       <c r="G214" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="H214" t="s">
-        <v>367</v>
-      </c>
-      <c r="K214" t="s">
-        <v>368</v>
-      </c>
-      <c r="L214" t="s">
-        <v>204</v>
-      </c>
-      <c r="M214" t="s">
-        <v>205</v>
+        <v>359</v>
       </c>
     </row>
     <row r="215">
@@ -4821,167 +4817,239 @@
         <v>41</v>
       </c>
       <c r="F215" t="s">
-        <v>369</v>
-      </c>
-      <c r="I215" t="s">
-        <v>370</v>
+        <v>315</v>
+      </c>
+      <c r="I215">
+        <v>1</v>
       </c>
     </row>
     <row r="216">
-      <c r="D216" t="s">
-        <v>78</v>
-      </c>
-      <c r="F216" t="s">
-        <v>371</v>
-      </c>
-      <c r="G216" t="s">
-        <v>372</v>
-      </c>
-      <c r="H216" t="s">
-        <v>373</v>
-      </c>
-      <c r="K216" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="L216" t="s">
-        <v>375</v>
-      </c>
-      <c r="M216" t="s">
-        <v>376</v>
+      <c r="B216" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="217">
-      <c r="D217" t="s">
-        <v>41</v>
-      </c>
-      <c r="F217" t="s">
-        <v>377</v>
-      </c>
-      <c r="I217" t="s">
-        <v>378</v>
+      <c r="B217" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="218">
       <c r="D218" t="s">
-        <v>322</v>
-      </c>
-      <c r="G218" t="s">
+        <v>41</v>
+      </c>
+      <c r="F218" t="s">
+        <v>360</v>
+      </c>
+      <c r="I218" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="D219" t="s">
+        <v>46</v>
+      </c>
+      <c r="F219" t="s">
+        <v>360</v>
+      </c>
+      <c r="G219" t="s">
+        <v>362</v>
+      </c>
+      <c r="H219" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q219" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="D220" t="s">
+        <v>364</v>
+      </c>
+      <c r="F220" t="s">
+        <v>365</v>
+      </c>
+      <c r="G220" t="s">
+        <v>366</v>
+      </c>
+      <c r="H220" t="s">
+        <v>367</v>
+      </c>
+      <c r="K220" t="s">
+        <v>368</v>
+      </c>
+      <c r="L220" t="s">
+        <v>198</v>
+      </c>
+      <c r="M220" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="D221" t="s">
+        <v>41</v>
+      </c>
+      <c r="F221" t="s">
+        <v>369</v>
+      </c>
+      <c r="I221" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="D222" t="s">
+        <v>78</v>
+      </c>
+      <c r="F222" t="s">
+        <v>371</v>
+      </c>
+      <c r="G222" t="s">
+        <v>372</v>
+      </c>
+      <c r="H222" t="s">
+        <v>373</v>
+      </c>
+      <c r="K222" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="L222" t="s">
+        <v>375</v>
+      </c>
+      <c r="M222" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="D223" t="s">
+        <v>41</v>
+      </c>
+      <c r="F223" t="s">
+        <v>377</v>
+      </c>
+      <c r="I223" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="D224" t="s">
+        <v>316</v>
+      </c>
+      <c r="G224" t="s">
         <v>379</v>
       </c>
-      <c r="H218" t="s">
+      <c r="H224" t="s">
         <v>380</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="B219" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="B220" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="B221" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="D222" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E222" t="s">
-        <v>381</v>
-      </c>
-      <c r="F222" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="G222" t="s">
-        <v>383</v>
-      </c>
-      <c r="H222" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="B223" t="s">
-        <v>55</v>
-      </c>
-      <c r="C223" t="s">
-        <v>385</v>
-      </c>
-      <c r="D223" s="4"/>
-      <c r="F223" s="4"/>
-    </row>
-    <row r="224">
-      <c r="D224" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E224" t="s">
-        <v>386</v>
-      </c>
-      <c r="F224" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="G224" t="s">
-        <v>388</v>
-      </c>
-      <c r="H224" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="225">
       <c r="B225" t="s">
-        <v>73</v>
-      </c>
-      <c r="D225" s="4"/>
-      <c r="F225" s="4"/>
+        <v>49</v>
+      </c>
     </row>
     <row r="226">
       <c r="B226" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="227">
       <c r="B227" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
     </row>
     <row r="228">
-      <c r="B228" t="s">
-        <v>40</v>
+      <c r="D228" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E228" t="s">
+        <v>381</v>
+      </c>
+      <c r="F228" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="G228" t="s">
+        <v>383</v>
+      </c>
+      <c r="H228" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="229">
-      <c r="D229" t="s">
-        <v>322</v>
-      </c>
-      <c r="G229" t="s">
-        <v>390</v>
-      </c>
-      <c r="H229" t="s">
-        <v>391</v>
-      </c>
+      <c r="B229" t="s">
+        <v>55</v>
+      </c>
+      <c r="C229" t="s">
+        <v>385</v>
+      </c>
+      <c r="D229" s="4"/>
+      <c r="F229" s="4"/>
     </row>
     <row r="230">
-      <c r="D230" t="s">
-        <v>41</v>
-      </c>
-      <c r="F230" t="s">
-        <v>321</v>
-      </c>
-      <c r="I230">
-        <v>2</v>
+      <c r="D230" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E230" t="s">
+        <v>386</v>
+      </c>
+      <c r="F230" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="G230" t="s">
+        <v>388</v>
+      </c>
+      <c r="H230" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="231">
       <c r="B231" t="s">
-        <v>49</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="D231" s="4"/>
+      <c r="F231" s="4"/>
     </row>
     <row r="232">
       <c r="B232" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="D235" t="s">
+        <v>316</v>
+      </c>
+      <c r="G235" t="s">
+        <v>390</v>
+      </c>
+      <c r="H235" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="D236" t="s">
+        <v>41</v>
+      </c>
+      <c r="F236" t="s">
+        <v>315</v>
+      </c>
+      <c r="I236">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="s">
         <v>73</v>
       </c>
     </row>
@@ -5052,7 +5120,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B4" t="str">
         <f>"1"</f>
@@ -5067,7 +5135,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B5" s="4" t="str">
         <f>"2"</f>
@@ -5082,7 +5150,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B6" s="4" t="str">
         <f>"1"</f>
@@ -5097,7 +5165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B7" t="str">
         <f>"2"</f>
@@ -5126,7 +5194,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B9" t="str">
         <f>"1"</f>
@@ -5141,7 +5209,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B10" s="4" t="str">
         <f>"2"</f>
@@ -5156,7 +5224,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B11" s="4" t="str">
         <f>"3"</f>
@@ -5297,7 +5365,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B20" t="str">
         <f>"1"</f>
@@ -5312,7 +5380,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B21" t="str">
         <f>"2"</f>
@@ -5327,7 +5395,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B22" t="str">
         <f>"3"</f>
@@ -5342,7 +5410,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B23" t="str">
         <f>"4"</f>
@@ -5357,7 +5425,7 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B24" t="str">
         <f>"5"</f>
@@ -5372,7 +5440,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B25" t="str">
         <f>"6"</f>
@@ -5387,7 +5455,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B26" t="str">
         <f>"7"</f>
@@ -5405,7 +5473,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B27" t="str">
         <f>"8"</f>
@@ -5423,7 +5491,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B28" t="str">
         <f>"9"</f>
@@ -5441,7 +5509,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B29" t="str">
         <f>"10"</f>
@@ -5459,7 +5527,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B30" t="str">
         <f>"11"</f>
@@ -5477,7 +5545,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B31" t="str">
         <f>"12"</f>
@@ -5495,7 +5563,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B32" t="str">
         <f>"13"</f>
@@ -5513,7 +5581,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B33" t="str">
         <f>"14"</f>
@@ -5531,7 +5599,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B34" t="str">
         <f>"15"</f>
@@ -5549,7 +5617,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B35" t="str">
         <f>"16"</f>
@@ -5567,7 +5635,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B36" t="str">
         <f>"17"</f>
@@ -5585,7 +5653,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B37" t="str">
         <f>"18"</f>
@@ -5603,7 +5671,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B38" t="str">
         <f>"77"</f>
@@ -5618,7 +5686,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B39" t="str">
         <f>"1"</f>
@@ -5633,7 +5701,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B40" s="4" t="str">
         <f>"2"</f>
@@ -5648,7 +5716,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B41" t="str">
         <f>"1"</f>
@@ -5663,7 +5731,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B42" s="4" t="str">
         <f>"2"</f>
@@ -5678,7 +5746,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B43" s="4" t="str">
         <f>"3"</f>
@@ -5723,7 +5791,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B46" t="str">
         <f>"1"</f>
@@ -5738,7 +5806,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B47" t="str">
         <f>"2"</f>
@@ -5813,7 +5881,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B52" t="str">
         <f>"1"</f>
@@ -6334,7 +6402,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B4" t="s">
         <v>78</v>
@@ -6378,10 +6446,10 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B8" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
@@ -6389,7 +6457,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B9" t="s">
         <v>98</v>
@@ -6422,7 +6490,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s">
         <v>98</v>
@@ -6434,7 +6502,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s">
         <v>98</v>
@@ -6445,7 +6513,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B14" t="s">
         <v>98</v>
@@ -6478,7 +6546,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B17" t="s">
         <v>98</v>
@@ -6489,7 +6557,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B18" t="s">
         <v>98</v>
@@ -6533,7 +6601,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s">
         <v>98</v>
@@ -6588,7 +6656,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B27" t="s">
         <v>78</v>
@@ -6610,7 +6678,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B29" t="s">
         <v>41</v>
@@ -6621,7 +6689,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
@@ -6632,7 +6700,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B31" t="s">
         <v>98</v>
@@ -6643,7 +6711,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B32" t="s">
         <v>98</v>
@@ -6654,7 +6722,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B33" t="s">
         <v>63</v>
@@ -6720,7 +6788,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B39" t="s">
         <v>63</v>
@@ -6731,7 +6799,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B40" t="s">
         <v>63</v>
@@ -6753,7 +6821,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B42" t="s">
         <v>98</v>
@@ -6764,7 +6832,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B43" t="s">
         <v>98</v>
@@ -6852,7 +6920,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B51" t="s">
         <v>98</v>
@@ -6874,7 +6942,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B53" t="s">
         <v>98</v>
@@ -6918,7 +6986,7 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B57" s="18" t="s">
         <v>106</v>
@@ -6929,7 +6997,7 @@
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B58" s="18" t="s">
         <v>106</v>
@@ -6940,7 +7008,7 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B59" s="18" t="s">
         <v>106</v>
@@ -6951,7 +7019,7 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B60" t="s">
         <v>78</v>
@@ -6962,7 +7030,7 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B61" t="s">
         <v>78</v>
@@ -6973,7 +7041,7 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B62" t="s">
         <v>78</v>
@@ -6984,7 +7052,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B63" t="s">
         <v>63</v>
@@ -6995,7 +7063,7 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>98</v>
@@ -7006,7 +7074,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B65" t="s">
         <v>98</v>
@@ -7028,7 +7096,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B67" t="s">
         <v>98</v>
@@ -7039,7 +7107,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B68" t="s">
         <v>98</v>
@@ -7050,10 +7118,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C69" t="b">
         <v>0</v>
@@ -7072,7 +7140,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B71" t="s">
         <v>82</v>
@@ -7083,7 +7151,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B72" t="s">
         <v>82</v>
@@ -7105,7 +7173,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B74" t="s">
         <v>63</v>
@@ -7116,7 +7184,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B75" t="s">
         <v>63</v>
@@ -7127,7 +7195,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B76" t="s">
         <v>98</v>
@@ -7138,7 +7206,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B77" t="s">
         <v>98</v>
@@ -7205,7 +7273,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B83" t="s">
         <v>46</v>
@@ -7222,7 +7290,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B85" s="19" t="s">
         <v>98</v>
@@ -7233,7 +7301,7 @@
     </row>
     <row r="86">
       <c r="A86" s="8" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B86" s="19" t="s">
         <v>98</v>

--- a/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
+++ b/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="493">
   <si>
     <t>setting_name</t>
   </si>
@@ -493,6 +493,15 @@
     <t xml:space="preserve">Idade - mes(es)</t>
   </si>
   <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The child has to be under 5 years and over 15 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A criança deve ter entre 15 méses e 5 anos de idade</t>
+  </si>
+  <si>
     <t>sim/não</t>
   </si>
   <si>
@@ -971,9 +980,6 @@
   </si>
   <si>
     <t>INC</t>
-  </si>
-  <si>
-    <t>note</t>
   </si>
   <si>
     <t xml:space="preserve">The child is not to be included, since:</t>
@@ -1525,7 +1531,6 @@
     </font>
     <font>
       <sz val="11.000000"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1605,7 +1610,7 @@
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
@@ -1616,12 +1621,6 @@
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
@@ -1632,7 +1631,6 @@
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="3"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="3"/>
   </cellXfs>
   <cellStyles count="4">
@@ -3176,101 +3174,107 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="s">
-        <v>49</v>
+      <c r="B73" s="8"/>
+      <c r="D73" t="s">
+        <v>156</v>
+      </c>
+      <c r="G73" t="s">
+        <v>157</v>
+      </c>
+      <c r="H73" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="75">
-      <c r="D75" t="s">
+    <row r="76">
+      <c r="D76" t="s">
         <v>98</v>
       </c>
-      <c r="E75" t="s">
-        <v>156</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G75" t="s">
-        <v>158</v>
-      </c>
-      <c r="H75" t="s">
+      <c r="E76" t="s">
         <v>159</v>
       </c>
-      <c r="R75" t="b">
+      <c r="F76" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G76" t="s">
+        <v>161</v>
+      </c>
+      <c r="H76" t="s">
+        <v>162</v>
+      </c>
+      <c r="R76" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" t="s">
+    <row r="77">
+      <c r="B77" t="s">
         <v>55</v>
       </c>
-      <c r="C76" t="s">
-        <v>160</v>
-      </c>
-      <c r="F76" s="4"/>
-    </row>
-    <row r="77">
-      <c r="D77" t="s">
+      <c r="C77" t="s">
+        <v>163</v>
+      </c>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78">
+      <c r="D78" t="s">
         <v>98</v>
       </c>
-      <c r="E77" t="s">
-        <v>161</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="G77" t="s">
-        <v>163</v>
-      </c>
-      <c r="H77" t="s">
+      <c r="E78" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="78">
-      <c r="B78" t="s">
+      <c r="F78" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G78" t="s">
+        <v>166</v>
+      </c>
+      <c r="H78" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="s">
         <v>55</v>
       </c>
-      <c r="C78" t="s">
-        <v>165</v>
-      </c>
-      <c r="F78" s="4"/>
-    </row>
-    <row r="79">
-      <c r="D79" s="4" t="s">
+      <c r="C79" t="s">
+        <v>168</v>
+      </c>
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80">
+      <c r="D80" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E79" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="H79" s="4" t="s">
+      <c r="E80" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="K79" t="s">
+      <c r="F80" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="L79" t="s">
+      <c r="G80" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="M79" t="s">
+      <c r="H80" s="4" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="80">
-      <c r="B80" t="s">
-        <v>73</v>
-      </c>
-      <c r="F80" s="4"/>
+      <c r="K80" t="s">
+        <v>173</v>
+      </c>
+      <c r="L80" t="s">
+        <v>174</v>
+      </c>
+      <c r="M80" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="81">
       <c r="B81" t="s">
@@ -3280,608 +3284,597 @@
     </row>
     <row r="82">
       <c r="B82" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="F82" s="4"/>
     </row>
     <row r="83">
       <c r="B83" t="s">
-        <v>55</v>
-      </c>
-      <c r="C83" t="s">
-        <v>160</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="F83" s="4"/>
     </row>
     <row r="84">
       <c r="B84" t="s">
+        <v>55</v>
+      </c>
+      <c r="C84" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="D85" t="s">
-        <v>78</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="H85" t="s">
-        <v>175</v>
-      </c>
-      <c r="K85" t="s">
-        <v>176</v>
-      </c>
-      <c r="L85" t="s">
-        <v>177</v>
-      </c>
-      <c r="M85" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="86">
       <c r="D86" t="s">
-        <v>106</v>
-      </c>
-      <c r="E86" t="s">
+        <v>78</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="H86" t="s">
+        <v>178</v>
+      </c>
+      <c r="K86" t="s">
         <v>179</v>
       </c>
-      <c r="F86" s="4" t="s">
+      <c r="L86" t="s">
         <v>180</v>
+      </c>
+      <c r="M86" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="87">
       <c r="D87" t="s">
-        <v>78</v>
+        <v>106</v>
+      </c>
+      <c r="E87" t="s">
+        <v>182</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="G87" t="s">
-        <v>182</v>
-      </c>
-      <c r="H87" t="s">
         <v>183</v>
-      </c>
-      <c r="K87" t="s">
-        <v>184</v>
-      </c>
-      <c r="L87" t="s">
-        <v>177</v>
-      </c>
-      <c r="M87" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="88">
       <c r="D88" t="s">
-        <v>106</v>
-      </c>
-      <c r="E88" t="s">
+        <v>78</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G88" t="s">
         <v>185</v>
       </c>
-      <c r="F88" s="4" t="s">
+      <c r="H88" t="s">
         <v>186</v>
+      </c>
+      <c r="K88" t="s">
+        <v>187</v>
+      </c>
+      <c r="L88" t="s">
+        <v>180</v>
+      </c>
+      <c r="M88" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="89">
       <c r="D89" t="s">
-        <v>78</v>
+        <v>106</v>
+      </c>
+      <c r="E89" t="s">
+        <v>188</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="G89" t="s">
-        <v>188</v>
-      </c>
-      <c r="H89" t="s">
         <v>189</v>
-      </c>
-      <c r="K89" t="s">
-        <v>190</v>
-      </c>
-      <c r="L89" t="s">
-        <v>177</v>
-      </c>
-      <c r="M89" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="90">
       <c r="D90" t="s">
+        <v>78</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G90" t="s">
+        <v>191</v>
+      </c>
+      <c r="H90" t="s">
+        <v>192</v>
+      </c>
+      <c r="K90" t="s">
+        <v>193</v>
+      </c>
+      <c r="L90" t="s">
+        <v>180</v>
+      </c>
+      <c r="M90" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="D91" t="s">
         <v>106</v>
       </c>
-      <c r="E90" t="s">
-        <v>185</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" t="s">
+      <c r="E91" t="s">
+        <v>188</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="s">
         <v>55</v>
       </c>
-      <c r="C91" t="s">
-        <v>192</v>
-      </c>
-      <c r="F91" s="4"/>
-    </row>
-    <row r="92">
-      <c r="D92" t="s">
+      <c r="C92" t="s">
+        <v>195</v>
+      </c>
+      <c r="F92" s="4"/>
+    </row>
+    <row r="93">
+      <c r="D93" t="s">
         <v>41</v>
       </c>
-      <c r="F92" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="I92">
+      <c r="F93" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I93">
         <v>999999999</v>
       </c>
-    </row>
-    <row r="93">
-      <c r="B93" t="s">
-        <v>73</v>
-      </c>
-      <c r="F93" s="4"/>
     </row>
     <row r="94">
       <c r="B94" t="s">
+        <v>73</v>
+      </c>
+      <c r="F94" s="4"/>
+    </row>
+    <row r="95">
+      <c r="B95" t="s">
         <v>55</v>
       </c>
-      <c r="C94" t="s">
-        <v>193</v>
-      </c>
-      <c r="F94" s="4"/>
-    </row>
-    <row r="95">
-      <c r="D95" t="s">
+      <c r="C95" t="s">
+        <v>196</v>
+      </c>
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96">
+      <c r="D96" t="s">
         <v>41</v>
       </c>
-      <c r="F95" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="I95">
+      <c r="F96" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="I96">
         <v>999999999</v>
       </c>
-    </row>
-    <row r="96">
-      <c r="B96" t="s">
-        <v>73</v>
-      </c>
-      <c r="F96" s="4"/>
     </row>
     <row r="97">
       <c r="B97" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="F97" s="4"/>
     </row>
     <row r="98">
       <c r="B98" t="s">
+        <v>49</v>
+      </c>
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99">
+      <c r="B99" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="99">
-      <c r="D99" t="s">
+    <row r="100">
+      <c r="D100" t="s">
         <v>98</v>
       </c>
-      <c r="E99" t="s">
-        <v>156</v>
-      </c>
-      <c r="F99" t="s">
-        <v>194</v>
-      </c>
-      <c r="G99" t="s">
-        <v>195</v>
-      </c>
-      <c r="H99" t="s">
-        <v>196</v>
-      </c>
-      <c r="K99" t="s">
+      <c r="E100" t="s">
+        <v>159</v>
+      </c>
+      <c r="F100" t="s">
         <v>197</v>
       </c>
-      <c r="L99" t="s">
+      <c r="G100" t="s">
         <v>198</v>
       </c>
-      <c r="M99" t="s">
+      <c r="H100" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="100">
-      <c r="B100" t="s">
+      <c r="K100" t="s">
+        <v>200</v>
+      </c>
+      <c r="L100" t="s">
+        <v>201</v>
+      </c>
+      <c r="M100" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="s">
         <v>55</v>
       </c>
-      <c r="C100" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="D101" t="s">
+      <c r="C101" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="D102" t="s">
         <v>98</v>
       </c>
-      <c r="E101" t="s">
-        <v>156</v>
-      </c>
-      <c r="F101" s="4" t="s">
+      <c r="E102" t="s">
+        <v>159</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G102" t="s">
+        <v>205</v>
+      </c>
+      <c r="H102" t="s">
+        <v>206</v>
+      </c>
+      <c r="K102" t="s">
+        <v>207</v>
+      </c>
+      <c r="L102" t="s">
         <v>201</v>
       </c>
-      <c r="G101" t="s">
+      <c r="M102" t="s">
         <v>202</v>
-      </c>
-      <c r="H101" t="s">
-        <v>203</v>
-      </c>
-      <c r="K101" t="s">
-        <v>204</v>
-      </c>
-      <c r="L101" t="s">
-        <v>198</v>
-      </c>
-      <c r="M101" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="s">
         <v>55</v>
       </c>
-      <c r="C103" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="D104" t="s">
+      <c r="C104" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="D105" t="s">
         <v>98</v>
       </c>
-      <c r="E104" t="s">
-        <v>156</v>
-      </c>
-      <c r="F104" t="s">
-        <v>206</v>
-      </c>
-      <c r="G104" t="s">
-        <v>207</v>
-      </c>
-      <c r="H104" t="s">
+      <c r="E105" t="s">
+        <v>159</v>
+      </c>
+      <c r="F105" t="s">
+        <v>209</v>
+      </c>
+      <c r="G105" t="s">
+        <v>210</v>
+      </c>
+      <c r="H105" t="s">
+        <v>211</v>
+      </c>
+      <c r="K105" t="s">
+        <v>212</v>
+      </c>
+      <c r="L105" t="s">
+        <v>201</v>
+      </c>
+      <c r="M105" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9"/>
+      <c r="B107" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D107" s="9"/>
+      <c r="E107" s="9"/>
+      <c r="F107" s="9"/>
+      <c r="G107" s="9"/>
+      <c r="H107" s="9"/>
+      <c r="I107" s="9"/>
+      <c r="J107" s="9"/>
+      <c r="K107" s="9"/>
+      <c r="L107" s="9"/>
+      <c r="M107" s="9"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="9"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="9"/>
+      <c r="D108" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E108" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I108" s="9"/>
+      <c r="J108" s="9"/>
+      <c r="K108" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="L108" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="M108" s="9" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9"/>
+      <c r="B109" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C109" s="9"/>
+      <c r="D109" s="9"/>
+      <c r="E109" s="9"/>
+      <c r="F109" s="9"/>
+      <c r="G109" s="9"/>
+      <c r="H109" s="9"/>
+      <c r="I109" s="9"/>
+      <c r="J109" s="9"/>
+      <c r="K109" s="9"/>
+      <c r="L109" s="9"/>
+      <c r="M109" s="9"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="9"/>
+      <c r="B110" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C110" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="K104" t="s">
-        <v>209</v>
-      </c>
-      <c r="L104" t="s">
-        <v>198</v>
-      </c>
-      <c r="M104" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" t="s">
+      <c r="D110" s="9"/>
+      <c r="E110" s="9"/>
+      <c r="F110" s="9"/>
+      <c r="G110" s="9"/>
+      <c r="H110" s="9"/>
+      <c r="I110" s="9"/>
+      <c r="J110" s="9"/>
+      <c r="K110" s="9"/>
+      <c r="L110" s="9"/>
+      <c r="M110" s="9"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="9"/>
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
+      <c r="D111" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E111" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="G111" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="I111" s="9"/>
+      <c r="J111" s="9"/>
+      <c r="K111" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="L111" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="M111" s="9" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9"/>
+      <c r="B112" s="9" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="8"/>
-      <c r="B106" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
-      <c r="G106" s="8"/>
-      <c r="H106" s="8"/>
-      <c r="I106" s="8"/>
-      <c r="J106" s="8"/>
-      <c r="K106" s="8"/>
-      <c r="L106" s="8"/>
-      <c r="M106" s="8"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="8"/>
-      <c r="B107" s="9"/>
-      <c r="C107" s="8"/>
-      <c r="D107" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E107" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="F107" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="G107" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="I107" s="8"/>
-      <c r="J107" s="8"/>
-      <c r="K107" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="L107" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="M107" s="8" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="8"/>
-      <c r="B108" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
-      <c r="F108" s="8"/>
-      <c r="G108" s="8"/>
-      <c r="H108" s="8"/>
-      <c r="I108" s="8"/>
-      <c r="J108" s="8"/>
-      <c r="K108" s="8"/>
-      <c r="L108" s="8"/>
-      <c r="M108" s="8"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="8"/>
-      <c r="B109" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="D109" s="8"/>
-      <c r="E109" s="8"/>
-      <c r="F109" s="8"/>
-      <c r="G109" s="8"/>
-      <c r="H109" s="8"/>
-      <c r="I109" s="8"/>
-      <c r="J109" s="8"/>
-      <c r="K109" s="8"/>
-      <c r="L109" s="8"/>
-      <c r="M109" s="8"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="8"/>
-      <c r="B110" s="9"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E110" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="F110" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="G110" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="H110" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="I110" s="8"/>
-      <c r="J110" s="8"/>
-      <c r="K110" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="L110" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="M110" s="8" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="8"/>
-      <c r="B111" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="8"/>
-      <c r="G111" s="8"/>
-      <c r="H111" s="8"/>
-      <c r="I111" s="8"/>
-      <c r="J111" s="8"/>
-      <c r="K111" s="8"/>
-      <c r="L111" s="8"/>
-      <c r="M111" s="8"/>
-    </row>
-    <row r="112">
-      <c r="B112" t="s">
-        <v>49</v>
-      </c>
+      <c r="C112" s="9"/>
+      <c r="D112" s="9"/>
+      <c r="E112" s="9"/>
+      <c r="F112" s="9"/>
+      <c r="G112" s="9"/>
+      <c r="H112" s="9"/>
+      <c r="I112" s="9"/>
+      <c r="J112" s="9"/>
+      <c r="K112" s="9"/>
+      <c r="L112" s="9"/>
+      <c r="M112" s="9"/>
     </row>
     <row r="113">
       <c r="B113" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="s">
         <v>55</v>
       </c>
-      <c r="C113" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="D114" t="s">
-        <v>216</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="G114" t="s">
-        <v>218</v>
-      </c>
-      <c r="H114" t="s">
+      <c r="C114" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="D115" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="115">
-      <c r="B115" t="s">
-        <v>73</v>
+      <c r="F115" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="G115" t="s">
+        <v>221</v>
+      </c>
+      <c r="H115" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="116">
       <c r="B116" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="D117" t="s">
-        <v>63</v>
-      </c>
-      <c r="F117" t="s">
-        <v>220</v>
-      </c>
-      <c r="G117" t="s">
-        <v>221</v>
-      </c>
-      <c r="H117" t="s">
-        <v>222</v>
-      </c>
-      <c r="K117" t="s">
-        <v>223</v>
-      </c>
-      <c r="L117" t="s">
-        <v>224</v>
-      </c>
-      <c r="M117" t="s">
-        <v>225</v>
-      </c>
-      <c r="N117" t="s">
-        <v>226</v>
-      </c>
-      <c r="O117" t="s">
-        <v>227</v>
-      </c>
-      <c r="P117" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="118">
       <c r="D118" t="s">
+        <v>63</v>
+      </c>
+      <c r="F118" t="s">
+        <v>223</v>
+      </c>
+      <c r="G118" t="s">
+        <v>224</v>
+      </c>
+      <c r="H118" t="s">
+        <v>225</v>
+      </c>
+      <c r="K118" t="s">
+        <v>226</v>
+      </c>
+      <c r="L118" t="s">
+        <v>227</v>
+      </c>
+      <c r="M118" t="s">
+        <v>228</v>
+      </c>
+      <c r="N118" t="s">
+        <v>229</v>
+      </c>
+      <c r="O118" t="s">
+        <v>230</v>
+      </c>
+      <c r="P118" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="D119" t="s">
         <v>78</v>
       </c>
-      <c r="F118" t="s">
-        <v>228</v>
-      </c>
-      <c r="G118" t="s">
-        <v>229</v>
-      </c>
-      <c r="H118" t="s">
-        <v>230</v>
-      </c>
-      <c r="K118" t="s">
+      <c r="F119" t="s">
         <v>231</v>
       </c>
-      <c r="L118" t="s">
+      <c r="G119" t="s">
         <v>232</v>
       </c>
-      <c r="M118" t="s">
+      <c r="H119" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="119">
-      <c r="B119" t="s">
-        <v>49</v>
+      <c r="K119" t="s">
+        <v>234</v>
+      </c>
+      <c r="L119" t="s">
+        <v>235</v>
+      </c>
+      <c r="M119" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="121">
-      <c r="D121" t="s">
+    <row r="122">
+      <c r="D122" t="s">
         <v>98</v>
       </c>
-      <c r="E121" t="s">
-        <v>234</v>
-      </c>
-      <c r="F121" t="s">
-        <v>235</v>
-      </c>
-      <c r="G121" t="s">
-        <v>236</v>
-      </c>
-      <c r="H121" t="s">
+      <c r="E122" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="122">
-      <c r="B122" t="s">
+      <c r="F122" t="s">
+        <v>238</v>
+      </c>
+      <c r="G122" t="s">
+        <v>239</v>
+      </c>
+      <c r="H122" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="s">
         <v>55</v>
       </c>
-      <c r="C122" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="D123" s="4" t="s">
+      <c r="C123" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="D124" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E123" s="4"/>
-      <c r="F123" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="G123" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="I123" s="4"/>
-      <c r="K123" t="s">
+      <c r="E124" s="4"/>
+      <c r="F124" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="L123" t="s">
+      <c r="G124" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="H124" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I124" s="4"/>
+      <c r="K124" t="s">
+        <v>245</v>
+      </c>
+      <c r="L124" t="s">
         <v>143</v>
       </c>
-      <c r="M123" t="s">
+      <c r="M124" t="s">
         <v>144</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="125">
       <c r="B125" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="126">
       <c r="B126" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="D127" t="s">
-        <v>98</v>
-      </c>
-      <c r="E127" t="s">
-        <v>243</v>
-      </c>
-      <c r="F127" t="s">
-        <v>244</v>
-      </c>
-      <c r="G127" t="s">
-        <v>245</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="128">
@@ -3889,7 +3882,7 @@
         <v>98</v>
       </c>
       <c r="E128" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F128" t="s">
         <v>247</v>
@@ -3906,7 +3899,7 @@
         <v>98</v>
       </c>
       <c r="E129" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F129" t="s">
         <v>250</v>
@@ -3919,100 +3912,100 @@
       </c>
     </row>
     <row r="130">
-      <c r="B130" s="12" t="s">
+      <c r="D130" t="s">
+        <v>98</v>
+      </c>
+      <c r="E130" t="s">
+        <v>246</v>
+      </c>
+      <c r="F130" t="s">
+        <v>253</v>
+      </c>
+      <c r="G130" t="s">
+        <v>254</v>
+      </c>
+      <c r="H130" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C130" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="D130" s="12"/>
-      <c r="E130" s="12"/>
-      <c r="F130" s="12"/>
-      <c r="G130" s="12"/>
-      <c r="H130" s="12"/>
-      <c r="I130" s="12"/>
-    </row>
-    <row r="131">
-      <c r="B131" s="12"/>
-      <c r="C131" s="12"/>
-      <c r="D131" s="12" t="s">
+      <c r="C131" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="D131" s="10"/>
+      <c r="E131" s="10"/>
+      <c r="F131" s="10"/>
+      <c r="G131" s="10"/>
+      <c r="H131" s="10"/>
+      <c r="I131" s="10"/>
+    </row>
+    <row r="132">
+      <c r="B132" s="10"/>
+      <c r="C132" s="10"/>
+      <c r="D132" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E131" s="12"/>
-      <c r="F131" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="G131" s="12"/>
-      <c r="H131" s="12"/>
-      <c r="I131" s="12" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="B132" s="12" t="s">
+      <c r="E132" s="10"/>
+      <c r="F132" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="G132" s="10"/>
+      <c r="H132" s="10"/>
+      <c r="I132" s="10" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C132" s="12"/>
-      <c r="D132" s="12"/>
-      <c r="E132" s="12"/>
-      <c r="F132" s="12"/>
-      <c r="G132" s="12"/>
-      <c r="H132" s="12"/>
-      <c r="I132" s="12"/>
-    </row>
-    <row r="133">
-      <c r="B133" s="12"/>
-      <c r="C133" s="12"/>
-      <c r="D133" s="12" t="s">
+      <c r="C133" s="10"/>
+      <c r="D133" s="10"/>
+      <c r="E133" s="10"/>
+      <c r="F133" s="10"/>
+      <c r="G133" s="10"/>
+      <c r="H133" s="10"/>
+      <c r="I133" s="10"/>
+    </row>
+    <row r="134">
+      <c r="B134" s="10"/>
+      <c r="C134" s="10"/>
+      <c r="D134" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E133" s="12"/>
-      <c r="F133" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="G133" s="12"/>
-      <c r="H133" s="12"/>
-      <c r="I133" s="12" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="B134" s="12" t="s">
+      <c r="E134" s="10"/>
+      <c r="F134" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="G134" s="10"/>
+      <c r="H134" s="10"/>
+      <c r="I134" s="10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C134" s="12"/>
-      <c r="D134" s="12"/>
-      <c r="E134" s="12"/>
-      <c r="F134" s="12"/>
-      <c r="G134" s="12"/>
-      <c r="H134" s="12"/>
-      <c r="I134" s="12"/>
-    </row>
-    <row r="135">
-      <c r="B135" t="s">
-        <v>49</v>
-      </c>
+      <c r="C135" s="10"/>
+      <c r="D135" s="10"/>
+      <c r="E135" s="10"/>
+      <c r="F135" s="10"/>
+      <c r="G135" s="10"/>
+      <c r="H135" s="10"/>
+      <c r="I135" s="10"/>
     </row>
     <row r="136">
       <c r="B136" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="D137" t="s">
-        <v>98</v>
-      </c>
-      <c r="E137" t="s">
-        <v>243</v>
-      </c>
-      <c r="F137" t="s">
-        <v>257</v>
-      </c>
-      <c r="G137" t="s">
-        <v>258</v>
-      </c>
-      <c r="H137" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="138">
@@ -4020,7 +4013,7 @@
         <v>98</v>
       </c>
       <c r="E138" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F138" t="s">
         <v>260</v>
@@ -4037,7 +4030,7 @@
         <v>98</v>
       </c>
       <c r="E139" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F139" t="s">
         <v>263</v>
@@ -4050,35 +4043,38 @@
       </c>
     </row>
     <row r="140">
-      <c r="B140" t="s">
-        <v>49</v>
+      <c r="D140" t="s">
+        <v>98</v>
+      </c>
+      <c r="E140" t="s">
+        <v>246</v>
+      </c>
+      <c r="F140" t="s">
+        <v>266</v>
+      </c>
+      <c r="G140" t="s">
+        <v>267</v>
+      </c>
+      <c r="H140" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="141">
       <c r="B141" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="D142" t="s">
-        <v>98</v>
-      </c>
-      <c r="E142" t="s">
-        <v>243</v>
-      </c>
-      <c r="F142" t="s">
-        <v>266</v>
-      </c>
-      <c r="G142" t="s">
-        <v>267</v>
-      </c>
-      <c r="H142" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="143">
       <c r="D143" t="s">
-        <v>63</v>
+        <v>98</v>
+      </c>
+      <c r="E143" t="s">
+        <v>246</v>
       </c>
       <c r="F143" t="s">
         <v>269</v>
@@ -4091,166 +4087,175 @@
       </c>
     </row>
     <row r="144">
-      <c r="B144" t="s">
+      <c r="D144" t="s">
+        <v>63</v>
+      </c>
+      <c r="F144" t="s">
+        <v>272</v>
+      </c>
+      <c r="G144" t="s">
+        <v>273</v>
+      </c>
+      <c r="H144" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="145" s="13" customFormat="1">
-      <c r="B145" s="13" t="s">
+    <row r="146" s="11" customFormat="1">
+      <c r="B146" s="11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="146" s="13" customFormat="1">
-      <c r="D146" s="13" t="s">
+    <row r="147" s="11" customFormat="1">
+      <c r="D147" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="E146" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="F146" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="G146" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="H146" s="13" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="147" s="13" customFormat="1">
-      <c r="B147" s="13" t="s">
+      <c r="E147" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="F147" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="G147" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="H147" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="148" s="11" customFormat="1">
+      <c r="B148" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C147" s="13" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="148" s="13" customFormat="1">
-      <c r="D148" s="13" t="s">
+      <c r="C148" s="11" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="149" s="11" customFormat="1">
+      <c r="D149" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="E148" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="F148" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="G148" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="H148" s="13" t="s">
+      <c r="E149" s="11" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="149" s="13" customFormat="1">
-      <c r="B149" s="13" t="s">
+      <c r="F149" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="G149" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="H149" s="11" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="150" s="11" customFormat="1">
+      <c r="B150" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C149" s="13" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="150" s="13" customFormat="1">
-      <c r="D150" s="13" t="s">
+      <c r="C150" s="11" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="151" s="11" customFormat="1">
+      <c r="D151" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F150" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="G150" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="H150" s="13" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="151" s="13" customFormat="1">
-      <c r="B151" s="13" t="s">
+      <c r="F151" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="G151" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="H151" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="152" s="11" customFormat="1">
+      <c r="B152" s="11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="152" s="13" customFormat="1">
-      <c r="B152" s="13" t="s">
+    <row r="153" s="11" customFormat="1">
+      <c r="B153" s="11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="153" s="13" customFormat="1">
-      <c r="B153" s="13" t="s">
+    <row r="154" s="11" customFormat="1">
+      <c r="B154" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="154" s="13" customFormat="1">
-      <c r="B154" s="13" t="s">
+    <row r="155" s="11" customFormat="1">
+      <c r="B155" s="11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="155" s="6" customFormat="1">
-      <c r="D155" s="6" t="s">
+    <row r="156" s="6" customFormat="1">
+      <c r="D156" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E155" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="F155" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="G155" s="6" t="s">
+      <c r="E156" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="G156" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="H156" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="157" s="6" customFormat="1">
+      <c r="B157" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="158" s="6" customFormat="1">
+      <c r="D158" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G158" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="H158" s="6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="159" s="6" customFormat="1">
+      <c r="B159" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="160" s="6" customFormat="1">
+      <c r="D160" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="G160" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="H155" s="6" t="s">
+      <c r="H160" s="6" t="s">
         <v>286</v>
-      </c>
-    </row>
-    <row r="156" s="6" customFormat="1">
-      <c r="B156" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C156" s="6" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="157" s="6" customFormat="1">
-      <c r="D157" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E157" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="F157" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="G157" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="H157" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="158" s="6" customFormat="1">
-      <c r="B158" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C158" s="6" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="159" s="6" customFormat="1">
-      <c r="D159" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F159" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G159" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="H159" s="6" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="160" s="6" customFormat="1">
-      <c r="B160" s="6" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="161" s="6" customFormat="1">
@@ -4260,511 +4265,490 @@
     </row>
     <row r="162" s="6" customFormat="1">
       <c r="B162" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="163" s="6" customFormat="1">
+      <c r="B163" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="163">
-      <c r="B163" t="s">
+    <row r="164">
+      <c r="B164" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="164">
-      <c r="D164" t="s">
-        <v>216</v>
-      </c>
-      <c r="F164" t="s">
-        <v>293</v>
-      </c>
-      <c r="G164" t="s">
-        <v>294</v>
-      </c>
-      <c r="H164" t="s">
-        <v>295</v>
-      </c>
-    </row>
     <row r="165">
-      <c r="B165" t="s">
-        <v>49</v>
+      <c r="D165" t="s">
+        <v>219</v>
+      </c>
+      <c r="F165" t="s">
+        <v>296</v>
+      </c>
+      <c r="G165" t="s">
+        <v>297</v>
+      </c>
+      <c r="H165" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="166">
       <c r="B166" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="167">
-      <c r="D167" t="s">
+    <row r="168">
+      <c r="D168" t="s">
         <v>98</v>
       </c>
-      <c r="E167" t="s">
-        <v>156</v>
-      </c>
-      <c r="F167" t="s">
-        <v>296</v>
-      </c>
-      <c r="G167" t="s">
-        <v>297</v>
-      </c>
-      <c r="H167" t="s">
-        <v>298</v>
-      </c>
-      <c r="K167" t="s">
+      <c r="E168" t="s">
+        <v>159</v>
+      </c>
+      <c r="F168" t="s">
         <v>299</v>
       </c>
-      <c r="L167" t="s">
-        <v>198</v>
-      </c>
-      <c r="M167" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="B168" t="s">
+      <c r="G168" t="s">
+        <v>300</v>
+      </c>
+      <c r="H168" t="s">
+        <v>301</v>
+      </c>
+      <c r="K168" t="s">
+        <v>302</v>
+      </c>
+      <c r="L168" t="s">
+        <v>201</v>
+      </c>
+      <c r="M168" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="s">
         <v>55</v>
       </c>
-      <c r="C168" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="D169" t="s">
+      <c r="C169" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="D170" t="s">
         <v>63</v>
       </c>
-      <c r="F169" t="s">
-        <v>301</v>
-      </c>
-      <c r="G169" t="s">
-        <v>302</v>
-      </c>
-      <c r="H169" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="B170" t="s">
+      <c r="F170" t="s">
+        <v>304</v>
+      </c>
+      <c r="G170" t="s">
+        <v>305</v>
+      </c>
+      <c r="H170" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="171">
-      <c r="D171" t="s">
+    <row r="172">
+      <c r="D172" t="s">
         <v>98</v>
       </c>
-      <c r="E171" t="s">
-        <v>156</v>
-      </c>
-      <c r="F171" t="s">
-        <v>304</v>
-      </c>
-      <c r="G171" t="s">
+      <c r="E172" t="s">
+        <v>159</v>
+      </c>
+      <c r="F172" t="s">
+        <v>307</v>
+      </c>
+      <c r="G172" t="s">
+        <v>308</v>
+      </c>
+      <c r="H172" t="s">
+        <v>309</v>
+      </c>
+      <c r="K172" t="s">
+        <v>310</v>
+      </c>
+      <c r="L172" t="s">
+        <v>201</v>
+      </c>
+      <c r="M172" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="s">
+        <v>55</v>
+      </c>
+      <c r="C173" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="D174" t="s">
+        <v>63</v>
+      </c>
+      <c r="F174" t="s">
+        <v>312</v>
+      </c>
+      <c r="G174" t="s">
         <v>305</v>
       </c>
-      <c r="H171" t="s">
+      <c r="H174" t="s">
         <v>306</v>
       </c>
-      <c r="K171" t="s">
-        <v>307</v>
-      </c>
-      <c r="L171" t="s">
-        <v>198</v>
-      </c>
-      <c r="M171" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="B172" t="s">
-        <v>55</v>
-      </c>
-      <c r="C172" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="D173" t="s">
-        <v>63</v>
-      </c>
-      <c r="F173" t="s">
-        <v>309</v>
-      </c>
-      <c r="G173" t="s">
-        <v>302</v>
-      </c>
-      <c r="H173" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="B174" t="s">
+    </row>
+    <row r="175">
+      <c r="B175" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="175">
-      <c r="D175" t="s">
+    <row r="176">
+      <c r="D176" t="s">
         <v>98</v>
       </c>
-      <c r="E175" t="s">
-        <v>243</v>
-      </c>
-      <c r="F175" t="s">
-        <v>310</v>
-      </c>
-      <c r="G175" t="s">
-        <v>311</v>
-      </c>
-      <c r="H175" t="s">
-        <v>312</v>
-      </c>
-      <c r="K175" t="s">
+      <c r="E176" t="s">
+        <v>246</v>
+      </c>
+      <c r="F176" t="s">
         <v>313</v>
       </c>
-      <c r="L175" t="s">
-        <v>198</v>
-      </c>
-      <c r="M175" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="B176" t="s">
-        <v>49</v>
+      <c r="G176" t="s">
+        <v>314</v>
+      </c>
+      <c r="H176" t="s">
+        <v>315</v>
+      </c>
+      <c r="K176" t="s">
+        <v>316</v>
+      </c>
+      <c r="L176" t="s">
+        <v>201</v>
+      </c>
+      <c r="M176" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="177">
       <c r="B177" t="s">
-        <v>55</v>
-      </c>
-      <c r="C177" t="s">
-        <v>314</v>
+        <v>49</v>
       </c>
     </row>
     <row r="178">
       <c r="B178" t="s">
+        <v>55</v>
+      </c>
+      <c r="C178" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="D179" t="s">
-        <v>41</v>
-      </c>
-      <c r="F179" t="s">
-        <v>315</v>
-      </c>
-      <c r="I179">
-        <v>2</v>
       </c>
     </row>
     <row r="180">
       <c r="D180" t="s">
-        <v>316</v>
-      </c>
-      <c r="G180" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="H180" t="s">
+        <v>41</v>
+      </c>
+      <c r="F180" t="s">
         <v>318</v>
       </c>
+      <c r="I180">
+        <v>2</v>
+      </c>
     </row>
     <row r="181">
-      <c r="B181" t="s">
+      <c r="D181" t="s">
+        <v>156</v>
+      </c>
+      <c r="G181" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="H181" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="s">
         <v>55</v>
       </c>
-      <c r="C181" t="s">
-        <v>300</v>
-      </c>
-      <c r="G181" s="4"/>
-    </row>
-    <row r="182">
-      <c r="D182" t="s">
-        <v>316</v>
-      </c>
-      <c r="G182" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="H182" t="s">
-        <v>320</v>
-      </c>
+      <c r="C182" t="s">
+        <v>303</v>
+      </c>
+      <c r="G182" s="4"/>
     </row>
     <row r="183">
-      <c r="B183" t="s">
-        <v>73</v>
-      </c>
-      <c r="G183" s="4"/>
+      <c r="D183" t="s">
+        <v>156</v>
+      </c>
+      <c r="G183" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="H183" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="184">
       <c r="B184" t="s">
+        <v>73</v>
+      </c>
+      <c r="G184" s="4"/>
+    </row>
+    <row r="185">
+      <c r="B185" t="s">
         <v>55</v>
       </c>
-      <c r="C184" t="s">
-        <v>308</v>
-      </c>
-      <c r="G184" s="4"/>
-    </row>
-    <row r="185">
-      <c r="D185" t="s">
-        <v>316</v>
-      </c>
-      <c r="G185" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="H185" t="s">
-        <v>322</v>
-      </c>
+      <c r="C185" t="s">
+        <v>311</v>
+      </c>
+      <c r="G185" s="4"/>
     </row>
     <row r="186">
-      <c r="B186" t="s">
-        <v>73</v>
-      </c>
-      <c r="G186" s="4"/>
+      <c r="D186" t="s">
+        <v>156</v>
+      </c>
+      <c r="G186" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="H186" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="187">
       <c r="B187" t="s">
+        <v>73</v>
+      </c>
+      <c r="G187" s="4"/>
+    </row>
+    <row r="188">
+      <c r="B188" t="s">
         <v>55</v>
       </c>
-      <c r="C187" t="s">
-        <v>323</v>
-      </c>
-      <c r="G187" s="4"/>
-    </row>
-    <row r="188">
-      <c r="D188" t="s">
-        <v>316</v>
-      </c>
-      <c r="G188" t="s">
-        <v>324</v>
-      </c>
-      <c r="H188" t="s">
+      <c r="C188" t="s">
         <v>325</v>
       </c>
+      <c r="G188" s="4"/>
     </row>
     <row r="189">
-      <c r="B189" t="s">
-        <v>73</v>
-      </c>
-      <c r="G189" s="4"/>
+      <c r="D189" t="s">
+        <v>156</v>
+      </c>
+      <c r="G189" t="s">
+        <v>326</v>
+      </c>
+      <c r="H189" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="190">
       <c r="B190" t="s">
+        <v>73</v>
+      </c>
+      <c r="G190" s="4"/>
+    </row>
+    <row r="191">
+      <c r="B191" t="s">
         <v>55</v>
       </c>
-      <c r="C190" t="s">
-        <v>326</v>
-      </c>
-      <c r="G190" s="4"/>
-    </row>
-    <row r="191">
-      <c r="D191" t="s">
-        <v>316</v>
-      </c>
-      <c r="G191" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="H191" t="s">
+      <c r="C191" t="s">
         <v>328</v>
       </c>
+      <c r="G191" s="4"/>
     </row>
     <row r="192">
-      <c r="B192" t="s">
-        <v>73</v>
-      </c>
-      <c r="G192" s="4"/>
+      <c r="D192" t="s">
+        <v>156</v>
+      </c>
+      <c r="G192" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="H192" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="193">
       <c r="B193" t="s">
+        <v>73</v>
+      </c>
+      <c r="G193" s="4"/>
+    </row>
+    <row r="194">
+      <c r="B194" t="s">
         <v>55</v>
       </c>
-      <c r="C193" t="s">
-        <v>329</v>
-      </c>
-      <c r="G193" s="4"/>
-    </row>
-    <row r="194">
-      <c r="D194" t="s">
-        <v>316</v>
-      </c>
-      <c r="G194" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="H194" t="s">
+      <c r="C194" t="s">
         <v>331</v>
       </c>
+      <c r="G194" s="4"/>
     </row>
     <row r="195">
-      <c r="B195" t="s">
+      <c r="D195" t="s">
+        <v>156</v>
+      </c>
+      <c r="G195" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="H195" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="s">
         <v>73</v>
       </c>
-      <c r="G195" s="4"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="8"/>
-      <c r="B196" s="9" t="s">
+      <c r="G196" s="4"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="9"/>
+      <c r="B197" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C196" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="D196" s="8"/>
-      <c r="E196" s="8"/>
-      <c r="F196" s="8"/>
-      <c r="G196"/>
-      <c r="H196" s="8"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="8"/>
-      <c r="B197" s="9"/>
-      <c r="C197" s="8"/>
-      <c r="D197" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="E197" s="8"/>
-      <c r="F197" s="8"/>
-      <c r="G197" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="H197" s="11" t="s">
+      <c r="C197" s="9" t="s">
         <v>334</v>
       </c>
+      <c r="D197" s="9"/>
+      <c r="E197" s="9"/>
+      <c r="F197" s="9"/>
+      <c r="H197" s="9"/>
     </row>
     <row r="198">
-      <c r="A198" s="8"/>
-      <c r="B198" s="9" t="s">
+      <c r="A198" s="9"/>
+      <c r="B198" s="9"/>
+      <c r="C198" s="9"/>
+      <c r="D198" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E198" s="9"/>
+      <c r="F198" s="9"/>
+      <c r="G198" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="H198" s="9" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="9"/>
+      <c r="B199" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C198" s="8"/>
-      <c r="D198" s="8"/>
-      <c r="E198" s="8"/>
-      <c r="F198" s="8"/>
-      <c r="G198"/>
-      <c r="H198" s="8"/>
-    </row>
-    <row r="199">
-      <c r="B199" t="s">
+      <c r="C199" s="9"/>
+      <c r="D199" s="9"/>
+      <c r="E199" s="9"/>
+      <c r="F199" s="9"/>
+      <c r="H199" s="9"/>
+    </row>
+    <row r="200">
+      <c r="B200" t="s">
         <v>55</v>
       </c>
-      <c r="C199" t="s">
-        <v>335</v>
-      </c>
-      <c r="G199" s="4"/>
-    </row>
-    <row r="200">
-      <c r="D200" t="s">
-        <v>316</v>
-      </c>
-      <c r="G200" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="H200" t="s">
+      <c r="C200" t="s">
         <v>337</v>
       </c>
+      <c r="G200" s="4"/>
     </row>
     <row r="201">
-      <c r="B201" t="s">
+      <c r="D201" t="s">
+        <v>156</v>
+      </c>
+      <c r="G201" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="H201" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="s">
         <v>73</v>
       </c>
-      <c r="G201" s="4"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="8"/>
-      <c r="B202" s="9" t="s">
+      <c r="G202" s="4"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="9"/>
+      <c r="B203" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C202" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="D202" s="8"/>
-      <c r="E202" s="8"/>
-      <c r="F202" s="8"/>
-      <c r="G202"/>
-      <c r="H202" s="8"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="8"/>
-      <c r="B203" s="9"/>
-      <c r="C203" s="8"/>
-      <c r="D203" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="E203" s="8"/>
-      <c r="F203" s="8"/>
-      <c r="G203" t="s">
-        <v>339</v>
-      </c>
-      <c r="H203" s="10" t="s">
+      <c r="C203" s="4" t="s">
         <v>340</v>
       </c>
+      <c r="D203" s="9"/>
+      <c r="E203" s="9"/>
+      <c r="F203" s="9"/>
+      <c r="H203" s="9"/>
     </row>
     <row r="204">
-      <c r="A204" s="8"/>
-      <c r="B204" s="9" t="s">
+      <c r="A204" s="9"/>
+      <c r="B204" s="9"/>
+      <c r="C204" s="9"/>
+      <c r="D204" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E204" s="9"/>
+      <c r="F204" s="9"/>
+      <c r="G204" t="s">
+        <v>341</v>
+      </c>
+      <c r="H204" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="9"/>
+      <c r="B205" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C204" s="8"/>
-      <c r="D204" s="8"/>
-      <c r="E204" s="8"/>
-      <c r="F204" s="8"/>
-      <c r="G204" s="8"/>
-      <c r="H204" s="8"/>
-    </row>
-    <row r="205">
-      <c r="B205" t="s">
+      <c r="C205" s="9"/>
+      <c r="D205" s="9"/>
+      <c r="E205" s="9"/>
+      <c r="F205" s="9"/>
+      <c r="G205" s="9"/>
+      <c r="H205" s="9"/>
+    </row>
+    <row r="206">
+      <c r="B206" t="s">
         <v>55</v>
       </c>
-      <c r="C205" t="s">
-        <v>341</v>
-      </c>
-      <c r="G205" s="4"/>
-    </row>
-    <row r="206">
-      <c r="D206" t="s">
-        <v>316</v>
-      </c>
-      <c r="G206" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="H206" t="s">
+      <c r="C206" t="s">
         <v>343</v>
       </c>
+      <c r="G206" s="4"/>
     </row>
     <row r="207">
-      <c r="B207" t="s">
-        <v>73</v>
+      <c r="D207" t="s">
+        <v>156</v>
+      </c>
+      <c r="G207" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="H207" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="208">
       <c r="B208" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="209">
       <c r="B209" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
     </row>
     <row r="210">
       <c r="B210" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="D211" t="s">
-        <v>78</v>
-      </c>
-      <c r="F211" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G211" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="H211" t="s">
-        <v>346</v>
-      </c>
-      <c r="K211" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="L211" t="s">
-        <v>348</v>
-      </c>
-      <c r="M211" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="212">
@@ -4772,284 +4756,307 @@
         <v>78</v>
       </c>
       <c r="F212" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="G212" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="H212" t="s">
+        <v>348</v>
+      </c>
+      <c r="K212" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="L212" t="s">
         <v>350</v>
       </c>
-      <c r="G212" s="4" t="s">
+      <c r="M212" t="s">
         <v>351</v>
-      </c>
-      <c r="H212" t="s">
-        <v>352</v>
-      </c>
-      <c r="K212" t="s">
-        <v>353</v>
-      </c>
-      <c r="L212" t="s">
-        <v>354</v>
-      </c>
-      <c r="M212" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="213">
       <c r="D213" t="s">
-        <v>41</v>
-      </c>
-      <c r="F213" t="s">
+        <v>78</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="G213" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="H213" t="s">
+        <v>354</v>
+      </c>
+      <c r="K213" t="s">
+        <v>355</v>
+      </c>
+      <c r="L213" t="s">
         <v>356</v>
       </c>
-      <c r="I213" t="s">
+      <c r="M213" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="214">
       <c r="D214" t="s">
-        <v>316</v>
-      </c>
-      <c r="G214" t="s">
+        <v>41</v>
+      </c>
+      <c r="F214" t="s">
         <v>358</v>
       </c>
-      <c r="H214" t="s">
+      <c r="I214" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="215">
       <c r="D215" t="s">
+        <v>156</v>
+      </c>
+      <c r="G215" t="s">
+        <v>360</v>
+      </c>
+      <c r="H215" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="D216" t="s">
         <v>41</v>
       </c>
-      <c r="F215" t="s">
-        <v>315</v>
-      </c>
-      <c r="I215">
+      <c r="F216" t="s">
+        <v>318</v>
+      </c>
+      <c r="I216">
         <v>1</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="B216" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="217">
       <c r="B217" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="D218" t="s">
-        <v>41</v>
-      </c>
-      <c r="F218" t="s">
-        <v>360</v>
-      </c>
-      <c r="I218" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="219">
       <c r="D219" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F219" t="s">
-        <v>360</v>
-      </c>
-      <c r="G219" t="s">
         <v>362</v>
       </c>
-      <c r="H219" t="s">
+      <c r="I219" t="s">
         <v>363</v>
-      </c>
-      <c r="Q219" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="220">
       <c r="D220" t="s">
+        <v>46</v>
+      </c>
+      <c r="F220" t="s">
+        <v>362</v>
+      </c>
+      <c r="G220" t="s">
         <v>364</v>
       </c>
-      <c r="F220" t="s">
+      <c r="H220" t="s">
         <v>365</v>
       </c>
-      <c r="G220" t="s">
-        <v>366</v>
-      </c>
-      <c r="H220" t="s">
-        <v>367</v>
-      </c>
-      <c r="K220" t="s">
-        <v>368</v>
-      </c>
-      <c r="L220" t="s">
-        <v>198</v>
-      </c>
-      <c r="M220" t="s">
-        <v>199</v>
+      <c r="Q220" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="221">
       <c r="D221" t="s">
-        <v>41</v>
+        <v>366</v>
       </c>
       <c r="F221" t="s">
+        <v>367</v>
+      </c>
+      <c r="G221" t="s">
+        <v>368</v>
+      </c>
+      <c r="H221" t="s">
         <v>369</v>
       </c>
-      <c r="I221" t="s">
+      <c r="K221" t="s">
         <v>370</v>
+      </c>
+      <c r="L221" t="s">
+        <v>201</v>
+      </c>
+      <c r="M221" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="222">
       <c r="D222" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="F222" t="s">
         <v>371</v>
       </c>
-      <c r="G222" t="s">
+      <c r="I222" t="s">
         <v>372</v>
-      </c>
-      <c r="H222" t="s">
-        <v>373</v>
-      </c>
-      <c r="K222" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="L222" t="s">
-        <v>375</v>
-      </c>
-      <c r="M222" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="223">
       <c r="D223" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="F223" t="s">
+        <v>373</v>
+      </c>
+      <c r="G223" t="s">
+        <v>374</v>
+      </c>
+      <c r="H223" t="s">
+        <v>375</v>
+      </c>
+      <c r="K223" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="L223" t="s">
         <v>377</v>
       </c>
-      <c r="I223" t="s">
+      <c r="M223" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="224">
       <c r="D224" t="s">
-        <v>316</v>
-      </c>
-      <c r="G224" t="s">
+        <v>41</v>
+      </c>
+      <c r="F224" t="s">
         <v>379</v>
       </c>
-      <c r="H224" t="s">
+      <c r="I224" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="225">
-      <c r="B225" t="s">
-        <v>49</v>
+      <c r="D225" t="s">
+        <v>156</v>
+      </c>
+      <c r="G225" t="s">
+        <v>381</v>
+      </c>
+      <c r="H225" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="226">
       <c r="B226" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
     </row>
     <row r="227">
       <c r="B227" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="228">
-      <c r="D228" s="4" t="s">
+    <row r="229">
+      <c r="D229" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E228" t="s">
-        <v>381</v>
-      </c>
-      <c r="F228" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="G228" t="s">
+      <c r="E229" t="s">
         <v>383</v>
       </c>
-      <c r="H228" t="s">
+      <c r="F229" s="4" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="229">
-      <c r="B229" t="s">
+      <c r="G229" t="s">
+        <v>385</v>
+      </c>
+      <c r="H229" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="s">
         <v>55</v>
       </c>
-      <c r="C229" t="s">
-        <v>385</v>
-      </c>
-      <c r="D229" s="4"/>
-      <c r="F229" s="4"/>
-    </row>
-    <row r="230">
-      <c r="D230" s="4" t="s">
+      <c r="C230" t="s">
+        <v>387</v>
+      </c>
+      <c r="D230" s="4"/>
+      <c r="F230" s="4"/>
+    </row>
+    <row r="231">
+      <c r="D231" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E230" t="s">
-        <v>386</v>
-      </c>
-      <c r="F230" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="G230" t="s">
+      <c r="E231" t="s">
         <v>388</v>
       </c>
-      <c r="H230" t="s">
+      <c r="F231" s="4" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="231">
-      <c r="B231" t="s">
-        <v>73</v>
-      </c>
-      <c r="D231" s="4"/>
-      <c r="F231" s="4"/>
+      <c r="G231" t="s">
+        <v>390</v>
+      </c>
+      <c r="H231" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="232">
       <c r="B232" t="s">
-        <v>49</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="D232" s="4"/>
+      <c r="F232" s="4"/>
     </row>
     <row r="233">
       <c r="B233" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
     </row>
     <row r="234">
       <c r="B234" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="D235" t="s">
-        <v>316</v>
-      </c>
-      <c r="G235" t="s">
-        <v>390</v>
-      </c>
-      <c r="H235" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="236">
       <c r="D236" t="s">
+        <v>156</v>
+      </c>
+      <c r="G236" t="s">
+        <v>392</v>
+      </c>
+      <c r="H236" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="D237" t="s">
         <v>41</v>
       </c>
-      <c r="F236" t="s">
-        <v>315</v>
-      </c>
-      <c r="I236">
+      <c r="F237" t="s">
+        <v>318</v>
+      </c>
+      <c r="I237">
         <v>2</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="B237" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="238">
       <c r="B238" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="s">
         <v>73</v>
       </c>
     </row>
@@ -5071,12 +5078,12 @@
     <col bestFit="1" customWidth="1" min="4" max="4" width="43"/>
   </cols>
   <sheetData>
-    <row r="1" s="14" customFormat="1">
+    <row r="1" s="12" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -5084,8 +5091,8 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
-        <v>394</v>
+      <c r="E1" s="12" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="2">
@@ -5097,10 +5104,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="3">
@@ -5112,70 +5119,70 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B4" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B5" s="4" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B6" s="4" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B7" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8">
@@ -5186,55 +5193,55 @@
         <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B9" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D9" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B10" s="4" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B11" s="4" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12">
@@ -5246,517 +5253,517 @@
         <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B13" s="4" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B14" s="4" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B15" s="4" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B16" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B17" s="4" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B18" s="4" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B19" s="4" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B20" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B21" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B22" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B23" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B24" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B25" t="str">
         <f>"6"</f>
         <v>6</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B26" t="str">
         <f>"7"</f>
         <v>7</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E26" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B27" t="str">
         <f>"8"</f>
         <v>8</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E27" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B28" t="str">
         <f>"9"</f>
         <v>9</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E28" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B29" t="str">
         <f>"10"</f>
         <v>10</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E29" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B30" t="str">
         <f>"11"</f>
         <v>11</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E30" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B31" t="str">
         <f>"12"</f>
         <v>12</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E31" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B32" t="str">
         <f>"13"</f>
         <v>13</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E32" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B33" t="str">
         <f>"14"</f>
         <v>14</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E33" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B34" t="str">
         <f>"15"</f>
         <v>15</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E34" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B35" t="str">
         <f>"16"</f>
         <v>16</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E35" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B36" t="str">
         <f>"17"</f>
         <v>17</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E36" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B37" t="str">
         <f>"18"</f>
         <v>18</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E37" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B38" t="str">
         <f>"77"</f>
         <v>77</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B39" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B40" s="4" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B41" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B42" s="4" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B43" s="4" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="44">
@@ -5768,10 +5775,10 @@
         <v>99</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D44" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="45">
@@ -5783,40 +5790,40 @@
         <v>99</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B46" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D46" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B47" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D47" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="48">
@@ -5828,10 +5835,10 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D48" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="49">
@@ -5843,10 +5850,10 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D49" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="50">
@@ -5858,10 +5865,10 @@
         <v>3</v>
       </c>
       <c r="C50" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D50" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="51">
@@ -5873,25 +5880,25 @@
         <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D51" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B52" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D52" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="59">
@@ -5944,275 +5951,275 @@
       <c r="D74" s="4"/>
     </row>
     <row r="76">
-      <c r="B76" s="15"/>
+      <c r="B76" s="13"/>
     </row>
     <row r="77">
-      <c r="B77" s="15"/>
+      <c r="B77" s="13"/>
     </row>
     <row r="78">
-      <c r="B78" s="15"/>
+      <c r="B78" s="13"/>
     </row>
     <row r="79">
-      <c r="B79" s="15"/>
+      <c r="B79" s="13"/>
     </row>
     <row r="80">
-      <c r="B80" s="15"/>
+      <c r="B80" s="13"/>
     </row>
     <row r="81">
-      <c r="B81" s="15"/>
+      <c r="B81" s="13"/>
     </row>
     <row r="82">
-      <c r="B82" s="15"/>
+      <c r="B82" s="13"/>
     </row>
     <row r="83">
-      <c r="B83" s="15"/>
+      <c r="B83" s="13"/>
     </row>
     <row r="84">
-      <c r="B84" s="15"/>
+      <c r="B84" s="13"/>
     </row>
     <row r="85">
-      <c r="B85" s="15"/>
+      <c r="B85" s="13"/>
     </row>
     <row r="86">
-      <c r="B86" s="15"/>
+      <c r="B86" s="13"/>
     </row>
     <row r="87">
-      <c r="B87" s="15"/>
+      <c r="B87" s="13"/>
     </row>
     <row r="88">
-      <c r="B88" s="15"/>
+      <c r="B88" s="13"/>
     </row>
     <row r="89">
-      <c r="B89" s="15"/>
+      <c r="B89" s="13"/>
     </row>
     <row r="90">
-      <c r="B90" s="15"/>
+      <c r="B90" s="13"/>
     </row>
     <row r="91">
-      <c r="B91" s="15"/>
+      <c r="B91" s="13"/>
     </row>
     <row r="92">
-      <c r="B92" s="15"/>
+      <c r="B92" s="13"/>
     </row>
     <row r="93">
-      <c r="B93" s="15"/>
+      <c r="B93" s="13"/>
     </row>
     <row r="94">
-      <c r="B94" s="15"/>
+      <c r="B94" s="13"/>
     </row>
     <row r="95">
-      <c r="B95" s="15"/>
+      <c r="B95" s="13"/>
     </row>
     <row r="96">
-      <c r="B96" s="15"/>
+      <c r="B96" s="13"/>
     </row>
     <row r="97">
-      <c r="B97" s="15"/>
+      <c r="B97" s="13"/>
     </row>
     <row r="98">
-      <c r="B98" s="15"/>
+      <c r="B98" s="13"/>
     </row>
     <row r="99">
-      <c r="B99" s="15"/>
+      <c r="B99" s="13"/>
     </row>
     <row r="100">
-      <c r="B100" s="15"/>
+      <c r="B100" s="13"/>
     </row>
     <row r="101">
-      <c r="B101" s="15"/>
+      <c r="B101" s="13"/>
     </row>
     <row r="102">
-      <c r="B102" s="15"/>
+      <c r="B102" s="13"/>
     </row>
     <row r="103">
-      <c r="B103" s="15"/>
+      <c r="B103" s="13"/>
     </row>
     <row r="104">
-      <c r="B104" s="15"/>
+      <c r="B104" s="13"/>
     </row>
     <row r="105">
-      <c r="B105" s="15"/>
+      <c r="B105" s="13"/>
     </row>
     <row r="106">
-      <c r="B106" s="15"/>
+      <c r="B106" s="13"/>
     </row>
     <row r="107">
-      <c r="B107" s="15"/>
-      <c r="C107" s="15"/>
+      <c r="B107" s="13"/>
+      <c r="C107" s="13"/>
     </row>
     <row r="108">
-      <c r="B108" s="15"/>
-      <c r="C108" s="15"/>
+      <c r="B108" s="13"/>
+      <c r="C108" s="13"/>
     </row>
     <row r="109">
-      <c r="B109" s="15"/>
-      <c r="C109" s="15"/>
+      <c r="B109" s="13"/>
+      <c r="C109" s="13"/>
     </row>
     <row r="110">
-      <c r="B110" s="15"/>
-      <c r="C110" s="15"/>
+      <c r="B110" s="13"/>
+      <c r="C110" s="13"/>
     </row>
     <row r="111">
-      <c r="B111" s="15"/>
-      <c r="C111" s="15"/>
+      <c r="B111" s="13"/>
+      <c r="C111" s="13"/>
     </row>
     <row r="112">
-      <c r="B112" s="15"/>
-      <c r="C112" s="15"/>
+      <c r="B112" s="13"/>
+      <c r="C112" s="13"/>
     </row>
     <row r="113">
-      <c r="B113" s="15"/>
-      <c r="C113" s="15"/>
+      <c r="B113" s="13"/>
+      <c r="C113" s="13"/>
     </row>
     <row r="114">
-      <c r="C114" s="15"/>
+      <c r="C114" s="13"/>
     </row>
     <row r="115">
-      <c r="B115" s="15"/>
-      <c r="C115" s="15"/>
+      <c r="B115" s="13"/>
+      <c r="C115" s="13"/>
     </row>
     <row r="116">
-      <c r="B116" s="15"/>
-      <c r="C116" s="15"/>
+      <c r="B116" s="13"/>
+      <c r="C116" s="13"/>
     </row>
     <row r="117">
-      <c r="B117" s="15"/>
-      <c r="C117" s="15"/>
+      <c r="B117" s="13"/>
+      <c r="C117" s="13"/>
     </row>
     <row r="118">
-      <c r="B118" s="15"/>
-      <c r="C118" s="15"/>
+      <c r="B118" s="13"/>
+      <c r="C118" s="13"/>
     </row>
     <row r="119">
-      <c r="B119" s="15"/>
-      <c r="C119" s="15"/>
+      <c r="B119" s="13"/>
+      <c r="C119" s="13"/>
     </row>
     <row r="120">
-      <c r="B120" s="15"/>
-      <c r="C120" s="15"/>
+      <c r="B120" s="13"/>
+      <c r="C120" s="13"/>
     </row>
     <row r="121">
-      <c r="B121" s="15"/>
-      <c r="C121" s="15"/>
+      <c r="B121" s="13"/>
+      <c r="C121" s="13"/>
     </row>
     <row r="122">
-      <c r="B122" s="15"/>
-      <c r="C122" s="15"/>
+      <c r="B122" s="13"/>
+      <c r="C122" s="13"/>
     </row>
     <row r="123">
-      <c r="B123" s="15"/>
-      <c r="C123" s="15"/>
+      <c r="B123" s="13"/>
+      <c r="C123" s="13"/>
     </row>
     <row r="124">
-      <c r="B124" s="15"/>
-      <c r="C124" s="15"/>
+      <c r="B124" s="13"/>
+      <c r="C124" s="13"/>
     </row>
     <row r="125">
-      <c r="B125" s="15"/>
-      <c r="C125" s="15"/>
+      <c r="B125" s="13"/>
+      <c r="C125" s="13"/>
     </row>
     <row r="126">
-      <c r="B126" s="15"/>
-      <c r="C126" s="15"/>
+      <c r="B126" s="13"/>
+      <c r="C126" s="13"/>
     </row>
     <row r="127">
-      <c r="B127" s="15"/>
-      <c r="C127" s="15"/>
+      <c r="B127" s="13"/>
+      <c r="C127" s="13"/>
     </row>
     <row r="128">
-      <c r="B128" s="15"/>
-      <c r="C128" s="15"/>
+      <c r="B128" s="13"/>
+      <c r="C128" s="13"/>
     </row>
     <row r="129">
-      <c r="B129" s="15"/>
-      <c r="C129" s="15"/>
+      <c r="B129" s="13"/>
+      <c r="C129" s="13"/>
     </row>
     <row r="130">
-      <c r="B130" s="15"/>
-      <c r="C130" s="15"/>
+      <c r="B130" s="13"/>
+      <c r="C130" s="13"/>
     </row>
     <row r="131">
-      <c r="B131" s="15"/>
-      <c r="C131" s="15"/>
+      <c r="B131" s="13"/>
+      <c r="C131" s="13"/>
     </row>
     <row r="132">
-      <c r="B132" s="15"/>
-      <c r="C132" s="15"/>
+      <c r="B132" s="13"/>
+      <c r="C132" s="13"/>
     </row>
     <row r="133">
-      <c r="B133" s="15"/>
+      <c r="B133" s="13"/>
     </row>
     <row r="134">
-      <c r="B134" s="15"/>
+      <c r="B134" s="13"/>
     </row>
     <row r="135">
-      <c r="B135" s="15"/>
+      <c r="B135" s="13"/>
     </row>
     <row r="136">
-      <c r="B136" s="15"/>
+      <c r="B136" s="13"/>
     </row>
     <row r="137">
-      <c r="B137" s="15"/>
+      <c r="B137" s="13"/>
     </row>
     <row r="138">
-      <c r="B138" s="15"/>
+      <c r="B138" s="13"/>
     </row>
     <row r="139">
-      <c r="B139" s="15"/>
+      <c r="B139" s="13"/>
     </row>
     <row r="141">
-      <c r="B141" s="15"/>
+      <c r="B141" s="13"/>
     </row>
     <row r="142">
-      <c r="B142" s="15"/>
+      <c r="B142" s="13"/>
     </row>
     <row r="143">
-      <c r="B143" s="15"/>
+      <c r="B143" s="13"/>
     </row>
     <row r="144">
-      <c r="B144" s="15"/>
+      <c r="B144" s="13"/>
     </row>
     <row r="145">
-      <c r="B145" s="15"/>
+      <c r="B145" s="13"/>
     </row>
     <row r="146">
-      <c r="B146" s="15"/>
+      <c r="B146" s="13"/>
     </row>
     <row r="147">
-      <c r="B147" s="15"/>
+      <c r="B147" s="13"/>
     </row>
     <row r="148">
-      <c r="B148" s="15"/>
+      <c r="B148" s="13"/>
     </row>
     <row r="149">
-      <c r="B149" s="15"/>
+      <c r="B149" s="13"/>
     </row>
     <row r="150">
-      <c r="B150" s="15"/>
+      <c r="B150" s="13"/>
     </row>
     <row r="151">
-      <c r="B151" s="15"/>
+      <c r="B151" s="13"/>
     </row>
     <row r="152">
-      <c r="B152" s="15"/>
+      <c r="B152" s="13"/>
     </row>
     <row r="153">
-      <c r="B153" s="15"/>
+      <c r="B153" s="13"/>
     </row>
     <row r="154">
-      <c r="B154" s="15"/>
+      <c r="B154" s="13"/>
     </row>
     <row r="155">
-      <c r="B155" s="15"/>
+      <c r="B155" s="13"/>
     </row>
     <row r="156">
-      <c r="B156" s="15"/>
+      <c r="B156" s="13"/>
     </row>
     <row r="157">
-      <c r="B157" s="15"/>
+      <c r="B157" s="13"/>
     </row>
     <row r="158">
-      <c r="B158" s="15"/>
+      <c r="B158" s="13"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -6231,10 +6238,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="s">
-        <v>466</v>
-      </c>
-      <c r="B1" s="16" t="s">
+      <c r="A1" s="14" t="s">
+        <v>468</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6256,18 +6263,18 @@
     <col customWidth="1" min="4" max="4" width="40.1796875"/>
   </cols>
   <sheetData>
-    <row r="1" s="14" customFormat="1">
+    <row r="1" s="12" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2" ht="130.5">
@@ -6275,13 +6282,13 @@
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" ht="87">
@@ -6289,13 +6296,13 @@
         <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -6316,18 +6323,18 @@
     <col bestFit="1" customWidth="1" min="4" max="4" width="34.1796875"/>
   </cols>
   <sheetData>
-    <row r="1" s="17" customFormat="1">
-      <c r="A1" s="17" t="s">
-        <v>475</v>
-      </c>
-      <c r="B1" s="17" t="s">
+    <row r="1" s="15" customFormat="1">
+      <c r="A1" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="17" t="s">
-        <v>476</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>477</v>
+      <c r="C1" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="2">
@@ -6335,13 +6342,13 @@
         <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -6369,15 +6376,15 @@
         <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B2" t="s">
         <v>106</v>
@@ -6386,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3">
@@ -6402,7 +6409,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B4" t="s">
         <v>78</v>
@@ -6446,10 +6453,10 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B8" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
@@ -6457,7 +6464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B9" t="s">
         <v>98</v>
@@ -6470,7 +6477,7 @@
       <c r="A10" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>63</v>
       </c>
       <c r="C10" t="b">
@@ -6481,7 +6488,7 @@
       <c r="A11" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="16" t="s">
         <v>82</v>
       </c>
       <c r="C11" t="b">
@@ -6490,7 +6497,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s">
         <v>98</v>
@@ -6502,7 +6509,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s">
         <v>98</v>
@@ -6513,7 +6520,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B14" t="s">
         <v>98</v>
@@ -6535,7 +6542,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B16" t="s">
         <v>46</v>
@@ -6546,7 +6553,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B17" t="s">
         <v>98</v>
@@ -6557,7 +6564,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B18" t="s">
         <v>98</v>
@@ -6590,7 +6597,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B21" t="s">
         <v>106</v>
@@ -6601,7 +6608,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s">
         <v>98</v>
@@ -6612,10 +6619,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B23" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C23" t="b">
         <v>0</v>
@@ -6623,7 +6630,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
@@ -6669,7 +6676,7 @@
       <c r="A28" t="s">
         <v>128</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="16" t="s">
         <v>82</v>
       </c>
       <c r="C28" t="b">
@@ -6678,7 +6685,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B29" t="s">
         <v>41</v>
@@ -6689,7 +6696,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
@@ -6700,7 +6707,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B31" t="s">
         <v>98</v>
@@ -6711,7 +6718,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B32" t="s">
         <v>98</v>
@@ -6722,7 +6729,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s">
         <v>63</v>
@@ -6766,7 +6773,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B37" t="s">
         <v>78</v>
@@ -6777,7 +6784,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B38" t="s">
         <v>41</v>
@@ -6788,7 +6795,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B39" t="s">
         <v>63</v>
@@ -6799,7 +6806,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B40" t="s">
         <v>63</v>
@@ -6821,7 +6828,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B42" t="s">
         <v>98</v>
@@ -6832,7 +6839,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B43" t="s">
         <v>98</v>
@@ -6843,9 +6850,9 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>356</v>
-      </c>
-      <c r="B44" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="B44" s="16" t="s">
         <v>63</v>
       </c>
       <c r="C44" t="b">
@@ -6854,7 +6861,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B45" t="s">
         <v>78</v>
@@ -6865,7 +6872,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B46" t="s">
         <v>78</v>
@@ -6878,7 +6885,7 @@
       <c r="A47" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="16" t="s">
         <v>78</v>
       </c>
       <c r="C47" t="b">
@@ -6920,7 +6927,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B51" t="s">
         <v>98</v>
@@ -6942,7 +6949,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B53" t="s">
         <v>98</v>
@@ -6986,9 +6993,9 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="B57" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="B57" s="16" t="s">
         <v>106</v>
       </c>
       <c r="C57" t="b">
@@ -6997,9 +7004,9 @@
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="B58" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="B58" s="16" t="s">
         <v>106</v>
       </c>
       <c r="C58" t="b">
@@ -7008,9 +7015,9 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B59" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="B59" s="16" t="s">
         <v>106</v>
       </c>
       <c r="C59" t="b">
@@ -7019,7 +7026,7 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B60" t="s">
         <v>78</v>
@@ -7030,7 +7037,7 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B61" t="s">
         <v>78</v>
@@ -7041,7 +7048,7 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B62" t="s">
         <v>78</v>
@@ -7052,7 +7059,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B63" t="s">
         <v>63</v>
@@ -7063,7 +7070,7 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>98</v>
@@ -7074,7 +7081,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B65" t="s">
         <v>98</v>
@@ -7085,7 +7092,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B66" t="s">
         <v>98</v>
@@ -7096,7 +7103,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B67" t="s">
         <v>98</v>
@@ -7107,7 +7114,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B68" t="s">
         <v>98</v>
@@ -7118,10 +7125,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>293</v>
-      </c>
-      <c r="B69" s="18" t="s">
-        <v>216</v>
+        <v>296</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>219</v>
       </c>
       <c r="C69" t="b">
         <v>0</v>
@@ -7129,7 +7136,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B70" t="s">
         <v>82</v>
@@ -7140,7 +7147,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B71" t="s">
         <v>82</v>
@@ -7151,7 +7158,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B72" t="s">
         <v>82</v>
@@ -7162,7 +7169,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B73" t="s">
         <v>63</v>
@@ -7173,7 +7180,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B74" t="s">
         <v>63</v>
@@ -7184,7 +7191,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B75" t="s">
         <v>63</v>
@@ -7195,7 +7202,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B76" t="s">
         <v>98</v>
@@ -7206,7 +7213,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B77" t="s">
         <v>98</v>
@@ -7216,27 +7223,27 @@
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="18"/>
+      <c r="B78" s="16"/>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>486</v>
-      </c>
-      <c r="B79" s="18" t="s">
+        <v>488</v>
+      </c>
+      <c r="B79" s="16" t="s">
         <v>98</v>
       </c>
       <c r="C79" t="b">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>488</v>
-      </c>
-      <c r="B80" s="18" t="s">
+        <v>490</v>
+      </c>
+      <c r="B80" s="16" t="s">
         <v>98</v>
       </c>
       <c r="C80" t="b">
@@ -7245,35 +7252,35 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>489</v>
-      </c>
-      <c r="B81" s="18" t="s">
+        <v>491</v>
+      </c>
+      <c r="B81" s="16" t="s">
         <v>98</v>
       </c>
       <c r="C81" t="b">
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>490</v>
-      </c>
-      <c r="B82" s="18" t="s">
+        <v>492</v>
+      </c>
+      <c r="B82" s="16" t="s">
         <v>98</v>
       </c>
       <c r="C82" t="b">
         <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B83" t="s">
         <v>46</v>
@@ -7282,17 +7289,17 @@
         <v>0</v>
       </c>
       <c r="D83" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="18"/>
+      <c r="B84" s="16"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>210</v>
-      </c>
-      <c r="B85" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="B85" s="16" t="s">
         <v>98</v>
       </c>
       <c r="C85" t="b">
@@ -7300,10 +7307,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="B86" s="19" t="s">
+      <c r="A86" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B86" s="16" t="s">
         <v>98</v>
       </c>
       <c r="C86" t="b">
@@ -7311,118 +7318,118 @@
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="18"/>
+      <c r="B87" s="16"/>
     </row>
     <row r="88">
-      <c r="B88" s="18"/>
+      <c r="B88" s="16"/>
     </row>
     <row r="89">
-      <c r="B89" s="18"/>
+      <c r="B89" s="16"/>
     </row>
     <row r="90">
-      <c r="B90" s="18"/>
+      <c r="B90" s="16"/>
     </row>
     <row r="91">
-      <c r="B91" s="18"/>
+      <c r="B91" s="16"/>
     </row>
     <row r="92">
-      <c r="B92" s="18"/>
+      <c r="B92" s="16"/>
     </row>
     <row r="93">
-      <c r="B93" s="18"/>
+      <c r="B93" s="16"/>
     </row>
     <row r="94">
-      <c r="B94" s="18"/>
+      <c r="B94" s="16"/>
     </row>
     <row r="95">
-      <c r="B95" s="18"/>
+      <c r="B95" s="16"/>
     </row>
     <row r="96">
-      <c r="B96" s="18"/>
+      <c r="B96" s="16"/>
     </row>
     <row r="97">
-      <c r="B97" s="18"/>
+      <c r="B97" s="16"/>
     </row>
     <row r="98">
-      <c r="B98" s="18"/>
+      <c r="B98" s="16"/>
     </row>
     <row r="99">
-      <c r="B99" s="18"/>
+      <c r="B99" s="16"/>
     </row>
     <row r="100">
-      <c r="B100" s="18"/>
+      <c r="B100" s="16"/>
     </row>
     <row r="101">
-      <c r="B101" s="18"/>
+      <c r="B101" s="16"/>
     </row>
     <row r="102">
-      <c r="B102" s="18"/>
+      <c r="B102" s="16"/>
     </row>
     <row r="103">
-      <c r="B103" s="18"/>
+      <c r="B103" s="16"/>
     </row>
     <row r="104">
-      <c r="B104" s="18"/>
+      <c r="B104" s="16"/>
     </row>
     <row r="105">
-      <c r="B105" s="18"/>
+      <c r="B105" s="16"/>
     </row>
     <row r="106">
-      <c r="B106" s="18"/>
+      <c r="B106" s="16"/>
     </row>
     <row r="107">
-      <c r="B107" s="18"/>
+      <c r="B107" s="16"/>
     </row>
     <row r="108">
-      <c r="B108" s="18"/>
+      <c r="B108" s="16"/>
     </row>
     <row r="109">
-      <c r="B109" s="18"/>
+      <c r="B109" s="16"/>
     </row>
     <row r="110">
-      <c r="B110" s="18"/>
+      <c r="B110" s="16"/>
     </row>
     <row r="111">
-      <c r="B111" s="18"/>
+      <c r="B111" s="16"/>
     </row>
     <row r="112">
-      <c r="B112" s="18"/>
+      <c r="B112" s="16"/>
     </row>
     <row r="113">
-      <c r="B113" s="18"/>
+      <c r="B113" s="16"/>
     </row>
     <row r="114">
-      <c r="B114" s="18"/>
+      <c r="B114" s="16"/>
     </row>
     <row r="115">
-      <c r="B115" s="18"/>
+      <c r="B115" s="16"/>
     </row>
     <row r="116">
-      <c r="B116" s="18"/>
+      <c r="B116" s="16"/>
     </row>
     <row r="117">
-      <c r="B117" s="18"/>
+      <c r="B117" s="16"/>
     </row>
     <row r="118">
-      <c r="B118" s="18"/>
+      <c r="B118" s="16"/>
     </row>
     <row r="119">
-      <c r="B119" s="18"/>
+      <c r="B119" s="16"/>
     </row>
     <row r="120">
-      <c r="B120" s="18"/>
+      <c r="B120" s="16"/>
     </row>
     <row r="121">
-      <c r="B121" s="18"/>
+      <c r="B121" s="16"/>
     </row>
     <row r="122">
-      <c r="B122" s="18"/>
+      <c r="B122" s="16"/>
     </row>
     <row r="123">
-      <c r="B123" s="18"/>
+      <c r="B123" s="16"/>
     </row>
     <row r="124">
-      <c r="B124" s="18"/>
+      <c r="B124" s="16"/>
     </row>
   </sheetData>
   <sortState ref="A2:C77">

--- a/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
+++ b/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
@@ -1,29 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\MADtrials2\MADtrial\app\config\tables\MADTRIAL_INC\Forms\MADTRIAL_INC\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFE6F06-97ED-425F-A0FE-DE3298648C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="survey" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inc" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="choices" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="calculates" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="queries" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="prompt_types" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="model" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="settings" sheetId="1" r:id="rId1"/>
+    <sheet name="survey" sheetId="2" r:id="rId2"/>
+    <sheet name="inc" sheetId="3" r:id="rId3"/>
+    <sheet name="choices" sheetId="4" r:id="rId4"/>
+    <sheet name="calculates" sheetId="5" r:id="rId5"/>
+    <sheet name="queries" sheetId="6" r:id="rId6"/>
+    <sheet name="prompt_types" sheetId="7" r:id="rId7"/>
+    <sheet name="model" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="495">
   <si>
     <t>setting_name</t>
   </si>
@@ -58,10 +75,10 @@
     <t>survey</t>
   </si>
   <si>
-    <t xml:space="preserve">MADtrial - Inclusion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MADtrial - Inclusão</t>
+    <t>MADtrial - Inclusion</t>
+  </si>
+  <si>
+    <t>MADtrial - Inclusão</t>
   </si>
   <si>
     <t>default</t>
@@ -118,7 +135,7 @@
     <t>choice_filter</t>
   </si>
   <si>
-    <t xml:space="preserve">do section inc</t>
+    <t>do section inc</t>
   </si>
   <si>
     <t>constraint</t>
@@ -145,7 +162,7 @@
     <t>required</t>
   </si>
   <si>
-    <t xml:space="preserve">begin screen</t>
+    <t>begin screen</t>
   </si>
   <si>
     <t>assign</t>
@@ -166,13 +183,13 @@
     <t>adate</t>
   </si>
   <si>
-    <t xml:space="preserve">Date of inclusion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data de inclusão</t>
-  </si>
-  <si>
-    <t xml:space="preserve">end screen</t>
+    <t>Date of inclusion</t>
+  </si>
+  <si>
+    <t>Data de inclusão</t>
+  </si>
+  <si>
+    <t>end screen</t>
   </si>
   <si>
     <t>select_one_dropdown</t>
@@ -193,7 +210,7 @@
     <t>if</t>
   </si>
   <si>
-    <t xml:space="preserve">data('BAIRRO') == 77</t>
+    <t>data('BAIRRO') == 77</t>
   </si>
   <si>
     <t>tabz_csv</t>
@@ -202,16 +219,16 @@
     <t>TABZ</t>
   </si>
   <si>
-    <t xml:space="preserve">Neighborhood outside project area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bairro fora da área do projeto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choice_item.BAIRRONR === data('BAIRRO')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('TABZ') == 7777</t>
+    <t>Neighborhood outside project area</t>
+  </si>
+  <si>
+    <t>Bairro fora da área do projeto</t>
+  </si>
+  <si>
+    <t>choice_item.BAIRRONR === data('BAIRRO')</t>
+  </si>
+  <si>
+    <t>data('TABZ') == 7777</t>
   </si>
   <si>
     <t>text</t>
@@ -220,10 +237,10 @@
     <t>OUBAIRRO</t>
   </si>
   <si>
-    <t xml:space="preserve">What neighborhood?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Que bairro?</t>
+    <t>What neighborhood?</t>
+  </si>
+  <si>
+    <t>Que bairro?</t>
   </si>
   <si>
     <t>else</t>
@@ -232,19 +249,19 @@
     <t>CAMOONDE</t>
   </si>
   <si>
-    <t xml:space="preserve">Pleace describe how to find the house</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Por favor, descreva como encontrar a casa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CAMOONDE') != null || data('TABZ') == 7777 || data('CAMO') != 9999</t>
+    <t>Pleace describe how to find the house</t>
+  </si>
+  <si>
+    <t>Por favor, descreva como encontrar a casa</t>
+  </si>
+  <si>
+    <t>data('CAMOONDE') != null || data('TABZ') == 7777 || data('CAMO') != 9999</t>
   </si>
   <si>
     <t>OBS</t>
   </si>
   <si>
-    <t xml:space="preserve">end if</t>
+    <t>end if</t>
   </si>
   <si>
     <t>CAMO</t>
@@ -262,13 +279,13 @@
     <t>integer</t>
   </si>
   <si>
-    <t xml:space="preserve">House number (camo)</t>
+    <t>House number (camo)</t>
   </si>
   <si>
     <t>Camo</t>
   </si>
   <si>
-    <t xml:space="preserve">data('CAMO') != null || data('CAMOONDE') != null</t>
+    <t>data('CAMO') != null || data('CAMOONDE') != null</t>
   </si>
   <si>
     <t>select_multiple</t>
@@ -280,7 +297,7 @@
     <t>camons</t>
   </si>
   <si>
-    <t xml:space="preserve">data('camons') !=null</t>
+    <t>data('camons') !=null</t>
   </si>
   <si>
     <t>Where?</t>
@@ -292,13 +309,13 @@
     <t>CNO</t>
   </si>
   <si>
-    <t xml:space="preserve">data('BAIRRO') == 77 || freebase.characters(data('CNO')) == 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be 5 digits long:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve ter 5 dígitos:</t>
+    <t>data('BAIRRO') == 77 || freebase.characters(data('CNO')) == 5</t>
+  </si>
+  <si>
+    <t>Must be 5 digits long:</t>
+  </si>
+  <si>
+    <t>Deve ter 5 dígitos:</t>
   </si>
   <si>
     <t>number</t>
@@ -307,16 +324,16 @@
     <t>cnons</t>
   </si>
   <si>
-    <t xml:space="preserve">data('cnons') != null</t>
+    <t>data('cnons') != null</t>
   </si>
   <si>
     <t>NOMECRI</t>
   </si>
   <si>
-    <t xml:space="preserve">Child's name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome de criança</t>
+    <t>Child's name</t>
+  </si>
+  <si>
+    <t>Nome de criança</t>
   </si>
   <si>
     <t>select_one</t>
@@ -328,19 +345,19 @@
     <t>SEX</t>
   </si>
   <si>
-    <t xml:space="preserve">Sex of the child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sexo da criança</t>
+    <t>Sex of the child</t>
+  </si>
+  <si>
+    <t>Sexo da criança</t>
   </si>
   <si>
     <t>NOMEMAE</t>
   </si>
   <si>
-    <t xml:space="preserve">Name of mother</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome da mãe</t>
+    <t>Name of mother</t>
+  </si>
+  <si>
+    <t>Nome da mãe</t>
   </si>
   <si>
     <t>select_one_with_other</t>
@@ -352,58 +369,58 @@
     <t>RESP</t>
   </si>
   <si>
-    <t xml:space="preserve">Who brought the child?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quem trouxe a criança?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('RESP') != '1' &amp;&amp; data('RESP') != null</t>
+    <t>Who brought the child?</t>
+  </si>
+  <si>
+    <t>Quem trouxe a criança?</t>
+  </si>
+  <si>
+    <t>data('RESP') != '1' &amp;&amp; data('RESP') != null</t>
   </si>
   <si>
     <t>NOMERESP</t>
   </si>
   <si>
-    <t xml:space="preserve">Name of person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome da pessoa</t>
+    <t>Name of person</t>
+  </si>
+  <si>
+    <t>Nome da pessoa</t>
   </si>
   <si>
     <t>REGNO</t>
   </si>
   <si>
-    <t xml:space="preserve">Register number (triage survey)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de registo (ficha de triagem)</t>
+    <t>Register number (triage survey)</t>
+  </si>
+  <si>
+    <t>Número de registo (ficha de triagem)</t>
   </si>
   <si>
     <t>regnons</t>
   </si>
   <si>
-    <t xml:space="preserve">data('regnons') != null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('BAIRRO') != 77</t>
+    <t>data('regnons') != null</t>
+  </si>
+  <si>
+    <t>data('BAIRRO') != 77</t>
   </si>
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t xml:space="preserve">ID (BHP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID (PSB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(data('ID')&gt;999999  &amp;&amp; data('ID')&lt;10000000) || data('BAIRRO') == 77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be 7 digits long:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve ter 7 dígitos:</t>
+    <t>ID (BHP)</t>
+  </si>
+  <si>
+    <t>ID (PSB)</t>
+  </si>
+  <si>
+    <t>(data('ID')&gt;999999  &amp;&amp; data('ID')&lt;10000000) || data('BAIRRO') == 77</t>
+  </si>
+  <si>
+    <t>Must be 7 digits long:</t>
+  </si>
+  <si>
+    <t>Deve ter 7 dígitos:</t>
   </si>
   <si>
     <t>nsID</t>
@@ -412,25 +429,25 @@
     <t>idns</t>
   </si>
   <si>
-    <t xml:space="preserve">data('idns') != null</t>
+    <t>data('idns') != null</t>
   </si>
   <si>
     <t>REGIDC</t>
   </si>
   <si>
-    <t xml:space="preserve">Equipa móvel ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID da equipa móvel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('REGIDC') &gt; 10000000 &amp;&amp; data('REGIDC') &lt; 1000000000 || data('BAIRRO') != 77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be 8 digits long:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve ter 8 dígitos:</t>
+    <t>Equipa móvel ID</t>
+  </si>
+  <si>
+    <t>ID da equipa móvel</t>
+  </si>
+  <si>
+    <t>data('REGIDC') &gt; 10000000 &amp;&amp; data('REGIDC') &lt; 1000000000 || data('BAIRRO') != 77</t>
+  </si>
+  <si>
+    <t>Must be 8 digits long:</t>
+  </si>
+  <si>
+    <t>Deve ter 8 dígitos:</t>
   </si>
   <si>
     <t>nsREGIDC</t>
@@ -439,25 +456,25 @@
     <t>regidcns</t>
   </si>
   <si>
-    <t xml:space="preserve">data('regidcns') !=null</t>
+    <t>data('regidcns') !=null</t>
   </si>
   <si>
     <t>DOB</t>
   </si>
   <si>
-    <t xml:space="preserve">Day of birth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data de nascimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adate.diffInDays(data('DATINC'), data('DOB'))&lt;1 || adate.hasUncertainty(data('DOB'))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The date cannot be in the future:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A data não pode estar no futuro:</t>
+    <t>Day of birth</t>
+  </si>
+  <si>
+    <t>Data de nascimento</t>
+  </si>
+  <si>
+    <t>adate.diffInDays(data('DATINC'), data('DOB'))&lt;1 || adate.hasUncertainty(data('DOB'))</t>
+  </si>
+  <si>
+    <t>The date cannot be in the future:</t>
+  </si>
+  <si>
+    <t>A data não pode estar no futuro:</t>
   </si>
   <si>
     <t>datens</t>
@@ -466,7 +483,7 @@
     <t>dobns</t>
   </si>
   <si>
-    <t xml:space="preserve">data('dobns') != null</t>
+    <t>data('dobns') != null</t>
   </si>
   <si>
     <t>"D:NS,M:NS,Y:NS"</t>
@@ -478,43 +495,37 @@
     <t>IDADEANO</t>
   </si>
   <si>
-    <t xml:space="preserve">Age - year(s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idade - ano(s)</t>
+    <t>Age - year(s)</t>
+  </si>
+  <si>
+    <t>Idade - ano(s)</t>
   </si>
   <si>
     <t>IDADEMES</t>
   </si>
   <si>
-    <t xml:space="preserve">Age - month(s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idade - mes(es)</t>
+    <t>Age - month(s)</t>
+  </si>
+  <si>
+    <t>Idade - mes(es)</t>
   </si>
   <si>
     <t>note</t>
   </si>
   <si>
-    <t xml:space="preserve">The child has to be under 5 years and over 15 months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança deve ter entre 15 méses e 5 anos de idade</t>
-  </si>
-  <si>
     <t>sim/não</t>
   </si>
   <si>
     <t>CONSENT</t>
   </si>
   <si>
-    <t xml:space="preserve">Does the mother/father/guardian consent to enrolment?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A mãe/pai/tutor aceita inclusão no estudo?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CONSENT') == '1'</t>
+    <t>Does the mother/father/guardian consent to enrolment?</t>
+  </si>
+  <si>
+    <t>A mãe/pai/tutor aceita inclusão no estudo?</t>
+  </si>
+  <si>
+    <t>data('CONSENT') == '1'</t>
   </si>
   <si>
     <t>signature</t>
@@ -523,13 +534,13 @@
     <t>CONSENTTIPO</t>
   </si>
   <si>
-    <t xml:space="preserve">Type of signature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipo da assinatura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CONSENTTIPO') == '2'</t>
+    <t>Type of signature</t>
+  </si>
+  <si>
+    <t>Tipo da assinatura</t>
+  </si>
+  <si>
+    <t>data('CONSENTTIPO') == '2'</t>
   </si>
   <si>
     <t>sim</t>
@@ -538,37 +549,37 @@
     <t>TESTEMUNHO</t>
   </si>
   <si>
-    <t xml:space="preserve">The witness signed the consent form</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O testemunho assina o formulário de consentimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">selected(data('TESTEMUNHO'),'1') || data('CONSENTTIPO') != '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A witness has to sign the consent form:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Um testemunho deve assinar o formulário de consentimento:</t>
+    <t>The witness signed the consent form</t>
+  </si>
+  <si>
+    <t>O testemunho assina o formulário de consentimento</t>
+  </si>
+  <si>
+    <t>selected(data('TESTEMUNHO'),'1') || data('CONSENTTIPO') != '2'</t>
+  </si>
+  <si>
+    <t>A witness has to sign the consent form:</t>
+  </si>
+  <si>
+    <t>Um testemunho deve assinar o formulário de consentimento:</t>
   </si>
   <si>
     <t>TELEMOVEL1</t>
   </si>
   <si>
-    <t xml:space="preserve">Phone number 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de telemovel 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('TELEMOVEL1') &gt; 99999999 &amp;&amp; data('TELEMOVEL1') &lt; 1000000000 || data('CONSENT') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be 9 digits long:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve ter 9 dígitos:</t>
+    <t>Phone number 1</t>
+  </si>
+  <si>
+    <t>Número de telemovel 1</t>
+  </si>
+  <si>
+    <t>data('TELEMOVEL1') &gt; 99999999 &amp;&amp; data('TELEMOVEL1') &lt; 1000000000 || data('CONSENT') == '2'</t>
+  </si>
+  <si>
+    <t>Must be 9 digits long:</t>
+  </si>
+  <si>
+    <t>Deve ter 9 dígitos:</t>
   </si>
   <si>
     <t>telinf1</t>
@@ -580,13 +591,13 @@
     <t>TELEMOVEL2</t>
   </si>
   <si>
-    <t xml:space="preserve">Phone number 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de telemovel 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('TELEMOVEL2') &gt; 99999999 &amp;&amp; data('TELEMOVEL2') &lt; 1000000000 || data('CONSENT') == '2'</t>
+    <t>Phone number 2</t>
+  </si>
+  <si>
+    <t>Número de telemovel 2</t>
+  </si>
+  <si>
+    <t>data('TELEMOVEL2') &gt; 99999999 &amp;&amp; data('TELEMOVEL2') &lt; 1000000000 || data('CONSENT') == '2'</t>
   </si>
   <si>
     <t>telinf2</t>
@@ -598,88 +609,88 @@
     <t>TELEMOVEL3</t>
   </si>
   <si>
-    <t xml:space="preserve">Phone number 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de telemovel 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('TELEMOVEL3') &gt; 99999999 &amp;&amp; data('TELEMOVEL3') &lt; 1000000000 || data('CONSENT') == '2'</t>
+    <t>Phone number 3</t>
+  </si>
+  <si>
+    <t>Número de telemovel 3</t>
+  </si>
+  <si>
+    <t>data('TELEMOVEL3') &gt; 99999999 &amp;&amp; data('TELEMOVEL3') &lt; 1000000000 || data('CONSENT') == '2'</t>
   </si>
   <si>
     <t>TELEINF3</t>
   </si>
   <si>
-    <t xml:space="preserve">data('TELEINF2') == '3'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('TELEINF3') == '3'</t>
+    <t>data('TELEINF2') == '3'</t>
+  </si>
+  <si>
+    <t>data('TELEINF3') == '3'</t>
   </si>
   <si>
     <t>CARTVIS</t>
   </si>
   <si>
-    <t xml:space="preserve">Was the vaccine card seen?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O cartão de vacina foi visto?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CARTVIS') != null || data('CONSENT') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required value not provided.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor requerido não fornecido.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CARTVIS') == '1'</t>
+    <t>Was the vaccine card seen?</t>
+  </si>
+  <si>
+    <t>O cartão de vacina foi visto?</t>
+  </si>
+  <si>
+    <t>data('CARTVIS') != null || data('CONSENT') == '2'</t>
+  </si>
+  <si>
+    <t>Required value not provided.</t>
+  </si>
+  <si>
+    <t>Valor requerido não fornecido.</t>
+  </si>
+  <si>
+    <t>data('CARTVIS') == '1'</t>
   </si>
   <si>
     <t>SARVAC</t>
   </si>
   <si>
-    <t xml:space="preserve">Has the child received the first measles vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança recebeu a primeira vacina do sarampo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('SARVAC') != null || data('CONSENT') == '2' || data('CARTVIS') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CARTVIS') == '2'</t>
+    <t>Has the child received the first measles vaccine</t>
+  </si>
+  <si>
+    <t>A criança recebeu a primeira vacina do sarampo</t>
+  </si>
+  <si>
+    <t>data('SARVAC') != null || data('CONSENT') == '2' || data('CARTVIS') == '2'</t>
+  </si>
+  <si>
+    <t>data('CARTVIS') == '2'</t>
   </si>
   <si>
     <t>VENAOVAS</t>
   </si>
   <si>
-    <t xml:space="preserve">Mother/guardian confirmed that the child did not receive the second measles vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A mãe/tutor confirmou que a criança não recebeu a vacina do sarampo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('VENAOVAS') != null || data('CONSENT') == '2' || data('CARTVIS') == '1'</t>
+    <t>Mother/guardian confirmed that the child did not receive the second measles vaccine</t>
+  </si>
+  <si>
+    <t>A mãe/tutor confirmou que a criança não recebeu a vacina do sarampo</t>
+  </si>
+  <si>
+    <t>data('VENAOVAS') != null || data('CONSENT') == '2' || data('CARTVIS') == '1'</t>
   </si>
   <si>
     <t>SARVAC2</t>
   </si>
   <si>
-    <t xml:space="preserve">Has the child received the second measles vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança recebeu a seguna vacina do sarampo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('SARVAC2') != null || data('CONSENT') == '2' || data('CARTVIS') == '2'</t>
+    <t>Has the child received the second measles vaccine</t>
+  </si>
+  <si>
+    <t>A criança recebeu a seguna vacina do sarampo</t>
+  </si>
+  <si>
+    <t>data('SARVAC2') != null || data('CONSENT') == '2' || data('CARTVIS') == '2'</t>
   </si>
   <si>
     <t>VENAOVAS2</t>
   </si>
   <si>
-    <t xml:space="preserve">A mãe/tutor confirmou que a criança não recebeu a segunda vacina do sarampo</t>
+    <t>A mãe/tutor confirmou que a criança não recebeu a segunda vacina do sarampo</t>
   </si>
   <si>
     <t>image</t>
@@ -688,10 +699,10 @@
     <t>CARTIMG</t>
   </si>
   <si>
-    <t xml:space="preserve">Please take a picture of the vaccine card</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Por favor, tire uma foto do cartão de vacina</t>
+    <t>Please take a picture of the vaccine card</t>
+  </si>
+  <si>
+    <t>Por favor, tire uma foto do cartão de vacina</t>
   </si>
   <si>
     <t>TEMPERATURA</t>
@@ -703,37 +714,37 @@
     <t>Temperatura</t>
   </si>
   <si>
-    <t xml:space="preserve">freebase.decimalPlaces(data('TEMPERATURA'))==1 || data('CONSENT') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must have 1 decimal:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve ter 1 decimal:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Write the temperature with 1 decimal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escreva a temperatura com 1 decimal</t>
+    <t>freebase.decimalPlaces(data('TEMPERATURA'))==1 || data('CONSENT') == '2'</t>
+  </si>
+  <si>
+    <t>Must have 1 decimal:</t>
+  </si>
+  <si>
+    <t>Deve ter 1 decimal:</t>
+  </si>
+  <si>
+    <t>Write the temperature with 1 decimal</t>
+  </si>
+  <si>
+    <t>Escreva a temperatura com 1 decimal</t>
   </si>
   <si>
     <t>BRACOCRI</t>
   </si>
   <si>
-    <t xml:space="preserve">Middle upper arm circumference</t>
+    <t>Middle upper arm circumference</t>
   </si>
   <si>
     <t>Braço</t>
   </si>
   <si>
-    <t xml:space="preserve">(data('BRACOCRI')&gt;49 &amp;&amp; data('BRACOCRI')&lt;343 &amp;&amp; data('BRACOCRI')%2 == 0) || data('CONSENT') == '2' || data('BRACOCRI') == 999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be between 50 and 342 and a even number:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve estar entre 50 e 342 e um número par:</t>
+    <t>(data('BRACOCRI')&gt;49 &amp;&amp; data('BRACOCRI')&lt;343 &amp;&amp; data('BRACOCRI')%2 == 0) || data('CONSENT') == '2' || data('BRACOCRI') == 999</t>
+  </si>
+  <si>
+    <t>Must be between 50 and 342 and a even number:</t>
+  </si>
+  <si>
+    <t>Deve estar entre 50 e 342 e um número par:</t>
   </si>
   <si>
     <t>Motivo</t>
@@ -742,10 +753,10 @@
     <t>MOTCONT</t>
   </si>
   <si>
-    <t xml:space="preserve">Reason for contact with the pediatric ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motivo de contato com a pediatria</t>
+    <t>Reason for contact with the pediatric ward</t>
+  </si>
+  <si>
+    <t>Motivo de contato com a pediatria</t>
   </si>
   <si>
     <t>data('MOTCONT')=='2'</t>
@@ -754,13 +765,13 @@
     <t>INTINICI</t>
   </si>
   <si>
-    <t xml:space="preserve">Since day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desde dia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adate.diffInDays(data('DATINC'), data('INTINICI'))&lt;1 || adate.hasUncertainty(data('INTINICI')) ||data('CONSENT') == '2'</t>
+    <t>Since day</t>
+  </si>
+  <si>
+    <t>Desde dia</t>
+  </si>
+  <si>
+    <t>adate.diffInDays(data('DATINC'), data('INTINICI'))&lt;1 || adate.hasUncertainty(data('INTINICI')) ||data('CONSENT') == '2'</t>
   </si>
   <si>
     <t>sim/não/ns</t>
@@ -808,10 +819,10 @@
     <t>RENORREI</t>
   </si>
   <si>
-    <t xml:space="preserve">Runny nose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rinorreia (ranho)</t>
+    <t>Runny nose</t>
+  </si>
+  <si>
+    <t>Rinorreia (ranho)</t>
   </si>
   <si>
     <t>TOSSE</t>
@@ -826,10 +837,10 @@
     <t>DIFRESP</t>
   </si>
   <si>
-    <t xml:space="preserve">Respiratory difficulty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dificuldade respiratória</t>
+    <t>Respiratory difficulty</t>
+  </si>
+  <si>
+    <t>Dificuldade respiratória</t>
   </si>
   <si>
     <t>CONVULSA</t>
@@ -844,22 +855,22 @@
     <t>OSIMP</t>
   </si>
   <si>
-    <t xml:space="preserve">Other symptoms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outros sintomas</t>
+    <t>Other symptoms</t>
+  </si>
+  <si>
+    <t>Outros sintomas</t>
   </si>
   <si>
     <t>TRATAMENT_A</t>
   </si>
   <si>
-    <t xml:space="preserve">Did the child receive any treatments?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança recebeu algum tratamento (antes inclusao)?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('TRATAMENT_A') =='1'</t>
+    <t>Did the child receive any treatments?</t>
+  </si>
+  <si>
+    <t>A criança recebeu algum tratamento (antes inclusao)?</t>
+  </si>
+  <si>
+    <t>data('TRATAMENT_A') =='1'</t>
   </si>
   <si>
     <t>tratament</t>
@@ -868,10 +879,10 @@
     <t>TRATQUAL_A</t>
   </si>
   <si>
-    <t xml:space="preserve">What treatments did the child recieve?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qual tratamento foi dado?</t>
+    <t>What treatments did the child recieve?</t>
+  </si>
+  <si>
+    <t>Qual tratamento foi dado?</t>
   </si>
   <si>
     <t>selected(data('TRATQUAL_A'),'77')</t>
@@ -889,22 +900,22 @@
     <t>TRATAMENT_R</t>
   </si>
   <si>
-    <t xml:space="preserve">Did the child get any treatments prescribed?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança deve receber algum tratamento (receita)?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('TRATAMENT_R') =='1'</t>
+    <t>Did the child get any treatments prescribed?</t>
+  </si>
+  <si>
+    <t>A criança deve receber algum tratamento (receita)?</t>
+  </si>
+  <si>
+    <t>data('TRATAMENT_R') =='1'</t>
   </si>
   <si>
     <t>TRATQUAL_R</t>
   </si>
   <si>
-    <t xml:space="preserve">What treatments are prescribed ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qual tratamento foi receitado?</t>
+    <t>What treatments are prescribed ?</t>
+  </si>
+  <si>
+    <t>Qual tratamento foi receitado?</t>
   </si>
   <si>
     <t>selected(data('TRATQUAL_R'),'77')</t>
@@ -916,22 +927,22 @@
     <t>TRATIMG</t>
   </si>
   <si>
-    <t xml:space="preserve">If the child have a prescription, please take a photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se a criança tiver uma receita médica, por favor tire uma foto</t>
+    <t>If the child have a prescription, please take a photo</t>
+  </si>
+  <si>
+    <t>Se a criança tiver uma receita médica, por favor tire uma foto</t>
   </si>
   <si>
     <t>PODEVAC</t>
   </si>
   <si>
-    <t xml:space="preserve">Can the child receive a vaccine (VAS) today?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança pode receber uma vacina (VAS) hoje?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('PODEVAC') != null || data('CONSENT') == '2'</t>
+    <t>Can the child receive a vaccine (VAS) today?</t>
+  </si>
+  <si>
+    <t>A criança pode receber uma vacina (VAS) hoje?</t>
+  </si>
+  <si>
+    <t>data('PODEVAC') != null || data('CONSENT') == '2'</t>
   </si>
   <si>
     <t>data('PODEVAC')=='2'</t>
@@ -949,13 +960,13 @@
     <t>PODEINC</t>
   </si>
   <si>
-    <t xml:space="preserve">Can the child be included today?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança pode ser incluída hoje?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('PODEINC') != null || data('CONSENT') == '2'</t>
+    <t>Can the child be included today?</t>
+  </si>
+  <si>
+    <t>A criança pode ser incluída hoje?</t>
+  </si>
+  <si>
+    <t>data('PODEINC') != null || data('CONSENT') == '2'</t>
   </si>
   <si>
     <t>data('PODEINC')=='2'</t>
@@ -967,136 +978,124 @@
     <t>JAINC</t>
   </si>
   <si>
-    <t xml:space="preserve">Is the child already participating in the study?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança já está participando do estudo?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('JAINC') != null || data('CONSENT') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('PODEVAC')=='2'|| data('PODEINC')=='2'  || data('JAINC') == '1' || data('BRACOCRI') &lt;110 || data('TEMPERATURA')&gt;37.9 || data('VENAOVAS') == '2' ||  data('VENAOVAS2') == '2' || data('SARVAC') != '1' || data('SARVAC2') == '1'</t>
+    <t>Is the child already participating in the study?</t>
+  </si>
+  <si>
+    <t>A criança já está participando do estudo?</t>
+  </si>
+  <si>
+    <t>data('JAINC') != null || data('CONSENT') == '2'</t>
   </si>
   <si>
     <t>INC</t>
   </si>
   <si>
-    <t xml:space="preserve">The child is not to be included, since:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança não deve ser incluída, porque:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The nurse assessed that the child should not be vaccinated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A enfermeira avaliou que a criança não deve ser vacinada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The nurse assessed that the child should not be included</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A enfermeira avaliou que a criança não deveria ser incluída</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('JAINC') == '1'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The child already participating in the study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança já participa no estudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('BRACOCRI') &lt;110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upper middle arm circumference is smaller than 110 mm ({{data.BRACOCRI}})</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A braço é menor do que 110 mm ({{data.BRACOCRI}})</t>
+    <t>The child is not to be included, since:</t>
+  </si>
+  <si>
+    <t>A criança não deve ser incluída, porque:</t>
+  </si>
+  <si>
+    <t>The nurse assessed that the child should not be vaccinated</t>
+  </si>
+  <si>
+    <t>A enfermeira avaliou que a criança não deve ser vacinada</t>
+  </si>
+  <si>
+    <t>The nurse assessed that the child should not be included</t>
+  </si>
+  <si>
+    <t>A enfermeira avaliou que a criança não deveria ser incluída</t>
+  </si>
+  <si>
+    <t>data('JAINC') == '1'</t>
+  </si>
+  <si>
+    <t>The child already participating in the study</t>
+  </si>
+  <si>
+    <t>A criança já participa no estudo</t>
+  </si>
+  <si>
+    <t>data('BRACOCRI') &lt;110</t>
+  </si>
+  <si>
+    <t>Upper middle arm circumference is smaller than 110 mm ({{data.BRACOCRI}})</t>
+  </si>
+  <si>
+    <t>A braço é menor do que 110 mm ({{data.BRACOCRI}})</t>
   </si>
   <si>
     <t>data('TEMPERATURA')&gt;38</t>
   </si>
   <si>
-    <t xml:space="preserve">The temperature is greater than 37.9 ({{data.TEMPERATURA}})</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A temperatura é mais alta do que 37,9 ({{data.TEMPERATURA}})</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('VENAOVAS2') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mother/guardian could not confirm that the child did not receive the first measles vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mãe/tutor não pôde confirmar que a criança não recebeu a primeira vacina do sarampo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('VENAOVAS') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mother/guardian could not confirm that the child did not receive the second measles vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mãe/tutor não pôde confirmar que a criança não recebeu a segunda vacina do sarampo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('SARVAC') != '1'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The child has not previously received the first measles vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança não recebeu a primeira vacina do sarampo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('SARVAC2') == '1'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The child has previously received the second measles vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança recebeu a segunda vacina do sarampo</t>
+    <t>The temperature is greater than 37.9 ({{data.TEMPERATURA}})</t>
+  </si>
+  <si>
+    <t>A temperatura é mais alta do que 37,9 ({{data.TEMPERATURA}})</t>
+  </si>
+  <si>
+    <t>data('VENAOVAS2') == '2'</t>
+  </si>
+  <si>
+    <t>Mother/guardian could not confirm that the child did not receive the first measles vaccine</t>
+  </si>
+  <si>
+    <t>Mãe/tutor não pôde confirmar que a criança não recebeu a primeira vacina do sarampo</t>
+  </si>
+  <si>
+    <t>data('VENAOVAS') == '2'</t>
+  </si>
+  <si>
+    <t>Mother/guardian could not confirm that the child did not receive the second measles vaccine</t>
+  </si>
+  <si>
+    <t>Mãe/tutor não pôde confirmar que a criança não recebeu a segunda vacina do sarampo</t>
+  </si>
+  <si>
+    <t>data('SARVAC2') == '1'</t>
+  </si>
+  <si>
+    <t>The child has previously received the second measles vaccine</t>
+  </si>
+  <si>
+    <t>A criança recebeu a segunda vacina do sarampo</t>
   </si>
   <si>
     <t>RANDOM1</t>
   </si>
   <si>
-    <t xml:space="preserve">First randomization number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primeiro número de randomização</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('RANDOM2')&lt;501 &amp;&amp; data('RANDOM1')&gt;0 || data('INC') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be 1-500:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve ser de 1 a 500:</t>
+    <t>First randomization number</t>
+  </si>
+  <si>
+    <t>Primeiro número de randomização</t>
+  </si>
+  <si>
+    <t>data('RANDOM2')&lt;501 &amp;&amp; data('RANDOM1')&gt;0 || data('INC') == '2'</t>
+  </si>
+  <si>
+    <t>Must be 1-500:</t>
+  </si>
+  <si>
+    <t>Deve ser de 1 a 500:</t>
   </si>
   <si>
     <t>RANDOM2</t>
   </si>
   <si>
-    <t xml:space="preserve">Second randomization number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segundo número de randomização</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('RANDOM2')&lt;13 &amp;&amp; data('RANDOM2')&gt;0 || data('INC') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be 1-12:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve ser de 1 a 12:</t>
+    <t>Second randomization number</t>
+  </si>
+  <si>
+    <t>Segundo número de randomização</t>
+  </si>
+  <si>
+    <t>data('RANDOM2')&lt;13 &amp;&amp; data('RANDOM2')&gt;0 || data('INC') == '2'</t>
+  </si>
+  <si>
+    <t>Must be 1-12:</t>
+  </si>
+  <si>
+    <t>Deve ser de 1 a 12:</t>
   </si>
   <si>
     <t>RANDOM</t>
@@ -1105,10 +1104,10 @@
     <t>freebase.randomLabel(data('SEX'),data('RANDOM1'),data('RANDOM2'))</t>
   </si>
   <si>
-    <t xml:space="preserve">Label: &lt;b&gt;{{data.RANDOM}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etiqueta: &lt;b&gt;{{data.RANDOM}}&lt;/b&gt;</t>
+    <t>Label: &lt;b&gt;{{data.RANDOM}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Etiqueta: &lt;b&gt;{{data.RANDOM}}&lt;/b&gt;</t>
   </si>
   <si>
     <t>DATVACVAS</t>
@@ -1117,10 +1116,10 @@
     <t>data('DATINC')</t>
   </si>
   <si>
-    <t xml:space="preserve">Date of vaccination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data da vacinação</t>
+    <t>Date of vaccination</t>
+  </si>
+  <si>
+    <t>Data da vacinação</t>
   </si>
   <si>
     <t>time</t>
@@ -1129,10 +1128,10 @@
     <t>HORA</t>
   </si>
   <si>
-    <t xml:space="preserve">Time of vaccination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hora da vacinação</t>
+    <t>Time of vaccination</t>
+  </si>
+  <si>
+    <t>Hora da vacinação</t>
   </si>
   <si>
     <t xml:space="preserve">data('HORVACVAS') != null || data('INC') == '2' </t>
@@ -1147,19 +1146,19 @@
     <t>NUM</t>
   </si>
   <si>
-    <t xml:space="preserve">Study number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de estudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('NUM')&gt;0 || data('INC') == '2' || data('changeid') != null || data('changetabz') != null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cannot be negative:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não pode ser negativo:</t>
+    <t>Study number</t>
+  </si>
+  <si>
+    <t>Número de estudo</t>
+  </si>
+  <si>
+    <t>data('NUM')&gt;0 || data('INC') == '2' || data('changeid') != null || data('changetabz') != null</t>
+  </si>
+  <si>
+    <t>Cannot be negative:</t>
+  </si>
+  <si>
+    <t>Não pode ser negativo:</t>
   </si>
   <si>
     <t>NUMEST</t>
@@ -1168,10 +1167,10 @@
     <t>freebase.studyNumber("MAD",4,data('NUM'))</t>
   </si>
   <si>
-    <t xml:space="preserve">Study number: &lt;b&gt;{{data.NUMEST}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de estudo: &lt;b&gt;{{data.NUMEST}}&lt;/b&gt;</t>
+    <t>Study number: &lt;b&gt;{{data.NUMEST}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Número de estudo: &lt;b&gt;{{data.NUMEST}}&lt;/b&gt;</t>
   </si>
   <si>
     <t>enf</t>
@@ -1186,7 +1185,7 @@
     <t>Enfermeira</t>
   </si>
   <si>
-    <t xml:space="preserve">data('INC') == '1'</t>
+    <t>data('INC') == '1'</t>
   </si>
   <si>
     <t>ass</t>
@@ -1201,10 +1200,10 @@
     <t>Assistente</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;font color = "red"&gt;End the enrolment as consent has not been obtained&lt;/font &gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;font color = "red"&gt; Finalize a inclusão porque o consentimento não foi dado &lt;/font&gt;</t>
+    <t>&lt;font color = "red"&gt;End the enrolment as consent has not been obtained&lt;/font &gt;</t>
+  </si>
+  <si>
+    <t>&lt;font color = "red"&gt; Finalize a inclusão porque o consentimento não foi dado &lt;/font&gt;</t>
   </si>
   <si>
     <t>choice_list_name</t>
@@ -1252,31 +1251,28 @@
     <t>Internamento</t>
   </si>
   <si>
-    <t xml:space="preserve">Dont't know</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não sabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don't know</t>
+    <t>Dont't know</t>
+  </si>
+  <si>
+    <t>Não sabe</t>
+  </si>
+  <si>
+    <t>Don't know</t>
   </si>
   <si>
     <t>Abrao</t>
   </si>
   <si>
-    <t xml:space="preserve">removed Suzete (enf=1) on 19-01-2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augosto Da Costa</t>
+    <t>removed Suzete (enf=1) on 19-01-2022</t>
+  </si>
+  <si>
+    <t>Augosto Da Costa</t>
   </si>
   <si>
     <t>Abdel</t>
   </si>
   <si>
-    <t>Fatima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">removed Suzete (ass=11) on 19-01-2022</t>
+    <t>removed Suzete (ass=11) on 19-01-2022</t>
   </si>
   <si>
     <t>Paracetamol</t>
@@ -1285,7 +1281,7 @@
     <t>Amoxicillina</t>
   </si>
   <si>
-    <t xml:space="preserve">Complexo B</t>
+    <t>Complexo B</t>
   </si>
   <si>
     <t>Salbutamol</t>
@@ -1297,76 +1293,76 @@
     <t>Prometazina</t>
   </si>
   <si>
-    <t xml:space="preserve">Soro fisiologico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">added 16-02-2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitamina C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">added 16-02-2023</t>
+    <t>Soro fisiologico</t>
+  </si>
+  <si>
+    <t>added 16-02-2022</t>
+  </si>
+  <si>
+    <t>Vitamina C</t>
+  </si>
+  <si>
+    <t>added 16-02-2023</t>
   </si>
   <si>
     <t>SRO</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sulfate de Zinco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">added 16-02-2025</t>
+    <t>added 16-02-2024</t>
+  </si>
+  <si>
+    <t>Sulfate de Zinco</t>
+  </si>
+  <si>
+    <t>added 16-02-2025</t>
   </si>
   <si>
     <t>Azitomicina</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2026</t>
+    <t>added 16-02-2026</t>
   </si>
   <si>
     <t>Brufen</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2027</t>
+    <t>added 16-02-2027</t>
   </si>
   <si>
     <t>Albendazol</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2028</t>
+    <t>added 16-02-2028</t>
   </si>
   <si>
     <t>Mebendazol</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2029</t>
+    <t>added 16-02-2029</t>
   </si>
   <si>
     <t>Metroniazol</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2030</t>
+    <t>added 16-02-2030</t>
   </si>
   <si>
     <t>Nistatina</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2031</t>
+    <t>added 16-02-2031</t>
   </si>
   <si>
     <t>Augmentin</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2032</t>
+    <t>added 16-02-2032</t>
   </si>
   <si>
     <t>Erytromecina</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2033</t>
+    <t>added 16-02-2033</t>
   </si>
   <si>
     <t>Other</t>
@@ -1387,22 +1383,22 @@
     <t>Pai</t>
   </si>
   <si>
-    <t xml:space="preserve">Don't have another phone number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não tem outro número de telefone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Didn't suceed to identify ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não conseguiu identifcar o ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don't have ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não tem ID</t>
+    <t>Don't have another phone number</t>
+  </si>
+  <si>
+    <t>Não tem outro número de telefone</t>
+  </si>
+  <si>
+    <t>Didn't suceed to identify ID</t>
+  </si>
+  <si>
+    <t>Não conseguiu identifcar o ID</t>
+  </si>
+  <si>
+    <t>Don't have ID</t>
+  </si>
+  <si>
+    <t>Não tem ID</t>
   </si>
   <si>
     <t>Signature</t>
@@ -1414,7 +1410,7 @@
     <t>Fingerprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Impressão digital</t>
+    <t>Impressão digital</t>
   </si>
   <si>
     <t>Sibling</t>
@@ -1423,7 +1419,7 @@
     <t>Irmã(o)</t>
   </si>
   <si>
-    <t xml:space="preserve">Mothers mother</t>
+    <t>Mothers mother</t>
   </si>
   <si>
     <t>Avó</t>
@@ -1450,7 +1446,7 @@
     <t>"TABZ.csv"</t>
   </si>
   <si>
-    <t xml:space="preserve">_.chain(context)
+    <t>_.chain(context)
 .uniq(function(x) {
 return x.BAIRRONR
 })
@@ -1461,7 +1457,7 @@
 }).value()</t>
   </si>
   <si>
-    <t xml:space="preserve">_.map(context, function(place){place.data_value = place.TABZ;
+    <t>_.map(context, function(place){place.data_value = place.TABZ;
 place.display = {title: {text: place.ZONE} };
 return place;
 })</t>
@@ -1479,7 +1475,7 @@
     <t>string</t>
   </si>
   <si>
-    <t xml:space="preserve">Save only mm.dd.yyyy with support for ?? at all positions</t>
+    <t>Save only mm.dd.yyyy with support for ?? at all positions</t>
   </si>
   <si>
     <t>isSessionVariable</t>
@@ -1513,52 +1509,85 @@
   </si>
   <si>
     <t>changeregdate</t>
+  </si>
+  <si>
+    <t>The child has to be under 5 years and over 9 months</t>
+  </si>
+  <si>
+    <t>A criança deve ter entre 9 méses e 5 anos de idade</t>
+  </si>
+  <si>
+    <t>data('PODEVAC')=='2'|| data('PODEINC')=='2'  || data('JAINC') == '1' || data('BRACOCRI') &lt;110 || data('TEMPERATURA')&gt;37.9 || data('VENAOVAS') == '2' ||  data('VENAOVAS2') == '2' || (data('SARVAC') == '1' &amp;&amp;  data('SARVAC2') == '1')||data('SARVAC2') == '1'</t>
+  </si>
+  <si>
+    <t>Josemira</t>
+  </si>
+  <si>
+    <t>removed fatima - ass=1 on 20250723</t>
+  </si>
+  <si>
+    <t>Justiniano</t>
+  </si>
+  <si>
+    <t>data('SARVAC') == '1'&amp;&amp; data('SARVAC2')==1</t>
+  </si>
+  <si>
+    <t>The child has previously received both measles vaccines</t>
+  </si>
+  <si>
+    <t>A criança recebeu os seus vacinas do sarampo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-406]General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.000000"/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -1578,69 +1607,68 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="4">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="164" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Excel Built-in Normal" xfId="1"/>
+    <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 4" xfId="3"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 4" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{6BFC12A9-29D4-4643-AD82-2911AB8B1BCB}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1652,291 +1680,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2139,22 +1884,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="13.26953125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="10.1796875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="29"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="27"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="24.7265625"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="28.54296875"/>
+    <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2174,7 +1921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2182,7 +1929,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2190,7 +1937,7 @@
         <v>60120</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2198,7 +1945,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2209,7 +1956,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -2220,7 +1967,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2231,7 +1978,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
@@ -2240,28 +1987,27 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="12.453125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="14.26953125"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="24.7265625"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="10.453125"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" width="26.1796875"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="18.81640625"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="10.54296875"/>
-    <col bestFit="1" customWidth="1" min="10" max="10" width="12.1796875"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -2293,41 +2039,40 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:R239"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="12.453125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="12.26953125"/>
-    <col customWidth="1" min="3" max="3" width="32.81640625"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="22"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="13.1796875"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="14.54296875"/>
-    <col customWidth="1" min="7" max="7" width="45.54296875"/>
-    <col customWidth="1" min="8" max="8" width="35.453125"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="15.7265625"/>
-    <col customWidth="1" min="10" max="10" width="13.54296875"/>
-    <col customWidth="1" min="11" max="11" width="30.7265625"/>
-    <col bestFit="1" customWidth="1" min="12" max="12" width="37.453125"/>
-    <col bestFit="1" customWidth="1" min="13" max="13" width="30.26953125"/>
-    <col bestFit="1" customWidth="1" min="14" max="14" width="23"/>
-    <col bestFit="1" customWidth="1" min="15" max="15" width="15.7265625"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.81640625" customWidth="1"/>
+    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="45.54296875" customWidth="1"/>
+    <col min="8" max="8" width="35.453125" customWidth="1"/>
+    <col min="9" max="9" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.54296875" customWidth="1"/>
+    <col min="11" max="11" width="30.7265625" customWidth="1"/>
+    <col min="12" max="12" width="37.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -2383,12 +2128,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="D3" t="s">
         <v>41</v>
       </c>
@@ -2399,7 +2144,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="D4" t="s">
         <v>41</v>
       </c>
@@ -2410,7 +2155,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="D5" t="s">
         <v>46</v>
       </c>
@@ -2427,17 +2172,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="D8" t="s">
         <v>50</v>
       </c>
@@ -2454,7 +2199,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>55</v>
       </c>
@@ -2462,7 +2207,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="D10" t="s">
         <v>50</v>
       </c>
@@ -2472,59 +2217,55 @@
       <c r="F10" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" t="s">
         <v>59</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" t="s">
         <v>60</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>55</v>
       </c>
       <c r="C11" t="s">
         <v>62</v>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="J11" s="5"/>
-    </row>
-    <row r="12">
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="D12" t="s">
         <v>63</v>
       </c>
       <c r="F12" t="s">
         <v>64</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14">
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="D14" t="s">
         <v>63</v>
       </c>
       <c r="F14" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" t="s">
         <v>70</v>
       </c>
       <c r="K14" t="s">
@@ -2537,12 +2278,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
         <v>41</v>
       </c>
@@ -2553,13 +2294,12 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18">
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>75</v>
       </c>
@@ -2578,15 +2318,14 @@
       <c r="H18" t="s">
         <v>77</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D19" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="4"/>
       <c r="F19" t="s">
         <v>74</v>
       </c>
@@ -2606,31 +2345,29 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D20" t="s">
         <v>82</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" t="s">
         <v>83</v>
       </c>
       <c r="F20" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>55</v>
       </c>
       <c r="C21" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22">
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D22" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="4"/>
       <c r="F22" t="s">
         <v>74</v>
       </c>
@@ -2638,11 +2375,10 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D23" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="4"/>
       <c r="F23" t="s">
         <v>68</v>
       </c>
@@ -2662,17 +2398,15 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>73</v>
       </c>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25">
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D25" t="s">
         <v>63</v>
       </c>
-      <c r="E25" s="4"/>
       <c r="F25" t="s">
         <v>88</v>
       </c>
@@ -2695,31 +2429,29 @@
         <v>92</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D26" t="s">
         <v>82</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" t="s">
         <v>83</v>
       </c>
       <c r="F26" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>55</v>
       </c>
       <c r="C27" t="s">
         <v>94</v>
       </c>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28">
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D28" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="4"/>
       <c r="F28" t="s">
         <v>88</v>
       </c>
@@ -2727,36 +2459,34 @@
         <v>99999</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>73</v>
       </c>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30">
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>73</v>
       </c>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31">
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D33" t="s">
         <v>63</v>
       </c>
       <c r="F33" t="s">
         <v>95</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" t="s">
         <v>96</v>
       </c>
       <c r="H33" t="s">
@@ -2766,7 +2496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D34" t="s">
         <v>98</v>
       </c>
@@ -2776,7 +2506,7 @@
       <c r="F34" t="s">
         <v>100</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" t="s">
         <v>101</v>
       </c>
       <c r="H34" t="s">
@@ -2786,33 +2516,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D35" t="s">
         <v>63</v>
       </c>
       <c r="F35" t="s">
         <v>103</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" t="s">
         <v>104</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="H35" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>49</v>
       </c>
-      <c r="G36" s="4"/>
-    </row>
-    <row r="37">
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>40</v>
       </c>
-      <c r="G37" s="4"/>
-    </row>
-    <row r="38">
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D38" t="s">
         <v>106</v>
       </c>
@@ -2822,23 +2550,22 @@
       <c r="F38" t="s">
         <v>108</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" t="s">
         <v>109</v>
       </c>
       <c r="H38" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>55</v>
       </c>
       <c r="C39" t="s">
         <v>111</v>
       </c>
-      <c r="G39" s="4"/>
-    </row>
-    <row r="40">
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D40" t="s">
         <v>63</v>
       </c>
@@ -2852,23 +2579,22 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>73</v>
       </c>
-      <c r="G41" s="4"/>
-    </row>
-    <row r="42">
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D44" t="s">
         <v>78</v>
       </c>
@@ -2882,7 +2608,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D45" t="s">
         <v>82</v>
       </c>
@@ -2893,7 +2619,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>55</v>
       </c>
@@ -2901,7 +2627,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D47" t="s">
         <v>41</v>
       </c>
@@ -2912,21 +2638,20 @@
         <v>999</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>55</v>
       </c>
       <c r="C49" t="s">
         <v>120</v>
       </c>
-      <c r="G49" s="4"/>
-    </row>
-    <row r="50" ht="16.5" customHeight="1">
+    </row>
+    <row r="50" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D50" t="s">
         <v>78</v>
       </c>
@@ -2939,7 +2664,7 @@
       <c r="H50" t="s">
         <v>123</v>
       </c>
-      <c r="K50" s="6" t="s">
+      <c r="K50" s="5" t="s">
         <v>124</v>
       </c>
       <c r="L50" t="s">
@@ -2949,7 +2674,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="51" ht="16.5" customHeight="1">
+    <row r="51" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D51" t="s">
         <v>82</v>
       </c>
@@ -2959,18 +2684,16 @@
       <c r="F51" t="s">
         <v>128</v>
       </c>
-      <c r="K51" s="4"/>
-    </row>
-    <row r="52" ht="16.5" customHeight="1">
+    </row>
+    <row r="52" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>55</v>
       </c>
       <c r="C52" t="s">
         <v>129</v>
       </c>
-      <c r="K52" s="4"/>
-    </row>
-    <row r="53" ht="16.5" customHeight="1">
+    </row>
+    <row r="53" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D53" t="s">
         <v>41</v>
       </c>
@@ -2980,21 +2703,18 @@
       <c r="I53">
         <v>9999999</v>
       </c>
-      <c r="K53" s="4"/>
-    </row>
-    <row r="54" ht="16.5" customHeight="1">
+    </row>
+    <row r="54" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>73</v>
       </c>
-      <c r="K54" s="4"/>
-    </row>
-    <row r="55" ht="16.5" customHeight="1">
+    </row>
+    <row r="55" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>67</v>
       </c>
-      <c r="K55" s="4"/>
-    </row>
-    <row r="56">
+    </row>
+    <row r="56" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D56" t="s">
         <v>78</v>
       </c>
@@ -3017,31 +2737,29 @@
         <v>135</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D57" t="s">
         <v>82</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="E57" t="s">
         <v>136</v>
       </c>
       <c r="F57" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
         <v>55</v>
       </c>
       <c r="C58" t="s">
         <v>138</v>
       </c>
-      <c r="E58" s="4"/>
-    </row>
-    <row r="59">
+    </row>
+    <row r="59" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D59" t="s">
         <v>41</v>
       </c>
-      <c r="E59" s="4"/>
       <c r="F59" t="s">
         <v>130</v>
       </c>
@@ -3049,27 +2767,27 @@
         <v>999999999</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D64" t="s">
         <v>46</v>
       </c>
@@ -3095,7 +2813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D65" t="s">
         <v>82</v>
       </c>
@@ -3106,7 +2824,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
         <v>55</v>
       </c>
@@ -3114,23 +2832,23 @@
         <v>147</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D67" t="s">
         <v>41</v>
       </c>
       <c r="F67" t="s">
         <v>139</v>
       </c>
-      <c r="I67" s="7" t="s">
+      <c r="I67" s="6" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
         <v>55</v>
       </c>
@@ -3138,7 +2856,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D70" t="s">
         <v>78</v>
       </c>
@@ -3151,9 +2869,8 @@
       <c r="H70" t="s">
         <v>152</v>
       </c>
-      <c r="K70" s="4"/>
-    </row>
-    <row r="71">
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D71" t="s">
         <v>78</v>
       </c>
@@ -3166,694 +2883,624 @@
       <c r="H71" t="s">
         <v>155</v>
       </c>
-      <c r="K71" s="4"/>
-    </row>
-    <row r="72">
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="8"/>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D73" t="s">
         <v>156</v>
       </c>
       <c r="G73" t="s">
-        <v>157</v>
+        <v>486</v>
       </c>
       <c r="H73" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D76" t="s">
         <v>98</v>
       </c>
       <c r="E76" t="s">
+        <v>157</v>
+      </c>
+      <c r="F76" t="s">
+        <v>158</v>
+      </c>
+      <c r="G76" t="s">
         <v>159</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="H76" t="s">
         <v>160</v>
-      </c>
-      <c r="G76" t="s">
-        <v>161</v>
-      </c>
-      <c r="H76" t="s">
-        <v>162</v>
       </c>
       <c r="R76" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>55</v>
       </c>
       <c r="C77" t="s">
-        <v>163</v>
-      </c>
-      <c r="F77" s="4"/>
-    </row>
-    <row r="78">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="78" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D78" t="s">
         <v>98</v>
       </c>
       <c r="E78" t="s">
+        <v>162</v>
+      </c>
+      <c r="F78" t="s">
+        <v>163</v>
+      </c>
+      <c r="G78" t="s">
         <v>164</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="H78" t="s">
         <v>165</v>
       </c>
-      <c r="G78" t="s">
-        <v>166</v>
-      </c>
-      <c r="H78" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="79">
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>55</v>
       </c>
       <c r="C79" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="80" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D80" t="s">
+        <v>98</v>
+      </c>
+      <c r="E80" t="s">
+        <v>167</v>
+      </c>
+      <c r="F80" t="s">
         <v>168</v>
       </c>
-      <c r="F79" s="4"/>
-    </row>
-    <row r="80">
-      <c r="D80" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E80" s="4" t="s">
+      <c r="G80" t="s">
         <v>169</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="H80" t="s">
         <v>170</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="K80" t="s">
         <v>171</v>
       </c>
-      <c r="H80" s="4" t="s">
+      <c r="L80" t="s">
         <v>172</v>
       </c>
-      <c r="K80" t="s">
+      <c r="M80" t="s">
         <v>173</v>
       </c>
-      <c r="L80" t="s">
-        <v>174</v>
-      </c>
-      <c r="M80" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="81">
+    </row>
+    <row r="81" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>73</v>
       </c>
-      <c r="F81" s="4"/>
-    </row>
-    <row r="82">
+    </row>
+    <row r="82" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>73</v>
       </c>
-      <c r="F82" s="4"/>
-    </row>
-    <row r="83">
+    </row>
+    <row r="83" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
         <v>49</v>
       </c>
-      <c r="F83" s="4"/>
-    </row>
-    <row r="84">
+    </row>
+    <row r="84" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>55</v>
       </c>
       <c r="C84" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="85">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="85" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D86" t="s">
         <v>78</v>
       </c>
-      <c r="F86" s="4" t="s">
+      <c r="F86" t="s">
+        <v>174</v>
+      </c>
+      <c r="G86" t="s">
+        <v>175</v>
+      </c>
+      <c r="H86" t="s">
         <v>176</v>
       </c>
-      <c r="G86" s="4" t="s">
+      <c r="K86" t="s">
         <v>177</v>
       </c>
-      <c r="H86" t="s">
+      <c r="L86" t="s">
         <v>178</v>
       </c>
-      <c r="K86" t="s">
+      <c r="M86" t="s">
         <v>179</v>
       </c>
-      <c r="L86" t="s">
-        <v>180</v>
-      </c>
-      <c r="M86" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="87">
+    </row>
+    <row r="87" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D87" t="s">
         <v>106</v>
       </c>
       <c r="E87" t="s">
-        <v>182</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>180</v>
+      </c>
+      <c r="F87" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="88" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D88" t="s">
         <v>78</v>
       </c>
-      <c r="F88" s="4" t="s">
+      <c r="F88" t="s">
+        <v>182</v>
+      </c>
+      <c r="G88" t="s">
+        <v>183</v>
+      </c>
+      <c r="H88" t="s">
         <v>184</v>
       </c>
-      <c r="G88" t="s">
+      <c r="K88" t="s">
         <v>185</v>
       </c>
-      <c r="H88" t="s">
-        <v>186</v>
-      </c>
-      <c r="K88" t="s">
-        <v>187</v>
-      </c>
       <c r="L88" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M88" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="89" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D89" t="s">
         <v>106</v>
       </c>
       <c r="E89" t="s">
-        <v>188</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>186</v>
+      </c>
+      <c r="F89" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="90" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D90" t="s">
         <v>78</v>
       </c>
-      <c r="F90" s="4" t="s">
+      <c r="F90" t="s">
+        <v>188</v>
+      </c>
+      <c r="G90" t="s">
+        <v>189</v>
+      </c>
+      <c r="H90" t="s">
         <v>190</v>
       </c>
-      <c r="G90" t="s">
+      <c r="K90" t="s">
         <v>191</v>
       </c>
-      <c r="H90" t="s">
-        <v>192</v>
-      </c>
-      <c r="K90" t="s">
-        <v>193</v>
-      </c>
       <c r="L90" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M90" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="91">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="91" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D91" t="s">
         <v>106</v>
       </c>
       <c r="E91" t="s">
-        <v>188</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="92">
+        <v>186</v>
+      </c>
+      <c r="F91" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="92" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
         <v>55</v>
       </c>
       <c r="C92" t="s">
-        <v>195</v>
-      </c>
-      <c r="F92" s="4"/>
-    </row>
-    <row r="93">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="93" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D93" t="s">
         <v>41</v>
       </c>
-      <c r="F93" s="4" t="s">
-        <v>184</v>
+      <c r="F93" t="s">
+        <v>182</v>
       </c>
       <c r="I93">
         <v>999999999</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
         <v>73</v>
       </c>
-      <c r="F94" s="4"/>
-    </row>
-    <row r="95">
+    </row>
+    <row r="95" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
         <v>55</v>
       </c>
       <c r="C95" t="s">
-        <v>196</v>
-      </c>
-      <c r="F95" s="4"/>
-    </row>
-    <row r="96">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="96" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D96" t="s">
         <v>41</v>
       </c>
-      <c r="F96" s="4" t="s">
-        <v>190</v>
+      <c r="F96" t="s">
+        <v>188</v>
       </c>
       <c r="I96">
         <v>999999999</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
         <v>73</v>
       </c>
-      <c r="F97" s="4"/>
-    </row>
-    <row r="98">
+    </row>
+    <row r="98" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
         <v>49</v>
       </c>
-      <c r="F98" s="4"/>
-    </row>
-    <row r="99">
+    </row>
+    <row r="99" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D100" t="s">
         <v>98</v>
       </c>
       <c r="E100" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F100" t="s">
+        <v>195</v>
+      </c>
+      <c r="G100" t="s">
+        <v>196</v>
+      </c>
+      <c r="H100" t="s">
         <v>197</v>
       </c>
-      <c r="G100" t="s">
+      <c r="K100" t="s">
         <v>198</v>
       </c>
-      <c r="H100" t="s">
+      <c r="L100" t="s">
         <v>199</v>
       </c>
-      <c r="K100" t="s">
+      <c r="M100" t="s">
         <v>200</v>
       </c>
-      <c r="L100" t="s">
-        <v>201</v>
-      </c>
-      <c r="M100" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="101">
+    </row>
+    <row r="101" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
         <v>55</v>
       </c>
       <c r="C101" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="102">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="102" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D102" t="s">
         <v>98</v>
       </c>
       <c r="E102" t="s">
-        <v>159</v>
-      </c>
-      <c r="F102" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="F102" t="s">
+        <v>202</v>
+      </c>
+      <c r="G102" t="s">
+        <v>203</v>
+      </c>
+      <c r="H102" t="s">
         <v>204</v>
       </c>
-      <c r="G102" t="s">
+      <c r="K102" t="s">
         <v>205</v>
       </c>
-      <c r="H102" t="s">
-        <v>206</v>
-      </c>
-      <c r="K102" t="s">
-        <v>207</v>
-      </c>
       <c r="L102" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M102" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="103">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="103" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
         <v>55</v>
       </c>
       <c r="C104" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="105">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="105" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D105" t="s">
         <v>98</v>
       </c>
       <c r="E105" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F105" t="s">
+        <v>207</v>
+      </c>
+      <c r="G105" t="s">
+        <v>208</v>
+      </c>
+      <c r="H105" t="s">
         <v>209</v>
       </c>
-      <c r="G105" t="s">
+      <c r="K105" t="s">
         <v>210</v>
       </c>
-      <c r="H105" t="s">
-        <v>211</v>
-      </c>
-      <c r="K105" t="s">
-        <v>212</v>
-      </c>
       <c r="L105" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M105" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="106">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="106" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="9"/>
-      <c r="B107" s="9" t="s">
+    <row r="107" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B107" t="s">
         <v>55</v>
       </c>
-      <c r="C107" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="D107" s="9"/>
-      <c r="E107" s="9"/>
-      <c r="F107" s="9"/>
-      <c r="G107" s="9"/>
-      <c r="H107" s="9"/>
-      <c r="I107" s="9"/>
-      <c r="J107" s="9"/>
-      <c r="K107" s="9"/>
-      <c r="L107" s="9"/>
-      <c r="M107" s="9"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="9"/>
-      <c r="B108" s="9"/>
-      <c r="C108" s="9"/>
-      <c r="D108" s="9" t="s">
+      <c r="C107" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="108" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D108" t="s">
         <v>98</v>
       </c>
-      <c r="E108" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="F108" s="4" t="s">
+      <c r="E108" t="s">
+        <v>157</v>
+      </c>
+      <c r="F108" t="s">
+        <v>211</v>
+      </c>
+      <c r="G108" t="s">
+        <v>212</v>
+      </c>
+      <c r="H108" t="s">
         <v>213</v>
       </c>
-      <c r="G108" s="4" t="s">
+      <c r="K108" t="s">
         <v>214</v>
       </c>
-      <c r="H108" s="4" t="s">
+      <c r="L108" t="s">
+        <v>199</v>
+      </c>
+      <c r="M108" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="109" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B109" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="110" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B110" t="s">
+        <v>55</v>
+      </c>
+      <c r="C110" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="111" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D111" t="s">
+        <v>98</v>
+      </c>
+      <c r="E111" t="s">
+        <v>157</v>
+      </c>
+      <c r="F111" t="s">
         <v>215</v>
       </c>
-      <c r="I108" s="9"/>
-      <c r="J108" s="9"/>
-      <c r="K108" s="9" t="s">
+      <c r="G111" t="s">
+        <v>208</v>
+      </c>
+      <c r="H111" t="s">
         <v>216</v>
       </c>
-      <c r="L108" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="M108" s="9" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="9"/>
-      <c r="B109" s="9" t="s">
+      <c r="K111" t="s">
+        <v>210</v>
+      </c>
+      <c r="L111" t="s">
+        <v>199</v>
+      </c>
+      <c r="M111" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="112" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B112" t="s">
         <v>73</v>
       </c>
-      <c r="C109" s="9"/>
-      <c r="D109" s="9"/>
-      <c r="E109" s="9"/>
-      <c r="F109" s="9"/>
-      <c r="G109" s="9"/>
-      <c r="H109" s="9"/>
-      <c r="I109" s="9"/>
-      <c r="J109" s="9"/>
-      <c r="K109" s="9"/>
-      <c r="L109" s="9"/>
-      <c r="M109" s="9"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="9"/>
-      <c r="B110" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C110" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="D110" s="9"/>
-      <c r="E110" s="9"/>
-      <c r="F110" s="9"/>
-      <c r="G110" s="9"/>
-      <c r="H110" s="9"/>
-      <c r="I110" s="9"/>
-      <c r="J110" s="9"/>
-      <c r="K110" s="9"/>
-      <c r="L110" s="9"/>
-      <c r="M110" s="9"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="9"/>
-      <c r="B111" s="9"/>
-      <c r="C111" s="9"/>
-      <c r="D111" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E111" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="F111" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="G111" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="I111" s="9"/>
-      <c r="J111" s="9"/>
-      <c r="K111" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="L111" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="M111" s="9" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="9"/>
-      <c r="B112" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C112" s="9"/>
-      <c r="D112" s="9"/>
-      <c r="E112" s="9"/>
-      <c r="F112" s="9"/>
-      <c r="G112" s="9"/>
-      <c r="H112" s="9"/>
-      <c r="I112" s="9"/>
-      <c r="J112" s="9"/>
-      <c r="K112" s="9"/>
-      <c r="L112" s="9"/>
-      <c r="M112" s="9"/>
-    </row>
-    <row r="113">
+    </row>
+    <row r="113" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
         <v>55</v>
       </c>
       <c r="C114" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="115">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="115" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D115" t="s">
+        <v>217</v>
+      </c>
+      <c r="F115" t="s">
+        <v>218</v>
+      </c>
+      <c r="G115" t="s">
         <v>219</v>
       </c>
-      <c r="F115" s="4" t="s">
+      <c r="H115" t="s">
         <v>220</v>
       </c>
-      <c r="G115" t="s">
-        <v>221</v>
-      </c>
-      <c r="H115" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="116">
+    </row>
+    <row r="116" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D118" t="s">
         <v>63</v>
       </c>
       <c r="F118" t="s">
+        <v>221</v>
+      </c>
+      <c r="G118" t="s">
+        <v>222</v>
+      </c>
+      <c r="H118" t="s">
         <v>223</v>
       </c>
-      <c r="G118" t="s">
+      <c r="K118" t="s">
         <v>224</v>
       </c>
-      <c r="H118" t="s">
+      <c r="L118" t="s">
         <v>225</v>
       </c>
-      <c r="K118" t="s">
+      <c r="M118" t="s">
         <v>226</v>
       </c>
-      <c r="L118" t="s">
+      <c r="N118" t="s">
         <v>227</v>
       </c>
-      <c r="M118" t="s">
+      <c r="O118" t="s">
         <v>228</v>
-      </c>
-      <c r="N118" t="s">
-        <v>229</v>
-      </c>
-      <c r="O118" t="s">
-        <v>230</v>
       </c>
       <c r="P118" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D119" t="s">
         <v>78</v>
       </c>
       <c r="F119" t="s">
+        <v>229</v>
+      </c>
+      <c r="G119" t="s">
+        <v>230</v>
+      </c>
+      <c r="H119" t="s">
         <v>231</v>
       </c>
-      <c r="G119" t="s">
+      <c r="K119" t="s">
         <v>232</v>
       </c>
-      <c r="H119" t="s">
+      <c r="L119" t="s">
         <v>233</v>
       </c>
-      <c r="K119" t="s">
+      <c r="M119" t="s">
         <v>234</v>
       </c>
-      <c r="L119" t="s">
-        <v>235</v>
-      </c>
-      <c r="M119" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="120">
+    </row>
+    <row r="120" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B120" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D122" t="s">
         <v>98</v>
       </c>
       <c r="E122" t="s">
+        <v>235</v>
+      </c>
+      <c r="F122" t="s">
+        <v>236</v>
+      </c>
+      <c r="G122" t="s">
         <v>237</v>
       </c>
-      <c r="F122" t="s">
+      <c r="H122" t="s">
         <v>238</v>
       </c>
-      <c r="G122" t="s">
-        <v>239</v>
-      </c>
-      <c r="H122" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="123">
+    </row>
+    <row r="123" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
         <v>55</v>
       </c>
       <c r="C123" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="124" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="D124" t="s">
+        <v>46</v>
+      </c>
+      <c r="F124" t="s">
+        <v>240</v>
+      </c>
+      <c r="G124" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="124">
-      <c r="D124" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E124" s="4"/>
-      <c r="F124" s="4" t="s">
+      <c r="H124" t="s">
         <v>242</v>
       </c>
-      <c r="G124" s="4" t="s">
+      <c r="K124" t="s">
         <v>243</v>
-      </c>
-      <c r="H124" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="I124" s="4"/>
-      <c r="K124" t="s">
-        <v>245</v>
       </c>
       <c r="L124" t="s">
         <v>143</v>
@@ -3862,1228 +3509,1177 @@
         <v>144</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D128" t="s">
         <v>98</v>
       </c>
       <c r="E128" t="s">
+        <v>244</v>
+      </c>
+      <c r="F128" t="s">
+        <v>245</v>
+      </c>
+      <c r="G128" t="s">
         <v>246</v>
       </c>
-      <c r="F128" t="s">
+      <c r="H128" t="s">
         <v>247</v>
       </c>
-      <c r="G128" t="s">
-        <v>248</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="129">
+    </row>
+    <row r="129" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D129" t="s">
         <v>98</v>
       </c>
       <c r="E129" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F129" t="s">
+        <v>248</v>
+      </c>
+      <c r="G129" t="s">
+        <v>249</v>
+      </c>
+      <c r="H129" t="s">
         <v>250</v>
       </c>
-      <c r="G129" t="s">
-        <v>251</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="130">
+    </row>
+    <row r="130" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D130" t="s">
         <v>98</v>
       </c>
       <c r="E130" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F130" t="s">
+        <v>251</v>
+      </c>
+      <c r="G130" t="s">
+        <v>252</v>
+      </c>
+      <c r="H130" t="s">
         <v>253</v>
       </c>
-      <c r="G130" t="s">
+    </row>
+    <row r="131" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B131" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C131" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="H130" s="4" t="s">
+      <c r="D131" s="7"/>
+      <c r="E131" s="7"/>
+      <c r="F131" s="7"/>
+      <c r="G131" s="7"/>
+      <c r="H131" s="7"/>
+      <c r="I131" s="7"/>
+    </row>
+    <row r="132" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B132" s="7"/>
+      <c r="C132" s="7"/>
+      <c r="D132" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E132" s="7"/>
+      <c r="F132" s="7" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="131">
-      <c r="B131" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C131" s="10" t="s">
+      <c r="G132" s="7"/>
+      <c r="H132" s="7"/>
+      <c r="I132" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="D131" s="10"/>
-      <c r="E131" s="10"/>
-      <c r="F131" s="10"/>
-      <c r="G131" s="10"/>
-      <c r="H131" s="10"/>
-      <c r="I131" s="10"/>
-    </row>
-    <row r="132">
-      <c r="B132" s="10"/>
-      <c r="C132" s="10"/>
-      <c r="D132" s="10" t="s">
+    </row>
+    <row r="133" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B133" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C133" s="7"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="7"/>
+      <c r="F133" s="7"/>
+      <c r="G133" s="7"/>
+      <c r="H133" s="7"/>
+      <c r="I133" s="7"/>
+    </row>
+    <row r="134" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B134" s="7"/>
+      <c r="C134" s="7"/>
+      <c r="D134" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E132" s="10"/>
-      <c r="F132" s="10" t="s">
+      <c r="E134" s="7"/>
+      <c r="F134" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G134" s="7"/>
+      <c r="H134" s="7"/>
+      <c r="I134" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="G132" s="10"/>
-      <c r="H132" s="10"/>
-      <c r="I132" s="10" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="B133" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C133" s="10"/>
-      <c r="D133" s="10"/>
-      <c r="E133" s="10"/>
-      <c r="F133" s="10"/>
-      <c r="G133" s="10"/>
-      <c r="H133" s="10"/>
-      <c r="I133" s="10"/>
-    </row>
-    <row r="134">
-      <c r="B134" s="10"/>
-      <c r="C134" s="10"/>
-      <c r="D134" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E134" s="10"/>
-      <c r="F134" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="G134" s="10"/>
-      <c r="H134" s="10"/>
-      <c r="I134" s="10" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="B135" s="10" t="s">
+    </row>
+    <row r="135" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B135" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C135" s="10"/>
-      <c r="D135" s="10"/>
-      <c r="E135" s="10"/>
-      <c r="F135" s="10"/>
-      <c r="G135" s="10"/>
-      <c r="H135" s="10"/>
-      <c r="I135" s="10"/>
-    </row>
-    <row r="136">
+      <c r="C135" s="7"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="7"/>
+      <c r="F135" s="7"/>
+      <c r="G135" s="7"/>
+      <c r="H135" s="7"/>
+      <c r="I135" s="7"/>
+    </row>
+    <row r="136" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B137" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D138" t="s">
         <v>98</v>
       </c>
       <c r="E138" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F138" t="s">
+        <v>258</v>
+      </c>
+      <c r="G138" t="s">
+        <v>259</v>
+      </c>
+      <c r="H138" t="s">
         <v>260</v>
       </c>
-      <c r="G138" t="s">
-        <v>261</v>
-      </c>
-      <c r="H138" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="139">
+    </row>
+    <row r="139" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D139" t="s">
         <v>98</v>
       </c>
       <c r="E139" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F139" t="s">
+        <v>261</v>
+      </c>
+      <c r="G139" t="s">
+        <v>262</v>
+      </c>
+      <c r="H139" t="s">
         <v>263</v>
       </c>
-      <c r="G139" t="s">
-        <v>264</v>
-      </c>
-      <c r="H139" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="140">
+    </row>
+    <row r="140" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D140" t="s">
         <v>98</v>
       </c>
       <c r="E140" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F140" t="s">
+        <v>264</v>
+      </c>
+      <c r="G140" t="s">
+        <v>265</v>
+      </c>
+      <c r="H140" t="s">
         <v>266</v>
       </c>
-      <c r="G140" t="s">
-        <v>267</v>
-      </c>
-      <c r="H140" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="141">
+    </row>
+    <row r="141" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B142" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D143" t="s">
         <v>98</v>
       </c>
       <c r="E143" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F143" t="s">
+        <v>267</v>
+      </c>
+      <c r="G143" t="s">
+        <v>268</v>
+      </c>
+      <c r="H143" t="s">
         <v>269</v>
       </c>
-      <c r="G143" t="s">
-        <v>270</v>
-      </c>
-      <c r="H143" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="144">
+    </row>
+    <row r="144" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D144" t="s">
         <v>63</v>
       </c>
       <c r="F144" t="s">
+        <v>270</v>
+      </c>
+      <c r="G144" t="s">
+        <v>271</v>
+      </c>
+      <c r="H144" t="s">
         <v>272</v>
       </c>
-      <c r="G144" t="s">
-        <v>273</v>
-      </c>
-      <c r="H144" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="145">
+    </row>
+    <row r="145" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="146" s="11" customFormat="1">
-      <c r="B146" s="11" t="s">
+    <row r="146" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B146" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="147" s="11" customFormat="1">
-      <c r="D147" s="11" t="s">
+    <row r="147" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D147" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="E147" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="F147" s="11" t="s">
+      <c r="E147" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="H147" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="G147" s="11" t="s">
+    </row>
+    <row r="148" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B148" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C148" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="H147" s="11" t="s">
+    </row>
+    <row r="149" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D149" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E149" s="8" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="148" s="11" customFormat="1">
-      <c r="B148" s="11" t="s">
+      <c r="F149" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H149" s="8" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="150" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B150" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C148" s="11" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="149" s="11" customFormat="1">
-      <c r="D149" s="11" t="s">
+      <c r="C150" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="151" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D151" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="H151" s="8" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="152" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B152" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="153" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="154" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B154" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="155" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B155" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="156" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D156" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E156" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="G156" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="H156" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="157" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="158" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D158" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E149" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="F149" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="G149" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="H149" s="11" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="150" s="11" customFormat="1">
-      <c r="B150" s="11" t="s">
+      <c r="E158" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="H158" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="159" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B159" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C150" s="11" t="s">
+      <c r="C159" s="5" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="160" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D160" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="G160" s="5" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="151" s="11" customFormat="1">
-      <c r="D151" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F151" s="11" t="s">
+      <c r="H160" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="G151" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="H151" s="11" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="152" s="11" customFormat="1">
-      <c r="B152" s="11" t="s">
+    </row>
+    <row r="161" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B161" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="153" s="11" customFormat="1">
-      <c r="B153" s="11" t="s">
+    <row r="162" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B162" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="154" s="11" customFormat="1">
-      <c r="B154" s="11" t="s">
+    <row r="163" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B163" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="155" s="11" customFormat="1">
-      <c r="B155" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="156" s="6" customFormat="1">
-      <c r="D156" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E156" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="F156" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="G156" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="157" s="6" customFormat="1">
-      <c r="B157" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C157" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="158" s="6" customFormat="1">
-      <c r="D158" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E158" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="F158" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="G158" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="159" s="6" customFormat="1">
-      <c r="B159" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C159" s="6" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="160" s="6" customFormat="1">
-      <c r="D160" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F160" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="G160" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="161" s="6" customFormat="1">
-      <c r="B161" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="162" s="6" customFormat="1">
-      <c r="B162" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="163" s="6" customFormat="1">
-      <c r="B163" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="164">
+    <row r="164" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B164" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D165" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F165" t="s">
+        <v>294</v>
+      </c>
+      <c r="G165" t="s">
+        <v>295</v>
+      </c>
+      <c r="H165" t="s">
         <v>296</v>
       </c>
-      <c r="G165" t="s">
-        <v>297</v>
-      </c>
-      <c r="H165" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="166">
+    </row>
+    <row r="166" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B166" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B167" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D168" t="s">
         <v>98</v>
       </c>
       <c r="E168" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F168" t="s">
+        <v>297</v>
+      </c>
+      <c r="G168" t="s">
+        <v>298</v>
+      </c>
+      <c r="H168" t="s">
         <v>299</v>
       </c>
-      <c r="G168" t="s">
+      <c r="K168" t="s">
         <v>300</v>
       </c>
-      <c r="H168" t="s">
-        <v>301</v>
-      </c>
-      <c r="K168" t="s">
-        <v>302</v>
-      </c>
       <c r="L168" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M168" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="169">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="169" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B169" t="s">
         <v>55</v>
       </c>
       <c r="C169" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="170">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="170" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D170" t="s">
         <v>63</v>
       </c>
       <c r="F170" t="s">
+        <v>302</v>
+      </c>
+      <c r="G170" t="s">
+        <v>303</v>
+      </c>
+      <c r="H170" t="s">
         <v>304</v>
       </c>
-      <c r="G170" t="s">
-        <v>305</v>
-      </c>
-      <c r="H170" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="171">
+    </row>
+    <row r="171" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B171" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D172" t="s">
         <v>98</v>
       </c>
       <c r="E172" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F172" t="s">
+        <v>305</v>
+      </c>
+      <c r="G172" t="s">
+        <v>306</v>
+      </c>
+      <c r="H172" t="s">
         <v>307</v>
       </c>
-      <c r="G172" t="s">
+      <c r="K172" t="s">
         <v>308</v>
       </c>
-      <c r="H172" t="s">
-        <v>309</v>
-      </c>
-      <c r="K172" t="s">
-        <v>310</v>
-      </c>
       <c r="L172" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M172" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="173">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="173" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B173" t="s">
         <v>55</v>
       </c>
       <c r="C173" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="174">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="174" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D174" t="s">
         <v>63</v>
       </c>
       <c r="F174" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G174" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H174" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="175">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="175" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B175" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D176" t="s">
         <v>98</v>
       </c>
       <c r="E176" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F176" t="s">
+        <v>311</v>
+      </c>
+      <c r="G176" t="s">
+        <v>312</v>
+      </c>
+      <c r="H176" t="s">
         <v>313</v>
       </c>
-      <c r="G176" t="s">
+      <c r="K176" t="s">
         <v>314</v>
       </c>
-      <c r="H176" t="s">
-        <v>315</v>
-      </c>
-      <c r="K176" t="s">
-        <v>316</v>
-      </c>
       <c r="L176" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M176" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="177">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="177" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B177" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B178" t="s">
         <v>55</v>
       </c>
       <c r="C178" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="179">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="179" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B179" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D180" t="s">
         <v>41</v>
       </c>
       <c r="F180" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="I180">
         <v>2</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D181" t="s">
         <v>156</v>
       </c>
-      <c r="G181" s="4" t="s">
-        <v>319</v>
+      <c r="G181" t="s">
+        <v>316</v>
       </c>
       <c r="H181" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="182">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="182" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B182" t="s">
         <v>55</v>
       </c>
       <c r="C182" t="s">
-        <v>303</v>
-      </c>
-      <c r="G182" s="4"/>
-    </row>
-    <row r="183">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="183" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D183" t="s">
         <v>156</v>
       </c>
-      <c r="G183" s="4" t="s">
-        <v>321</v>
+      <c r="G183" t="s">
+        <v>318</v>
       </c>
       <c r="H183" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="184">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="184" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B184" t="s">
         <v>73</v>
       </c>
-      <c r="G184" s="4"/>
-    </row>
-    <row r="185">
+    </row>
+    <row r="185" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B185" t="s">
         <v>55</v>
       </c>
       <c r="C185" t="s">
-        <v>311</v>
-      </c>
-      <c r="G185" s="4"/>
-    </row>
-    <row r="186">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="186" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D186" t="s">
         <v>156</v>
       </c>
-      <c r="G186" s="4" t="s">
-        <v>323</v>
+      <c r="G186" t="s">
+        <v>320</v>
       </c>
       <c r="H186" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="187">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="187" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B187" t="s">
         <v>73</v>
       </c>
-      <c r="G187" s="4"/>
-    </row>
-    <row r="188">
+    </row>
+    <row r="188" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B188" t="s">
         <v>55</v>
       </c>
       <c r="C188" t="s">
-        <v>325</v>
-      </c>
-      <c r="G188" s="4"/>
-    </row>
-    <row r="189">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="189" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D189" t="s">
         <v>156</v>
       </c>
       <c r="G189" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H189" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="190">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="190" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B190" t="s">
         <v>73</v>
       </c>
-      <c r="G190" s="4"/>
-    </row>
-    <row r="191">
+    </row>
+    <row r="191" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B191" t="s">
         <v>55</v>
       </c>
       <c r="C191" t="s">
-        <v>328</v>
-      </c>
-      <c r="G191" s="4"/>
-    </row>
-    <row r="192">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="192" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D192" t="s">
         <v>156</v>
       </c>
-      <c r="G192" s="4" t="s">
-        <v>329</v>
+      <c r="G192" t="s">
+        <v>326</v>
       </c>
       <c r="H192" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="193">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="193" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B193" t="s">
         <v>73</v>
       </c>
-      <c r="G193" s="4"/>
-    </row>
-    <row r="194">
+    </row>
+    <row r="194" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B194" t="s">
         <v>55</v>
       </c>
       <c r="C194" t="s">
-        <v>331</v>
-      </c>
-      <c r="G194" s="4"/>
-    </row>
-    <row r="195">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="195" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D195" t="s">
         <v>156</v>
       </c>
-      <c r="G195" s="4" t="s">
-        <v>332</v>
+      <c r="G195" t="s">
+        <v>329</v>
       </c>
       <c r="H195" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="196">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="196" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B196" t="s">
         <v>73</v>
       </c>
-      <c r="G196" s="4"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="9"/>
-      <c r="B197" s="9" t="s">
+    </row>
+    <row r="197" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B197" t="s">
         <v>55</v>
       </c>
-      <c r="C197" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="D197" s="9"/>
-      <c r="E197" s="9"/>
-      <c r="F197" s="9"/>
-      <c r="H197" s="9"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="9"/>
-      <c r="B198" s="9"/>
-      <c r="C198" s="9"/>
-      <c r="D198" s="9" t="s">
+      <c r="C197" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="198" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D198" t="s">
         <v>156</v>
       </c>
-      <c r="E198" s="9"/>
-      <c r="F198" s="9"/>
-      <c r="G198" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="H198" s="9" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="9"/>
-      <c r="B199" s="9" t="s">
+      <c r="G198" t="s">
+        <v>332</v>
+      </c>
+      <c r="H198" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="199" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B199" t="s">
         <v>73</v>
       </c>
-      <c r="C199" s="9"/>
-      <c r="D199" s="9"/>
-      <c r="E199" s="9"/>
-      <c r="F199" s="9"/>
-      <c r="H199" s="9"/>
-    </row>
-    <row r="200">
+    </row>
+    <row r="200" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B200" t="s">
         <v>55</v>
       </c>
       <c r="C200" t="s">
-        <v>337</v>
-      </c>
-      <c r="G200" s="4"/>
-    </row>
-    <row r="201">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="201" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D201" t="s">
         <v>156</v>
       </c>
-      <c r="G201" s="4" t="s">
-        <v>338</v>
+      <c r="G201" t="s">
+        <v>335</v>
       </c>
       <c r="H201" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="202">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="202" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B202" t="s">
         <v>73</v>
       </c>
-      <c r="G202" s="4"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="9"/>
-      <c r="B203" s="9" t="s">
+    </row>
+    <row r="203" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B203" t="s">
         <v>55</v>
       </c>
-      <c r="C203" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="D203" s="9"/>
-      <c r="E203" s="9"/>
-      <c r="F203" s="9"/>
-      <c r="H203" s="9"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="9"/>
-      <c r="B204" s="9"/>
-      <c r="C204" s="9"/>
-      <c r="D204" s="9" t="s">
+      <c r="C203" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="204" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D204" t="s">
         <v>156</v>
       </c>
-      <c r="E204" s="9"/>
-      <c r="F204" s="9"/>
       <c r="G204" t="s">
-        <v>341</v>
-      </c>
-      <c r="H204" s="4" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="9"/>
-      <c r="B205" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="H204" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="205" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B205" t="s">
         <v>73</v>
       </c>
-      <c r="C205" s="9"/>
-      <c r="D205" s="9"/>
-      <c r="E205" s="9"/>
-      <c r="F205" s="9"/>
-      <c r="G205" s="9"/>
-      <c r="H205" s="9"/>
-    </row>
-    <row r="206">
+    </row>
+    <row r="206" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B206" t="s">
         <v>55</v>
       </c>
       <c r="C206" t="s">
-        <v>343</v>
-      </c>
-      <c r="G206" s="4"/>
-    </row>
-    <row r="207">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="207" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D207" t="s">
         <v>156</v>
       </c>
-      <c r="G207" s="4" t="s">
-        <v>344</v>
+      <c r="G207" t="s">
+        <v>338</v>
       </c>
       <c r="H207" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="208">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="208" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B208" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B209" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B210" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B211" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D212" t="s">
         <v>78</v>
       </c>
-      <c r="F212" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="G212" s="4" t="s">
-        <v>347</v>
+      <c r="F212" t="s">
+        <v>340</v>
+      </c>
+      <c r="G212" t="s">
+        <v>341</v>
       </c>
       <c r="H212" t="s">
-        <v>348</v>
-      </c>
-      <c r="K212" s="4" t="s">
-        <v>349</v>
+        <v>342</v>
+      </c>
+      <c r="K212" t="s">
+        <v>343</v>
       </c>
       <c r="L212" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="M212" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="213">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="213" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D213" t="s">
         <v>78</v>
       </c>
-      <c r="F213" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="G213" s="4" t="s">
-        <v>353</v>
+      <c r="F213" t="s">
+        <v>346</v>
+      </c>
+      <c r="G213" t="s">
+        <v>347</v>
       </c>
       <c r="H213" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="K213" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="L213" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="M213" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="214">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="214" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D214" t="s">
         <v>41</v>
       </c>
       <c r="F214" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="I214" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="215">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="215" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D215" t="s">
         <v>156</v>
       </c>
       <c r="G215" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="H215" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="216">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="216" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D216" t="s">
         <v>41</v>
       </c>
       <c r="F216" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="I216">
         <v>1</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B217" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B218" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D219" t="s">
         <v>41</v>
       </c>
       <c r="F219" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="I219" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="220">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="220" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D220" t="s">
         <v>46</v>
       </c>
       <c r="F220" t="s">
+        <v>356</v>
+      </c>
+      <c r="G220" t="s">
+        <v>358</v>
+      </c>
+      <c r="H220" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q220" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D221" t="s">
+        <v>360</v>
+      </c>
+      <c r="F221" t="s">
+        <v>361</v>
+      </c>
+      <c r="G221" t="s">
         <v>362</v>
       </c>
-      <c r="G220" t="s">
+      <c r="H221" t="s">
+        <v>363</v>
+      </c>
+      <c r="K221" t="s">
         <v>364</v>
       </c>
-      <c r="H220" t="s">
-        <v>365</v>
-      </c>
-      <c r="Q220" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="D221" t="s">
-        <v>366</v>
-      </c>
-      <c r="F221" t="s">
-        <v>367</v>
-      </c>
-      <c r="G221" t="s">
-        <v>368</v>
-      </c>
-      <c r="H221" t="s">
-        <v>369</v>
-      </c>
-      <c r="K221" t="s">
-        <v>370</v>
-      </c>
       <c r="L221" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M221" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="222">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="222" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D222" t="s">
         <v>41</v>
       </c>
       <c r="F222" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="I222" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="223">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="223" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D223" t="s">
         <v>78</v>
       </c>
       <c r="F223" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="G223" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="H223" t="s">
-        <v>375</v>
-      </c>
-      <c r="K223" s="4" t="s">
-        <v>376</v>
+        <v>369</v>
+      </c>
+      <c r="K223" t="s">
+        <v>370</v>
       </c>
       <c r="L223" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="M223" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="224">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="224" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D224" t="s">
         <v>41</v>
       </c>
       <c r="F224" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="I224" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="225">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="225" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D225" t="s">
         <v>156</v>
       </c>
       <c r="G225" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="H225" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="226">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="226" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B226" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B227" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B228" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="229">
-      <c r="D229" s="4" t="s">
+    <row r="229" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D229" t="s">
         <v>106</v>
       </c>
       <c r="E229" t="s">
-        <v>383</v>
-      </c>
-      <c r="F229" s="4" t="s">
-        <v>384</v>
+        <v>377</v>
+      </c>
+      <c r="F229" t="s">
+        <v>378</v>
       </c>
       <c r="G229" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="H229" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="230">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="230" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B230" t="s">
         <v>55</v>
       </c>
       <c r="C230" t="s">
-        <v>387</v>
-      </c>
-      <c r="D230" s="4"/>
-      <c r="F230" s="4"/>
-    </row>
-    <row r="231">
-      <c r="D231" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="231" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D231" t="s">
         <v>106</v>
       </c>
       <c r="E231" t="s">
-        <v>388</v>
-      </c>
-      <c r="F231" s="4" t="s">
-        <v>389</v>
+        <v>382</v>
+      </c>
+      <c r="F231" t="s">
+        <v>383</v>
       </c>
       <c r="G231" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="H231" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="232">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="232" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B232" t="s">
         <v>73</v>
       </c>
-      <c r="D232" s="4"/>
-      <c r="F232" s="4"/>
-    </row>
-    <row r="233">
+    </row>
+    <row r="233" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B233" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B234" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B235" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D236" t="s">
         <v>156</v>
       </c>
       <c r="G236" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="H236" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="237">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="237" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D237" t="s">
         <v>41</v>
       </c>
       <c r="F237" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="I237">
         <v>2</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B238" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B239" t="s">
         <v>73</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967293" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E160"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="16.54296875"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="13.81640625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="31.453125"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="43"/>
+    <col min="1" max="1" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="12" customFormat="1">
+    <row r="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -5091,11 +4687,11 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="2">
+      <c r="E1" s="9" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>99</v>
       </c>
@@ -5104,13 +4700,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>99</v>
       </c>
@@ -5119,73 +4715,73 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="D3" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B4" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="D4" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B5" s="4" t="str">
+        <v>157</v>
+      </c>
+      <c r="B5" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="C5" t="s">
+        <v>397</v>
+      </c>
+      <c r="D5" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B6" s="4" t="str">
+        <v>235</v>
+      </c>
+      <c r="B6" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="C6" t="s">
+        <v>399</v>
+      </c>
+      <c r="D6" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B7" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="C7" t="s">
+        <v>401</v>
+      </c>
+      <c r="D7" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>145</v>
       </c>
@@ -5193,58 +4789,58 @@
         <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>409</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>403</v>
+      </c>
+      <c r="D8" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B9" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="D9" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>246</v>
-      </c>
-      <c r="B10" s="4" t="str">
+        <v>244</v>
+      </c>
+      <c r="B10" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="C10" t="s">
+        <v>397</v>
+      </c>
+      <c r="D10" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>246</v>
-      </c>
-      <c r="B11" s="4" t="str">
+        <v>244</v>
+      </c>
+      <c r="B11" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>411</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>405</v>
+      </c>
+      <c r="D11" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>83</v>
       </c>
@@ -5253,1122 +4849,1102 @@
         <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>411</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="B13" s="4" t="str">
+        <v>405</v>
+      </c>
+      <c r="D12" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>377</v>
+      </c>
+      <c r="B13" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="B14" s="4" t="str">
+      <c r="C13" t="s">
+        <v>406</v>
+      </c>
+      <c r="D13" t="s">
+        <v>406</v>
+      </c>
+      <c r="E13" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>377</v>
+      </c>
+      <c r="B14" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="B15" s="4" t="str">
+      <c r="C14" t="s">
+        <v>408</v>
+      </c>
+      <c r="D14" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>377</v>
+      </c>
+      <c r="B15" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="s">
-        <v>388</v>
+      <c r="C15" t="s">
+        <v>409</v>
+      </c>
+      <c r="D15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>377</v>
       </c>
       <c r="B16" t="str">
+        <f>"5"</f>
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>491</v>
+      </c>
+      <c r="D16" t="s">
+        <v>491</v>
+      </c>
+      <c r="E16" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>382</v>
+      </c>
+      <c r="B17" t="str">
+        <f>"2"</f>
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>406</v>
+      </c>
+      <c r="D17" t="s">
+        <v>406</v>
+      </c>
+      <c r="E17" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>382</v>
+      </c>
+      <c r="B18" t="str">
+        <f>"3"</f>
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>408</v>
+      </c>
+      <c r="D18" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B19" t="str">
+        <f>"4"</f>
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
+        <v>409</v>
+      </c>
+      <c r="D19" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>382</v>
+      </c>
+      <c r="B20" t="str">
+        <f>"5"</f>
+        <v>5</v>
+      </c>
+      <c r="C20" t="s">
+        <v>489</v>
+      </c>
+      <c r="D20" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>377</v>
+      </c>
+      <c r="B21" t="str">
+        <f>"6"</f>
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>491</v>
+      </c>
+      <c r="D21" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>277</v>
+      </c>
+      <c r="B22" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="B17" s="4" t="str">
+      <c r="C22" t="s">
+        <v>411</v>
+      </c>
+      <c r="D22" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>277</v>
+      </c>
+      <c r="B23" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C23" t="s">
         <v>412</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D23" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="B18" s="4" t="str">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>277</v>
+      </c>
+      <c r="B24" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="B19" s="4" t="str">
+      <c r="C24" t="s">
+        <v>413</v>
+      </c>
+      <c r="D24" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>277</v>
+      </c>
+      <c r="B25" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="B20" t="str">
-        <f>"1"</f>
-        <v>1</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>279</v>
-      </c>
-      <c r="B21" t="str">
-        <f>"2"</f>
-        <v>2</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>279</v>
-      </c>
-      <c r="B22" t="str">
-        <f>"3"</f>
-        <v>3</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>279</v>
-      </c>
-      <c r="B23" t="str">
-        <f>"4"</f>
-        <v>4</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="B24" t="str">
+      <c r="C25" t="s">
+        <v>414</v>
+      </c>
+      <c r="D25" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B26" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>279</v>
-      </c>
-      <c r="B25" t="str">
+      <c r="C26" t="s">
+        <v>415</v>
+      </c>
+      <c r="D26" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>277</v>
+      </c>
+      <c r="B27" t="str">
         <f>"6"</f>
         <v>6</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>279</v>
-      </c>
-      <c r="B26" t="str">
+      <c r="C27" t="s">
+        <v>416</v>
+      </c>
+      <c r="D27" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>277</v>
+      </c>
+      <c r="B28" t="str">
         <f>"7"</f>
         <v>7</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="E26" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>279</v>
-      </c>
-      <c r="B27" t="str">
+      <c r="C28" t="s">
+        <v>417</v>
+      </c>
+      <c r="D28" t="s">
+        <v>417</v>
+      </c>
+      <c r="E28" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>277</v>
+      </c>
+      <c r="B29" t="str">
         <f>"8"</f>
         <v>8</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="E27" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>279</v>
-      </c>
-      <c r="B28" t="str">
+      <c r="C29" t="s">
+        <v>419</v>
+      </c>
+      <c r="D29" t="s">
+        <v>419</v>
+      </c>
+      <c r="E29" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>277</v>
+      </c>
+      <c r="B30" t="str">
         <f>"9"</f>
         <v>9</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="E28" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>279</v>
-      </c>
-      <c r="B29" t="str">
+      <c r="C30" t="s">
+        <v>421</v>
+      </c>
+      <c r="D30" t="s">
+        <v>421</v>
+      </c>
+      <c r="E30" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>277</v>
+      </c>
+      <c r="B31" t="str">
         <f>"10"</f>
         <v>10</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="E29" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>279</v>
-      </c>
-      <c r="B30" t="str">
+      <c r="C31" t="s">
+        <v>423</v>
+      </c>
+      <c r="D31" t="s">
+        <v>423</v>
+      </c>
+      <c r="E31" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>277</v>
+      </c>
+      <c r="B32" t="str">
         <f>"11"</f>
         <v>11</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="E30" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>279</v>
-      </c>
-      <c r="B31" t="str">
+      <c r="C32" t="s">
+        <v>425</v>
+      </c>
+      <c r="D32" t="s">
+        <v>425</v>
+      </c>
+      <c r="E32" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>277</v>
+      </c>
+      <c r="B33" t="str">
         <f>"12"</f>
         <v>12</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="E31" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>279</v>
-      </c>
-      <c r="B32" t="str">
+      <c r="C33" t="s">
+        <v>427</v>
+      </c>
+      <c r="D33" t="s">
+        <v>427</v>
+      </c>
+      <c r="E33" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>277</v>
+      </c>
+      <c r="B34" t="str">
         <f>"13"</f>
         <v>13</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="E32" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>279</v>
-      </c>
-      <c r="B33" t="str">
+      <c r="C34" t="s">
+        <v>429</v>
+      </c>
+      <c r="D34" t="s">
+        <v>429</v>
+      </c>
+      <c r="E34" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>277</v>
+      </c>
+      <c r="B35" t="str">
         <f>"14"</f>
         <v>14</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="E33" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>279</v>
-      </c>
-      <c r="B34" t="str">
+      <c r="C35" t="s">
+        <v>431</v>
+      </c>
+      <c r="D35" t="s">
+        <v>431</v>
+      </c>
+      <c r="E35" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>277</v>
+      </c>
+      <c r="B36" t="str">
         <f>"15"</f>
         <v>15</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="E34" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>279</v>
-      </c>
-      <c r="B35" t="str">
+      <c r="C36" t="s">
+        <v>433</v>
+      </c>
+      <c r="D36" t="s">
+        <v>433</v>
+      </c>
+      <c r="E36" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>277</v>
+      </c>
+      <c r="B37" t="str">
         <f>"16"</f>
         <v>16</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="E35" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>279</v>
-      </c>
-      <c r="B36" t="str">
+      <c r="C37" t="s">
+        <v>435</v>
+      </c>
+      <c r="D37" t="s">
+        <v>435</v>
+      </c>
+      <c r="E37" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>277</v>
+      </c>
+      <c r="B38" t="str">
         <f>"17"</f>
         <v>17</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="E36" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>279</v>
-      </c>
-      <c r="B37" t="str">
+      <c r="C38" t="s">
+        <v>437</v>
+      </c>
+      <c r="D38" t="s">
+        <v>437</v>
+      </c>
+      <c r="E38" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>277</v>
+      </c>
+      <c r="B39" t="str">
         <f>"18"</f>
         <v>18</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="E37" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>279</v>
-      </c>
-      <c r="B38" t="str">
+      <c r="C39" t="s">
+        <v>439</v>
+      </c>
+      <c r="D39" t="s">
+        <v>439</v>
+      </c>
+      <c r="E39" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>277</v>
+      </c>
+      <c r="B40" t="str">
         <f>"77"</f>
         <v>77</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>182</v>
-      </c>
-      <c r="B39" t="str">
-        <f>"1"</f>
-        <v>1</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>182</v>
-      </c>
-      <c r="B40" s="4" t="str">
-        <f>"2"</f>
-        <v>2</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="41">
+      <c r="C40" t="s">
+        <v>441</v>
+      </c>
+      <c r="D40" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B41" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="42">
+      <c r="C41" t="s">
+        <v>443</v>
+      </c>
+      <c r="D41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>188</v>
-      </c>
-      <c r="B42" s="4" t="str">
+        <v>180</v>
+      </c>
+      <c r="B42" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="43">
+      <c r="C42" t="s">
+        <v>445</v>
+      </c>
+      <c r="D42" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>188</v>
-      </c>
-      <c r="B43" s="4" t="str">
+        <v>186</v>
+      </c>
+      <c r="B43" t="str">
+        <f>"1"</f>
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>443</v>
+      </c>
+      <c r="D43" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>186</v>
+      </c>
+      <c r="B44" t="str">
+        <f>"2"</f>
+        <v>2</v>
+      </c>
+      <c r="C44" t="s">
+        <v>445</v>
+      </c>
+      <c r="D44" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>186</v>
+      </c>
+      <c r="B45" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
+      <c r="C45" t="s">
+        <v>447</v>
+      </c>
+      <c r="D45" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>127</v>
       </c>
-      <c r="B44" t="str">
-        <f t="shared" ref="B44:B45" si="0">"99"</f>
+      <c r="B46" t="str">
+        <f t="shared" ref="B46:B47" si="0">"99"</f>
         <v>99</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="D44" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="s">
+      <c r="C46" t="s">
+        <v>449</v>
+      </c>
+      <c r="D46" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>136</v>
       </c>
-      <c r="B45" t="str">
+      <c r="B47" t="str">
         <f t="shared" si="0"/>
         <v>99</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>164</v>
-      </c>
-      <c r="B46" t="str">
-        <f>"1"</f>
-        <v>1</v>
-      </c>
-      <c r="C46" t="s">
-        <v>460</v>
-      </c>
-      <c r="D46" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>164</v>
-      </c>
-      <c r="B47" t="str">
-        <f>"2"</f>
-        <v>2</v>
-      </c>
       <c r="C47" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="D47" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="B48" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D48" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>107</v>
-      </c>
-      <c r="B49" s="4" t="str">
+        <v>162</v>
+      </c>
+      <c r="B49" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D49" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>107</v>
       </c>
-      <c r="B50" s="4" t="str">
+      <c r="B50" t="str">
+        <f>"1"</f>
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>443</v>
+      </c>
+      <c r="D50" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>107</v>
+      </c>
+      <c r="B51" t="str">
+        <f>"2"</f>
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>445</v>
+      </c>
+      <c r="D51" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>107</v>
+      </c>
+      <c r="B52" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
-      <c r="C50" t="s">
-        <v>464</v>
-      </c>
-      <c r="D50" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
+      <c r="C52" t="s">
+        <v>457</v>
+      </c>
+      <c r="D52" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>107</v>
       </c>
-      <c r="B51" t="str">
+      <c r="B53" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
-      <c r="C51" t="s">
-        <v>466</v>
-      </c>
-      <c r="D51" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>169</v>
-      </c>
-      <c r="B52" t="str">
+      <c r="C53" t="s">
+        <v>459</v>
+      </c>
+      <c r="D53" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>167</v>
+      </c>
+      <c r="B54" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="C52" t="s">
-        <v>401</v>
-      </c>
-      <c r="D52" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="4"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="4"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="4"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="4"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="4"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="4"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="4"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="4"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="4"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="4"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="4"/>
-      <c r="D74" s="4"/>
-    </row>
-    <row r="76">
-      <c r="B76" s="13"/>
-    </row>
-    <row r="77">
-      <c r="B77" s="13"/>
-    </row>
-    <row r="78">
-      <c r="B78" s="13"/>
-    </row>
-    <row r="79">
-      <c r="B79" s="13"/>
-    </row>
-    <row r="80">
-      <c r="B80" s="13"/>
-    </row>
-    <row r="81">
-      <c r="B81" s="13"/>
-    </row>
-    <row r="82">
-      <c r="B82" s="13"/>
-    </row>
-    <row r="83">
-      <c r="B83" s="13"/>
-    </row>
-    <row r="84">
-      <c r="B84" s="13"/>
-    </row>
-    <row r="85">
-      <c r="B85" s="13"/>
-    </row>
-    <row r="86">
-      <c r="B86" s="13"/>
-    </row>
-    <row r="87">
-      <c r="B87" s="13"/>
-    </row>
-    <row r="88">
-      <c r="B88" s="13"/>
-    </row>
-    <row r="89">
-      <c r="B89" s="13"/>
-    </row>
-    <row r="90">
-      <c r="B90" s="13"/>
-    </row>
-    <row r="91">
-      <c r="B91" s="13"/>
-    </row>
-    <row r="92">
-      <c r="B92" s="13"/>
-    </row>
-    <row r="93">
-      <c r="B93" s="13"/>
-    </row>
-    <row r="94">
-      <c r="B94" s="13"/>
-    </row>
-    <row r="95">
-      <c r="B95" s="13"/>
-    </row>
-    <row r="96">
-      <c r="B96" s="13"/>
-    </row>
-    <row r="97">
-      <c r="B97" s="13"/>
-    </row>
-    <row r="98">
-      <c r="B98" s="13"/>
-    </row>
-    <row r="99">
-      <c r="B99" s="13"/>
-    </row>
-    <row r="100">
-      <c r="B100" s="13"/>
-    </row>
-    <row r="101">
-      <c r="B101" s="13"/>
-    </row>
-    <row r="102">
-      <c r="B102" s="13"/>
-    </row>
-    <row r="103">
-      <c r="B103" s="13"/>
-    </row>
-    <row r="104">
-      <c r="B104" s="13"/>
-    </row>
-    <row r="105">
-      <c r="B105" s="13"/>
-    </row>
-    <row r="106">
-      <c r="B106" s="13"/>
-    </row>
-    <row r="107">
-      <c r="B107" s="13"/>
-      <c r="C107" s="13"/>
-    </row>
-    <row r="108">
-      <c r="B108" s="13"/>
-      <c r="C108" s="13"/>
-    </row>
-    <row r="109">
-      <c r="B109" s="13"/>
-      <c r="C109" s="13"/>
-    </row>
-    <row r="110">
-      <c r="B110" s="13"/>
-      <c r="C110" s="13"/>
-    </row>
-    <row r="111">
-      <c r="B111" s="13"/>
-      <c r="C111" s="13"/>
-    </row>
-    <row r="112">
-      <c r="B112" s="13"/>
-      <c r="C112" s="13"/>
-    </row>
-    <row r="113">
-      <c r="B113" s="13"/>
-      <c r="C113" s="13"/>
-    </row>
-    <row r="114">
-      <c r="C114" s="13"/>
-    </row>
-    <row r="115">
-      <c r="B115" s="13"/>
-      <c r="C115" s="13"/>
-    </row>
-    <row r="116">
-      <c r="B116" s="13"/>
-      <c r="C116" s="13"/>
-    </row>
-    <row r="117">
-      <c r="B117" s="13"/>
-      <c r="C117" s="13"/>
-    </row>
-    <row r="118">
-      <c r="B118" s="13"/>
-      <c r="C118" s="13"/>
-    </row>
-    <row r="119">
-      <c r="B119" s="13"/>
-      <c r="C119" s="13"/>
-    </row>
-    <row r="120">
-      <c r="B120" s="13"/>
-      <c r="C120" s="13"/>
-    </row>
-    <row r="121">
-      <c r="B121" s="13"/>
-      <c r="C121" s="13"/>
-    </row>
-    <row r="122">
-      <c r="B122" s="13"/>
-      <c r="C122" s="13"/>
-    </row>
-    <row r="123">
-      <c r="B123" s="13"/>
-      <c r="C123" s="13"/>
-    </row>
-    <row r="124">
-      <c r="B124" s="13"/>
-      <c r="C124" s="13"/>
-    </row>
-    <row r="125">
-      <c r="B125" s="13"/>
-      <c r="C125" s="13"/>
-    </row>
-    <row r="126">
-      <c r="B126" s="13"/>
-      <c r="C126" s="13"/>
-    </row>
-    <row r="127">
-      <c r="B127" s="13"/>
-      <c r="C127" s="13"/>
-    </row>
-    <row r="128">
-      <c r="B128" s="13"/>
-      <c r="C128" s="13"/>
-    </row>
-    <row r="129">
-      <c r="B129" s="13"/>
-      <c r="C129" s="13"/>
-    </row>
-    <row r="130">
-      <c r="B130" s="13"/>
-      <c r="C130" s="13"/>
-    </row>
-    <row r="131">
-      <c r="B131" s="13"/>
-      <c r="C131" s="13"/>
-    </row>
-    <row r="132">
-      <c r="B132" s="13"/>
-      <c r="C132" s="13"/>
-    </row>
-    <row r="133">
-      <c r="B133" s="13"/>
-    </row>
-    <row r="134">
-      <c r="B134" s="13"/>
-    </row>
-    <row r="135">
-      <c r="B135" s="13"/>
-    </row>
-    <row r="136">
-      <c r="B136" s="13"/>
-    </row>
-    <row r="137">
-      <c r="B137" s="13"/>
-    </row>
-    <row r="138">
-      <c r="B138" s="13"/>
-    </row>
-    <row r="139">
-      <c r="B139" s="13"/>
-    </row>
-    <row r="141">
-      <c r="B141" s="13"/>
-    </row>
-    <row r="142">
-      <c r="B142" s="13"/>
-    </row>
-    <row r="143">
-      <c r="B143" s="13"/>
-    </row>
-    <row r="144">
-      <c r="B144" s="13"/>
-    </row>
-    <row r="145">
-      <c r="B145" s="13"/>
-    </row>
-    <row r="146">
-      <c r="B146" s="13"/>
-    </row>
-    <row r="147">
-      <c r="B147" s="13"/>
-    </row>
-    <row r="148">
-      <c r="B148" s="13"/>
-    </row>
-    <row r="149">
-      <c r="B149" s="13"/>
-    </row>
-    <row r="150">
-      <c r="B150" s="13"/>
-    </row>
-    <row r="151">
-      <c r="B151" s="13"/>
-    </row>
-    <row r="152">
-      <c r="B152" s="13"/>
-    </row>
-    <row r="153">
-      <c r="B153" s="13"/>
-    </row>
-    <row r="154">
-      <c r="B154" s="13"/>
-    </row>
-    <row r="155">
-      <c r="B155" s="13"/>
-    </row>
-    <row r="156">
-      <c r="B156" s="13"/>
-    </row>
-    <row r="157">
-      <c r="B157" s="13"/>
-    </row>
-    <row r="158">
-      <c r="B158" s="13"/>
+      <c r="C54" t="s">
+        <v>395</v>
+      </c>
+      <c r="D54" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B78" s="10"/>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B79" s="10"/>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B80" s="10"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B81" s="10"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B82" s="10"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B83" s="10"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B84" s="10"/>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B85" s="10"/>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B86" s="10"/>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B87" s="10"/>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B88" s="10"/>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B89" s="10"/>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B90" s="10"/>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B91" s="10"/>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B92" s="10"/>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B93" s="10"/>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B94" s="10"/>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B95" s="10"/>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B96" s="10"/>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B97" s="10"/>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B98" s="10"/>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B99" s="10"/>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B100" s="10"/>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B101" s="10"/>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B102" s="10"/>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B103" s="10"/>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B104" s="10"/>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B105" s="10"/>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B106" s="10"/>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B107" s="10"/>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B108" s="10"/>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B109" s="10"/>
+      <c r="C109" s="10"/>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B110" s="10"/>
+      <c r="C110" s="10"/>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B111" s="10"/>
+      <c r="C111" s="10"/>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B112" s="10"/>
+      <c r="C112" s="10"/>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B113" s="10"/>
+      <c r="C113" s="10"/>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B114" s="10"/>
+      <c r="C114" s="10"/>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B115" s="10"/>
+      <c r="C115" s="10"/>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C116" s="10"/>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B117" s="10"/>
+      <c r="C117" s="10"/>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B118" s="10"/>
+      <c r="C118" s="10"/>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B119" s="10"/>
+      <c r="C119" s="10"/>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B120" s="10"/>
+      <c r="C120" s="10"/>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B121" s="10"/>
+      <c r="C121" s="10"/>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B122" s="10"/>
+      <c r="C122" s="10"/>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B123" s="10"/>
+      <c r="C123" s="10"/>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B124" s="10"/>
+      <c r="C124" s="10"/>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B125" s="10"/>
+      <c r="C125" s="10"/>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B126" s="10"/>
+      <c r="C126" s="10"/>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B127" s="10"/>
+      <c r="C127" s="10"/>
+    </row>
+    <row r="128" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B128" s="10"/>
+      <c r="C128" s="10"/>
+    </row>
+    <row r="129" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B129" s="10"/>
+      <c r="C129" s="10"/>
+    </row>
+    <row r="130" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B130" s="10"/>
+      <c r="C130" s="10"/>
+    </row>
+    <row r="131" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B131" s="10"/>
+      <c r="C131" s="10"/>
+    </row>
+    <row r="132" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B132" s="10"/>
+      <c r="C132" s="10"/>
+    </row>
+    <row r="133" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B133" s="10"/>
+      <c r="C133" s="10"/>
+    </row>
+    <row r="134" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B134" s="10"/>
+      <c r="C134" s="10"/>
+    </row>
+    <row r="135" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B135" s="10"/>
+    </row>
+    <row r="136" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B136" s="10"/>
+    </row>
+    <row r="137" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B137" s="10"/>
+    </row>
+    <row r="138" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B138" s="10"/>
+    </row>
+    <row r="139" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B139" s="10"/>
+    </row>
+    <row r="140" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B140" s="10"/>
+    </row>
+    <row r="141" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B141" s="10"/>
+    </row>
+    <row r="143" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B143" s="10"/>
+    </row>
+    <row r="144" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B144" s="10"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B145" s="10"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B146" s="10"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B147" s="10"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B148" s="10"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B149" s="10"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B150" s="10"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B151" s="10"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B152" s="10"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B153" s="10"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B154" s="10"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B155" s="10"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B156" s="10"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B157" s="10"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B158" s="10"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B159" s="10"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B160" s="10"/>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="16.7265625"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="40.54296875"/>
+    <col min="1" max="1" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="14" t="s">
-        <v>468</v>
-      </c>
-      <c r="B1" s="14" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>461</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>29</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="15.453125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="12.1796875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="20.7265625"/>
-    <col customWidth="1" min="4" max="4" width="40.1796875"/>
+    <col min="1" max="1" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="12" customFormat="1">
+    <row r="1" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="2" ht="130.5">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C2" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="3" ht="87">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C3" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="18.81640625"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="6"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="12.81640625"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="34.1796875"/>
+    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="15" customFormat="1">
-      <c r="A1" s="15" t="s">
-        <v>477</v>
-      </c>
-      <c r="B1" s="15" t="s">
+    <row r="1" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>478</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="2">
+      <c r="C1" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="C2" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="D2" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:D124"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="13.7265625"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="23.1796875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="16.7265625"/>
+    <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
@@ -6376,15 +5952,15 @@
         <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B2" t="s">
         <v>106</v>
@@ -6393,10 +5969,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -6407,9 +5983,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B4" t="s">
         <v>78</v>
@@ -6418,7 +5994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -6429,7 +6005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>84</v>
       </c>
@@ -6440,7 +6016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>68</v>
       </c>
@@ -6451,20 +6027,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>220</v>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>218</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B9" t="s">
         <v>98</v>
@@ -6473,31 +6049,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="13" t="s">
         <v>63</v>
       </c>
       <c r="C10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="13" t="s">
         <v>82</v>
       </c>
       <c r="C11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s">
         <v>98</v>
@@ -6505,11 +6081,10 @@
       <c r="C12" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="s">
-        <v>165</v>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>163</v>
       </c>
       <c r="B13" t="s">
         <v>98</v>
@@ -6518,9 +6093,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B14" t="s">
         <v>98</v>
@@ -6529,7 +6104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -6540,9 +6115,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B16" t="s">
         <v>46</v>
@@ -6551,9 +6126,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B17" t="s">
         <v>98</v>
@@ -6562,9 +6137,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B18" t="s">
         <v>98</v>
@@ -6573,7 +6148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>139</v>
       </c>
@@ -6584,7 +6159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>146</v>
       </c>
@@ -6595,9 +6170,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B21" t="s">
         <v>106</v>
@@ -6606,9 +6181,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s">
         <v>98</v>
@@ -6617,20 +6192,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B23" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C23" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
@@ -6639,7 +6214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>121</v>
       </c>
@@ -6650,7 +6225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>150</v>
       </c>
@@ -6661,7 +6236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>153</v>
       </c>
@@ -6672,20 +6247,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>128</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="13" t="s">
         <v>82</v>
       </c>
       <c r="C28" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B29" t="s">
         <v>41</v>
@@ -6694,9 +6269,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
@@ -6705,9 +6280,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B31" t="s">
         <v>98</v>
@@ -6716,9 +6291,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B32" t="s">
         <v>98</v>
@@ -6727,9 +6302,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s">
         <v>63</v>
@@ -6738,7 +6313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>95</v>
       </c>
@@ -6749,7 +6324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>103</v>
       </c>
@@ -6760,7 +6335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>112</v>
       </c>
@@ -6771,9 +6346,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B37" t="s">
         <v>78</v>
@@ -6782,9 +6357,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B38" t="s">
         <v>41</v>
@@ -6793,9 +6368,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B39" t="s">
         <v>63</v>
@@ -6804,9 +6379,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B40" t="s">
         <v>63</v>
@@ -6815,7 +6390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>64</v>
       </c>
@@ -6826,9 +6401,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B42" t="s">
         <v>98</v>
@@ -6837,9 +6412,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B43" t="s">
         <v>98</v>
@@ -6848,20 +6423,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>358</v>
-      </c>
-      <c r="B44" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="B44" s="13" t="s">
         <v>63</v>
       </c>
       <c r="C44" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B45" t="s">
         <v>78</v>
@@ -6870,9 +6445,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B46" t="s">
         <v>78</v>
@@ -6881,18 +6456,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="13" t="s">
         <v>78</v>
       </c>
       <c r="C47" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>137</v>
       </c>
@@ -6903,7 +6478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>115</v>
       </c>
@@ -6914,7 +6489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>118</v>
       </c>
@@ -6925,9 +6500,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B51" t="s">
         <v>98</v>
@@ -6936,7 +6511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>108</v>
       </c>
@@ -6947,9 +6522,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B53" t="s">
         <v>98</v>
@@ -6958,7 +6533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>100</v>
       </c>
@@ -6969,7 +6544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>42</v>
       </c>
@@ -6980,7 +6555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -6991,42 +6566,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B57" s="16" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>181</v>
+      </c>
+      <c r="B57" s="13" t="s">
         <v>106</v>
       </c>
       <c r="C57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B58" s="16" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>187</v>
+      </c>
+      <c r="B58" s="13" t="s">
         <v>106</v>
       </c>
       <c r="C58" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B59" s="16" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>192</v>
+      </c>
+      <c r="B59" s="13" t="s">
         <v>106</v>
       </c>
       <c r="C59" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="4" t="s">
-        <v>176</v>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>174</v>
       </c>
       <c r="B60" t="s">
         <v>78</v>
@@ -7035,9 +6610,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="4" t="s">
-        <v>184</v>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>182</v>
       </c>
       <c r="B61" t="s">
         <v>78</v>
@@ -7046,9 +6621,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="4" t="s">
-        <v>190</v>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>188</v>
       </c>
       <c r="B62" t="s">
         <v>78</v>
@@ -7057,9 +6632,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B63" t="s">
         <v>63</v>
@@ -7068,20 +6643,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B64" s="4" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>168</v>
+      </c>
+      <c r="B64" t="s">
         <v>98</v>
       </c>
-      <c r="C64" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
+      <c r="C64" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B65" t="s">
         <v>98</v>
@@ -7090,9 +6665,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="B66" t="s">
         <v>98</v>
@@ -7101,9 +6676,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B67" t="s">
         <v>98</v>
@@ -7112,9 +6687,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B68" t="s">
         <v>98</v>
@@ -7123,20 +6698,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>296</v>
-      </c>
-      <c r="B69" s="16" t="s">
-        <v>219</v>
+        <v>294</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>217</v>
       </c>
       <c r="C69" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="B70" t="s">
         <v>82</v>
@@ -7145,9 +6720,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B71" t="s">
         <v>82</v>
@@ -7156,9 +6731,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B72" t="s">
         <v>82</v>
@@ -7167,9 +6742,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B73" t="s">
         <v>63</v>
@@ -7178,9 +6753,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B74" t="s">
         <v>63</v>
@@ -7189,9 +6764,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B75" t="s">
         <v>63</v>
@@ -7200,9 +6775,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B76" t="s">
         <v>98</v>
@@ -7211,9 +6786,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B77" t="s">
         <v>98</v>
@@ -7222,65 +6797,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="16"/>
-    </row>
-    <row r="79">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B78" s="13"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>488</v>
-      </c>
-      <c r="B79" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="B79" s="13" t="s">
         <v>98</v>
       </c>
       <c r="C79" t="b">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>490</v>
-      </c>
-      <c r="B80" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="B80" s="13" t="s">
         <v>98</v>
       </c>
       <c r="C80" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>491</v>
-      </c>
-      <c r="B81" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="B81" s="13" t="s">
         <v>98</v>
       </c>
       <c r="C81" t="b">
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>492</v>
-      </c>
-      <c r="B82" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="B82" s="13" t="s">
         <v>98</v>
       </c>
       <c r="C82" t="b">
         <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B83" t="s">
         <v>46</v>
@@ -7289,155 +6864,153 @@
         <v>0</v>
       </c>
       <c r="D83" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="16"/>
-    </row>
-    <row r="85">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B84" s="13"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>213</v>
-      </c>
-      <c r="B85" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="B85" s="13" t="s">
         <v>98</v>
       </c>
       <c r="C85" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="B86" s="16" t="s">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>215</v>
+      </c>
+      <c r="B86" s="13" t="s">
         <v>98</v>
       </c>
       <c r="C86" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="16"/>
-    </row>
-    <row r="88">
-      <c r="B88" s="16"/>
-    </row>
-    <row r="89">
-      <c r="B89" s="16"/>
-    </row>
-    <row r="90">
-      <c r="B90" s="16"/>
-    </row>
-    <row r="91">
-      <c r="B91" s="16"/>
-    </row>
-    <row r="92">
-      <c r="B92" s="16"/>
-    </row>
-    <row r="93">
-      <c r="B93" s="16"/>
-    </row>
-    <row r="94">
-      <c r="B94" s="16"/>
-    </row>
-    <row r="95">
-      <c r="B95" s="16"/>
-    </row>
-    <row r="96">
-      <c r="B96" s="16"/>
-    </row>
-    <row r="97">
-      <c r="B97" s="16"/>
-    </row>
-    <row r="98">
-      <c r="B98" s="16"/>
-    </row>
-    <row r="99">
-      <c r="B99" s="16"/>
-    </row>
-    <row r="100">
-      <c r="B100" s="16"/>
-    </row>
-    <row r="101">
-      <c r="B101" s="16"/>
-    </row>
-    <row r="102">
-      <c r="B102" s="16"/>
-    </row>
-    <row r="103">
-      <c r="B103" s="16"/>
-    </row>
-    <row r="104">
-      <c r="B104" s="16"/>
-    </row>
-    <row r="105">
-      <c r="B105" s="16"/>
-    </row>
-    <row r="106">
-      <c r="B106" s="16"/>
-    </row>
-    <row r="107">
-      <c r="B107" s="16"/>
-    </row>
-    <row r="108">
-      <c r="B108" s="16"/>
-    </row>
-    <row r="109">
-      <c r="B109" s="16"/>
-    </row>
-    <row r="110">
-      <c r="B110" s="16"/>
-    </row>
-    <row r="111">
-      <c r="B111" s="16"/>
-    </row>
-    <row r="112">
-      <c r="B112" s="16"/>
-    </row>
-    <row r="113">
-      <c r="B113" s="16"/>
-    </row>
-    <row r="114">
-      <c r="B114" s="16"/>
-    </row>
-    <row r="115">
-      <c r="B115" s="16"/>
-    </row>
-    <row r="116">
-      <c r="B116" s="16"/>
-    </row>
-    <row r="117">
-      <c r="B117" s="16"/>
-    </row>
-    <row r="118">
-      <c r="B118" s="16"/>
-    </row>
-    <row r="119">
-      <c r="B119" s="16"/>
-    </row>
-    <row r="120">
-      <c r="B120" s="16"/>
-    </row>
-    <row r="121">
-      <c r="B121" s="16"/>
-    </row>
-    <row r="122">
-      <c r="B122" s="16"/>
-    </row>
-    <row r="123">
-      <c r="B123" s="16"/>
-    </row>
-    <row r="124">
-      <c r="B124" s="16"/>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B87" s="13"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B88" s="13"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B89" s="13"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B90" s="13"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B91" s="13"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B92" s="13"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B93" s="13"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B94" s="13"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B95" s="13"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B96" s="13"/>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B97" s="13"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B98" s="13"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B99" s="13"/>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B100" s="13"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B101" s="13"/>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B102" s="13"/>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B103" s="13"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B104" s="13"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B105" s="13"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B106" s="13"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B107" s="13"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B108" s="13"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B109" s="13"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B110" s="13"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B111" s="13"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B112" s="13"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B113" s="13"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B114" s="13"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B115" s="13"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B116" s="13"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B117" s="13"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B118" s="13"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B119" s="13"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B120" s="13"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B121" s="13"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B122" s="13"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B123" s="13"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B124" s="13"/>
     </row>
   </sheetData>
-  <sortState ref="A2:C77">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C77">
     <sortCondition ref="A2"/>
   </sortState>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
+++ b/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\MADtrials2\MADtrial\app\config\tables\MADTRIAL_INC\Forms\MADTRIAL_INC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFE6F06-97ED-425F-A0FE-DE3298648C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7E5E4E-5D4E-4A7A-B760-922CB714689C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="502">
   <si>
     <t>setting_name</t>
   </si>
@@ -1517,9 +1517,6 @@
     <t>A criança deve ter entre 9 méses e 5 anos de idade</t>
   </si>
   <si>
-    <t>data('PODEVAC')=='2'|| data('PODEINC')=='2'  || data('JAINC') == '1' || data('BRACOCRI') &lt;110 || data('TEMPERATURA')&gt;37.9 || data('VENAOVAS') == '2' ||  data('VENAOVAS2') == '2' || (data('SARVAC') == '1' &amp;&amp;  data('SARVAC2') == '1')||data('SARVAC2') == '1'</t>
-  </si>
-  <si>
     <t>Josemira</t>
   </si>
   <si>
@@ -1536,6 +1533,30 @@
   </si>
   <si>
     <t>A criança recebeu os seus vacinas do sarampo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if </t>
+  </si>
+  <si>
+    <t>childAGE</t>
+  </si>
+  <si>
+    <t>adate.diffInDays(data("DOB"),data("DATINC"))</t>
+  </si>
+  <si>
+    <t>calculates.childAGE &lt;453 || adate.hasUncertainty(data('DOB')) &amp;&amp; (date('IDADEANO') == '1' &amp;&amp; data('IDADEMES')&lt; '3' || data('IDADEMES')&lt; '15')</t>
+  </si>
+  <si>
+    <t>data('PODEVAC')=='2'|| data('PODEINC')=='2'  || data('JAINC') == '1' || data('BRACOCRI') &lt;110 || data('TEMPERATURA')&gt;37.9 || data('VENAOVAS') == '2' ||  data('VENAOVAS2') == '2' || (data('SARVAC') == '1' &amp;&amp;  data('SARVAC2') != '2')||data('SARVAC2') == '1'</t>
+  </si>
+  <si>
+    <t>data('SARVAC') == '1' &amp;&amp; calculates.childAGE &lt;453</t>
+  </si>
+  <si>
+    <t>The child is not yet 15 months and has already received MV1</t>
+  </si>
+  <si>
+    <t>A crianca ainda nao completou 15 meses e ja tomou VAS1</t>
   </si>
 </sst>
 </file>
@@ -1592,7 +1613,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1614,6 +1635,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1641,7 +1668,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1658,6 +1685,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2052,7 +2080,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R239"/>
+  <dimension ref="A1:R246"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
@@ -3283,437 +3311,423 @@
     </row>
     <row r="107" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
+        <v>494</v>
+      </c>
+      <c r="C107" s="14" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="108" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B108" t="s">
         <v>55</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C108" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="108" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D108" t="s">
+    <row r="109" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D109" t="s">
         <v>98</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E109" t="s">
         <v>157</v>
       </c>
-      <c r="F108" t="s">
+      <c r="F109" t="s">
         <v>211</v>
       </c>
-      <c r="G108" t="s">
+      <c r="G109" t="s">
         <v>212</v>
       </c>
-      <c r="H108" t="s">
+      <c r="H109" t="s">
         <v>213</v>
       </c>
-      <c r="K108" t="s">
+      <c r="K109" t="s">
         <v>214</v>
       </c>
-      <c r="L108" t="s">
+      <c r="L109" t="s">
         <v>199</v>
       </c>
-      <c r="M108" t="s">
+      <c r="M109" t="s">
         <v>200</v>
-      </c>
-    </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B109" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="110" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
-        <v>55</v>
-      </c>
-      <c r="C110" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="111" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D111" t="s">
-        <v>98</v>
-      </c>
-      <c r="E111" t="s">
-        <v>157</v>
-      </c>
-      <c r="F111" t="s">
-        <v>215</v>
-      </c>
-      <c r="G111" t="s">
-        <v>208</v>
-      </c>
-      <c r="H111" t="s">
-        <v>216</v>
-      </c>
-      <c r="K111" t="s">
-        <v>210</v>
-      </c>
-      <c r="L111" t="s">
-        <v>199</v>
-      </c>
-      <c r="M111" t="s">
-        <v>200</v>
+        <v>73</v>
       </c>
     </row>
     <row r="112" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
+        <v>55</v>
+      </c>
+      <c r="C112" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="113" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="D113" t="s">
+        <v>98</v>
+      </c>
+      <c r="E113" t="s">
+        <v>157</v>
+      </c>
+      <c r="F113" t="s">
+        <v>215</v>
+      </c>
+      <c r="G113" t="s">
+        <v>208</v>
+      </c>
+      <c r="H113" t="s">
+        <v>216</v>
+      </c>
+      <c r="K113" t="s">
+        <v>210</v>
+      </c>
+      <c r="L113" t="s">
+        <v>199</v>
+      </c>
+      <c r="M113" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="114" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B114" s="14" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="113" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B113" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="114" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B114" t="s">
-        <v>55</v>
-      </c>
-      <c r="C114" t="s">
-        <v>201</v>
-      </c>
-    </row>
     <row r="115" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="D115" t="s">
-        <v>217</v>
-      </c>
-      <c r="F115" t="s">
-        <v>218</v>
-      </c>
-      <c r="G115" t="s">
-        <v>219</v>
-      </c>
-      <c r="H115" t="s">
-        <v>220</v>
+      <c r="B115" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="116" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
     </row>
     <row r="117" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
-        <v>40</v>
+        <v>55</v>
+      </c>
+      <c r="C117" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="118" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D118" t="s">
-        <v>63</v>
+        <v>217</v>
       </c>
       <c r="F118" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G118" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H118" t="s">
-        <v>223</v>
-      </c>
-      <c r="K118" t="s">
-        <v>224</v>
-      </c>
-      <c r="L118" t="s">
-        <v>225</v>
-      </c>
-      <c r="M118" t="s">
-        <v>226</v>
-      </c>
-      <c r="N118" t="s">
-        <v>227</v>
-      </c>
-      <c r="O118" t="s">
-        <v>228</v>
-      </c>
-      <c r="P118" t="s">
-        <v>92</v>
+        <v>220</v>
       </c>
     </row>
     <row r="119" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="D119" t="s">
-        <v>78</v>
-      </c>
-      <c r="F119" t="s">
-        <v>229</v>
-      </c>
-      <c r="G119" t="s">
-        <v>230</v>
-      </c>
-      <c r="H119" t="s">
-        <v>231</v>
-      </c>
-      <c r="K119" t="s">
-        <v>232</v>
-      </c>
-      <c r="L119" t="s">
-        <v>233</v>
-      </c>
-      <c r="M119" t="s">
-        <v>234</v>
+      <c r="B119" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="120" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B120" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="121" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B121" t="s">
-        <v>40</v>
+      <c r="D121" t="s">
+        <v>63</v>
+      </c>
+      <c r="F121" t="s">
+        <v>221</v>
+      </c>
+      <c r="G121" t="s">
+        <v>222</v>
+      </c>
+      <c r="H121" t="s">
+        <v>223</v>
+      </c>
+      <c r="K121" t="s">
+        <v>224</v>
+      </c>
+      <c r="L121" t="s">
+        <v>225</v>
+      </c>
+      <c r="M121" t="s">
+        <v>226</v>
+      </c>
+      <c r="N121" t="s">
+        <v>227</v>
+      </c>
+      <c r="O121" t="s">
+        <v>228</v>
+      </c>
+      <c r="P121" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="122" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D122" t="s">
-        <v>98</v>
-      </c>
-      <c r="E122" t="s">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="F122" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G122" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="H122" t="s">
-        <v>238</v>
+        <v>231</v>
+      </c>
+      <c r="K122" t="s">
+        <v>232</v>
+      </c>
+      <c r="L122" t="s">
+        <v>233</v>
+      </c>
+      <c r="M122" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="123" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
-        <v>55</v>
-      </c>
-      <c r="C123" t="s">
-        <v>239</v>
+        <v>49</v>
       </c>
     </row>
     <row r="124" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="D124" t="s">
-        <v>46</v>
-      </c>
-      <c r="F124" t="s">
-        <v>240</v>
-      </c>
-      <c r="G124" t="s">
-        <v>241</v>
-      </c>
-      <c r="H124" t="s">
-        <v>242</v>
-      </c>
-      <c r="K124" t="s">
-        <v>243</v>
-      </c>
-      <c r="L124" t="s">
-        <v>143</v>
-      </c>
-      <c r="M124" t="s">
-        <v>144</v>
+      <c r="B124" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="125" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B125" t="s">
-        <v>73</v>
+      <c r="D125" t="s">
+        <v>98</v>
+      </c>
+      <c r="E125" t="s">
+        <v>235</v>
+      </c>
+      <c r="F125" t="s">
+        <v>236</v>
+      </c>
+      <c r="G125" t="s">
+        <v>237</v>
+      </c>
+      <c r="H125" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="126" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
+        <v>55</v>
+      </c>
+      <c r="C126" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="127" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="D127" t="s">
+        <v>46</v>
+      </c>
+      <c r="F127" t="s">
+        <v>240</v>
+      </c>
+      <c r="G127" t="s">
+        <v>241</v>
+      </c>
+      <c r="H127" t="s">
+        <v>242</v>
+      </c>
+      <c r="K127" t="s">
+        <v>243</v>
+      </c>
+      <c r="L127" t="s">
+        <v>143</v>
+      </c>
+      <c r="M127" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="128" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B128" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="129" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B129" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="127" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B127" t="s">
+    <row r="130" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B130" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="128" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="D128" t="s">
+    <row r="131" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D131" t="s">
         <v>98</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E131" t="s">
         <v>244</v>
       </c>
-      <c r="F128" t="s">
+      <c r="F131" t="s">
         <v>245</v>
       </c>
-      <c r="G128" t="s">
+      <c r="G131" t="s">
         <v>246</v>
       </c>
-      <c r="H128" t="s">
+      <c r="H131" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="129" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D129" t="s">
+    <row r="132" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D132" t="s">
         <v>98</v>
       </c>
-      <c r="E129" t="s">
+      <c r="E132" t="s">
         <v>244</v>
       </c>
-      <c r="F129" t="s">
+      <c r="F132" t="s">
         <v>248</v>
       </c>
-      <c r="G129" t="s">
+      <c r="G132" t="s">
         <v>249</v>
       </c>
-      <c r="H129" t="s">
+      <c r="H132" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="130" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D130" t="s">
+    <row r="133" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D133" t="s">
         <v>98</v>
       </c>
-      <c r="E130" t="s">
+      <c r="E133" t="s">
         <v>244</v>
       </c>
-      <c r="F130" t="s">
+      <c r="F133" t="s">
         <v>251</v>
       </c>
-      <c r="G130" t="s">
+      <c r="G133" t="s">
         <v>252</v>
       </c>
-      <c r="H130" t="s">
+      <c r="H133" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="131" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B131" s="7" t="s">
+    <row r="134" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B134" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C131" s="7" t="s">
+      <c r="C134" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="D131" s="7"/>
-      <c r="E131" s="7"/>
-      <c r="F131" s="7"/>
-      <c r="G131" s="7"/>
-      <c r="H131" s="7"/>
-      <c r="I131" s="7"/>
-    </row>
-    <row r="132" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B132" s="7"/>
-      <c r="C132" s="7"/>
-      <c r="D132" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E132" s="7"/>
-      <c r="F132" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="G132" s="7"/>
-      <c r="H132" s="7"/>
-      <c r="I132" s="7" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B133" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C133" s="7"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="7"/>
-      <c r="F133" s="7"/>
-      <c r="G133" s="7"/>
-      <c r="H133" s="7"/>
-      <c r="I133" s="7"/>
-    </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B134" s="7"/>
-      <c r="C134" s="7"/>
-      <c r="D134" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="D134" s="7"/>
       <c r="E134" s="7"/>
-      <c r="F134" s="7" t="s">
-        <v>255</v>
-      </c>
+      <c r="F134" s="7"/>
       <c r="G134" s="7"/>
       <c r="H134" s="7"/>
-      <c r="I134" s="7" t="s">
-        <v>257</v>
-      </c>
+      <c r="I134" s="7"/>
     </row>
     <row r="135" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B135" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="B135" s="7"/>
       <c r="C135" s="7"/>
-      <c r="D135" s="7"/>
+      <c r="D135" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="E135" s="7"/>
-      <c r="F135" s="7"/>
+      <c r="F135" s="7" t="s">
+        <v>255</v>
+      </c>
       <c r="G135" s="7"/>
       <c r="H135" s="7"/>
-      <c r="I135" s="7"/>
+      <c r="I135" s="7" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="136" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B136" t="s">
+      <c r="B136" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C136" s="7"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="7"/>
+      <c r="F136" s="7"/>
+      <c r="G136" s="7"/>
+      <c r="H136" s="7"/>
+      <c r="I136" s="7"/>
+    </row>
+    <row r="137" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B137" s="7"/>
+      <c r="C137" s="7"/>
+      <c r="D137" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E137" s="7"/>
+      <c r="F137" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G137" s="7"/>
+      <c r="H137" s="7"/>
+      <c r="I137" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="138" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B138" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C138" s="7"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="7"/>
+      <c r="F138" s="7"/>
+      <c r="G138" s="7"/>
+      <c r="H138" s="7"/>
+      <c r="I138" s="7"/>
+    </row>
+    <row r="139" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B139" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="137" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B137" t="s">
+    <row r="140" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B140" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="138" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D138" t="s">
+    <row r="141" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D141" t="s">
         <v>98</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E141" t="s">
         <v>244</v>
       </c>
-      <c r="F138" t="s">
+      <c r="F141" t="s">
         <v>258</v>
       </c>
-      <c r="G138" t="s">
+      <c r="G141" t="s">
         <v>259</v>
       </c>
-      <c r="H138" t="s">
+      <c r="H141" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D139" t="s">
+    <row r="142" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D142" t="s">
         <v>98</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E142" t="s">
         <v>244</v>
       </c>
-      <c r="F139" t="s">
+      <c r="F142" t="s">
         <v>261</v>
       </c>
-      <c r="G139" t="s">
+      <c r="G142" t="s">
         <v>262</v>
       </c>
-      <c r="H139" t="s">
+      <c r="H142" t="s">
         <v>263</v>
-      </c>
-    </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D140" t="s">
-        <v>98</v>
-      </c>
-      <c r="E140" t="s">
-        <v>244</v>
-      </c>
-      <c r="F140" t="s">
-        <v>264</v>
-      </c>
-      <c r="G140" t="s">
-        <v>265</v>
-      </c>
-      <c r="H140" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="141" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B141" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B142" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="143" spans="2:9" x14ac:dyDescent="0.35">
@@ -3724,223 +3738,226 @@
         <v>244</v>
       </c>
       <c r="F143" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G143" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H143" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="144" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D144" t="s">
-        <v>63</v>
-      </c>
-      <c r="F144" t="s">
-        <v>270</v>
-      </c>
-      <c r="G144" t="s">
-        <v>271</v>
-      </c>
-      <c r="H144" t="s">
-        <v>272</v>
+      <c r="B144" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="145" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="146" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D146" t="s">
+        <v>98</v>
+      </c>
+      <c r="E146" t="s">
+        <v>244</v>
+      </c>
+      <c r="F146" t="s">
+        <v>267</v>
+      </c>
+      <c r="G146" t="s">
+        <v>268</v>
+      </c>
+      <c r="H146" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="147" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D147" t="s">
+        <v>63</v>
+      </c>
+      <c r="F147" t="s">
+        <v>270</v>
+      </c>
+      <c r="G147" t="s">
+        <v>271</v>
+      </c>
+      <c r="H147" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="148" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B148" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="146" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="8" t="s">
+    <row r="149" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B149" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="147" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="D147" s="8" t="s">
+    <row r="150" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D150" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="E147" s="8" t="s">
+      <c r="E150" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="F147" s="8" t="s">
+      <c r="F150" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="G147" s="8" t="s">
+      <c r="G150" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="H147" s="8" t="s">
+      <c r="H150" s="8" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="148" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B148" s="8" t="s">
+    <row r="151" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B151" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C148" s="8" t="s">
+      <c r="C151" s="8" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="149" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="D149" s="8" t="s">
+    <row r="152" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D152" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="E149" s="8" t="s">
+      <c r="E152" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="F149" s="8" t="s">
+      <c r="F152" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="G149" s="8" t="s">
+      <c r="G152" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="H149" s="8" t="s">
+      <c r="H152" s="8" t="s">
         <v>280</v>
-      </c>
-    </row>
-    <row r="150" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B150" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C150" s="8" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="151" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="D151" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F151" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="G151" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="H151" s="8" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="152" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B152" s="8" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="153" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B153" s="8" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="154" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B154" s="8" t="s">
-        <v>49</v>
+      <c r="D154" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="H154" s="8" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="155" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B155" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="156" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B156" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="157" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="158" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B158" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="156" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="D156" s="5" t="s">
+    <row r="159" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D159" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E156" s="5" t="s">
+      <c r="E159" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="F156" s="5" t="s">
+      <c r="F159" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="G156" s="5" t="s">
+      <c r="G159" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="H156" s="5" t="s">
+      <c r="H159" s="5" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="157" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B157" s="5" t="s">
+    <row r="160" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B160" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C157" s="5" t="s">
+      <c r="C160" s="5" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="158" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="D158" s="5" t="s">
+    <row r="161" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D161" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E158" s="5" t="s">
+      <c r="E161" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="F158" s="5" t="s">
+      <c r="F161" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="G158" s="5" t="s">
+      <c r="G161" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="H158" s="5" t="s">
+      <c r="H161" s="5" t="s">
         <v>291</v>
-      </c>
-    </row>
-    <row r="159" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B159" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="160" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="D160" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F160" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="G160" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="H160" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="161" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B161" s="5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="162" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B162" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="163" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D163" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="H163" s="5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="164" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B164" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="163" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B163" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="164" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B164" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="165" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D165" t="s">
-        <v>217</v>
-      </c>
-      <c r="F165" t="s">
-        <v>294</v>
-      </c>
-      <c r="G165" t="s">
-        <v>295</v>
-      </c>
-      <c r="H165" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="166" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B166" t="s">
+    <row r="165" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B165" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="166" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B166" s="5" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3951,265 +3968,265 @@
     </row>
     <row r="168" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D168" t="s">
-        <v>98</v>
-      </c>
-      <c r="E168" t="s">
-        <v>157</v>
+        <v>217</v>
       </c>
       <c r="F168" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G168" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H168" t="s">
-        <v>299</v>
-      </c>
-      <c r="K168" t="s">
-        <v>300</v>
-      </c>
-      <c r="L168" t="s">
-        <v>199</v>
-      </c>
-      <c r="M168" t="s">
-        <v>200</v>
+        <v>296</v>
       </c>
     </row>
     <row r="169" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B169" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="170" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B170" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="171" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D171" t="s">
+        <v>98</v>
+      </c>
+      <c r="E171" t="s">
+        <v>157</v>
+      </c>
+      <c r="F171" t="s">
+        <v>297</v>
+      </c>
+      <c r="G171" t="s">
+        <v>298</v>
+      </c>
+      <c r="H171" t="s">
+        <v>299</v>
+      </c>
+      <c r="K171" t="s">
+        <v>300</v>
+      </c>
+      <c r="L171" t="s">
+        <v>199</v>
+      </c>
+      <c r="M171" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="172" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B172" t="s">
         <v>55</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C172" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="170" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D170" t="s">
+    <row r="173" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D173" t="s">
         <v>63</v>
       </c>
-      <c r="F170" t="s">
+      <c r="F173" t="s">
         <v>302</v>
       </c>
-      <c r="G170" t="s">
+      <c r="G173" t="s">
         <v>303</v>
       </c>
-      <c r="H170" t="s">
+      <c r="H173" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="171" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B171" t="s">
+    <row r="174" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B174" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="172" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D172" t="s">
+    <row r="175" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D175" t="s">
         <v>98</v>
       </c>
-      <c r="E172" t="s">
+      <c r="E175" t="s">
         <v>157</v>
       </c>
-      <c r="F172" t="s">
+      <c r="F175" t="s">
         <v>305</v>
       </c>
-      <c r="G172" t="s">
+      <c r="G175" t="s">
         <v>306</v>
       </c>
-      <c r="H172" t="s">
+      <c r="H175" t="s">
         <v>307</v>
       </c>
-      <c r="K172" t="s">
+      <c r="K175" t="s">
         <v>308</v>
       </c>
-      <c r="L172" t="s">
+      <c r="L175" t="s">
         <v>199</v>
       </c>
-      <c r="M172" t="s">
+      <c r="M175" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="173" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B173" t="s">
+    <row r="176" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B176" t="s">
         <v>55</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C176" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="174" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D174" t="s">
+    <row r="177" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D177" t="s">
         <v>63</v>
       </c>
-      <c r="F174" t="s">
+      <c r="F177" t="s">
         <v>310</v>
       </c>
-      <c r="G174" t="s">
+      <c r="G177" t="s">
         <v>303</v>
       </c>
-      <c r="H174" t="s">
+      <c r="H177" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="175" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B175" t="s">
+    <row r="178" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B178" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="176" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D176" t="s">
+    <row r="179" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D179" t="s">
         <v>98</v>
       </c>
-      <c r="E176" t="s">
+      <c r="E179" t="s">
         <v>244</v>
       </c>
-      <c r="F176" t="s">
+      <c r="F179" t="s">
         <v>311</v>
       </c>
-      <c r="G176" t="s">
+      <c r="G179" t="s">
         <v>312</v>
       </c>
-      <c r="H176" t="s">
+      <c r="H179" t="s">
         <v>313</v>
       </c>
-      <c r="K176" t="s">
+      <c r="K179" t="s">
         <v>314</v>
       </c>
-      <c r="L176" t="s">
+      <c r="L179" t="s">
         <v>199</v>
       </c>
-      <c r="M176" t="s">
+      <c r="M179" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="177" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B177" t="s">
+    <row r="180" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B180" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="178" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B178" t="s">
+    <row r="181" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B181" t="s">
         <v>55</v>
       </c>
-      <c r="C178" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="179" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B179" t="s">
+      <c r="C181" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="182" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B182" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="180" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D180" t="s">
+    <row r="183" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D183" t="s">
         <v>41</v>
       </c>
-      <c r="F180" t="s">
+      <c r="F183" t="s">
         <v>315</v>
       </c>
-      <c r="I180">
+      <c r="I183">
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D181" t="s">
+    <row r="184" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D184" t="s">
         <v>156</v>
       </c>
-      <c r="G181" t="s">
+      <c r="G184" t="s">
         <v>316</v>
       </c>
-      <c r="H181" t="s">
+      <c r="H184" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="182" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B182" t="s">
-        <v>55</v>
-      </c>
-      <c r="C182" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="183" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D183" t="s">
-        <v>156</v>
-      </c>
-      <c r="G183" t="s">
-        <v>318</v>
-      </c>
-      <c r="H183" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="184" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B184" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="185" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B185" t="s">
         <v>55</v>
       </c>
       <c r="C185" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="186" spans="2:9" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="186" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D186" t="s">
         <v>156</v>
       </c>
       <c r="G186" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H186" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="187" spans="2:9" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="187" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B187" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="188" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="188" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B188" t="s">
         <v>55</v>
       </c>
       <c r="C188" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="189" spans="2:9" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="189" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D189" t="s">
         <v>156</v>
       </c>
       <c r="G189" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H189" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="190" spans="2:9" x14ac:dyDescent="0.35">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="190" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B190" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="191" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="191" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B191" t="s">
         <v>55</v>
       </c>
       <c r="C191" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="192" spans="2:9" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="192" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D192" t="s">
         <v>156</v>
       </c>
       <c r="G192" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H192" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="193" spans="2:8" x14ac:dyDescent="0.35">
@@ -4222,7 +4239,7 @@
         <v>55</v>
       </c>
       <c r="C194" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="195" spans="2:8" x14ac:dyDescent="0.35">
@@ -4230,10 +4247,10 @@
         <v>156</v>
       </c>
       <c r="G195" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H195" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="196" spans="2:8" x14ac:dyDescent="0.35">
@@ -4246,7 +4263,7 @@
         <v>55</v>
       </c>
       <c r="C197" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="198" spans="2:8" x14ac:dyDescent="0.35">
@@ -4254,10 +4271,10 @@
         <v>156</v>
       </c>
       <c r="G198" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="H198" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="199" spans="2:8" x14ac:dyDescent="0.35">
@@ -4270,7 +4287,7 @@
         <v>55</v>
       </c>
       <c r="C200" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="201" spans="2:8" x14ac:dyDescent="0.35">
@@ -4278,10 +4295,10 @@
         <v>156</v>
       </c>
       <c r="G201" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H201" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="202" spans="2:8" x14ac:dyDescent="0.35">
@@ -4294,7 +4311,7 @@
         <v>55</v>
       </c>
       <c r="C203" t="s">
-        <v>492</v>
+        <v>334</v>
       </c>
     </row>
     <row r="204" spans="2:8" x14ac:dyDescent="0.35">
@@ -4302,10 +4319,10 @@
         <v>156</v>
       </c>
       <c r="G204" t="s">
-        <v>493</v>
+        <v>335</v>
       </c>
       <c r="H204" t="s">
-        <v>494</v>
+        <v>336</v>
       </c>
     </row>
     <row r="205" spans="2:8" x14ac:dyDescent="0.35">
@@ -4318,7 +4335,7 @@
         <v>55</v>
       </c>
       <c r="C206" t="s">
-        <v>337</v>
+        <v>491</v>
       </c>
     </row>
     <row r="207" spans="2:8" x14ac:dyDescent="0.35">
@@ -4326,10 +4343,10 @@
         <v>156</v>
       </c>
       <c r="G207" t="s">
-        <v>338</v>
+        <v>492</v>
       </c>
       <c r="H207" t="s">
-        <v>339</v>
+        <v>493</v>
       </c>
     </row>
     <row r="208" spans="2:8" x14ac:dyDescent="0.35">
@@ -4337,323 +4354,371 @@
         <v>73</v>
       </c>
     </row>
-    <row r="209" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="209" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B209" t="s">
+        <v>55</v>
+      </c>
+      <c r="C209" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="210" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D210" t="s">
+        <v>156</v>
+      </c>
+      <c r="G210" t="s">
+        <v>338</v>
+      </c>
+      <c r="H210" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="211" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B211" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="213" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B213" t="s">
+        <v>55</v>
+      </c>
+      <c r="C213" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="214" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D214" t="s">
+        <v>156</v>
+      </c>
+      <c r="G214" t="s">
+        <v>500</v>
+      </c>
+      <c r="H214" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="215" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B215" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="216" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B216" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="210" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B210" t="s">
+    <row r="217" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B217" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="211" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B211" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="212" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D212" t="s">
-        <v>78</v>
-      </c>
-      <c r="F212" t="s">
-        <v>340</v>
-      </c>
-      <c r="G212" t="s">
-        <v>341</v>
-      </c>
-      <c r="H212" t="s">
-        <v>342</v>
-      </c>
-      <c r="K212" t="s">
-        <v>343</v>
-      </c>
-      <c r="L212" t="s">
-        <v>344</v>
-      </c>
-      <c r="M212" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="213" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D213" t="s">
-        <v>78</v>
-      </c>
-      <c r="F213" t="s">
-        <v>346</v>
-      </c>
-      <c r="G213" t="s">
-        <v>347</v>
-      </c>
-      <c r="H213" t="s">
-        <v>348</v>
-      </c>
-      <c r="K213" t="s">
-        <v>349</v>
-      </c>
-      <c r="L213" t="s">
-        <v>350</v>
-      </c>
-      <c r="M213" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="214" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D214" t="s">
-        <v>41</v>
-      </c>
-      <c r="F214" t="s">
-        <v>352</v>
-      </c>
-      <c r="I214" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="215" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D215" t="s">
-        <v>156</v>
-      </c>
-      <c r="G215" t="s">
-        <v>354</v>
-      </c>
-      <c r="H215" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="216" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D216" t="s">
-        <v>41</v>
-      </c>
-      <c r="F216" t="s">
-        <v>315</v>
-      </c>
-      <c r="I216">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="217" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B217" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="218" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="218" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B218" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="219" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="219" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D219" t="s">
+        <v>78</v>
+      </c>
+      <c r="F219" t="s">
+        <v>340</v>
+      </c>
+      <c r="G219" t="s">
+        <v>341</v>
+      </c>
+      <c r="H219" t="s">
+        <v>342</v>
+      </c>
+      <c r="K219" t="s">
+        <v>343</v>
+      </c>
+      <c r="L219" t="s">
+        <v>344</v>
+      </c>
+      <c r="M219" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="220" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D220" t="s">
+        <v>78</v>
+      </c>
+      <c r="F220" t="s">
+        <v>346</v>
+      </c>
+      <c r="G220" t="s">
+        <v>347</v>
+      </c>
+      <c r="H220" t="s">
+        <v>348</v>
+      </c>
+      <c r="K220" t="s">
+        <v>349</v>
+      </c>
+      <c r="L220" t="s">
+        <v>350</v>
+      </c>
+      <c r="M220" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="221" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D221" t="s">
         <v>41</v>
       </c>
-      <c r="F219" t="s">
+      <c r="F221" t="s">
+        <v>352</v>
+      </c>
+      <c r="I221" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="222" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D222" t="s">
+        <v>156</v>
+      </c>
+      <c r="G222" t="s">
+        <v>354</v>
+      </c>
+      <c r="H222" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="223" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D223" t="s">
+        <v>41</v>
+      </c>
+      <c r="F223" t="s">
+        <v>315</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B224" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="225" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B225" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="226" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D226" t="s">
+        <v>41</v>
+      </c>
+      <c r="F226" t="s">
         <v>356</v>
       </c>
-      <c r="I219" t="s">
+      <c r="I226" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="220" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D220" t="s">
+    <row r="227" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D227" t="s">
         <v>46</v>
       </c>
-      <c r="F220" t="s">
+      <c r="F227" t="s">
         <v>356</v>
       </c>
-      <c r="G220" t="s">
+      <c r="G227" t="s">
         <v>358</v>
       </c>
-      <c r="H220" t="s">
+      <c r="H227" t="s">
         <v>359</v>
       </c>
-      <c r="Q220" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D221" t="s">
+      <c r="Q227" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D228" t="s">
         <v>360</v>
       </c>
-      <c r="F221" t="s">
+      <c r="F228" t="s">
         <v>361</v>
       </c>
-      <c r="G221" t="s">
+      <c r="G228" t="s">
         <v>362</v>
       </c>
-      <c r="H221" t="s">
+      <c r="H228" t="s">
         <v>363</v>
       </c>
-      <c r="K221" t="s">
+      <c r="K228" t="s">
         <v>364</v>
       </c>
-      <c r="L221" t="s">
+      <c r="L228" t="s">
         <v>199</v>
       </c>
-      <c r="M221" t="s">
+      <c r="M228" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="222" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D222" t="s">
+    <row r="229" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D229" t="s">
         <v>41</v>
       </c>
-      <c r="F222" t="s">
+      <c r="F229" t="s">
         <v>365</v>
       </c>
-      <c r="I222" t="s">
+      <c r="I229" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="223" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D223" t="s">
+    <row r="230" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D230" t="s">
         <v>78</v>
       </c>
-      <c r="F223" t="s">
+      <c r="F230" t="s">
         <v>367</v>
       </c>
-      <c r="G223" t="s">
+      <c r="G230" t="s">
         <v>368</v>
       </c>
-      <c r="H223" t="s">
+      <c r="H230" t="s">
         <v>369</v>
       </c>
-      <c r="K223" t="s">
+      <c r="K230" t="s">
         <v>370</v>
       </c>
-      <c r="L223" t="s">
+      <c r="L230" t="s">
         <v>371</v>
       </c>
-      <c r="M223" t="s">
+      <c r="M230" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="224" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D224" t="s">
+    <row r="231" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D231" t="s">
         <v>41</v>
       </c>
-      <c r="F224" t="s">
+      <c r="F231" t="s">
         <v>373</v>
       </c>
-      <c r="I224" t="s">
+      <c r="I231" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="225" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D225" t="s">
+    <row r="232" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D232" t="s">
         <v>156</v>
       </c>
-      <c r="G225" t="s">
+      <c r="G232" t="s">
         <v>375</v>
       </c>
-      <c r="H225" t="s">
+      <c r="H232" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="226" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B226" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="227" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B227" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="228" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B228" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="229" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D229" t="s">
-        <v>106</v>
-      </c>
-      <c r="E229" t="s">
-        <v>377</v>
-      </c>
-      <c r="F229" t="s">
-        <v>378</v>
-      </c>
-      <c r="G229" t="s">
-        <v>379</v>
-      </c>
-      <c r="H229" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="230" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B230" t="s">
-        <v>55</v>
-      </c>
-      <c r="C230" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="231" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D231" t="s">
-        <v>106</v>
-      </c>
-      <c r="E231" t="s">
-        <v>382</v>
-      </c>
-      <c r="F231" t="s">
-        <v>383</v>
-      </c>
-      <c r="G231" t="s">
-        <v>384</v>
-      </c>
-      <c r="H231" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="232" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B232" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="233" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="233" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B233" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="234" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="234" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B234" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="235" spans="2:9" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="235" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B235" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="236" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="236" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D236" t="s">
+        <v>106</v>
+      </c>
+      <c r="E236" t="s">
+        <v>377</v>
+      </c>
+      <c r="F236" t="s">
+        <v>378</v>
+      </c>
+      <c r="G236" t="s">
+        <v>379</v>
+      </c>
+      <c r="H236" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="237" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B237" t="s">
+        <v>55</v>
+      </c>
+      <c r="C237" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="238" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D238" t="s">
+        <v>106</v>
+      </c>
+      <c r="E238" t="s">
+        <v>382</v>
+      </c>
+      <c r="F238" t="s">
+        <v>383</v>
+      </c>
+      <c r="G238" t="s">
+        <v>384</v>
+      </c>
+      <c r="H238" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="239" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B239" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="240" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B240" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="241" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B241" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="242" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B242" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="243" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D243" t="s">
         <v>156</v>
       </c>
-      <c r="G236" t="s">
+      <c r="G243" t="s">
         <v>386</v>
       </c>
-      <c r="H236" t="s">
+      <c r="H243" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="237" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D237" t="s">
+    <row r="244" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D244" t="s">
         <v>41</v>
       </c>
-      <c r="F237" t="s">
+      <c r="F244" t="s">
         <v>315</v>
       </c>
-      <c r="I237">
+      <c r="I244">
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B238" t="s">
+    <row r="245" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B245" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="239" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B239" t="s">
+    <row r="246" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B246" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4912,10 +4977,10 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D16" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E16" t="s">
         <v>410</v>
@@ -4936,7 +5001,7 @@
         <v>406</v>
       </c>
       <c r="E17" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -4978,10 +5043,10 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D20" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -4993,10 +5058,10 @@
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D21" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -5809,7 +5874,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.7265625" bestFit="1" customWidth="1"/>
@@ -5822,6 +5887,14 @@
       </c>
       <c r="B1" s="11" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B2" t="s">
+        <v>496</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
+++ b/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\MADtrials2\MADtrial\app\config\tables\MADTRIAL_INC\Forms\MADTRIAL_INC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7E5E4E-5D4E-4A7A-B760-922CB714689C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF95A3D9-47CF-49C9-8831-65CA056B2507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="504">
   <si>
     <t>setting_name</t>
   </si>
@@ -669,9 +669,6 @@
     <t>Mother/guardian confirmed that the child did not receive the second measles vaccine</t>
   </si>
   <si>
-    <t>A mãe/tutor confirmou que a criança não recebeu a vacina do sarampo</t>
-  </si>
-  <si>
     <t>data('VENAOVAS') != null || data('CONSENT') == '2' || data('CARTVIS') == '1'</t>
   </si>
   <si>
@@ -679,9 +676,6 @@
   </si>
   <si>
     <t>Has the child received the second measles vaccine</t>
-  </si>
-  <si>
-    <t>A criança recebeu a seguna vacina do sarampo</t>
   </si>
   <si>
     <t>data('SARVAC2') != null || data('CONSENT') == '2' || data('CARTVIS') == '2'</t>
@@ -1544,9 +1538,6 @@
     <t>adate.diffInDays(data("DOB"),data("DATINC"))</t>
   </si>
   <si>
-    <t>calculates.childAGE &lt;453 || adate.hasUncertainty(data('DOB')) &amp;&amp; (date('IDADEANO') == '1' &amp;&amp; data('IDADEMES')&lt; '3' || data('IDADEMES')&lt; '15')</t>
-  </si>
-  <si>
     <t>data('PODEVAC')=='2'|| data('PODEINC')=='2'  || data('JAINC') == '1' || data('BRACOCRI') &lt;110 || data('TEMPERATURA')&gt;37.9 || data('VENAOVAS') == '2' ||  data('VENAOVAS2') == '2' || (data('SARVAC') == '1' &amp;&amp;  data('SARVAC2') != '2')||data('SARVAC2') == '1'</t>
   </si>
   <si>
@@ -1557,6 +1548,21 @@
   </si>
   <si>
     <t>A crianca ainda nao completou 15 meses e ja tomou VAS1</t>
+  </si>
+  <si>
+    <t>data('DATINC') == null</t>
+  </si>
+  <si>
+    <t>added by Ane 2025-07-24 - to avoid overwriting information</t>
+  </si>
+  <si>
+    <t>calculates.childAGE &gt; '453' || adate.hasUncertainty(data('DOB')) &amp;&amp; (data('IDADEANO') == '1' &amp;&amp; data('IDADEMES') &gt; '3' || data('IDADEMES')&gt; '14' || data('IDADEANO') &gt; '1' )</t>
+  </si>
+  <si>
+    <t>Mother/guardian confirmed that the child did not receive the first measles vaccine</t>
+  </si>
+  <si>
+    <t>A mãe/tutor confirmou que a criança não recebeu o primero deose de vacina do sarampo</t>
   </si>
 </sst>
 </file>
@@ -2080,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R246"/>
+  <dimension ref="A1:S248"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
@@ -2100,7 +2106,7 @@
     <col min="15" max="15" width="15.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -2155,280 +2161,271 @@
       <c r="R1" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S1" s="1" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="D3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="B3" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>499</v>
+      </c>
+      <c r="S3" s="14" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="D4" t="s">
         <v>41</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="D5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F5" t="s">
         <v>44</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="B6" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
         <v>47</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H7" t="s">
         <v>48</v>
       </c>
-      <c r="Q5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="D8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="B9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="D10" t="s">
         <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G10" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H10" t="s">
-        <v>60</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>55</v>
       </c>
       <c r="C11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" t="s">
+        <v>60</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" t="s">
         <v>62</v>
       </c>
-      <c r="J11" s="4"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="D12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" t="s">
-        <v>65</v>
-      </c>
-      <c r="H12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="D14" t="s">
         <v>63</v>
       </c>
       <c r="F14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" t="s">
         <v>68</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G16" t="s">
         <v>69</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H16" t="s">
         <v>70</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K16" t="s">
         <v>71</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L16" t="s">
         <v>72</v>
       </c>
-      <c r="M14" t="s">
+      <c r="M16" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="D16" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" t="s">
-        <v>74</v>
-      </c>
-      <c r="I16">
-        <v>9999</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>75</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D20" t="s">
         <v>50</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E20" t="s">
         <v>57</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F20" t="s">
         <v>58</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G20" t="s">
         <v>76</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H20" t="s">
         <v>77</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J20" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D19" t="s">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D21" t="s">
         <v>78</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F21" t="s">
         <v>74</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G21" t="s">
         <v>79</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H21" t="s">
         <v>80</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K21" t="s">
         <v>81</v>
       </c>
-      <c r="L19" t="s">
+      <c r="L21" t="s">
         <v>72</v>
       </c>
-      <c r="M19" t="s">
+      <c r="M21" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" t="s">
-        <v>83</v>
-      </c>
-      <c r="F20" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D22" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D24" t="s">
         <v>41</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F24" t="s">
         <v>74</v>
       </c>
-      <c r="I22">
+      <c r="I24">
         <v>9999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D23" t="s">
-        <v>63</v>
-      </c>
-      <c r="F23" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" t="s">
-        <v>86</v>
-      </c>
-      <c r="H23" t="s">
-        <v>87</v>
-      </c>
-      <c r="K23" t="s">
-        <v>71</v>
-      </c>
-      <c r="L23" t="s">
-        <v>72</v>
-      </c>
-      <c r="M23" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B24" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
@@ -2436,112 +2433,103 @@
         <v>63</v>
       </c>
       <c r="F25" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" t="s">
+        <v>86</v>
+      </c>
+      <c r="H25" t="s">
+        <v>87</v>
+      </c>
+      <c r="K25" t="s">
+        <v>71</v>
+      </c>
+      <c r="L25" t="s">
+        <v>72</v>
+      </c>
+      <c r="M25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="D27" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" t="s">
         <v>88</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G27" t="s">
         <v>88</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H27" t="s">
         <v>88</v>
       </c>
-      <c r="K25" t="s">
+      <c r="K27" t="s">
         <v>89</v>
       </c>
-      <c r="L25" t="s">
+      <c r="L27" t="s">
         <v>90</v>
       </c>
-      <c r="M25" t="s">
+      <c r="M27" t="s">
         <v>91</v>
       </c>
-      <c r="P25" t="s">
+      <c r="P27" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="D26" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26" t="s">
-        <v>83</v>
-      </c>
-      <c r="F26" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D28" t="s">
-        <v>41</v>
+        <v>82</v>
+      </c>
+      <c r="E28" t="s">
+        <v>83</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
-      </c>
-      <c r="I28">
-        <v>99999</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C29" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B30" t="s">
-        <v>73</v>
+      <c r="D30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" t="s">
+        <v>88</v>
+      </c>
+      <c r="I30">
+        <v>99999</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B34" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D33" t="s">
-        <v>63</v>
-      </c>
-      <c r="F33" t="s">
-        <v>95</v>
-      </c>
-      <c r="G33" t="s">
-        <v>96</v>
-      </c>
-      <c r="H33" t="s">
-        <v>97</v>
-      </c>
-      <c r="R33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D34" t="s">
-        <v>98</v>
-      </c>
-      <c r="E34" t="s">
-        <v>99</v>
-      </c>
-      <c r="F34" t="s">
-        <v>100</v>
-      </c>
-      <c r="G34" t="s">
-        <v>101</v>
-      </c>
-      <c r="H34" t="s">
-        <v>102</v>
-      </c>
-      <c r="R34" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.35">
@@ -2549,421 +2537,430 @@
         <v>63</v>
       </c>
       <c r="F35" t="s">
+        <v>95</v>
+      </c>
+      <c r="G35" t="s">
+        <v>96</v>
+      </c>
+      <c r="H35" t="s">
+        <v>97</v>
+      </c>
+      <c r="R35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D36" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36" t="s">
+        <v>99</v>
+      </c>
+      <c r="F36" t="s">
+        <v>100</v>
+      </c>
+      <c r="G36" t="s">
+        <v>101</v>
+      </c>
+      <c r="H36" t="s">
+        <v>102</v>
+      </c>
+      <c r="R36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D37" t="s">
+        <v>63</v>
+      </c>
+      <c r="F37" t="s">
         <v>103</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G37" t="s">
         <v>104</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H37" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B36" t="s">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B37" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D38" t="s">
-        <v>106</v>
-      </c>
-      <c r="E38" t="s">
-        <v>107</v>
-      </c>
-      <c r="F38" t="s">
-        <v>108</v>
-      </c>
-      <c r="G38" t="s">
-        <v>109</v>
-      </c>
-      <c r="H38" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" t="s">
-        <v>111</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D40" t="s">
-        <v>63</v>
+        <v>106</v>
+      </c>
+      <c r="E40" t="s">
+        <v>107</v>
       </c>
       <c r="F40" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G40" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H40" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C41" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B42" t="s">
-        <v>49</v>
+      <c r="D42" t="s">
+        <v>63</v>
+      </c>
+      <c r="F42" t="s">
+        <v>112</v>
+      </c>
+      <c r="G42" t="s">
+        <v>113</v>
+      </c>
+      <c r="H42" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B45" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D44" t="s">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D46" t="s">
         <v>78</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F46" t="s">
         <v>115</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G46" t="s">
         <v>116</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H46" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D45" t="s">
-        <v>82</v>
-      </c>
-      <c r="E45" t="s">
-        <v>83</v>
-      </c>
-      <c r="F45" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B46" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D47" t="s">
-        <v>41</v>
+        <v>82</v>
+      </c>
+      <c r="E47" t="s">
+        <v>83</v>
       </c>
       <c r="F47" t="s">
-        <v>115</v>
-      </c>
-      <c r="I47">
-        <v>999</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D49" t="s">
+        <v>41</v>
+      </c>
+      <c r="F49" t="s">
+        <v>115</v>
+      </c>
+      <c r="I49">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B50" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B49" t="s">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B51" t="s">
         <v>55</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C51" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="50" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D50" t="s">
+    <row r="52" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D52" t="s">
         <v>78</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F52" t="s">
         <v>121</v>
       </c>
-      <c r="G50" t="s">
+      <c r="G52" t="s">
         <v>122</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H52" t="s">
         <v>123</v>
       </c>
-      <c r="K50" s="5" t="s">
+      <c r="K52" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="L50" t="s">
+      <c r="L52" t="s">
         <v>125</v>
       </c>
-      <c r="M50" t="s">
+      <c r="M52" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="51" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D51" t="s">
+    <row r="53" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D53" t="s">
         <v>82</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E53" t="s">
         <v>127</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F53" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="52" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" t="s">
+    <row r="54" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B54" t="s">
         <v>55</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C54" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="53" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D53" t="s">
+    <row r="55" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D55" t="s">
         <v>41</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F55" t="s">
         <v>121</v>
       </c>
-      <c r="I53">
+      <c r="I55">
         <v>9999999</v>
       </c>
     </row>
-    <row r="54" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" t="s">
+    <row r="56" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="55" spans="2:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" t="s">
+    <row r="57" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B57" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="56" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D56" t="s">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D58" t="s">
         <v>78</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F58" t="s">
         <v>130</v>
       </c>
-      <c r="G56" t="s">
+      <c r="G58" t="s">
         <v>131</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H58" t="s">
         <v>132</v>
       </c>
-      <c r="K56" t="s">
+      <c r="K58" t="s">
         <v>133</v>
       </c>
-      <c r="L56" t="s">
+      <c r="L58" t="s">
         <v>134</v>
       </c>
-      <c r="M56" t="s">
+      <c r="M58" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="57" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D57" t="s">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D59" t="s">
         <v>82</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E59" t="s">
         <v>136</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F59" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="58" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B58" t="s">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B60" t="s">
         <v>55</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C60" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="59" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D59" t="s">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D61" t="s">
         <v>41</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F61" t="s">
         <v>130</v>
       </c>
-      <c r="I59">
+      <c r="I61">
         <v>999999999</v>
       </c>
     </row>
-    <row r="60" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B60" t="s">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B62" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="61" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B61" t="s">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B63" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="62" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B62" t="s">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B64" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="63" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B63" t="s">
+    <row r="65" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B65" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="64" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D64" t="s">
+    <row r="66" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D66" t="s">
         <v>46</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F66" t="s">
         <v>139</v>
       </c>
-      <c r="G64" t="s">
+      <c r="G66" t="s">
         <v>140</v>
       </c>
-      <c r="H64" t="s">
+      <c r="H66" t="s">
         <v>141</v>
       </c>
-      <c r="K64" t="s">
+      <c r="K66" t="s">
         <v>142</v>
       </c>
-      <c r="L64" t="s">
+      <c r="L66" t="s">
         <v>143</v>
       </c>
-      <c r="M64" t="s">
+      <c r="M66" t="s">
         <v>144</v>
       </c>
-      <c r="R64" t="b">
+      <c r="R66" t="b">
         <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D65" t="s">
-        <v>82</v>
-      </c>
-      <c r="E65" t="s">
-        <v>145</v>
-      </c>
-      <c r="F65" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B66" t="s">
-        <v>55</v>
-      </c>
-      <c r="C66" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D67" t="s">
-        <v>41</v>
+        <v>82</v>
+      </c>
+      <c r="E67" t="s">
+        <v>145</v>
       </c>
       <c r="F67" t="s">
-        <v>139</v>
-      </c>
-      <c r="I67" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
+        <v>55</v>
+      </c>
+      <c r="C68" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D69" t="s">
+        <v>41</v>
+      </c>
+      <c r="F69" t="s">
+        <v>139</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B69" t="s">
+    <row r="71" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B71" t="s">
         <v>55</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C71" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D70" t="s">
+    <row r="72" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D72" t="s">
         <v>78</v>
       </c>
-      <c r="F70" t="s">
+      <c r="F72" t="s">
         <v>150</v>
       </c>
-      <c r="G70" t="s">
+      <c r="G72" t="s">
         <v>151</v>
       </c>
-      <c r="H70" t="s">
+      <c r="H72" t="s">
         <v>152</v>
-      </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D71" t="s">
-        <v>78</v>
-      </c>
-      <c r="F71" t="s">
-        <v>153</v>
-      </c>
-      <c r="G71" t="s">
-        <v>154</v>
-      </c>
-      <c r="H71" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B72" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D73" t="s">
-        <v>156</v>
+        <v>78</v>
+      </c>
+      <c r="F73" t="s">
+        <v>153</v>
       </c>
       <c r="G73" t="s">
-        <v>486</v>
+        <v>154</v>
       </c>
       <c r="H73" t="s">
-        <v>487</v>
+        <v>155</v>
       </c>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D75" t="s">
+        <v>156</v>
+      </c>
+      <c r="G75" t="s">
+        <v>484</v>
+      </c>
+      <c r="H75" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B76" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B75" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D76" t="s">
-        <v>98</v>
-      </c>
-      <c r="E76" t="s">
-        <v>157</v>
-      </c>
-      <c r="F76" t="s">
-        <v>158</v>
-      </c>
-      <c r="G76" t="s">
-        <v>159</v>
-      </c>
-      <c r="H76" t="s">
-        <v>160</v>
-      </c>
-      <c r="R76" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
-        <v>55</v>
-      </c>
-      <c r="C77" t="s">
-        <v>161</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.35">
@@ -2971,16 +2968,19 @@
         <v>98</v>
       </c>
       <c r="E78" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="F78" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G78" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H78" t="s">
-        <v>165</v>
+        <v>160</v>
+      </c>
+      <c r="R78" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.35">
@@ -2988,7 +2988,7 @@
         <v>55</v>
       </c>
       <c r="C79" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.35">
@@ -2996,87 +2996,78 @@
         <v>98</v>
       </c>
       <c r="E80" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F80" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G80" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="H80" t="s">
-        <v>170</v>
-      </c>
-      <c r="K80" t="s">
-        <v>171</v>
-      </c>
-      <c r="L80" t="s">
-        <v>172</v>
-      </c>
-      <c r="M80" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C81" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="82" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B82" t="s">
-        <v>73</v>
+      <c r="D82" t="s">
+        <v>98</v>
+      </c>
+      <c r="E82" t="s">
+        <v>167</v>
+      </c>
+      <c r="F82" t="s">
+        <v>168</v>
+      </c>
+      <c r="G82" t="s">
+        <v>169</v>
+      </c>
+      <c r="H82" t="s">
+        <v>170</v>
+      </c>
+      <c r="K82" t="s">
+        <v>171</v>
+      </c>
+      <c r="L82" t="s">
+        <v>172</v>
+      </c>
+      <c r="M82" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="83" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="84" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
-        <v>55</v>
-      </c>
-      <c r="C84" t="s">
-        <v>161</v>
+        <v>73</v>
       </c>
     </row>
     <row r="85" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="86" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B86" t="s">
+        <v>55</v>
+      </c>
+      <c r="C86" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="87" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B87" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D86" t="s">
-        <v>78</v>
-      </c>
-      <c r="F86" t="s">
-        <v>174</v>
-      </c>
-      <c r="G86" t="s">
-        <v>175</v>
-      </c>
-      <c r="H86" t="s">
-        <v>176</v>
-      </c>
-      <c r="K86" t="s">
-        <v>177</v>
-      </c>
-      <c r="L86" t="s">
-        <v>178</v>
-      </c>
-      <c r="M86" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D87" t="s">
-        <v>106</v>
-      </c>
-      <c r="E87" t="s">
-        <v>180</v>
-      </c>
-      <c r="F87" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="88" spans="2:13" x14ac:dyDescent="0.35">
@@ -3084,16 +3075,16 @@
         <v>78</v>
       </c>
       <c r="F88" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="G88" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="H88" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="K88" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="L88" t="s">
         <v>178</v>
@@ -3107,10 +3098,10 @@
         <v>106</v>
       </c>
       <c r="E89" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F89" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="90" spans="2:13" x14ac:dyDescent="0.35">
@@ -3118,16 +3109,16 @@
         <v>78</v>
       </c>
       <c r="F90" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G90" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="H90" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="K90" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="L90" t="s">
         <v>178</v>
@@ -3144,99 +3135,99 @@
         <v>186</v>
       </c>
       <c r="F91" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="92" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B92" t="s">
-        <v>55</v>
-      </c>
-      <c r="C92" t="s">
-        <v>193</v>
+      <c r="D92" t="s">
+        <v>78</v>
+      </c>
+      <c r="F92" t="s">
+        <v>188</v>
+      </c>
+      <c r="G92" t="s">
+        <v>189</v>
+      </c>
+      <c r="H92" t="s">
+        <v>190</v>
+      </c>
+      <c r="K92" t="s">
+        <v>191</v>
+      </c>
+      <c r="L92" t="s">
+        <v>178</v>
+      </c>
+      <c r="M92" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="93" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D93" t="s">
-        <v>41</v>
+        <v>106</v>
+      </c>
+      <c r="E93" t="s">
+        <v>186</v>
       </c>
       <c r="F93" t="s">
-        <v>182</v>
-      </c>
-      <c r="I93">
-        <v>999999999</v>
+        <v>192</v>
       </c>
     </row>
     <row r="94" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
+        <v>55</v>
+      </c>
+      <c r="C94" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="95" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D95" t="s">
+        <v>41</v>
+      </c>
+      <c r="F95" t="s">
+        <v>182</v>
+      </c>
+      <c r="I95">
+        <v>999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B96" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B95" t="s">
-        <v>55</v>
-      </c>
-      <c r="C95" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D96" t="s">
-        <v>41</v>
-      </c>
-      <c r="F96" t="s">
-        <v>188</v>
-      </c>
-      <c r="I96">
-        <v>999999999</v>
       </c>
     </row>
     <row r="97" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C97" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="98" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B98" t="s">
-        <v>49</v>
+      <c r="D98" t="s">
+        <v>41</v>
+      </c>
+      <c r="F98" t="s">
+        <v>188</v>
+      </c>
+      <c r="I98">
+        <v>999999999</v>
       </c>
     </row>
     <row r="99" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
     </row>
     <row r="100" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D100" t="s">
-        <v>98</v>
-      </c>
-      <c r="E100" t="s">
-        <v>157</v>
-      </c>
-      <c r="F100" t="s">
-        <v>195</v>
-      </c>
-      <c r="G100" t="s">
-        <v>196</v>
-      </c>
-      <c r="H100" t="s">
-        <v>197</v>
-      </c>
-      <c r="K100" t="s">
-        <v>198</v>
-      </c>
-      <c r="L100" t="s">
-        <v>199</v>
-      </c>
-      <c r="M100" t="s">
-        <v>200</v>
+      <c r="B100" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="101" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
-        <v>55</v>
-      </c>
-      <c r="C101" t="s">
-        <v>201</v>
+        <v>40</v>
       </c>
     </row>
     <row r="102" spans="2:13" x14ac:dyDescent="0.35">
@@ -3247,16 +3238,16 @@
         <v>157</v>
       </c>
       <c r="F102" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="G102" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="H102" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="K102" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="L102" t="s">
         <v>199</v>
@@ -3267,390 +3258,396 @@
     </row>
     <row r="103" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
+        <v>55</v>
+      </c>
+      <c r="C103" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="104" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D104" t="s">
+        <v>98</v>
+      </c>
+      <c r="E104" t="s">
+        <v>157</v>
+      </c>
+      <c r="F104" t="s">
+        <v>202</v>
+      </c>
+      <c r="G104" t="s">
+        <v>203</v>
+      </c>
+      <c r="H104" t="s">
+        <v>204</v>
+      </c>
+      <c r="K104" t="s">
+        <v>205</v>
+      </c>
+      <c r="L104" t="s">
+        <v>199</v>
+      </c>
+      <c r="M104" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="105" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B105" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="104" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B104" t="s">
-        <v>55</v>
-      </c>
-      <c r="C104" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="105" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D105" t="s">
-        <v>98</v>
-      </c>
-      <c r="E105" t="s">
-        <v>157</v>
-      </c>
-      <c r="F105" t="s">
-        <v>207</v>
-      </c>
-      <c r="G105" t="s">
-        <v>208</v>
-      </c>
-      <c r="H105" t="s">
-        <v>209</v>
-      </c>
-      <c r="K105" t="s">
-        <v>210</v>
-      </c>
-      <c r="L105" t="s">
-        <v>199</v>
-      </c>
-      <c r="M105" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="106" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C106" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="107" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B107" t="s">
-        <v>494</v>
-      </c>
-      <c r="C107" s="14" t="s">
-        <v>497</v>
+      <c r="D107" t="s">
+        <v>98</v>
+      </c>
+      <c r="E107" t="s">
+        <v>157</v>
+      </c>
+      <c r="F107" t="s">
+        <v>207</v>
+      </c>
+      <c r="G107" t="s">
+        <v>502</v>
+      </c>
+      <c r="H107" t="s">
+        <v>503</v>
+      </c>
+      <c r="K107" t="s">
+        <v>209</v>
+      </c>
+      <c r="L107" t="s">
+        <v>199</v>
+      </c>
+      <c r="M107" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="108" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
-        <v>55</v>
-      </c>
-      <c r="C108" t="s">
-        <v>201</v>
+        <v>73</v>
       </c>
     </row>
     <row r="109" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D109" t="s">
-        <v>98</v>
-      </c>
-      <c r="E109" t="s">
-        <v>157</v>
-      </c>
-      <c r="F109" t="s">
-        <v>211</v>
-      </c>
-      <c r="G109" t="s">
-        <v>212</v>
-      </c>
-      <c r="H109" t="s">
-        <v>213</v>
-      </c>
-      <c r="K109" t="s">
-        <v>214</v>
-      </c>
-      <c r="L109" t="s">
-        <v>199</v>
-      </c>
-      <c r="M109" t="s">
-        <v>200</v>
+      <c r="B109" t="s">
+        <v>492</v>
+      </c>
+      <c r="C109" s="14" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="110" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C110" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="111" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D111" t="s">
+        <v>98</v>
+      </c>
+      <c r="E111" t="s">
+        <v>157</v>
+      </c>
+      <c r="F111" t="s">
+        <v>210</v>
+      </c>
+      <c r="G111" t="s">
+        <v>211</v>
+      </c>
+      <c r="H111" t="s">
+        <v>337</v>
+      </c>
+      <c r="K111" t="s">
+        <v>212</v>
+      </c>
+      <c r="L111" t="s">
+        <v>199</v>
+      </c>
+      <c r="M111" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="112" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="114" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B114" t="s">
         <v>55</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C114" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="113" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="D113" t="s">
+    <row r="115" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="D115" t="s">
         <v>98</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E115" t="s">
         <v>157</v>
       </c>
-      <c r="F113" t="s">
-        <v>215</v>
-      </c>
-      <c r="G113" t="s">
+      <c r="F115" t="s">
+        <v>213</v>
+      </c>
+      <c r="G115" t="s">
         <v>208</v>
       </c>
-      <c r="H113" t="s">
-        <v>216</v>
-      </c>
-      <c r="K113" t="s">
-        <v>210</v>
-      </c>
-      <c r="L113" t="s">
+      <c r="H115" t="s">
+        <v>214</v>
+      </c>
+      <c r="K115" t="s">
+        <v>209</v>
+      </c>
+      <c r="L115" t="s">
         <v>199</v>
       </c>
-      <c r="M113" t="s">
+      <c r="M115" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="114" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B114" s="14" t="s">
+    <row r="116" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B116" s="14" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="115" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B115" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="116" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B116" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="117" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
-        <v>55</v>
-      </c>
-      <c r="C117" t="s">
-        <v>201</v>
+        <v>73</v>
       </c>
     </row>
     <row r="118" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="D118" t="s">
-        <v>217</v>
-      </c>
-      <c r="F118" t="s">
-        <v>218</v>
-      </c>
-      <c r="G118" t="s">
-        <v>219</v>
-      </c>
-      <c r="H118" t="s">
-        <v>220</v>
+      <c r="B118" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="119" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B119" t="s">
+        <v>55</v>
+      </c>
+      <c r="C119" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="120" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="D120" t="s">
+        <v>215</v>
+      </c>
+      <c r="F120" t="s">
+        <v>216</v>
+      </c>
+      <c r="G120" t="s">
+        <v>217</v>
+      </c>
+      <c r="H120" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="121" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B121" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="120" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B120" t="s">
+    <row r="122" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B122" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="121" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="D121" t="s">
+    <row r="123" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="D123" t="s">
         <v>63</v>
       </c>
-      <c r="F121" t="s">
+      <c r="F123" t="s">
+        <v>219</v>
+      </c>
+      <c r="G123" t="s">
+        <v>220</v>
+      </c>
+      <c r="H123" t="s">
         <v>221</v>
       </c>
-      <c r="G121" t="s">
+      <c r="K123" t="s">
         <v>222</v>
       </c>
-      <c r="H121" t="s">
+      <c r="L123" t="s">
         <v>223</v>
       </c>
-      <c r="K121" t="s">
+      <c r="M123" t="s">
         <v>224</v>
       </c>
-      <c r="L121" t="s">
+      <c r="N123" t="s">
         <v>225</v>
       </c>
-      <c r="M121" t="s">
+      <c r="O123" t="s">
         <v>226</v>
       </c>
-      <c r="N121" t="s">
+      <c r="P123" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="124" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="D124" t="s">
+        <v>78</v>
+      </c>
+      <c r="F124" t="s">
         <v>227</v>
       </c>
-      <c r="O121" t="s">
+      <c r="G124" t="s">
         <v>228</v>
       </c>
-      <c r="P121" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="122" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="D122" t="s">
-        <v>78</v>
-      </c>
-      <c r="F122" t="s">
+      <c r="H124" t="s">
         <v>229</v>
       </c>
-      <c r="G122" t="s">
+      <c r="K124" t="s">
         <v>230</v>
       </c>
-      <c r="H122" t="s">
+      <c r="L124" t="s">
         <v>231</v>
       </c>
-      <c r="K122" t="s">
+      <c r="M124" t="s">
         <v>232</v>
       </c>
-      <c r="L122" t="s">
-        <v>233</v>
-      </c>
-      <c r="M122" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="123" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B123" t="s">
+    </row>
+    <row r="125" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B125" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="124" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B124" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="125" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="D125" t="s">
-        <v>98</v>
-      </c>
-      <c r="E125" t="s">
-        <v>235</v>
-      </c>
-      <c r="F125" t="s">
-        <v>236</v>
-      </c>
-      <c r="G125" t="s">
-        <v>237</v>
-      </c>
-      <c r="H125" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="126" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
-        <v>55</v>
-      </c>
-      <c r="C126" t="s">
-        <v>239</v>
+        <v>40</v>
       </c>
     </row>
     <row r="127" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D127" t="s">
-        <v>46</v>
+        <v>98</v>
+      </c>
+      <c r="E127" t="s">
+        <v>233</v>
       </c>
       <c r="F127" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="G127" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="H127" t="s">
-        <v>242</v>
-      </c>
-      <c r="K127" t="s">
-        <v>243</v>
-      </c>
-      <c r="L127" t="s">
-        <v>143</v>
-      </c>
-      <c r="M127" t="s">
-        <v>144</v>
+        <v>236</v>
       </c>
     </row>
     <row r="128" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
+        <v>55</v>
+      </c>
+      <c r="C128" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="129" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D129" t="s">
+        <v>46</v>
+      </c>
+      <c r="F129" t="s">
+        <v>238</v>
+      </c>
+      <c r="G129" t="s">
+        <v>239</v>
+      </c>
+      <c r="H129" t="s">
+        <v>240</v>
+      </c>
+      <c r="K129" t="s">
+        <v>241</v>
+      </c>
+      <c r="L129" t="s">
+        <v>143</v>
+      </c>
+      <c r="M129" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="130" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B130" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="129" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B129" t="s">
+    <row r="131" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B131" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="130" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B130" t="s">
+    <row r="132" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B132" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="131" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D131" t="s">
-        <v>98</v>
-      </c>
-      <c r="E131" t="s">
-        <v>244</v>
-      </c>
-      <c r="F131" t="s">
-        <v>245</v>
-      </c>
-      <c r="G131" t="s">
-        <v>246</v>
-      </c>
-      <c r="H131" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="132" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D132" t="s">
-        <v>98</v>
-      </c>
-      <c r="E132" t="s">
-        <v>244</v>
-      </c>
-      <c r="F132" t="s">
-        <v>248</v>
-      </c>
-      <c r="G132" t="s">
-        <v>249</v>
-      </c>
-      <c r="H132" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D133" t="s">
         <v>98</v>
       </c>
       <c r="E133" t="s">
+        <v>242</v>
+      </c>
+      <c r="F133" t="s">
+        <v>243</v>
+      </c>
+      <c r="G133" t="s">
         <v>244</v>
       </c>
-      <c r="F133" t="s">
+      <c r="H133" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="134" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D134" t="s">
+        <v>98</v>
+      </c>
+      <c r="E134" t="s">
+        <v>242</v>
+      </c>
+      <c r="F134" t="s">
+        <v>246</v>
+      </c>
+      <c r="G134" t="s">
+        <v>247</v>
+      </c>
+      <c r="H134" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="135" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D135" t="s">
+        <v>98</v>
+      </c>
+      <c r="E135" t="s">
+        <v>242</v>
+      </c>
+      <c r="F135" t="s">
+        <v>249</v>
+      </c>
+      <c r="G135" t="s">
+        <v>250</v>
+      </c>
+      <c r="H135" t="s">
         <v>251</v>
       </c>
-      <c r="G133" t="s">
+    </row>
+    <row r="136" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B136" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C136" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="H133" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B134" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C134" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="D134" s="7"/>
-      <c r="E134" s="7"/>
-      <c r="F134" s="7"/>
-      <c r="G134" s="7"/>
-      <c r="H134" s="7"/>
-      <c r="I134" s="7"/>
-    </row>
-    <row r="135" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B135" s="7"/>
-      <c r="C135" s="7"/>
-      <c r="D135" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E135" s="7"/>
-      <c r="F135" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="G135" s="7"/>
-      <c r="H135" s="7"/>
-      <c r="I135" s="7" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B136" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C136" s="7"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7"/>
       <c r="F136" s="7"/>
@@ -3658,7 +3655,7 @@
       <c r="H136" s="7"/>
       <c r="I136" s="7"/>
     </row>
-    <row r="137" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
       <c r="D137" s="7" t="s">
@@ -3666,17 +3663,17 @@
       </c>
       <c r="E137" s="7"/>
       <c r="F137" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G137" s="7"/>
       <c r="H137" s="7"/>
       <c r="I137" s="7" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="138" spans="2:9" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="138" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B138" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
@@ -3686,158 +3683,161 @@
       <c r="H138" s="7"/>
       <c r="I138" s="7"/>
     </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B139" t="s">
+    <row r="139" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B139" s="7"/>
+      <c r="C139" s="7"/>
+      <c r="D139" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E139" s="7"/>
+      <c r="F139" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="G139" s="7"/>
+      <c r="H139" s="7"/>
+      <c r="I139" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="140" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B140" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C140" s="7"/>
+      <c r="D140" s="7"/>
+      <c r="E140" s="7"/>
+      <c r="F140" s="7"/>
+      <c r="G140" s="7"/>
+      <c r="H140" s="7"/>
+      <c r="I140" s="7"/>
+    </row>
+    <row r="141" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B141" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="140" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B140" t="s">
+    <row r="142" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B142" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="141" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D141" t="s">
-        <v>98</v>
-      </c>
-      <c r="E141" t="s">
-        <v>244</v>
-      </c>
-      <c r="F141" t="s">
-        <v>258</v>
-      </c>
-      <c r="G141" t="s">
-        <v>259</v>
-      </c>
-      <c r="H141" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D142" t="s">
-        <v>98</v>
-      </c>
-      <c r="E142" t="s">
-        <v>244</v>
-      </c>
-      <c r="F142" t="s">
-        <v>261</v>
-      </c>
-      <c r="G142" t="s">
-        <v>262</v>
-      </c>
-      <c r="H142" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D143" t="s">
         <v>98</v>
       </c>
       <c r="E143" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F143" t="s">
+        <v>256</v>
+      </c>
+      <c r="G143" t="s">
+        <v>257</v>
+      </c>
+      <c r="H143" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="144" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D144" t="s">
+        <v>98</v>
+      </c>
+      <c r="E144" t="s">
+        <v>242</v>
+      </c>
+      <c r="F144" t="s">
+        <v>259</v>
+      </c>
+      <c r="G144" t="s">
+        <v>260</v>
+      </c>
+      <c r="H144" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="145" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D145" t="s">
+        <v>98</v>
+      </c>
+      <c r="E145" t="s">
+        <v>242</v>
+      </c>
+      <c r="F145" t="s">
+        <v>262</v>
+      </c>
+      <c r="G145" t="s">
+        <v>263</v>
+      </c>
+      <c r="H145" t="s">
         <v>264</v>
       </c>
-      <c r="G143" t="s">
+    </row>
+    <row r="146" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B146" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="147" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B147" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="148" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D148" t="s">
+        <v>98</v>
+      </c>
+      <c r="E148" t="s">
+        <v>242</v>
+      </c>
+      <c r="F148" t="s">
         <v>265</v>
       </c>
-      <c r="H143" t="s">
+      <c r="G148" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="144" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B144" t="s">
+      <c r="H148" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="149" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D149" t="s">
+        <v>63</v>
+      </c>
+      <c r="F149" t="s">
+        <v>268</v>
+      </c>
+      <c r="G149" t="s">
+        <v>269</v>
+      </c>
+      <c r="H149" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="150" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B150" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="145" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B145" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="146" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="D146" t="s">
-        <v>98</v>
-      </c>
-      <c r="E146" t="s">
-        <v>244</v>
-      </c>
-      <c r="F146" t="s">
-        <v>267</v>
-      </c>
-      <c r="G146" t="s">
-        <v>268</v>
-      </c>
-      <c r="H146" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="147" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="D147" t="s">
-        <v>63</v>
-      </c>
-      <c r="F147" t="s">
-        <v>270</v>
-      </c>
-      <c r="G147" t="s">
-        <v>271</v>
-      </c>
-      <c r="H147" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="148" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B148" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="149" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B149" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="150" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="D150" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E150" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="F150" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="G150" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="H150" s="8" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="151" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B151" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C151" s="8" t="s">
-        <v>276</v>
+        <v>40</v>
       </c>
     </row>
     <row r="152" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="D152" s="8" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>277</v>
+        <v>242</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="G152" s="8" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="H152" s="8" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
     </row>
     <row r="153" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
@@ -3845,83 +3845,83 @@
         <v>55</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
     </row>
     <row r="154" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="D154" s="8" t="s">
-        <v>63</v>
+        <v>82</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>275</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="H154" s="8" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="155" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B155" s="8" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C155" s="8" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="156" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B156" s="8" t="s">
-        <v>73</v>
+      <c r="D156" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="H156" s="8" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="157" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B157" s="8" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="158" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B158" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="159" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B159" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="160" spans="2:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B160" s="8" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="159" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="D159" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E159" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="G159" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="H159" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="160" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B160" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="161" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="D161" s="5" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>277</v>
+        <v>242</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="H161" s="5" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="162" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
@@ -3929,245 +3929,251 @@
         <v>55</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="163" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="D163" s="5" t="s">
-        <v>63</v>
+        <v>82</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>275</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H163" s="5" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="164" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B164" s="5" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="165" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B165" s="5" t="s">
-        <v>73</v>
+      <c r="D165" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G165" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H165" s="5" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="166" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B166" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="167" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B167" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="168" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B168" s="5" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="167" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B167" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="168" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D168" t="s">
-        <v>217</v>
-      </c>
-      <c r="F168" t="s">
-        <v>294</v>
-      </c>
-      <c r="G168" t="s">
-        <v>295</v>
-      </c>
-      <c r="H168" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="169" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B169" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="170" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D170" t="s">
+        <v>215</v>
+      </c>
+      <c r="F170" t="s">
+        <v>292</v>
+      </c>
+      <c r="G170" t="s">
+        <v>293</v>
+      </c>
+      <c r="H170" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="171" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B171" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="170" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B170" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="171" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D171" t="s">
-        <v>98</v>
-      </c>
-      <c r="E171" t="s">
-        <v>157</v>
-      </c>
-      <c r="F171" t="s">
-        <v>297</v>
-      </c>
-      <c r="G171" t="s">
-        <v>298</v>
-      </c>
-      <c r="H171" t="s">
-        <v>299</v>
-      </c>
-      <c r="K171" t="s">
-        <v>300</v>
-      </c>
-      <c r="L171" t="s">
-        <v>199</v>
-      </c>
-      <c r="M171" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="172" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B172" t="s">
-        <v>55</v>
-      </c>
-      <c r="C172" t="s">
-        <v>301</v>
+        <v>40</v>
       </c>
     </row>
     <row r="173" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D173" t="s">
-        <v>63</v>
+        <v>98</v>
+      </c>
+      <c r="E173" t="s">
+        <v>157</v>
       </c>
       <c r="F173" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="G173" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="H173" t="s">
-        <v>304</v>
+        <v>297</v>
+      </c>
+      <c r="K173" t="s">
+        <v>298</v>
+      </c>
+      <c r="L173" t="s">
+        <v>199</v>
+      </c>
+      <c r="M173" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="174" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B174" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C174" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="175" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D175" t="s">
-        <v>98</v>
-      </c>
-      <c r="E175" t="s">
-        <v>157</v>
+        <v>63</v>
       </c>
       <c r="F175" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="G175" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="H175" t="s">
-        <v>307</v>
-      </c>
-      <c r="K175" t="s">
-        <v>308</v>
-      </c>
-      <c r="L175" t="s">
-        <v>199</v>
-      </c>
-      <c r="M175" t="s">
-        <v>200</v>
+        <v>302</v>
       </c>
     </row>
     <row r="176" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B176" t="s">
-        <v>55</v>
-      </c>
-      <c r="C176" t="s">
-        <v>309</v>
+        <v>73</v>
       </c>
     </row>
     <row r="177" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D177" t="s">
-        <v>63</v>
+        <v>98</v>
+      </c>
+      <c r="E177" t="s">
+        <v>157</v>
       </c>
       <c r="F177" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G177" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H177" t="s">
-        <v>304</v>
+        <v>305</v>
+      </c>
+      <c r="K177" t="s">
+        <v>306</v>
+      </c>
+      <c r="L177" t="s">
+        <v>199</v>
+      </c>
+      <c r="M177" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="178" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B178" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C178" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="179" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D179" t="s">
-        <v>98</v>
-      </c>
-      <c r="E179" t="s">
-        <v>244</v>
+        <v>63</v>
       </c>
       <c r="F179" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G179" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="H179" t="s">
-        <v>313</v>
-      </c>
-      <c r="K179" t="s">
-        <v>314</v>
-      </c>
-      <c r="L179" t="s">
-        <v>199</v>
-      </c>
-      <c r="M179" t="s">
-        <v>200</v>
+        <v>302</v>
       </c>
     </row>
     <row r="180" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B180" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="181" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B181" t="s">
-        <v>55</v>
-      </c>
-      <c r="C181" t="s">
-        <v>498</v>
+      <c r="D181" t="s">
+        <v>98</v>
+      </c>
+      <c r="E181" t="s">
+        <v>242</v>
+      </c>
+      <c r="F181" t="s">
+        <v>309</v>
+      </c>
+      <c r="G181" t="s">
+        <v>310</v>
+      </c>
+      <c r="H181" t="s">
+        <v>311</v>
+      </c>
+      <c r="K181" t="s">
+        <v>312</v>
+      </c>
+      <c r="L181" t="s">
+        <v>199</v>
+      </c>
+      <c r="M181" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="182" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B182" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="183" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B183" t="s">
+        <v>55</v>
+      </c>
+      <c r="C183" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="184" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B184" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="183" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D183" t="s">
+    <row r="185" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D185" t="s">
         <v>41</v>
       </c>
-      <c r="F183" t="s">
-        <v>315</v>
-      </c>
-      <c r="I183">
+      <c r="F185" t="s">
+        <v>313</v>
+      </c>
+      <c r="I185">
         <v>2</v>
-      </c>
-    </row>
-    <row r="184" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D184" t="s">
-        <v>156</v>
-      </c>
-      <c r="G184" t="s">
-        <v>316</v>
-      </c>
-      <c r="H184" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="185" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B185" t="s">
-        <v>55</v>
-      </c>
-      <c r="C185" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="186" spans="2:13" x14ac:dyDescent="0.35">
@@ -4175,314 +4181,311 @@
         <v>156</v>
       </c>
       <c r="G186" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="H186" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="187" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B187" t="s">
+        <v>55</v>
+      </c>
+      <c r="C187" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="188" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D188" t="s">
+        <v>156</v>
+      </c>
+      <c r="G188" t="s">
+        <v>316</v>
+      </c>
+      <c r="H188" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="189" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B189" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="188" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B188" t="s">
-        <v>55</v>
-      </c>
-      <c r="C188" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="189" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D189" t="s">
-        <v>156</v>
-      </c>
-      <c r="G189" t="s">
-        <v>320</v>
-      </c>
-      <c r="H189" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="190" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B190" t="s">
+        <v>55</v>
+      </c>
+      <c r="C190" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="191" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D191" t="s">
+        <v>156</v>
+      </c>
+      <c r="G191" t="s">
+        <v>318</v>
+      </c>
+      <c r="H191" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="192" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B192" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="191" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B191" t="s">
-        <v>55</v>
-      </c>
-      <c r="C191" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="192" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D192" t="s">
-        <v>156</v>
-      </c>
-      <c r="G192" t="s">
-        <v>323</v>
-      </c>
-      <c r="H192" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="193" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B193" t="s">
+        <v>55</v>
+      </c>
+      <c r="C193" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="194" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D194" t="s">
+        <v>156</v>
+      </c>
+      <c r="G194" t="s">
+        <v>321</v>
+      </c>
+      <c r="H194" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="195" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B195" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="194" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B194" t="s">
-        <v>55</v>
-      </c>
-      <c r="C194" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="195" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="D195" t="s">
-        <v>156</v>
-      </c>
-      <c r="G195" t="s">
-        <v>326</v>
-      </c>
-      <c r="H195" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="196" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B196" t="s">
+        <v>55</v>
+      </c>
+      <c r="C196" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="197" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D197" t="s">
+        <v>156</v>
+      </c>
+      <c r="G197" t="s">
+        <v>324</v>
+      </c>
+      <c r="H197" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="198" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B198" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="197" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B197" t="s">
-        <v>55</v>
-      </c>
-      <c r="C197" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="198" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="D198" t="s">
-        <v>156</v>
-      </c>
-      <c r="G198" t="s">
-        <v>329</v>
-      </c>
-      <c r="H198" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="199" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B199" t="s">
+        <v>55</v>
+      </c>
+      <c r="C199" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="200" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D200" t="s">
+        <v>156</v>
+      </c>
+      <c r="G200" t="s">
+        <v>327</v>
+      </c>
+      <c r="H200" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="201" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B201" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="200" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B200" t="s">
-        <v>55</v>
-      </c>
-      <c r="C200" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="201" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="D201" t="s">
-        <v>156</v>
-      </c>
-      <c r="G201" t="s">
-        <v>332</v>
-      </c>
-      <c r="H201" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="202" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B202" t="s">
+        <v>55</v>
+      </c>
+      <c r="C202" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="203" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D203" t="s">
+        <v>156</v>
+      </c>
+      <c r="G203" t="s">
+        <v>330</v>
+      </c>
+      <c r="H203" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="204" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B204" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="203" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B203" t="s">
-        <v>55</v>
-      </c>
-      <c r="C203" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="204" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="D204" t="s">
-        <v>156</v>
-      </c>
-      <c r="G204" t="s">
-        <v>335</v>
-      </c>
-      <c r="H204" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="205" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B205" t="s">
+        <v>55</v>
+      </c>
+      <c r="C205" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="206" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D206" t="s">
+        <v>156</v>
+      </c>
+      <c r="G206" t="s">
+        <v>333</v>
+      </c>
+      <c r="H206" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="207" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B207" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="206" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B206" t="s">
-        <v>55</v>
-      </c>
-      <c r="C206" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="207" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="D207" t="s">
-        <v>156</v>
-      </c>
-      <c r="G207" t="s">
-        <v>492</v>
-      </c>
-      <c r="H207" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="208" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B208" t="s">
+        <v>55</v>
+      </c>
+      <c r="C208" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="209" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D209" t="s">
+        <v>156</v>
+      </c>
+      <c r="G209" t="s">
+        <v>490</v>
+      </c>
+      <c r="H209" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="210" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B210" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="209" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B209" t="s">
-        <v>55</v>
-      </c>
-      <c r="C209" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="210" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D210" t="s">
-        <v>156</v>
-      </c>
-      <c r="G210" t="s">
-        <v>338</v>
-      </c>
-      <c r="H210" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="211" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B211" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C211" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="212" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D212" t="s">
+        <v>156</v>
+      </c>
+      <c r="G212" t="s">
+        <v>336</v>
+      </c>
+      <c r="H212" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="213" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B213" t="s">
-        <v>55</v>
-      </c>
-      <c r="C213" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="214" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D214" t="s">
-        <v>156</v>
-      </c>
-      <c r="G214" t="s">
-        <v>500</v>
-      </c>
-      <c r="H214" t="s">
-        <v>501</v>
+        <v>73</v>
       </c>
     </row>
     <row r="215" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B215" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C215" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="216" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B216" t="s">
-        <v>49</v>
+      <c r="D216" t="s">
+        <v>156</v>
+      </c>
+      <c r="G216" t="s">
+        <v>497</v>
+      </c>
+      <c r="H216" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="217" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B217" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="218" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B218" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="219" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B219" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="220" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B220" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="219" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D219" t="s">
-        <v>78</v>
-      </c>
-      <c r="F219" t="s">
-        <v>340</v>
-      </c>
-      <c r="G219" t="s">
-        <v>341</v>
-      </c>
-      <c r="H219" t="s">
-        <v>342</v>
-      </c>
-      <c r="K219" t="s">
-        <v>343</v>
-      </c>
-      <c r="L219" t="s">
-        <v>344</v>
-      </c>
-      <c r="M219" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="220" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D220" t="s">
-        <v>78</v>
-      </c>
-      <c r="F220" t="s">
-        <v>346</v>
-      </c>
-      <c r="G220" t="s">
-        <v>347</v>
-      </c>
-      <c r="H220" t="s">
-        <v>348</v>
-      </c>
-      <c r="K220" t="s">
-        <v>349</v>
-      </c>
-      <c r="L220" t="s">
-        <v>350</v>
-      </c>
-      <c r="M220" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="221" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D221" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="F221" t="s">
-        <v>352</v>
-      </c>
-      <c r="I221" t="s">
-        <v>353</v>
+        <v>338</v>
+      </c>
+      <c r="G221" t="s">
+        <v>339</v>
+      </c>
+      <c r="H221" t="s">
+        <v>340</v>
+      </c>
+      <c r="K221" t="s">
+        <v>341</v>
+      </c>
+      <c r="L221" t="s">
+        <v>342</v>
+      </c>
+      <c r="M221" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="222" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D222" t="s">
-        <v>156</v>
+        <v>78</v>
+      </c>
+      <c r="F222" t="s">
+        <v>344</v>
       </c>
       <c r="G222" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="H222" t="s">
-        <v>355</v>
+        <v>346</v>
+      </c>
+      <c r="K222" t="s">
+        <v>347</v>
+      </c>
+      <c r="L222" t="s">
+        <v>348</v>
+      </c>
+      <c r="M222" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="223" spans="2:13" x14ac:dyDescent="0.35">
@@ -4490,105 +4493,93 @@
         <v>41</v>
       </c>
       <c r="F223" t="s">
-        <v>315</v>
-      </c>
-      <c r="I223">
+        <v>350</v>
+      </c>
+      <c r="I223" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="224" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D224" t="s">
+        <v>156</v>
+      </c>
+      <c r="G224" t="s">
+        <v>352</v>
+      </c>
+      <c r="H224" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="225" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D225" t="s">
+        <v>41</v>
+      </c>
+      <c r="F225" t="s">
+        <v>313</v>
+      </c>
+      <c r="I225">
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B224" t="s">
+    <row r="226" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B226" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="225" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B225" t="s">
+    <row r="227" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B227" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="226" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D226" t="s">
-        <v>41</v>
-      </c>
-      <c r="F226" t="s">
-        <v>356</v>
-      </c>
-      <c r="I226" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="227" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D227" t="s">
-        <v>46</v>
-      </c>
-      <c r="F227" t="s">
-        <v>356</v>
-      </c>
-      <c r="G227" t="s">
-        <v>358</v>
-      </c>
-      <c r="H227" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q227" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="228" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D228" t="s">
-        <v>360</v>
+        <v>41</v>
       </c>
       <c r="F228" t="s">
-        <v>361</v>
-      </c>
-      <c r="G228" t="s">
-        <v>362</v>
-      </c>
-      <c r="H228" t="s">
-        <v>363</v>
-      </c>
-      <c r="K228" t="s">
-        <v>364</v>
-      </c>
-      <c r="L228" t="s">
-        <v>199</v>
-      </c>
-      <c r="M228" t="s">
-        <v>200</v>
+        <v>354</v>
+      </c>
+      <c r="I228" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="229" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D229" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F229" t="s">
-        <v>365</v>
-      </c>
-      <c r="I229" t="s">
-        <v>366</v>
+        <v>354</v>
+      </c>
+      <c r="G229" t="s">
+        <v>356</v>
+      </c>
+      <c r="H229" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q229" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D230" t="s">
-        <v>78</v>
+        <v>358</v>
       </c>
       <c r="F230" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="G230" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="H230" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="K230" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="L230" t="s">
-        <v>371</v>
+        <v>199</v>
       </c>
       <c r="M230" t="s">
-        <v>372</v>
+        <v>200</v>
       </c>
     </row>
     <row r="231" spans="2:17" x14ac:dyDescent="0.35">
@@ -4596,61 +4587,70 @@
         <v>41</v>
       </c>
       <c r="F231" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="I231" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
     </row>
     <row r="232" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D232" t="s">
+        <v>78</v>
+      </c>
+      <c r="F232" t="s">
+        <v>365</v>
+      </c>
+      <c r="G232" t="s">
+        <v>366</v>
+      </c>
+      <c r="H232" t="s">
+        <v>367</v>
+      </c>
+      <c r="K232" t="s">
+        <v>368</v>
+      </c>
+      <c r="L232" t="s">
+        <v>369</v>
+      </c>
+      <c r="M232" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="233" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D233" t="s">
+        <v>41</v>
+      </c>
+      <c r="F233" t="s">
+        <v>371</v>
+      </c>
+      <c r="I233" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="234" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D234" t="s">
         <v>156</v>
       </c>
-      <c r="G232" t="s">
-        <v>375</v>
-      </c>
-      <c r="H232" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="233" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B233" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="234" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B234" t="s">
-        <v>73</v>
+      <c r="G234" t="s">
+        <v>373</v>
+      </c>
+      <c r="H234" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="235" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B235" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="236" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D236" t="s">
-        <v>106</v>
-      </c>
-      <c r="E236" t="s">
-        <v>377</v>
-      </c>
-      <c r="F236" t="s">
-        <v>378</v>
-      </c>
-      <c r="G236" t="s">
-        <v>379</v>
-      </c>
-      <c r="H236" t="s">
-        <v>380</v>
+      <c r="B236" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="237" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B237" t="s">
-        <v>55</v>
-      </c>
-      <c r="C237" t="s">
-        <v>381</v>
+        <v>40</v>
       </c>
     </row>
     <row r="238" spans="2:17" x14ac:dyDescent="0.35">
@@ -4658,67 +4658,92 @@
         <v>106</v>
       </c>
       <c r="E238" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="F238" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="G238" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="H238" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="239" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B239" t="s">
-        <v>73</v>
+        <v>55</v>
+      </c>
+      <c r="C239" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="240" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B240" t="s">
-        <v>49</v>
+      <c r="D240" t="s">
+        <v>106</v>
+      </c>
+      <c r="E240" t="s">
+        <v>380</v>
+      </c>
+      <c r="F240" t="s">
+        <v>381</v>
+      </c>
+      <c r="G240" t="s">
+        <v>382</v>
+      </c>
+      <c r="H240" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="241" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B241" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="242" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B242" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="243" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B243" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="244" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B244" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="243" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D243" t="s">
+    <row r="245" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D245" t="s">
         <v>156</v>
       </c>
-      <c r="G243" t="s">
-        <v>386</v>
-      </c>
-      <c r="H243" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="244" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D244" t="s">
+      <c r="G245" t="s">
+        <v>384</v>
+      </c>
+      <c r="H245" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="246" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D246" t="s">
         <v>41</v>
       </c>
-      <c r="F244" t="s">
-        <v>315</v>
-      </c>
-      <c r="I244">
+      <c r="F246" t="s">
+        <v>313</v>
+      </c>
+      <c r="I246">
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B245" t="s">
+    <row r="247" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B247" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="246" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B246" t="s">
+    <row r="248" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B248" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4741,10 +4766,10 @@
   <sheetData>
     <row r="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4753,7 +4778,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -4765,10 +4790,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -4780,10 +4805,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -4795,10 +4820,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -4810,40 +4835,40 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D5" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B6" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B7" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D7" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -4854,55 +4879,55 @@
         <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D8" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B9" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D9" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B10" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D10" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B11" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D11" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -4914,475 +4939,475 @@
         <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D12" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B13" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D13" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E13" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B14" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B15" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D15" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B16" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D16" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E16" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B17" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D17" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E17" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B18" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D18" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B19" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D19" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B20" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D20" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B21" t="str">
         <f>"6"</f>
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D21" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B22" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D22" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B23" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D23" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B24" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D24" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B25" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D25" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B26" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D26" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B27" t="str">
         <f>"6"</f>
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D27" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B28" t="str">
         <f>"7"</f>
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D28" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E28" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B29" t="str">
         <f>"8"</f>
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D29" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E29" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B30" t="str">
         <f>"9"</f>
         <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D30" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E30" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B31" t="str">
         <f>"10"</f>
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D31" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E31" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B32" t="str">
         <f>"11"</f>
         <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D32" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E32" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B33" t="str">
         <f>"12"</f>
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D33" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E33" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B34" t="str">
         <f>"13"</f>
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D34" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E34" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B35" t="str">
         <f>"14"</f>
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D35" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E35" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B36" t="str">
         <f>"15"</f>
         <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D36" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E36" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B37" t="str">
         <f>"16"</f>
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D37" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E37" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B38" t="str">
         <f>"17"</f>
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D38" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E38" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B39" t="str">
         <f>"18"</f>
         <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D39" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E39" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B40" t="str">
         <f>"77"</f>
         <v>77</v>
       </c>
       <c r="C40" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D40" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -5394,10 +5419,10 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D41" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
@@ -5409,10 +5434,10 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D42" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -5424,10 +5449,10 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D43" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -5439,10 +5464,10 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D44" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -5454,10 +5479,10 @@
         <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D45" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
@@ -5469,10 +5494,10 @@
         <v>99</v>
       </c>
       <c r="C46" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D46" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -5484,10 +5509,10 @@
         <v>99</v>
       </c>
       <c r="C47" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D47" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
@@ -5499,10 +5524,10 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D48" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -5514,10 +5539,10 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D49" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -5529,10 +5554,10 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D50" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -5544,10 +5569,10 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D51" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -5559,10 +5584,10 @@
         <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D52" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -5574,10 +5599,10 @@
         <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D53" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -5589,10 +5614,10 @@
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D54" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="78" spans="2:2" x14ac:dyDescent="0.35">
@@ -5883,7 +5908,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>29</v>
@@ -5891,10 +5916,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -5916,16 +5941,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
@@ -5933,13 +5958,13 @@
         <v>51</v>
       </c>
       <c r="B2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="C2" t="s">
-        <v>467</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="87" x14ac:dyDescent="0.35">
@@ -5947,13 +5972,13 @@
         <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C3" t="s">
+        <v>465</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -5975,16 +6000,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>24</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -5992,13 +6017,13 @@
         <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>
@@ -6025,15 +6050,15 @@
         <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B2" t="s">
         <v>106</v>
@@ -6042,7 +6067,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -6058,7 +6083,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B4" t="s">
         <v>78</v>
@@ -6102,10 +6127,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
@@ -6168,7 +6193,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B14" t="s">
         <v>98</v>
@@ -6190,7 +6215,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B16" t="s">
         <v>46</v>
@@ -6201,7 +6226,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B17" t="s">
         <v>98</v>
@@ -6212,7 +6237,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B18" t="s">
         <v>98</v>
@@ -6245,7 +6270,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B21" t="s">
         <v>106</v>
@@ -6256,7 +6281,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s">
         <v>98</v>
@@ -6267,10 +6292,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B23" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C23" t="b">
         <v>0</v>
@@ -6278,7 +6303,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
@@ -6333,7 +6358,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B29" t="s">
         <v>41</v>
@@ -6344,7 +6369,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
@@ -6355,7 +6380,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s">
         <v>98</v>
@@ -6366,7 +6391,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B32" t="s">
         <v>98</v>
@@ -6377,7 +6402,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s">
         <v>63</v>
@@ -6421,7 +6446,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B37" t="s">
         <v>78</v>
@@ -6432,7 +6457,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B38" t="s">
         <v>41</v>
@@ -6443,7 +6468,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B39" t="s">
         <v>63</v>
@@ -6454,7 +6479,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B40" t="s">
         <v>63</v>
@@ -6476,7 +6501,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B42" t="s">
         <v>98</v>
@@ -6487,7 +6512,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B43" t="s">
         <v>98</v>
@@ -6498,7 +6523,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>63</v>
@@ -6509,7 +6534,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B45" t="s">
         <v>78</v>
@@ -6520,7 +6545,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B46" t="s">
         <v>78</v>
@@ -6575,7 +6600,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B51" t="s">
         <v>98</v>
@@ -6707,7 +6732,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B63" t="s">
         <v>63</v>
@@ -6729,7 +6754,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B65" t="s">
         <v>98</v>
@@ -6740,7 +6765,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B66" t="s">
         <v>98</v>
@@ -6751,7 +6776,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B67" t="s">
         <v>98</v>
@@ -6762,7 +6787,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B68" t="s">
         <v>98</v>
@@ -6773,10 +6798,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C69" t="b">
         <v>0</v>
@@ -6784,7 +6809,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B70" t="s">
         <v>82</v>
@@ -6795,7 +6820,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B71" t="s">
         <v>82</v>
@@ -6806,7 +6831,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B72" t="s">
         <v>82</v>
@@ -6817,7 +6842,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B73" t="s">
         <v>63</v>
@@ -6828,7 +6853,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B74" t="s">
         <v>63</v>
@@ -6839,7 +6864,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B75" t="s">
         <v>63</v>
@@ -6861,7 +6886,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B77" t="s">
         <v>98</v>
@@ -6875,7 +6900,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B79" s="13" t="s">
         <v>98</v>
@@ -6884,12 +6909,12 @@
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B80" s="13" t="s">
         <v>98</v>
@@ -6900,7 +6925,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B81" s="13" t="s">
         <v>98</v>
@@ -6909,12 +6934,12 @@
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B82" s="13" t="s">
         <v>98</v>
@@ -6923,12 +6948,12 @@
         <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B83" t="s">
         <v>46</v>
@@ -6937,7 +6962,7 @@
         <v>0</v>
       </c>
       <c r="D83" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
@@ -6945,7 +6970,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B85" s="13" t="s">
         <v>98</v>
@@ -6956,7 +6981,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B86" s="13" t="s">
         <v>98</v>

--- a/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
+++ b/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\MADtrials2\MADtrial\app\config\tables\MADTRIAL_INC\Forms\MADTRIAL_INC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF95A3D9-47CF-49C9-8831-65CA056B2507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91BFE49-D6A7-48FB-B3FF-272D35DECD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="508">
   <si>
     <t>setting_name</t>
   </si>
@@ -1538,12 +1538,6 @@
     <t>adate.diffInDays(data("DOB"),data("DATINC"))</t>
   </si>
   <si>
-    <t>data('PODEVAC')=='2'|| data('PODEINC')=='2'  || data('JAINC') == '1' || data('BRACOCRI') &lt;110 || data('TEMPERATURA')&gt;37.9 || data('VENAOVAS') == '2' ||  data('VENAOVAS2') == '2' || (data('SARVAC') == '1' &amp;&amp;  data('SARVAC2') != '2')||data('SARVAC2') == '1'</t>
-  </si>
-  <si>
-    <t>data('SARVAC') == '1' &amp;&amp; calculates.childAGE &lt;453</t>
-  </si>
-  <si>
     <t>The child is not yet 15 months and has already received MV1</t>
   </si>
   <si>
@@ -1563,6 +1557,24 @@
   </si>
   <si>
     <t>A mãe/tutor confirmou que a criança não recebeu o primero deose de vacina do sarampo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data('PODEVAC')=='2'|| data('PODEINC')=='2'  || data('JAINC') == '1' || data('BRACOCRI') &lt;110 || data('TEMPERATURA')&gt;37.9 || data('VENAOVAS') == '2' ||  data('VENAOVAS2') == '2' || (data('SARVAC') == '1' &amp;&amp;  data('SARVAC2') != '2')||data('SARVAC2') == '1' </t>
+  </si>
+  <si>
+    <t>The child is too old</t>
+  </si>
+  <si>
+    <t>A crianca tem idade maior de 5 anos</t>
+  </si>
+  <si>
+    <t>data('SARVAC') == '1' &amp;&amp; calculates.childAGE &lt;'453'</t>
+  </si>
+  <si>
+    <t>calculates.childAGE &gt;'1826'</t>
+  </si>
+  <si>
+    <t>|| calculates.childAGE &gt;'1826'</t>
   </si>
 </sst>
 </file>
@@ -2086,7 +2098,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:S248"/>
+  <dimension ref="A1:Y255"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
@@ -2175,10 +2187,10 @@
         <v>492</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="S3" s="14" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
@@ -3314,10 +3326,10 @@
         <v>207</v>
       </c>
       <c r="G107" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H107" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="K107" t="s">
         <v>209</v>
@@ -3339,7 +3351,7 @@
         <v>492</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="110" spans="2:13" x14ac:dyDescent="0.35">
@@ -4068,7 +4080,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="177" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="177" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D177" t="s">
         <v>98</v>
       </c>
@@ -4094,7 +4106,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="178" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="178" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B178" t="s">
         <v>55</v>
       </c>
@@ -4102,7 +4114,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="179" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="179" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D179" t="s">
         <v>63</v>
       </c>
@@ -4116,12 +4128,12 @@
         <v>302</v>
       </c>
     </row>
-    <row r="180" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="180" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B180" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="181" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="181" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D181" t="s">
         <v>98</v>
       </c>
@@ -4147,25 +4159,28 @@
         <v>200</v>
       </c>
     </row>
-    <row r="182" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="182" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B182" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="183" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="183" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B183" t="s">
         <v>55</v>
       </c>
       <c r="C183" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="184" spans="2:13" x14ac:dyDescent="0.35">
+        <v>502</v>
+      </c>
+      <c r="S183" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="184" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B184" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="185" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="185" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D185" t="s">
         <v>41</v>
       </c>
@@ -4176,7 +4191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="186" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D186" t="s">
         <v>156</v>
       </c>
@@ -4187,7 +4202,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="187" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="187" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B187" t="s">
         <v>55</v>
       </c>
@@ -4195,7 +4210,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="188" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="188" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D188" t="s">
         <v>156</v>
       </c>
@@ -4206,12 +4221,12 @@
         <v>317</v>
       </c>
     </row>
-    <row r="189" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="189" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B189" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="190" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="190" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B190" t="s">
         <v>55</v>
       </c>
@@ -4219,7 +4234,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="191" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="191" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D191" t="s">
         <v>156</v>
       </c>
@@ -4230,7 +4245,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="192" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="192" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B192" t="s">
         <v>73</v>
       </c>
@@ -4363,7 +4378,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="209" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="209" spans="2:25" x14ac:dyDescent="0.35">
       <c r="D209" t="s">
         <v>156</v>
       </c>
@@ -4374,12 +4389,12 @@
         <v>491</v>
       </c>
     </row>
-    <row r="210" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="210" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B210" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="211" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="211" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B211" t="s">
         <v>55</v>
       </c>
@@ -4387,7 +4402,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="212" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="212" spans="2:25" x14ac:dyDescent="0.35">
       <c r="D212" t="s">
         <v>156</v>
       </c>
@@ -4398,132 +4413,67 @@
         <v>337</v>
       </c>
     </row>
-    <row r="213" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="213" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B213" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="215" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="215" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B215" t="s">
         <v>55</v>
       </c>
       <c r="C215" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="216" spans="2:13" x14ac:dyDescent="0.35">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="216" spans="2:25" x14ac:dyDescent="0.35">
       <c r="D216" t="s">
         <v>156</v>
       </c>
       <c r="G216" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="H216" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="217" spans="2:13" x14ac:dyDescent="0.35">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="217" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B217" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="218" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B218" t="s">
+    <row r="218" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="S218" t="s">
+        <v>55</v>
+      </c>
+      <c r="T218" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="219" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="U219" t="s">
+        <v>156</v>
+      </c>
+      <c r="X219" t="s">
+        <v>503</v>
+      </c>
+      <c r="Y219" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="220" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="S220" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="225" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B225" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="219" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B219" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="220" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B220" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="221" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D221" t="s">
-        <v>78</v>
-      </c>
-      <c r="F221" t="s">
-        <v>338</v>
-      </c>
-      <c r="G221" t="s">
-        <v>339</v>
-      </c>
-      <c r="H221" t="s">
-        <v>340</v>
-      </c>
-      <c r="K221" t="s">
-        <v>341</v>
-      </c>
-      <c r="L221" t="s">
-        <v>342</v>
-      </c>
-      <c r="M221" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="222" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D222" t="s">
-        <v>78</v>
-      </c>
-      <c r="F222" t="s">
-        <v>344</v>
-      </c>
-      <c r="G222" t="s">
-        <v>345</v>
-      </c>
-      <c r="H222" t="s">
-        <v>346</v>
-      </c>
-      <c r="K222" t="s">
-        <v>347</v>
-      </c>
-      <c r="L222" t="s">
-        <v>348</v>
-      </c>
-      <c r="M222" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="223" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D223" t="s">
-        <v>41</v>
-      </c>
-      <c r="F223" t="s">
-        <v>350</v>
-      </c>
-      <c r="I223" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="224" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D224" t="s">
-        <v>156</v>
-      </c>
-      <c r="G224" t="s">
-        <v>352</v>
-      </c>
-      <c r="H224" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="225" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D225" t="s">
-        <v>41</v>
-      </c>
-      <c r="F225" t="s">
-        <v>313</v>
-      </c>
-      <c r="I225">
-        <v>1</v>
       </c>
     </row>
     <row r="226" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B226" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
     </row>
     <row r="227" spans="2:17" x14ac:dyDescent="0.35">
@@ -4533,171 +4483,198 @@
     </row>
     <row r="228" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D228" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="F228" t="s">
-        <v>354</v>
-      </c>
-      <c r="I228" t="s">
-        <v>355</v>
+        <v>338</v>
+      </c>
+      <c r="G228" t="s">
+        <v>339</v>
+      </c>
+      <c r="H228" t="s">
+        <v>340</v>
+      </c>
+      <c r="K228" t="s">
+        <v>341</v>
+      </c>
+      <c r="L228" t="s">
+        <v>342</v>
+      </c>
+      <c r="M228" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="229" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D229" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="F229" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="G229" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="H229" t="s">
-        <v>357</v>
-      </c>
-      <c r="Q229" t="b">
-        <v>0</v>
+        <v>346</v>
+      </c>
+      <c r="K229" t="s">
+        <v>347</v>
+      </c>
+      <c r="L229" t="s">
+        <v>348</v>
+      </c>
+      <c r="M229" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="230" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D230" t="s">
-        <v>358</v>
+        <v>41</v>
       </c>
       <c r="F230" t="s">
-        <v>359</v>
-      </c>
-      <c r="G230" t="s">
-        <v>360</v>
-      </c>
-      <c r="H230" t="s">
-        <v>361</v>
-      </c>
-      <c r="K230" t="s">
-        <v>362</v>
-      </c>
-      <c r="L230" t="s">
-        <v>199</v>
-      </c>
-      <c r="M230" t="s">
-        <v>200</v>
+        <v>350</v>
+      </c>
+      <c r="I230" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="231" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D231" t="s">
-        <v>41</v>
-      </c>
-      <c r="F231" t="s">
-        <v>363</v>
-      </c>
-      <c r="I231" t="s">
-        <v>364</v>
+        <v>156</v>
+      </c>
+      <c r="G231" t="s">
+        <v>352</v>
+      </c>
+      <c r="H231" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="232" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D232" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="F232" t="s">
-        <v>365</v>
-      </c>
-      <c r="G232" t="s">
-        <v>366</v>
-      </c>
-      <c r="H232" t="s">
-        <v>367</v>
-      </c>
-      <c r="K232" t="s">
-        <v>368</v>
-      </c>
-      <c r="L232" t="s">
-        <v>369</v>
-      </c>
-      <c r="M232" t="s">
-        <v>370</v>
+        <v>313</v>
+      </c>
+      <c r="I232">
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D233" t="s">
+      <c r="B233" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="234" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B234" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="235" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D235" t="s">
         <v>41</v>
       </c>
-      <c r="F233" t="s">
-        <v>371</v>
-      </c>
-      <c r="I233" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="234" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D234" t="s">
-        <v>156</v>
-      </c>
-      <c r="G234" t="s">
-        <v>373</v>
-      </c>
-      <c r="H234" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="235" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B235" t="s">
-        <v>49</v>
+      <c r="F235" t="s">
+        <v>354</v>
+      </c>
+      <c r="I235" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="236" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B236" t="s">
-        <v>73</v>
+      <c r="D236" t="s">
+        <v>46</v>
+      </c>
+      <c r="F236" t="s">
+        <v>354</v>
+      </c>
+      <c r="G236" t="s">
+        <v>356</v>
+      </c>
+      <c r="H236" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q236" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B237" t="s">
-        <v>40</v>
+      <c r="D237" t="s">
+        <v>358</v>
+      </c>
+      <c r="F237" t="s">
+        <v>359</v>
+      </c>
+      <c r="G237" t="s">
+        <v>360</v>
+      </c>
+      <c r="H237" t="s">
+        <v>361</v>
+      </c>
+      <c r="K237" t="s">
+        <v>362</v>
+      </c>
+      <c r="L237" t="s">
+        <v>199</v>
+      </c>
+      <c r="M237" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="238" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D238" t="s">
-        <v>106</v>
-      </c>
-      <c r="E238" t="s">
-        <v>375</v>
+        <v>41</v>
       </c>
       <c r="F238" t="s">
-        <v>376</v>
-      </c>
-      <c r="G238" t="s">
-        <v>377</v>
-      </c>
-      <c r="H238" t="s">
-        <v>378</v>
+        <v>363</v>
+      </c>
+      <c r="I238" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="239" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B239" t="s">
-        <v>55</v>
-      </c>
-      <c r="C239" t="s">
-        <v>379</v>
+      <c r="D239" t="s">
+        <v>78</v>
+      </c>
+      <c r="F239" t="s">
+        <v>365</v>
+      </c>
+      <c r="G239" t="s">
+        <v>366</v>
+      </c>
+      <c r="H239" t="s">
+        <v>367</v>
+      </c>
+      <c r="K239" t="s">
+        <v>368</v>
+      </c>
+      <c r="L239" t="s">
+        <v>369</v>
+      </c>
+      <c r="M239" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="240" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D240" t="s">
-        <v>106</v>
-      </c>
-      <c r="E240" t="s">
-        <v>380</v>
+        <v>41</v>
       </c>
       <c r="F240" t="s">
-        <v>381</v>
-      </c>
-      <c r="G240" t="s">
-        <v>382</v>
-      </c>
-      <c r="H240" t="s">
-        <v>383</v>
+        <v>371</v>
+      </c>
+      <c r="I240" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="241" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B241" t="s">
-        <v>73</v>
+      <c r="D241" t="s">
+        <v>156</v>
+      </c>
+      <c r="G241" t="s">
+        <v>373</v>
+      </c>
+      <c r="H241" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="242" spans="2:9" x14ac:dyDescent="0.35">
@@ -4707,7 +4684,7 @@
     </row>
     <row r="243" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B243" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="244" spans="2:9" x14ac:dyDescent="0.35">
@@ -4717,33 +4694,95 @@
     </row>
     <row r="245" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D245" t="s">
-        <v>156</v>
+        <v>106</v>
+      </c>
+      <c r="E245" t="s">
+        <v>375</v>
+      </c>
+      <c r="F245" t="s">
+        <v>376</v>
       </c>
       <c r="G245" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="H245" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="246" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D246" t="s">
-        <v>41</v>
-      </c>
-      <c r="F246" t="s">
-        <v>313</v>
-      </c>
-      <c r="I246">
-        <v>2</v>
+      <c r="B246" t="s">
+        <v>55</v>
+      </c>
+      <c r="C246" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="247" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B247" t="s">
-        <v>49</v>
+      <c r="D247" t="s">
+        <v>106</v>
+      </c>
+      <c r="E247" t="s">
+        <v>380</v>
+      </c>
+      <c r="F247" t="s">
+        <v>381</v>
+      </c>
+      <c r="G247" t="s">
+        <v>382</v>
+      </c>
+      <c r="H247" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="248" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B248" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="249" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B249" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="250" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B250" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="251" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B251" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="252" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D252" t="s">
+        <v>156</v>
+      </c>
+      <c r="G252" t="s">
+        <v>384</v>
+      </c>
+      <c r="H252" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="253" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D253" t="s">
+        <v>41</v>
+      </c>
+      <c r="F253" t="s">
+        <v>313</v>
+      </c>
+      <c r="I253">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="254" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B254" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="255" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B255" t="s">
         <v>73</v>
       </c>
     </row>

--- a/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
+++ b/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
@@ -1,29 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\MAD2_3\MADtrial\app\config\tables\MADTRIAL_INC\Forms\MADTRIAL_INC\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243D551D-CC65-4D4E-898A-E7CDCDD81F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="survey" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inc" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="choices" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="calculates" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="queries" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="prompt_types" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="model" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="settings" sheetId="1" r:id="rId1"/>
+    <sheet name="survey" sheetId="2" r:id="rId2"/>
+    <sheet name="inc" sheetId="3" r:id="rId3"/>
+    <sheet name="choices" sheetId="4" r:id="rId4"/>
+    <sheet name="calculates" sheetId="5" r:id="rId5"/>
+    <sheet name="queries" sheetId="6" r:id="rId6"/>
+    <sheet name="prompt_types" sheetId="7" r:id="rId7"/>
+    <sheet name="model" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="509">
   <si>
     <t>setting_name</t>
   </si>
@@ -58,10 +75,10 @@
     <t>survey</t>
   </si>
   <si>
-    <t xml:space="preserve">MADtrial - Inclusion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MADtrial - Inclusão</t>
+    <t>MADtrial - Inclusion</t>
+  </si>
+  <si>
+    <t>MADtrial - Inclusão</t>
   </si>
   <si>
     <t>default</t>
@@ -118,7 +135,7 @@
     <t>choice_filter</t>
   </si>
   <si>
-    <t xml:space="preserve">do section inc</t>
+    <t>do section inc</t>
   </si>
   <si>
     <t>constraint</t>
@@ -148,16 +165,16 @@
     <t>comment</t>
   </si>
   <si>
-    <t xml:space="preserve">begin screen</t>
+    <t>begin screen</t>
   </si>
   <si>
     <t xml:space="preserve">if </t>
   </si>
   <si>
-    <t xml:space="preserve">data('DATINC') == null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">added by Ane 2025-07-24 - to avoid overwriting information</t>
+    <t>data('DATINC') == null</t>
+  </si>
+  <si>
+    <t>added by Ane 2025-07-24 - to avoid overwriting information</t>
   </si>
   <si>
     <t>assign</t>
@@ -175,19 +192,19 @@
     <t>adate.today()</t>
   </si>
   <si>
-    <t xml:space="preserve">end if</t>
+    <t>end if</t>
   </si>
   <si>
     <t>adate</t>
   </si>
   <si>
-    <t xml:space="preserve">Date of inclusion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data de inclusão</t>
-  </si>
-  <si>
-    <t xml:space="preserve">end screen</t>
+    <t>Date of inclusion</t>
+  </si>
+  <si>
+    <t>Data de inclusão</t>
+  </si>
+  <si>
+    <t>end screen</t>
   </si>
   <si>
     <t>select_one_dropdown</t>
@@ -208,7 +225,7 @@
     <t>if</t>
   </si>
   <si>
-    <t xml:space="preserve">data('BAIRRO') == 77</t>
+    <t>data('BAIRRO') == 77</t>
   </si>
   <si>
     <t>tabz_csv</t>
@@ -217,16 +234,16 @@
     <t>TABZ</t>
   </si>
   <si>
-    <t xml:space="preserve">Neighborhood outside project area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bairro fora da área do projeto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choice_item.BAIRRONR === data('BAIRRO')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('TABZ') == 7777</t>
+    <t>Neighborhood outside project area</t>
+  </si>
+  <si>
+    <t>Bairro fora da área do projeto</t>
+  </si>
+  <si>
+    <t>choice_item.BAIRRONR === data('BAIRRO')</t>
+  </si>
+  <si>
+    <t>data('TABZ') == 7777</t>
   </si>
   <si>
     <t>text</t>
@@ -235,10 +252,10 @@
     <t>OUBAIRRO</t>
   </si>
   <si>
-    <t xml:space="preserve">What neighborhood?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Que bairro?</t>
+    <t>What neighborhood?</t>
+  </si>
+  <si>
+    <t>Que bairro?</t>
   </si>
   <si>
     <t>else</t>
@@ -247,13 +264,13 @@
     <t>CAMOONDE</t>
   </si>
   <si>
-    <t xml:space="preserve">Pleace describe how to find the house</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Por favor, descreva como encontrar a casa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CAMOONDE') != null || data('TABZ') == 7777 || data('CAMO') != 9999</t>
+    <t>Pleace describe how to find the house</t>
+  </si>
+  <si>
+    <t>Por favor, descreva como encontrar a casa</t>
+  </si>
+  <si>
+    <t>data('CAMOONDE') != null || data('TABZ') == 7777 || data('CAMO') != 9999</t>
   </si>
   <si>
     <t>OBS</t>
@@ -274,13 +291,13 @@
     <t>integer</t>
   </si>
   <si>
-    <t xml:space="preserve">House number (camo)</t>
+    <t>House number (camo)</t>
   </si>
   <si>
     <t>Camo</t>
   </si>
   <si>
-    <t xml:space="preserve">data('CAMO') != null || data('CAMOONDE') != null</t>
+    <t>data('CAMO') != null || data('CAMOONDE') != null</t>
   </si>
   <si>
     <t>select_multiple</t>
@@ -292,7 +309,7 @@
     <t>camons</t>
   </si>
   <si>
-    <t xml:space="preserve">data('camons') !=null</t>
+    <t>data('camons') !=null</t>
   </si>
   <si>
     <t>Where?</t>
@@ -304,13 +321,13 @@
     <t>CNO</t>
   </si>
   <si>
-    <t xml:space="preserve">data('BAIRRO') == 77 || freebase.characters(data('CNO')) == 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be 5 digits long:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve ter 5 dígitos:</t>
+    <t>data('BAIRRO') == 77 || freebase.characters(data('CNO')) == 5</t>
+  </si>
+  <si>
+    <t>Must be 5 digits long:</t>
+  </si>
+  <si>
+    <t>Deve ter 5 dígitos:</t>
   </si>
   <si>
     <t>number</t>
@@ -319,16 +336,16 @@
     <t>cnons</t>
   </si>
   <si>
-    <t xml:space="preserve">data('cnons') != null</t>
+    <t>data('cnons') != null</t>
   </si>
   <si>
     <t>NOMECRI</t>
   </si>
   <si>
-    <t xml:space="preserve">Child's name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome de criança</t>
+    <t>Child's name</t>
+  </si>
+  <si>
+    <t>Nome de criança</t>
   </si>
   <si>
     <t>select_one</t>
@@ -340,19 +357,19 @@
     <t>SEX</t>
   </si>
   <si>
-    <t xml:space="preserve">Sex of the child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sexo da criança</t>
+    <t>Sex of the child</t>
+  </si>
+  <si>
+    <t>Sexo da criança</t>
   </si>
   <si>
     <t>NOMEMAE</t>
   </si>
   <si>
-    <t xml:space="preserve">Name of mother</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome da mãe</t>
+    <t>Name of mother</t>
+  </si>
+  <si>
+    <t>Nome da mãe</t>
   </si>
   <si>
     <t>select_one_with_other</t>
@@ -364,58 +381,58 @@
     <t>RESP</t>
   </si>
   <si>
-    <t xml:space="preserve">Who brought the child?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quem trouxe a criança?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('RESP') != '1' &amp;&amp; data('RESP') != null</t>
+    <t>Who brought the child?</t>
+  </si>
+  <si>
+    <t>Quem trouxe a criança?</t>
+  </si>
+  <si>
+    <t>data('RESP') != '1' &amp;&amp; data('RESP') != null</t>
   </si>
   <si>
     <t>NOMERESP</t>
   </si>
   <si>
-    <t xml:space="preserve">Name of person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome da pessoa</t>
+    <t>Name of person</t>
+  </si>
+  <si>
+    <t>Nome da pessoa</t>
   </si>
   <si>
     <t>REGNO</t>
   </si>
   <si>
-    <t xml:space="preserve">Register number (triage survey)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de registo (ficha de triagem)</t>
+    <t>Register number (triage survey)</t>
+  </si>
+  <si>
+    <t>Número de registo (ficha de triagem)</t>
   </si>
   <si>
     <t>regnons</t>
   </si>
   <si>
-    <t xml:space="preserve">data('regnons') != null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('BAIRRO') != 77</t>
+    <t>data('regnons') != null</t>
+  </si>
+  <si>
+    <t>data('BAIRRO') != 77</t>
   </si>
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t xml:space="preserve">ID (BHP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID (PSB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(data('ID')&gt;999999  &amp;&amp; data('ID')&lt;10000000) || data('BAIRRO') == 77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be 7 digits long:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve ter 7 dígitos:</t>
+    <t>ID (BHP)</t>
+  </si>
+  <si>
+    <t>ID (PSB)</t>
+  </si>
+  <si>
+    <t>(data('ID')&gt;999999  &amp;&amp; data('ID')&lt;10000000) || data('BAIRRO') == 77</t>
+  </si>
+  <si>
+    <t>Must be 7 digits long:</t>
+  </si>
+  <si>
+    <t>Deve ter 7 dígitos:</t>
   </si>
   <si>
     <t>nsID</t>
@@ -424,25 +441,25 @@
     <t>idns</t>
   </si>
   <si>
-    <t xml:space="preserve">data('idns') != null</t>
+    <t>data('idns') != null</t>
   </si>
   <si>
     <t>REGIDC</t>
   </si>
   <si>
-    <t xml:space="preserve">Equipa móvel ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID da equipa móvel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('REGIDC') &gt; 10000000 &amp;&amp; data('REGIDC') &lt; 1000000000 || data('BAIRRO') != 77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be 8 digits long:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve ter 8 dígitos:</t>
+    <t>Equipa móvel ID</t>
+  </si>
+  <si>
+    <t>ID da equipa móvel</t>
+  </si>
+  <si>
+    <t>data('REGIDC') &gt; 10000000 &amp;&amp; data('REGIDC') &lt; 1000000000 || data('BAIRRO') != 77</t>
+  </si>
+  <si>
+    <t>Must be 8 digits long:</t>
+  </si>
+  <si>
+    <t>Deve ter 8 dígitos:</t>
   </si>
   <si>
     <t>nsREGIDC</t>
@@ -451,25 +468,25 @@
     <t>regidcns</t>
   </si>
   <si>
-    <t xml:space="preserve">data('regidcns') !=null</t>
+    <t>data('regidcns') !=null</t>
   </si>
   <si>
     <t>DOB</t>
   </si>
   <si>
-    <t xml:space="preserve">Day of birth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data de nascimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adate.diffInDays(data('DATINC'), data('DOB'))&lt;1 || adate.hasUncertainty(data('DOB'))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The date cannot be in the future:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A data não pode estar no futuro:</t>
+    <t>Day of birth</t>
+  </si>
+  <si>
+    <t>Data de nascimento</t>
+  </si>
+  <si>
+    <t>adate.diffInDays(data('DATINC'), data('DOB'))&lt;1 || adate.hasUncertainty(data('DOB'))</t>
+  </si>
+  <si>
+    <t>The date cannot be in the future:</t>
+  </si>
+  <si>
+    <t>A data não pode estar no futuro:</t>
   </si>
   <si>
     <t>datens</t>
@@ -478,7 +495,7 @@
     <t>dobns</t>
   </si>
   <si>
-    <t xml:space="preserve">data('dobns') != null</t>
+    <t>data('dobns') != null</t>
   </si>
   <si>
     <t>"D:NS,M:NS,Y:NS"</t>
@@ -490,28 +507,28 @@
     <t>IDADEANO</t>
   </si>
   <si>
-    <t xml:space="preserve">Age - year(s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idade - ano(s)</t>
+    <t>Age - year(s)</t>
+  </si>
+  <si>
+    <t>Idade - ano(s)</t>
   </si>
   <si>
     <t>IDADEMES</t>
   </si>
   <si>
-    <t xml:space="preserve">Age - month(s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idade - mes(es)</t>
+    <t>Age - month(s)</t>
+  </si>
+  <si>
+    <t>Idade - mes(es)</t>
   </si>
   <si>
     <t>note</t>
   </si>
   <si>
-    <t xml:space="preserve">The child has to be under 5 years and over 9 months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança deve ter entre 9 méses e 5 anos de idade</t>
+    <t>The child has to be under 5 years and over 9 months</t>
+  </si>
+  <si>
+    <t>A criança deve ter entre 9 méses e 5 anos de idade</t>
   </si>
   <si>
     <t>sim/não</t>
@@ -520,13 +537,13 @@
     <t>CONSENT</t>
   </si>
   <si>
-    <t xml:space="preserve">Does the mother/father/guardian consent to enrolment?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A mãe/pai/tutor aceita inclusão no estudo?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CONSENT') == '1'</t>
+    <t>Does the mother/father/guardian consent to enrolment?</t>
+  </si>
+  <si>
+    <t>A mãe/pai/tutor aceita inclusão no estudo?</t>
+  </si>
+  <si>
+    <t>data('CONSENT') == '1'</t>
   </si>
   <si>
     <t>signature</t>
@@ -535,13 +552,13 @@
     <t>CONSENTTIPO</t>
   </si>
   <si>
-    <t xml:space="preserve">Type of signature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipo da assinatura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CONSENTTIPO') == '2'</t>
+    <t>Type of signature</t>
+  </si>
+  <si>
+    <t>Tipo da assinatura</t>
+  </si>
+  <si>
+    <t>data('CONSENTTIPO') == '2'</t>
   </si>
   <si>
     <t>sim</t>
@@ -550,37 +567,37 @@
     <t>TESTEMUNHO</t>
   </si>
   <si>
-    <t xml:space="preserve">The witness signed the consent form</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O testemunho assina o formulário de consentimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">selected(data('TESTEMUNHO'),'1') || data('CONSENTTIPO') != '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A witness has to sign the consent form:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Um testemunho deve assinar o formulário de consentimento:</t>
+    <t>The witness signed the consent form</t>
+  </si>
+  <si>
+    <t>O testemunho assina o formulário de consentimento</t>
+  </si>
+  <si>
+    <t>selected(data('TESTEMUNHO'),'1') || data('CONSENTTIPO') != '2'</t>
+  </si>
+  <si>
+    <t>A witness has to sign the consent form:</t>
+  </si>
+  <si>
+    <t>Um testemunho deve assinar o formulário de consentimento:</t>
   </si>
   <si>
     <t>TELEMOVEL1</t>
   </si>
   <si>
-    <t xml:space="preserve">Phone number 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de telemovel 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('TELEMOVEL1') &gt; 99999999 &amp;&amp; data('TELEMOVEL1') &lt; 1000000000 || data('CONSENT') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be 9 digits long:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve ter 9 dígitos:</t>
+    <t>Phone number 1</t>
+  </si>
+  <si>
+    <t>Número de telemovel 1</t>
+  </si>
+  <si>
+    <t>data('TELEMOVEL1') &gt; 99999999 &amp;&amp; data('TELEMOVEL1') &lt; 1000000000 || data('CONSENT') == '2'</t>
+  </si>
+  <si>
+    <t>Must be 9 digits long:</t>
+  </si>
+  <si>
+    <t>Deve ter 9 dígitos:</t>
   </si>
   <si>
     <t>telinf1</t>
@@ -592,13 +609,13 @@
     <t>TELEMOVEL2</t>
   </si>
   <si>
-    <t xml:space="preserve">Phone number 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de telemovel 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('TELEMOVEL2') &gt; 99999999 &amp;&amp; data('TELEMOVEL2') &lt; 1000000000 || data('CONSENT') == '2'</t>
+    <t>Phone number 2</t>
+  </si>
+  <si>
+    <t>Número de telemovel 2</t>
+  </si>
+  <si>
+    <t>data('TELEMOVEL2') &gt; 99999999 &amp;&amp; data('TELEMOVEL2') &lt; 1000000000 || data('CONSENT') == '2'</t>
   </si>
   <si>
     <t>telinf2</t>
@@ -610,94 +627,91 @@
     <t>TELEMOVEL3</t>
   </si>
   <si>
-    <t xml:space="preserve">Phone number 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de telemovel 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('TELEMOVEL3') &gt; 99999999 &amp;&amp; data('TELEMOVEL3') &lt; 1000000000 || data('CONSENT') == '2'</t>
+    <t>Phone number 3</t>
+  </si>
+  <si>
+    <t>Número de telemovel 3</t>
+  </si>
+  <si>
+    <t>data('TELEMOVEL3') &gt; 99999999 &amp;&amp; data('TELEMOVEL3') &lt; 1000000000 || data('CONSENT') == '2'</t>
   </si>
   <si>
     <t>TELEINF3</t>
   </si>
   <si>
-    <t xml:space="preserve">data('TELEINF2') == '3'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('TELEINF3') == '3'</t>
+    <t>data('TELEINF2') == '3'</t>
+  </si>
+  <si>
+    <t>data('TELEINF3') == '3'</t>
   </si>
   <si>
     <t>CARTVIS</t>
   </si>
   <si>
-    <t xml:space="preserve">Was the vaccine card seen?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O cartão de vacina foi visto?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CARTVIS') != null || data('CONSENT') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required value not provided.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor requerido não fornecido.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CARTVIS') == '1'</t>
+    <t>Was the vaccine card seen?</t>
+  </si>
+  <si>
+    <t>O cartão de vacina foi visto?</t>
+  </si>
+  <si>
+    <t>data('CARTVIS') != null || data('CONSENT') == '2'</t>
+  </si>
+  <si>
+    <t>Required value not provided.</t>
+  </si>
+  <si>
+    <t>Valor requerido não fornecido.</t>
+  </si>
+  <si>
+    <t>data('CARTVIS') == '1'</t>
   </si>
   <si>
     <t>SARVAC</t>
   </si>
   <si>
-    <t xml:space="preserve">Has the child received the first measles vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança recebeu a primeira vacina do sarampo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('SARVAC') != null || data('CONSENT') == '2' || data('CARTVIS') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CARTVIS') == '2'</t>
+    <t>Has the child received the first measles vaccine</t>
+  </si>
+  <si>
+    <t>A criança recebeu a primeira vacina do sarampo</t>
+  </si>
+  <si>
+    <t>data('SARVAC') != null || data('CONSENT') == '2' || data('CARTVIS') == '2'</t>
+  </si>
+  <si>
+    <t>data('CARTVIS') == '2'</t>
   </si>
   <si>
     <t>VENAOVAS</t>
   </si>
   <si>
-    <t xml:space="preserve">Mother/guardian confirmed that the child did not receive the first measles vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A mãe/tutor confirmou que a criança não recebeu o primero deose de vacina do sarampo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('VENAOVAS') != null || data('CONSENT') == '2' || data('CARTVIS') == '1'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adate.diffInDays(data('DOB'), data('DATINC')) &gt; 453 || adate.hasUncertainty(data('DOB')) || (data('IDADEANO') == '1' &amp;&amp; data('IDADEMES') &gt; '3' || data('IDADEMES')&gt; '14' || data('IDADEANO') &gt; '1' )</t>
+    <t>Mother/guardian confirmed that the child did not receive the first measles vaccine</t>
+  </si>
+  <si>
+    <t>A mãe/tutor confirmou que a criança não recebeu o primero deose de vacina do sarampo</t>
+  </si>
+  <si>
+    <t>data('VENAOVAS') != null || data('CONSENT') == '2' || data('CARTVIS') == '1'</t>
+  </si>
+  <si>
+    <t>adate.diffInDays(data('DOB'), data('DATINC')) &gt; 453 || adate.hasUncertainty(data('DOB')) || (data('IDADEANO') == '1' &amp;&amp; data('IDADEMES') &gt; '3' || data('IDADEMES')&gt; '14' || data('IDADEANO') &gt; '1' )</t>
   </si>
   <si>
     <t>SARVAC2</t>
   </si>
   <si>
-    <t xml:space="preserve">Has the child received the second measles vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança recebeu a segunda vacina do sarampo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('SARVAC2') != null || data('CONSENT') == '2' || data('CARTVIS') == '2'</t>
+    <t>Has the child received the second measles vaccine</t>
+  </si>
+  <si>
+    <t>A criança recebeu a segunda vacina do sarampo</t>
   </si>
   <si>
     <t>VENAOVAS2</t>
   </si>
   <si>
-    <t xml:space="preserve">Mother/guardian confirmed that the child did not receive the second measles vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A mãe/tutor confirmou que a criança não recebeu a segunda vacina do sarampo</t>
+    <t>Mother/guardian confirmed that the child did not receive the second measles vaccine</t>
+  </si>
+  <si>
+    <t>A mãe/tutor confirmou que a criança não recebeu a segunda vacina do sarampo</t>
   </si>
   <si>
     <t>image</t>
@@ -706,10 +720,10 @@
     <t>CARTIMG</t>
   </si>
   <si>
-    <t xml:space="preserve">Please take a picture of the vaccine card</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Por favor, tire uma foto do cartão de vacina</t>
+    <t>Please take a picture of the vaccine card</t>
+  </si>
+  <si>
+    <t>Por favor, tire uma foto do cartão de vacina</t>
   </si>
   <si>
     <t>TEMPERATURA</t>
@@ -721,37 +735,37 @@
     <t>Temperatura</t>
   </si>
   <si>
-    <t xml:space="preserve">freebase.decimalPlaces(data('TEMPERATURA'))==1 || data('CONSENT') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must have 1 decimal:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve ter 1 decimal:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Write the temperature with 1 decimal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escreva a temperatura com 1 decimal</t>
+    <t>freebase.decimalPlaces(data('TEMPERATURA'))==1 || data('CONSENT') == '2'</t>
+  </si>
+  <si>
+    <t>Must have 1 decimal:</t>
+  </si>
+  <si>
+    <t>Deve ter 1 decimal:</t>
+  </si>
+  <si>
+    <t>Write the temperature with 1 decimal</t>
+  </si>
+  <si>
+    <t>Escreva a temperatura com 1 decimal</t>
   </si>
   <si>
     <t>BRACOCRI</t>
   </si>
   <si>
-    <t xml:space="preserve">Middle upper arm circumference</t>
+    <t>Middle upper arm circumference</t>
   </si>
   <si>
     <t>Braço</t>
   </si>
   <si>
-    <t xml:space="preserve">(data('BRACOCRI')&gt;49 &amp;&amp; data('BRACOCRI')&lt;343 &amp;&amp; data('BRACOCRI')%2 == 0) || data('CONSENT') == '2' || data('BRACOCRI') == 999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be between 50 and 342 and a even number:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve estar entre 50 e 342 e um número par:</t>
+    <t>(data('BRACOCRI')&gt;49 &amp;&amp; data('BRACOCRI')&lt;343 &amp;&amp; data('BRACOCRI')%2 == 0) || data('CONSENT') == '2' || data('BRACOCRI') == 999</t>
+  </si>
+  <si>
+    <t>Must be between 50 and 342 and a even number:</t>
+  </si>
+  <si>
+    <t>Deve estar entre 50 e 342 e um número par:</t>
   </si>
   <si>
     <t>Motivo</t>
@@ -760,10 +774,10 @@
     <t>MOTCONT</t>
   </si>
   <si>
-    <t xml:space="preserve">Reason for contact with the pediatric ward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motivo de contato com a pediatria</t>
+    <t>Reason for contact with the pediatric ward</t>
+  </si>
+  <si>
+    <t>Motivo de contato com a pediatria</t>
   </si>
   <si>
     <t>data('MOTCONT')=='2'</t>
@@ -772,13 +786,13 @@
     <t>INTINICI</t>
   </si>
   <si>
-    <t xml:space="preserve">Since day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desde dia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adate.diffInDays(data('DATINC'), data('INTINICI'))&lt;1 || adate.hasUncertainty(data('INTINICI')) ||data('CONSENT') == '2'</t>
+    <t>Since day</t>
+  </si>
+  <si>
+    <t>Desde dia</t>
+  </si>
+  <si>
+    <t>adate.diffInDays(data('DATINC'), data('INTINICI'))&lt;1 || adate.hasUncertainty(data('INTINICI')) ||data('CONSENT') == '2'</t>
   </si>
   <si>
     <t>sim/não/ns</t>
@@ -826,10 +840,10 @@
     <t>RENORREI</t>
   </si>
   <si>
-    <t xml:space="preserve">Runny nose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rinorreia (ranho)</t>
+    <t>Runny nose</t>
+  </si>
+  <si>
+    <t>Rinorreia (ranho)</t>
   </si>
   <si>
     <t>TOSSE</t>
@@ -844,10 +858,10 @@
     <t>DIFRESP</t>
   </si>
   <si>
-    <t xml:space="preserve">Respiratory difficulty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dificuldade respiratória</t>
+    <t>Respiratory difficulty</t>
+  </si>
+  <si>
+    <t>Dificuldade respiratória</t>
   </si>
   <si>
     <t>CONVULSA</t>
@@ -862,22 +876,22 @@
     <t>OSIMP</t>
   </si>
   <si>
-    <t xml:space="preserve">Other symptoms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outros sintomas</t>
+    <t>Other symptoms</t>
+  </si>
+  <si>
+    <t>Outros sintomas</t>
   </si>
   <si>
     <t>TRATAMENT_A</t>
   </si>
   <si>
-    <t xml:space="preserve">Did the child receive any treatments?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança recebeu algum tratamento (antes inclusao)?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('TRATAMENT_A') =='1'</t>
+    <t>Did the child receive any treatments?</t>
+  </si>
+  <si>
+    <t>A criança recebeu algum tratamento (antes inclusao)?</t>
+  </si>
+  <si>
+    <t>data('TRATAMENT_A') =='1'</t>
   </si>
   <si>
     <t>tratament</t>
@@ -886,10 +900,10 @@
     <t>TRATQUAL_A</t>
   </si>
   <si>
-    <t xml:space="preserve">What treatments did the child recieve?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qual tratamento foi dado?</t>
+    <t>What treatments did the child recieve?</t>
+  </si>
+  <si>
+    <t>Qual tratamento foi dado?</t>
   </si>
   <si>
     <t>selected(data('TRATQUAL_A'),'77')</t>
@@ -907,22 +921,22 @@
     <t>TRATAMENT_R</t>
   </si>
   <si>
-    <t xml:space="preserve">Did the child get any treatments prescribed?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança deve receber algum tratamento (receita)?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('TRATAMENT_R') =='1'</t>
+    <t>Did the child get any treatments prescribed?</t>
+  </si>
+  <si>
+    <t>A criança deve receber algum tratamento (receita)?</t>
+  </si>
+  <si>
+    <t>data('TRATAMENT_R') =='1'</t>
   </si>
   <si>
     <t>TRATQUAL_R</t>
   </si>
   <si>
-    <t xml:space="preserve">What treatments are prescribed ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qual tratamento foi receitado?</t>
+    <t>What treatments are prescribed ?</t>
+  </si>
+  <si>
+    <t>Qual tratamento foi receitado?</t>
   </si>
   <si>
     <t>selected(data('TRATQUAL_R'),'77')</t>
@@ -934,22 +948,22 @@
     <t>TRATIMG</t>
   </si>
   <si>
-    <t xml:space="preserve">If the child have a prescription, please take a photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se a criança tiver uma receita médica, por favor tire uma foto</t>
+    <t>If the child have a prescription, please take a photo</t>
+  </si>
+  <si>
+    <t>Se a criança tiver uma receita médica, por favor tire uma foto</t>
   </si>
   <si>
     <t>PODEVAC</t>
   </si>
   <si>
-    <t xml:space="preserve">Can the child receive a vaccine (VAS) today?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança pode receber uma vacina (VAS) hoje?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('PODEVAC') != null || data('CONSENT') == '2'</t>
+    <t>Can the child receive a vaccine (VAS) today?</t>
+  </si>
+  <si>
+    <t>A criança pode receber uma vacina (VAS) hoje?</t>
+  </si>
+  <si>
+    <t>data('PODEVAC') != null || data('CONSENT') == '2'</t>
   </si>
   <si>
     <t>data('PODEVAC')=='2'</t>
@@ -967,13 +981,13 @@
     <t>PODEINC</t>
   </si>
   <si>
-    <t xml:space="preserve">Can the child be included today?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança pode ser incluída hoje?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('PODEINC') != null || data('CONSENT') == '2'</t>
+    <t>Can the child be included today?</t>
+  </si>
+  <si>
+    <t>A criança pode ser incluída hoje?</t>
+  </si>
+  <si>
+    <t>data('PODEINC') != null || data('CONSENT') == '2'</t>
   </si>
   <si>
     <t>data('PODEINC')=='2'</t>
@@ -985,148 +999,142 @@
     <t>JAINC</t>
   </si>
   <si>
-    <t xml:space="preserve">Is the child already participating in the study?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança já está participando do estudo?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('JAINC') != null || data('CONSENT') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('PODEVAC')=='2'|| data('PODEINC')=='2'  || data('JAINC') == '1' || data('BRACOCRI') &lt;110 || data('TEMPERATURA')&gt;37.9 || data('VENAOVAS') == '2' ||  data('VENAOVAS2') == '2' || (data('SARVAC') == '1' &amp;&amp;  data('SARVAC2') != '2')||data('SARVAC2') == '1'  || adate.diffInDays(data('DOB'), data('DATINC')) &gt; 1826 || adate.diffInDays(data('DOB'), data('DATINC')) &lt; 270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">|| calculates.childAGE &gt;'1826</t>
+    <t>Is the child already participating in the study?</t>
+  </si>
+  <si>
+    <t>A criança já está participando do estudo?</t>
+  </si>
+  <si>
+    <t>data('JAINC') != null || data('CONSENT') == '2'</t>
+  </si>
+  <si>
+    <t>data('PODEVAC')=='2'|| data('PODEINC')=='2'  || data('JAINC') == '1' || data('BRACOCRI') &lt;110 || data('TEMPERATURA')&gt;37.9 || data('VENAOVAS') == '2' ||  data('VENAOVAS2') == '2' || (data('SARVAC') == '1' &amp;&amp;  data('SARVAC2') != '2')||data('SARVAC2') == '1'  || adate.diffInDays(data('DOB'), data('DATINC')) &gt; 1826 || adate.diffInDays(data('DOB'), data('DATINC')) &lt; 270</t>
+  </si>
+  <si>
+    <t>|| calculates.childAGE &gt;'1826</t>
   </si>
   <si>
     <t>INC</t>
   </si>
   <si>
-    <t xml:space="preserve">The child is not to be included, since:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança não deve ser incluída, porque:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The nurse assessed that the child should not be vaccinated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A enfermeira avaliou que a criança não deve ser vacinada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The nurse assessed that the child should not be included</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A enfermeira avaliou que a criança não deveria ser incluída</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('JAINC') == '1'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The child already participating in the study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança já participa no estudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('BRACOCRI') &lt;110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upper middle arm circumference is smaller than 110 mm ({{data.BRACOCRI}})</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A braço é menor do que 110 mm ({{data.BRACOCRI}})</t>
+    <t>The child is not to be included, since:</t>
+  </si>
+  <si>
+    <t>A criança não deve ser incluída, porque:</t>
+  </si>
+  <si>
+    <t>The nurse assessed that the child should not be vaccinated</t>
+  </si>
+  <si>
+    <t>A enfermeira avaliou que a criança não deve ser vacinada</t>
+  </si>
+  <si>
+    <t>The nurse assessed that the child should not be included</t>
+  </si>
+  <si>
+    <t>A enfermeira avaliou que a criança não deveria ser incluída</t>
+  </si>
+  <si>
+    <t>data('JAINC') == '1'</t>
+  </si>
+  <si>
+    <t>The child already participating in the study</t>
+  </si>
+  <si>
+    <t>A criança já participa no estudo</t>
+  </si>
+  <si>
+    <t>data('BRACOCRI') &lt;110</t>
+  </si>
+  <si>
+    <t>Upper middle arm circumference is smaller than 110 mm ({{data.BRACOCRI}})</t>
+  </si>
+  <si>
+    <t>A braço é menor do que 110 mm ({{data.BRACOCRI}})</t>
   </si>
   <si>
     <t>data('TEMPERATURA')&gt;38</t>
   </si>
   <si>
-    <t xml:space="preserve">The temperature is greater than 37.9 ({{data.TEMPERATURA}})</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A temperatura é mais alta do que 37,9 ({{data.TEMPERATURA}})</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('VENAOVAS2') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mother/guardian could not confirm that the child did not receive the first measles vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mãe/tutor não pôde confirmar que a criança não recebeu a primeira vacina do sarampo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('VENAOVAS') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mother/guardian could not confirm that the child did not receive the second measles vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mãe/tutor não pôde confirmar que a criança não recebeu a segunda vacina do sarampo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('SARVAC') == '1'&amp;&amp; data('SARVAC2')==1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The child has previously received both measles vaccines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança recebeu os seus vacinas do sarampo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('SARVAC2') == '1'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The child has previously received the second measles vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(adate.diffInDays(data('DOB'), data('DATINC'))&gt;1826) || (adate.diffInDays(data('DOB'), data('DATINC'))&lt;270)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calculates.childAGE &gt;'1826'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The child is too old</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A crianca tem idade maior de 5 anos</t>
+    <t>The temperature is greater than 37.9 ({{data.TEMPERATURA}})</t>
+  </si>
+  <si>
+    <t>A temperatura é mais alta do que 37,9 ({{data.TEMPERATURA}})</t>
+  </si>
+  <si>
+    <t>data('VENAOVAS2') == '2'</t>
+  </si>
+  <si>
+    <t>Mother/guardian could not confirm that the child did not receive the first measles vaccine</t>
+  </si>
+  <si>
+    <t>Mãe/tutor não pôde confirmar que a criança não recebeu a primeira vacina do sarampo</t>
+  </si>
+  <si>
+    <t>data('VENAOVAS') == '2'</t>
+  </si>
+  <si>
+    <t>Mother/guardian could not confirm that the child did not receive the second measles vaccine</t>
+  </si>
+  <si>
+    <t>Mãe/tutor não pôde confirmar que a criança não recebeu a segunda vacina do sarampo</t>
+  </si>
+  <si>
+    <t>The child has previously received both measles vaccines</t>
+  </si>
+  <si>
+    <t>A criança recebeu os seus vacinas do sarampo</t>
+  </si>
+  <si>
+    <t>data('SARVAC2') == '1'</t>
+  </si>
+  <si>
+    <t>The child has previously received the second measles vaccine</t>
+  </si>
+  <si>
+    <t>calculates.childAGE &gt;'1826'</t>
+  </si>
+  <si>
+    <t>The child is too old</t>
+  </si>
+  <si>
+    <t>A crianca tem idade maior de 5 anos</t>
   </si>
   <si>
     <t>RANDOM1</t>
   </si>
   <si>
-    <t xml:space="preserve">First randomization number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primeiro número de randomização</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('RANDOM2')&lt;501 &amp;&amp; data('RANDOM1')&gt;0 || data('INC') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be 1-500:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve ser de 1 a 500:</t>
+    <t>First randomization number</t>
+  </si>
+  <si>
+    <t>Primeiro número de randomização</t>
+  </si>
+  <si>
+    <t>data('RANDOM2')&lt;501 &amp;&amp; data('RANDOM1')&gt;0 || data('INC') == '2'</t>
+  </si>
+  <si>
+    <t>Must be 1-500:</t>
+  </si>
+  <si>
+    <t>Deve ser de 1 a 500:</t>
   </si>
   <si>
     <t>RANDOM2</t>
   </si>
   <si>
-    <t xml:space="preserve">Second randomization number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segundo número de randomização</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('RANDOM2')&lt;13 &amp;&amp; data('RANDOM2')&gt;0 || data('INC') == '2'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be 1-12:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve ser de 1 a 12:</t>
+    <t>Second randomization number</t>
+  </si>
+  <si>
+    <t>Segundo número de randomização</t>
+  </si>
+  <si>
+    <t>data('RANDOM2')&lt;13 &amp;&amp; data('RANDOM2')&gt;0 || data('INC') == '2'</t>
+  </si>
+  <si>
+    <t>Must be 1-12:</t>
+  </si>
+  <si>
+    <t>Deve ser de 1 a 12:</t>
   </si>
   <si>
     <t>RANDOM</t>
@@ -1135,10 +1143,10 @@
     <t>freebase.randomLabel(data('SEX'),data('RANDOM1'),data('RANDOM2'))</t>
   </si>
   <si>
-    <t xml:space="preserve">Label: &lt;b&gt;{{data.RANDOM}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etiqueta: &lt;b&gt;{{data.RANDOM}}&lt;/b&gt;</t>
+    <t>Label: &lt;b&gt;{{data.RANDOM}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Etiqueta: &lt;b&gt;{{data.RANDOM}}&lt;/b&gt;</t>
   </si>
   <si>
     <t>DATVACVAS</t>
@@ -1147,10 +1155,10 @@
     <t>data('DATINC')</t>
   </si>
   <si>
-    <t xml:space="preserve">Date of vaccination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data da vacinação</t>
+    <t>Date of vaccination</t>
+  </si>
+  <si>
+    <t>Data da vacinação</t>
   </si>
   <si>
     <t>time</t>
@@ -1159,10 +1167,10 @@
     <t>HORA</t>
   </si>
   <si>
-    <t xml:space="preserve">Time of vaccination</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hora da vacinação</t>
+    <t>Time of vaccination</t>
+  </si>
+  <si>
+    <t>Hora da vacinação</t>
   </si>
   <si>
     <t xml:space="preserve">data('HORVACVAS') != null || data('INC') == '2' </t>
@@ -1177,19 +1185,19 @@
     <t>NUM</t>
   </si>
   <si>
-    <t xml:space="preserve">Study number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de estudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('NUM')&gt;0 || data('INC') == '2' || data('changeid') != null || data('changetabz') != null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cannot be negative:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não pode ser negativo:</t>
+    <t>Study number</t>
+  </si>
+  <si>
+    <t>Número de estudo</t>
+  </si>
+  <si>
+    <t>data('NUM')&gt;0 || data('INC') == '2' || data('changeid') != null || data('changetabz') != null</t>
+  </si>
+  <si>
+    <t>Cannot be negative:</t>
+  </si>
+  <si>
+    <t>Não pode ser negativo:</t>
   </si>
   <si>
     <t>NUMEST</t>
@@ -1198,10 +1206,10 @@
     <t>freebase.studyNumber("MAD",4,data('NUM'))</t>
   </si>
   <si>
-    <t xml:space="preserve">Study number: &lt;b&gt;{{data.NUMEST}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número de estudo: &lt;b&gt;{{data.NUMEST}}&lt;/b&gt;</t>
+    <t>Study number: &lt;b&gt;{{data.NUMEST}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Número de estudo: &lt;b&gt;{{data.NUMEST}}&lt;/b&gt;</t>
   </si>
   <si>
     <t>enf</t>
@@ -1216,7 +1224,7 @@
     <t>Enfermeira</t>
   </si>
   <si>
-    <t xml:space="preserve">data('INC') == '1'</t>
+    <t>data('INC') == '1'</t>
   </si>
   <si>
     <t>ass</t>
@@ -1231,10 +1239,10 @@
     <t>Assistente</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;font color = "red"&gt;End the enrolment as consent has not been obtained&lt;/font &gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;font color = "red"&gt; Finalize a inclusão porque o consentimento não foi dado &lt;/font&gt;</t>
+    <t>&lt;font color = "red"&gt;End the enrolment as consent has not been obtained&lt;/font &gt;</t>
+  </si>
+  <si>
+    <t>&lt;font color = "red"&gt; Finalize a inclusão porque o consentimento não foi dado &lt;/font&gt;</t>
   </si>
   <si>
     <t>choice_list_name</t>
@@ -1282,22 +1290,22 @@
     <t>Internamento</t>
   </si>
   <si>
-    <t xml:space="preserve">Dont't know</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não sabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don't know</t>
+    <t>Dont't know</t>
+  </si>
+  <si>
+    <t>Não sabe</t>
+  </si>
+  <si>
+    <t>Don't know</t>
   </si>
   <si>
     <t>Abrao</t>
   </si>
   <si>
-    <t xml:space="preserve">removed Suzete (enf=1) on 19-01-2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augosto Da Costa</t>
+    <t>removed Suzete (enf=1) on 19-01-2022</t>
+  </si>
+  <si>
+    <t>Augosto Da Costa</t>
   </si>
   <si>
     <t>Abdel</t>
@@ -1306,10 +1314,10 @@
     <t>Justiniano</t>
   </si>
   <si>
-    <t xml:space="preserve">removed Suzete (ass=11) on 19-01-2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">removed fatima - ass=1 on 20250723</t>
+    <t>removed Suzete (ass=11) on 19-01-2022</t>
+  </si>
+  <si>
+    <t>removed fatima - ass=1 on 20250723</t>
   </si>
   <si>
     <t>Josemira</t>
@@ -1321,7 +1329,7 @@
     <t>Amoxicillina</t>
   </si>
   <si>
-    <t xml:space="preserve">Complexo B</t>
+    <t>Complexo B</t>
   </si>
   <si>
     <t>Salbutamol</t>
@@ -1333,76 +1341,76 @@
     <t>Prometazina</t>
   </si>
   <si>
-    <t xml:space="preserve">Soro fisiologico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">added 16-02-2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitamina C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">added 16-02-2023</t>
+    <t>Soro fisiologico</t>
+  </si>
+  <si>
+    <t>added 16-02-2022</t>
+  </si>
+  <si>
+    <t>Vitamina C</t>
+  </si>
+  <si>
+    <t>added 16-02-2023</t>
   </si>
   <si>
     <t>SRO</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sulfate de Zinco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">added 16-02-2025</t>
+    <t>added 16-02-2024</t>
+  </si>
+  <si>
+    <t>Sulfate de Zinco</t>
+  </si>
+  <si>
+    <t>added 16-02-2025</t>
   </si>
   <si>
     <t>Azitomicina</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2026</t>
+    <t>added 16-02-2026</t>
   </si>
   <si>
     <t>Brufen</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2027</t>
+    <t>added 16-02-2027</t>
   </si>
   <si>
     <t>Albendazol</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2028</t>
+    <t>added 16-02-2028</t>
   </si>
   <si>
     <t>Mebendazol</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2029</t>
+    <t>added 16-02-2029</t>
   </si>
   <si>
     <t>Metroniazol</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2030</t>
+    <t>added 16-02-2030</t>
   </si>
   <si>
     <t>Nistatina</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2031</t>
+    <t>added 16-02-2031</t>
   </si>
   <si>
     <t>Augmentin</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2032</t>
+    <t>added 16-02-2032</t>
   </si>
   <si>
     <t>Erytromecina</t>
   </si>
   <si>
-    <t xml:space="preserve">added 16-02-2033</t>
+    <t>added 16-02-2033</t>
   </si>
   <si>
     <t>Other</t>
@@ -1423,22 +1431,19 @@
     <t>Pai</t>
   </si>
   <si>
-    <t xml:space="preserve">Don't have another phone number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não tem outro número de telefone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Didn't suceed to identify ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não conseguiu identifcar o ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don't have ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não tem ID</t>
+    <t>Don't have another phone number</t>
+  </si>
+  <si>
+    <t>Não tem outro número de telefone</t>
+  </si>
+  <si>
+    <t>Didn't suceed to identify ID</t>
+  </si>
+  <si>
+    <t>Don't have ID</t>
+  </si>
+  <si>
+    <t>Não tem ID</t>
   </si>
   <si>
     <t>Signature</t>
@@ -1450,7 +1455,7 @@
     <t>Fingerprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Impressão digital</t>
+    <t>Impressão digital</t>
   </si>
   <si>
     <t>Sibling</t>
@@ -1459,7 +1464,7 @@
     <t>Irmã(o)</t>
   </si>
   <si>
-    <t xml:space="preserve">Mothers mother</t>
+    <t>Mothers mother</t>
   </si>
   <si>
     <t>Avó</t>
@@ -1492,7 +1497,7 @@
     <t>"TABZ.csv"</t>
   </si>
   <si>
-    <t xml:space="preserve">_.chain(context)
+    <t>_.chain(context)
 .uniq(function(x) {
 return x.BAIRRONR
 })
@@ -1503,7 +1508,7 @@
 }).value()</t>
   </si>
   <si>
-    <t xml:space="preserve">_.map(context, function(place){place.data_value = place.TABZ;
+    <t>_.map(context, function(place){place.data_value = place.TABZ;
 place.display = {title: {text: place.ZONE} };
 return place;
 })</t>
@@ -1518,7 +1523,7 @@
     <t>string</t>
   </si>
   <si>
-    <t xml:space="preserve">Save only mm.dd.yyyy with support for ?? at all positions</t>
+    <t>Save only mm.dd.yyyy with support for ?? at all positions</t>
   </si>
   <si>
     <t>isSessionVariable</t>
@@ -1552,52 +1557,79 @@
   </si>
   <si>
     <t>changeregdate</t>
+  </si>
+  <si>
+    <t>Não conseguiu identificar o ID</t>
+  </si>
+  <si>
+    <t>((adate.diffInDays(data('DOB'), data('DATINC'))&gt;1826) || (adate.diffInDays(data('DOB'), data('DATINC'))&lt;270)) &amp;&amp; data('DOB') != "D:NS,M:NS,Y:NS"</t>
+  </si>
+  <si>
+    <t>data('SARVAC') == '1'&amp;&amp; data('SARVAC2')=='1'</t>
+  </si>
+  <si>
+    <t>The child is &lt;15 months and has received the first MV</t>
+  </si>
+  <si>
+    <t>((adate.diffInDays(data('DOB'), data('DATINC'))&lt;453) &amp;&amp; data('SARVAC')=='1') &amp;&amp; data('DOB') != "D:NS,M:NS,Y:NS"</t>
+  </si>
+  <si>
+    <t>A criança recebeu a primeia vacina do sarampo e ainda não tem idade para o segundo dose</t>
+  </si>
+  <si>
+    <t>data('SARVAC2') != null || data('CONSENT') == '2' || data('CARTVIS') == '2' || data('SARVAC') == '1'</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-406]General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.000000"/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -1635,64 +1667,57 @@
   </fills>
   <borders count="2">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="4">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="164" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Excel Built-in Normal" xfId="1"/>
+    <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 4" xfId="3"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 4" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{57B66A72-3F33-4BAC-B051-48D61178ACC8}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1704,291 +1729,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2191,22 +1933,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="13.26953125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="10.1796875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="29"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="27"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="24.7265625"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="28.54296875"/>
+    <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2226,7 +1970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2234,7 +1978,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2242,7 +1986,7 @@
         <v>60120</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2250,7 +1994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2261,7 +2005,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -2272,7 +2016,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2283,7 +2027,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
@@ -2292,28 +2036,27 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="12.453125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="14.26953125"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="24.7265625"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="10.453125"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" width="26.1796875"/>
-    <col bestFit="1" customWidth="1" min="8" max="8" width="18.81640625"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="10.54296875"/>
-    <col bestFit="1" customWidth="1" min="10" max="10" width="12.1796875"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -2345,41 +2088,40 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:Y261"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="12.453125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="12.26953125"/>
-    <col customWidth="1" min="3" max="3" width="32.81640625"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="22"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="13.1796875"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="14.54296875"/>
-    <col customWidth="1" min="7" max="7" width="45.54296875"/>
-    <col customWidth="1" min="8" max="8" width="35.453125"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="15.7265625"/>
-    <col customWidth="1" min="10" max="10" width="13.54296875"/>
-    <col customWidth="1" min="11" max="11" width="30.7265625"/>
-    <col bestFit="1" customWidth="1" min="12" max="12" width="37.453125"/>
-    <col bestFit="1" customWidth="1" min="13" max="13" width="30.26953125"/>
-    <col bestFit="1" customWidth="1" min="14" max="14" width="23"/>
-    <col bestFit="1" customWidth="1" min="15" max="15" width="15.7265625"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.81640625" customWidth="1"/>
+    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="45.54296875" customWidth="1"/>
+    <col min="8" max="8" width="35.453125" customWidth="1"/>
+    <col min="9" max="9" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.54296875" customWidth="1"/>
+    <col min="11" max="11" width="30.7265625" customWidth="1"/>
+    <col min="12" max="12" width="37.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -2438,12 +2180,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
         <v>42</v>
       </c>
@@ -2454,7 +2196,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="D4" t="s">
         <v>45</v>
       </c>
@@ -2465,7 +2207,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="D5" t="s">
         <v>45</v>
       </c>
@@ -2476,12 +2218,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="D7" t="s">
         <v>51</v>
       </c>
@@ -2498,21 +2240,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="D14" t="s">
         <v>55</v>
       </c>
@@ -2529,7 +2267,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>60</v>
       </c>
@@ -2537,7 +2275,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
         <v>55</v>
       </c>
@@ -2557,7 +2295,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>60</v>
       </c>
@@ -2566,7 +2304,7 @@
       </c>
       <c r="J17" s="5"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D18" t="s">
         <v>68</v>
       </c>
@@ -2580,12 +2318,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D20" t="s">
         <v>68</v>
       </c>
@@ -2608,12 +2346,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D22" t="s">
         <v>45</v>
       </c>
@@ -2624,12 +2362,12 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>79</v>
       </c>
@@ -2652,7 +2390,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D25" t="s">
         <v>82</v>
       </c>
@@ -2675,7 +2413,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D26" t="s">
         <v>86</v>
       </c>
@@ -2686,7 +2424,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>60</v>
       </c>
@@ -2694,7 +2432,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D28" t="s">
         <v>45</v>
       </c>
@@ -2705,7 +2443,7 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D29" t="s">
         <v>68</v>
       </c>
@@ -2728,12 +2466,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D31" t="s">
         <v>68</v>
       </c>
@@ -2759,7 +2497,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D32" t="s">
         <v>86</v>
       </c>
@@ -2770,7 +2508,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>60</v>
       </c>
@@ -2778,7 +2516,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D34" t="s">
         <v>45</v>
       </c>
@@ -2789,27 +2527,27 @@
         <v>99999</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D39" t="s">
         <v>68</v>
       </c>
@@ -2826,7 +2564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D40" t="s">
         <v>102</v>
       </c>
@@ -2846,7 +2584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D41" t="s">
         <v>68</v>
       </c>
@@ -2860,17 +2598,17 @@
         <v>109</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D44" t="s">
         <v>110</v>
       </c>
@@ -2887,7 +2625,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>60</v>
       </c>
@@ -2895,7 +2633,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D46" t="s">
         <v>68</v>
       </c>
@@ -2909,22 +2647,22 @@
         <v>118</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D50" t="s">
         <v>82</v>
       </c>
@@ -2938,7 +2676,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D51" t="s">
         <v>86</v>
       </c>
@@ -2949,7 +2687,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>60</v>
       </c>
@@ -2957,7 +2695,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D53" t="s">
         <v>45</v>
       </c>
@@ -2968,12 +2706,12 @@
         <v>999</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>60</v>
       </c>
@@ -2981,7 +2719,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="56" ht="16.5" customHeight="1">
+    <row r="56" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D56" t="s">
         <v>82</v>
       </c>
@@ -3004,7 +2742,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="57" ht="16.5" customHeight="1">
+    <row r="57" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D57" t="s">
         <v>86</v>
       </c>
@@ -3015,7 +2753,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="58" ht="16.5" customHeight="1">
+    <row r="58" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
         <v>60</v>
       </c>
@@ -3023,7 +2761,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="59" ht="16.5" customHeight="1">
+    <row r="59" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D59" t="s">
         <v>45</v>
       </c>
@@ -3034,17 +2772,17 @@
         <v>9999999</v>
       </c>
     </row>
-    <row r="60" ht="16.5" customHeight="1">
+    <row r="60" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="61" ht="16.5" customHeight="1">
+    <row r="61" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D62" t="s">
         <v>82</v>
       </c>
@@ -3067,7 +2805,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D63" t="s">
         <v>86</v>
       </c>
@@ -3078,7 +2816,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
         <v>60</v>
       </c>
@@ -3086,7 +2824,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D65" t="s">
         <v>45</v>
       </c>
@@ -3097,27 +2835,27 @@
         <v>999999999</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D70" t="s">
         <v>51</v>
       </c>
@@ -3143,7 +2881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D71" t="s">
         <v>86</v>
       </c>
@@ -3154,7 +2892,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
         <v>60</v>
       </c>
@@ -3162,7 +2900,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D73" t="s">
         <v>45</v>
       </c>
@@ -3173,12 +2911,12 @@
         <v>152</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
         <v>60</v>
       </c>
@@ -3186,7 +2924,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D76" t="s">
         <v>82</v>
       </c>
@@ -3200,7 +2938,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D77" t="s">
         <v>82</v>
       </c>
@@ -3214,12 +2952,12 @@
         <v>159</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D79" t="s">
         <v>160</v>
       </c>
@@ -3230,17 +2968,17 @@
         <v>162</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D82" t="s">
         <v>102</v>
       </c>
@@ -3260,7 +2998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
         <v>60</v>
       </c>
@@ -3268,7 +3006,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D84" t="s">
         <v>102</v>
       </c>
@@ -3285,7 +3023,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>60</v>
       </c>
@@ -3293,7 +3031,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D86" t="s">
         <v>102</v>
       </c>
@@ -3319,22 +3057,22 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
         <v>60</v>
       </c>
@@ -3342,12 +3080,12 @@
         <v>167</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D92" t="s">
         <v>82</v>
       </c>
@@ -3370,7 +3108,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D93" t="s">
         <v>110</v>
       </c>
@@ -3381,7 +3119,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D94" t="s">
         <v>82</v>
       </c>
@@ -3404,7 +3142,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D95" t="s">
         <v>110</v>
       </c>
@@ -3415,7 +3153,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D96" t="s">
         <v>82</v>
       </c>
@@ -3438,7 +3176,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D97" t="s">
         <v>110</v>
       </c>
@@ -3449,7 +3187,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
         <v>60</v>
       </c>
@@ -3457,7 +3195,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D99" t="s">
         <v>45</v>
       </c>
@@ -3468,12 +3206,12 @@
         <v>999999999</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
         <v>60</v>
       </c>
@@ -3481,7 +3219,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D102" t="s">
         <v>45</v>
       </c>
@@ -3492,25 +3230,22 @@
         <v>999999999</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="105">
-      <c r="B105" s="7"/>
-    </row>
-    <row r="106">
+    <row r="106" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D107" t="s">
         <v>102</v>
       </c>
@@ -3536,7 +3271,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
         <v>60</v>
       </c>
@@ -3544,7 +3279,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D109" t="s">
         <v>102</v>
       </c>
@@ -3570,12 +3305,12 @@
         <v>206</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B111" t="s">
         <v>60</v>
       </c>
@@ -3583,7 +3318,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D112" t="s">
         <v>102</v>
       </c>
@@ -3609,20 +3344,20 @@
         <v>206</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="114">
-      <c r="B114" s="8" t="s">
+    <row r="114" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B114" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C114" s="9" t="s">
+      <c r="C114" s="4" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B115" t="s">
         <v>60</v>
       </c>
@@ -3630,7 +3365,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D116" t="s">
         <v>102</v>
       </c>
@@ -3647,7 +3382,7 @@
         <v>220</v>
       </c>
       <c r="K116" t="s">
-        <v>221</v>
+        <v>508</v>
       </c>
       <c r="L116" t="s">
         <v>205</v>
@@ -3656,12 +3391,12 @@
         <v>206</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B119" t="s">
         <v>60</v>
       </c>
@@ -3669,7 +3404,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D120" t="s">
         <v>102</v>
       </c>
@@ -3677,13 +3412,13 @@
         <v>163</v>
       </c>
       <c r="F120" t="s">
+        <v>221</v>
+      </c>
+      <c r="G120" t="s">
         <v>222</v>
       </c>
-      <c r="G120" t="s">
+      <c r="H120" t="s">
         <v>223</v>
-      </c>
-      <c r="H120" t="s">
-        <v>224</v>
       </c>
       <c r="K120" t="s">
         <v>216</v>
@@ -3695,25 +3430,25 @@
         <v>206</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="122">
-      <c r="B122" s="8" t="s">
+    <row r="122" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B122" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="123">
-      <c r="B123" s="10"/>
-    </row>
-    <row r="124">
+    <row r="123" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B123" s="7"/>
+    </row>
+    <row r="124" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
         <v>60</v>
       </c>
@@ -3721,135 +3456,135 @@
         <v>207</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D126" t="s">
+        <v>224</v>
+      </c>
+      <c r="F126" t="s">
         <v>225</v>
       </c>
-      <c r="F126" t="s">
+      <c r="G126" t="s">
         <v>226</v>
       </c>
-      <c r="G126" t="s">
+      <c r="H126" t="s">
         <v>227</v>
       </c>
-      <c r="H126" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="127">
+    </row>
+    <row r="127" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D129" t="s">
         <v>68</v>
       </c>
       <c r="F129" t="s">
+        <v>228</v>
+      </c>
+      <c r="G129" t="s">
         <v>229</v>
       </c>
-      <c r="G129" t="s">
+      <c r="H129" t="s">
         <v>230</v>
       </c>
-      <c r="H129" t="s">
+      <c r="K129" t="s">
         <v>231</v>
       </c>
-      <c r="K129" t="s">
+      <c r="L129" t="s">
         <v>232</v>
       </c>
-      <c r="L129" t="s">
+      <c r="M129" t="s">
         <v>233</v>
       </c>
-      <c r="M129" t="s">
+      <c r="N129" t="s">
         <v>234</v>
       </c>
-      <c r="N129" t="s">
+      <c r="O129" t="s">
         <v>235</v>
-      </c>
-      <c r="O129" t="s">
-        <v>236</v>
       </c>
       <c r="P129" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D130" t="s">
         <v>82</v>
       </c>
       <c r="F130" t="s">
+        <v>236</v>
+      </c>
+      <c r="G130" t="s">
         <v>237</v>
       </c>
-      <c r="G130" t="s">
+      <c r="H130" t="s">
         <v>238</v>
       </c>
-      <c r="H130" t="s">
+      <c r="K130" t="s">
         <v>239</v>
       </c>
-      <c r="K130" t="s">
+      <c r="L130" t="s">
         <v>240</v>
       </c>
-      <c r="L130" t="s">
+      <c r="M130" t="s">
         <v>241</v>
       </c>
-      <c r="M130" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="131">
+    </row>
+    <row r="131" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D133" t="s">
         <v>102</v>
       </c>
       <c r="E133" t="s">
+        <v>242</v>
+      </c>
+      <c r="F133" t="s">
         <v>243</v>
       </c>
-      <c r="F133" t="s">
+      <c r="G133" t="s">
         <v>244</v>
       </c>
-      <c r="G133" t="s">
+      <c r="H133" t="s">
         <v>245</v>
       </c>
-      <c r="H133" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="134">
+    </row>
+    <row r="134" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B134" t="s">
         <v>60</v>
       </c>
       <c r="C134" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="135">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="135" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D135" t="s">
         <v>51</v>
       </c>
       <c r="F135" t="s">
+        <v>247</v>
+      </c>
+      <c r="G135" t="s">
         <v>248</v>
       </c>
-      <c r="G135" t="s">
+      <c r="H135" t="s">
         <v>249</v>
       </c>
-      <c r="H135" t="s">
+      <c r="K135" t="s">
         <v>250</v>
-      </c>
-      <c r="K135" t="s">
-        <v>251</v>
       </c>
       <c r="L135" t="s">
         <v>147</v>
@@ -3858,447 +3593,447 @@
         <v>148</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B137" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B138" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D139" t="s">
         <v>102</v>
       </c>
       <c r="E139" t="s">
+        <v>251</v>
+      </c>
+      <c r="F139" t="s">
         <v>252</v>
       </c>
-      <c r="F139" t="s">
+      <c r="G139" t="s">
         <v>253</v>
       </c>
-      <c r="G139" t="s">
+      <c r="H139" t="s">
         <v>254</v>
       </c>
-      <c r="H139" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="140">
+    </row>
+    <row r="140" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D140" t="s">
         <v>102</v>
       </c>
       <c r="E140" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F140" t="s">
+        <v>255</v>
+      </c>
+      <c r="G140" t="s">
         <v>256</v>
       </c>
-      <c r="G140" t="s">
+      <c r="H140" t="s">
         <v>257</v>
       </c>
-      <c r="H140" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="141">
+    </row>
+    <row r="141" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D141" t="s">
         <v>102</v>
       </c>
       <c r="E141" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F141" t="s">
+        <v>258</v>
+      </c>
+      <c r="G141" t="s">
         <v>259</v>
       </c>
-      <c r="G141" t="s">
+      <c r="H141" t="s">
         <v>260</v>
       </c>
-      <c r="H141" t="s">
+    </row>
+    <row r="142" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B142" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C142" s="8" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="142">
-      <c r="B142" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C142" s="11" t="s">
+      <c r="D142" s="8"/>
+      <c r="E142" s="8"/>
+      <c r="F142" s="8"/>
+      <c r="G142" s="8"/>
+      <c r="H142" s="8"/>
+      <c r="I142" s="8"/>
+    </row>
+    <row r="143" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B143" s="8"/>
+      <c r="C143" s="8"/>
+      <c r="D143" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E143" s="8"/>
+      <c r="F143" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="D142" s="11"/>
-      <c r="E142" s="11"/>
-      <c r="F142" s="11"/>
-      <c r="G142" s="11"/>
-      <c r="H142" s="11"/>
-      <c r="I142" s="11"/>
-    </row>
-    <row r="143">
-      <c r="B143" s="11"/>
-      <c r="C143" s="11"/>
-      <c r="D143" s="11" t="s">
+      <c r="G143" s="8"/>
+      <c r="H143" s="8"/>
+      <c r="I143" s="8" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="144" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B144" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C144" s="8"/>
+      <c r="D144" s="8"/>
+      <c r="E144" s="8"/>
+      <c r="F144" s="8"/>
+      <c r="G144" s="8"/>
+      <c r="H144" s="8"/>
+      <c r="I144" s="8"/>
+    </row>
+    <row r="145" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B145" s="8"/>
+      <c r="C145" s="8"/>
+      <c r="D145" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E143" s="11"/>
-      <c r="F143" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="G143" s="11"/>
-      <c r="H143" s="11"/>
-      <c r="I143" s="11" t="s">
+      <c r="E145" s="8"/>
+      <c r="F145" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="G145" s="8"/>
+      <c r="H145" s="8"/>
+      <c r="I145" s="8" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="144">
-      <c r="B144" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C144" s="11"/>
-      <c r="D144" s="11"/>
-      <c r="E144" s="11"/>
-      <c r="F144" s="11"/>
-      <c r="G144" s="11"/>
-      <c r="H144" s="11"/>
-      <c r="I144" s="11"/>
-    </row>
-    <row r="145">
-      <c r="B145" s="11"/>
-      <c r="C145" s="11"/>
-      <c r="D145" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E145" s="11"/>
-      <c r="F145" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="G145" s="11"/>
-      <c r="H145" s="11"/>
-      <c r="I145" s="11" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="B146" s="11" t="s">
+    <row r="146" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B146" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C146" s="11"/>
-      <c r="D146" s="11"/>
-      <c r="E146" s="11"/>
-      <c r="F146" s="11"/>
-      <c r="G146" s="11"/>
-      <c r="H146" s="11"/>
-      <c r="I146" s="11"/>
-    </row>
-    <row r="147">
+      <c r="C146" s="8"/>
+      <c r="D146" s="8"/>
+      <c r="E146" s="8"/>
+      <c r="F146" s="8"/>
+      <c r="G146" s="8"/>
+      <c r="H146" s="8"/>
+      <c r="I146" s="8"/>
+    </row>
+    <row r="147" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B147" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B148" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D149" t="s">
         <v>102</v>
       </c>
       <c r="E149" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F149" t="s">
+        <v>265</v>
+      </c>
+      <c r="G149" t="s">
         <v>266</v>
       </c>
-      <c r="G149" t="s">
+      <c r="H149" t="s">
         <v>267</v>
       </c>
-      <c r="H149" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="150">
+    </row>
+    <row r="150" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D150" t="s">
         <v>102</v>
       </c>
       <c r="E150" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F150" t="s">
+        <v>268</v>
+      </c>
+      <c r="G150" t="s">
         <v>269</v>
       </c>
-      <c r="G150" t="s">
+      <c r="H150" t="s">
         <v>270</v>
       </c>
-      <c r="H150" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="151">
+    </row>
+    <row r="151" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D151" t="s">
         <v>102</v>
       </c>
       <c r="E151" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F151" t="s">
+        <v>271</v>
+      </c>
+      <c r="G151" t="s">
         <v>272</v>
       </c>
-      <c r="G151" t="s">
+      <c r="H151" t="s">
         <v>273</v>
       </c>
-      <c r="H151" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="152">
+    </row>
+    <row r="152" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B152" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B153" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D154" t="s">
         <v>102</v>
       </c>
       <c r="E154" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F154" t="s">
+        <v>274</v>
+      </c>
+      <c r="G154" t="s">
         <v>275</v>
       </c>
-      <c r="G154" t="s">
+      <c r="H154" t="s">
         <v>276</v>
       </c>
-      <c r="H154" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="155">
+    </row>
+    <row r="155" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D155" t="s">
         <v>68</v>
       </c>
       <c r="F155" t="s">
+        <v>277</v>
+      </c>
+      <c r="G155" t="s">
         <v>278</v>
       </c>
-      <c r="G155" t="s">
+      <c r="H155" t="s">
         <v>279</v>
       </c>
-      <c r="H155" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="156">
+    </row>
+    <row r="156" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B156" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="157" s="12" customFormat="1">
-      <c r="B157" s="12" t="s">
+    <row r="157" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="158" s="12" customFormat="1">
-      <c r="D158" s="12" t="s">
+    <row r="158" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D158" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E158" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="F158" s="12" t="s">
+      <c r="E158" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="F158" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="G158" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="G158" s="12" t="s">
+      <c r="H158" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="H158" s="12" t="s">
+    </row>
+    <row r="159" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B159" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C159" s="9" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="159" s="12" customFormat="1">
-      <c r="B159" s="12" t="s">
+    <row r="160" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D160" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E160" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="F160" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="G160" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="H160" s="9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="161" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B161" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C159" s="12" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="160" s="12" customFormat="1">
-      <c r="D160" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E160" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="F160" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="G160" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="H160" s="12" t="s">
+      <c r="C161" s="9" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="161" s="12" customFormat="1">
-      <c r="B161" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C161" s="12" t="s">
+    <row r="162" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D162" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F162" s="9" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="162" s="12" customFormat="1">
-      <c r="D162" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="F162" s="12" t="s">
+      <c r="G162" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="G162" s="12" t="s">
+      <c r="H162" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="H162" s="12" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="163" s="12" customFormat="1">
-      <c r="B163" s="12" t="s">
+    </row>
+    <row r="163" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B163" s="9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="164" s="12" customFormat="1">
-      <c r="B164" s="12" t="s">
+    <row r="164" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B164" s="9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="165" s="12" customFormat="1">
-      <c r="B165" s="12" t="s">
+    <row r="165" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B165" s="9" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="166" s="12" customFormat="1">
-      <c r="B166" s="12" t="s">
+    <row r="166" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B166" s="9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="167" s="4" customFormat="1">
+    <row r="167" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="D167" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F167" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="G167" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="G167" s="4" t="s">
+      <c r="H167" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="H167" s="4" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="168" s="4" customFormat="1">
+    </row>
+    <row r="168" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B168" s="4" t="s">
         <v>60</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="169" s="4" customFormat="1">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="169" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="D169" s="4" t="s">
         <v>86</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F169" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="G169" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="G169" s="4" t="s">
+      <c r="H169" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="H169" s="4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="170" s="4" customFormat="1">
+    </row>
+    <row r="170" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B170" s="4" t="s">
         <v>60</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="171" s="4" customFormat="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="171" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="D171" s="4" t="s">
         <v>68</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G171" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="H171" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="H171" s="4" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="172" s="4" customFormat="1">
+    </row>
+    <row r="172" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B172" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="173" s="4" customFormat="1">
+    <row r="173" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B173" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="174" s="4" customFormat="1">
+    <row r="174" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B174" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B175" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D176" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F176" t="s">
+        <v>301</v>
+      </c>
+      <c r="G176" t="s">
         <v>302</v>
       </c>
-      <c r="G176" t="s">
+      <c r="H176" t="s">
         <v>303</v>
       </c>
-      <c r="H176" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="177">
+    </row>
+    <row r="177" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B177" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B178" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D179" t="s">
         <v>102</v>
       </c>
@@ -4306,16 +4041,16 @@
         <v>163</v>
       </c>
       <c r="F179" t="s">
+        <v>304</v>
+      </c>
+      <c r="G179" t="s">
         <v>305</v>
       </c>
-      <c r="G179" t="s">
+      <c r="H179" t="s">
         <v>306</v>
       </c>
-      <c r="H179" t="s">
+      <c r="K179" t="s">
         <v>307</v>
-      </c>
-      <c r="K179" t="s">
-        <v>308</v>
       </c>
       <c r="L179" t="s">
         <v>205</v>
@@ -4324,34 +4059,34 @@
         <v>206</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B180" t="s">
         <v>60</v>
       </c>
       <c r="C180" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="181">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="181" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D181" t="s">
         <v>68</v>
       </c>
       <c r="F181" t="s">
+        <v>309</v>
+      </c>
+      <c r="G181" t="s">
         <v>310</v>
       </c>
-      <c r="G181" t="s">
+      <c r="H181" t="s">
         <v>311</v>
       </c>
-      <c r="H181" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="182">
+    </row>
+    <row r="182" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B182" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D183" t="s">
         <v>102</v>
       </c>
@@ -4359,16 +4094,16 @@
         <v>163</v>
       </c>
       <c r="F183" t="s">
+        <v>312</v>
+      </c>
+      <c r="G183" t="s">
         <v>313</v>
       </c>
-      <c r="G183" t="s">
+      <c r="H183" t="s">
         <v>314</v>
       </c>
-      <c r="H183" t="s">
+      <c r="K183" t="s">
         <v>315</v>
-      </c>
-      <c r="K183" t="s">
-        <v>316</v>
       </c>
       <c r="L183" t="s">
         <v>205</v>
@@ -4377,51 +4112,51 @@
         <v>206</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B184" t="s">
         <v>60</v>
       </c>
       <c r="C184" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="185">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="185" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D185" t="s">
         <v>68</v>
       </c>
       <c r="F185" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G185" t="s">
+        <v>310</v>
+      </c>
+      <c r="H185" t="s">
         <v>311</v>
       </c>
-      <c r="H185" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="186">
+    </row>
+    <row r="186" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B186" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D187" t="s">
         <v>102</v>
       </c>
       <c r="E187" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F187" t="s">
+        <v>318</v>
+      </c>
+      <c r="G187" t="s">
         <v>319</v>
       </c>
-      <c r="G187" t="s">
+      <c r="H187" t="s">
         <v>320</v>
       </c>
-      <c r="H187" t="s">
+      <c r="K187" t="s">
         <v>321</v>
-      </c>
-      <c r="K187" t="s">
-        <v>322</v>
       </c>
       <c r="L187" t="s">
         <v>205</v>
@@ -4430,460 +4165,479 @@
         <v>206</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B188" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B189" t="s">
         <v>60</v>
       </c>
       <c r="C189" t="s">
+        <v>322</v>
+      </c>
+      <c r="S189" t="s">
         <v>323</v>
       </c>
-      <c r="S189" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="190">
+    </row>
+    <row r="190" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B190" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D191" t="s">
         <v>45</v>
       </c>
       <c r="F191" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I191">
         <v>2</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D192" t="s">
         <v>160</v>
       </c>
       <c r="G192" t="s">
+        <v>325</v>
+      </c>
+      <c r="H192" t="s">
         <v>326</v>
       </c>
-      <c r="H192" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="193">
+    </row>
+    <row r="193" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B193" t="s">
         <v>60</v>
       </c>
       <c r="C193" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="194">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="194" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D194" t="s">
         <v>160</v>
       </c>
       <c r="G194" t="s">
+        <v>327</v>
+      </c>
+      <c r="H194" t="s">
         <v>328</v>
       </c>
-      <c r="H194" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="195">
+    </row>
+    <row r="195" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B195" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B196" t="s">
         <v>60</v>
       </c>
       <c r="C196" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="197">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="197" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D197" t="s">
         <v>160</v>
       </c>
       <c r="G197" t="s">
+        <v>329</v>
+      </c>
+      <c r="H197" t="s">
         <v>330</v>
       </c>
-      <c r="H197" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="198">
+    </row>
+    <row r="198" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B198" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B199" t="s">
         <v>60</v>
       </c>
       <c r="C199" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="200">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="200" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D200" t="s">
         <v>160</v>
       </c>
       <c r="G200" t="s">
+        <v>332</v>
+      </c>
+      <c r="H200" t="s">
         <v>333</v>
       </c>
-      <c r="H200" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="201">
+    </row>
+    <row r="201" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B201" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B202" t="s">
         <v>60</v>
       </c>
       <c r="C202" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="203">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="203" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D203" t="s">
         <v>160</v>
       </c>
       <c r="G203" t="s">
+        <v>335</v>
+      </c>
+      <c r="H203" t="s">
         <v>336</v>
       </c>
-      <c r="H203" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="204">
+    </row>
+    <row r="204" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B204" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B205" t="s">
         <v>60</v>
       </c>
       <c r="C205" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="206">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="206" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D206" t="s">
         <v>160</v>
       </c>
       <c r="G206" t="s">
+        <v>338</v>
+      </c>
+      <c r="H206" t="s">
         <v>339</v>
       </c>
-      <c r="H206" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="207">
+    </row>
+    <row r="207" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B207" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B208" t="s">
         <v>60</v>
       </c>
       <c r="C208" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="209">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="209" spans="2:20" x14ac:dyDescent="0.35">
       <c r="D209" t="s">
         <v>160</v>
       </c>
       <c r="G209" t="s">
+        <v>341</v>
+      </c>
+      <c r="H209" t="s">
         <v>342</v>
       </c>
-      <c r="H209" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="210">
+    </row>
+    <row r="210" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B210" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B211" t="s">
         <v>60</v>
       </c>
       <c r="C211" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="212">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="212" spans="2:20" x14ac:dyDescent="0.35">
       <c r="D212" t="s">
         <v>160</v>
       </c>
       <c r="G212" t="s">
+        <v>344</v>
+      </c>
+      <c r="H212" t="s">
         <v>345</v>
       </c>
-      <c r="H212" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="213">
+    </row>
+    <row r="213" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B213" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B214" t="s">
         <v>60</v>
       </c>
       <c r="C214" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="215">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="215" spans="2:20" x14ac:dyDescent="0.35">
       <c r="D215" t="s">
         <v>160</v>
       </c>
       <c r="G215" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H215" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="216">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="216" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B216" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B217" t="s">
         <v>60</v>
       </c>
       <c r="C217" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="218">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="218" spans="2:20" x14ac:dyDescent="0.35">
       <c r="D218" t="s">
         <v>160</v>
       </c>
       <c r="G218" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H218" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B219" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B221" t="s">
         <v>60</v>
       </c>
-      <c r="C221" s="13" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="222">
+      <c r="C221" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="222" spans="2:20" x14ac:dyDescent="0.35">
       <c r="D222" t="s">
         <v>160</v>
       </c>
-      <c r="G222" s="14" t="s">
+      <c r="G222" t="s">
         <v>161</v>
       </c>
-      <c r="H222" s="14" t="s">
+      <c r="H222" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B223" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B224" t="s">
+        <v>60</v>
+      </c>
+      <c r="C224" t="s">
+        <v>506</v>
+      </c>
       <c r="S224" t="s">
         <v>60</v>
       </c>
       <c r="T224" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="225">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="225" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="C225" s="2"/>
+      <c r="D225" t="s">
+        <v>160</v>
+      </c>
+      <c r="G225" t="s">
+        <v>505</v>
+      </c>
+      <c r="H225" t="s">
+        <v>507</v>
+      </c>
       <c r="U225" t="s">
         <v>160</v>
       </c>
       <c r="X225" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="Y225" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="226">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="226" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B226" t="s">
+        <v>50</v>
+      </c>
       <c r="S226" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B231" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B232" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B233" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="2:25" x14ac:dyDescent="0.35">
       <c r="D234" t="s">
         <v>82</v>
       </c>
       <c r="F234" t="s">
+        <v>353</v>
+      </c>
+      <c r="G234" t="s">
+        <v>354</v>
+      </c>
+      <c r="H234" t="s">
+        <v>355</v>
+      </c>
+      <c r="K234" t="s">
         <v>356</v>
       </c>
-      <c r="G234" t="s">
+      <c r="L234" t="s">
         <v>357</v>
       </c>
-      <c r="H234" t="s">
+      <c r="M234" t="s">
         <v>358</v>
       </c>
-      <c r="K234" t="s">
-        <v>359</v>
-      </c>
-      <c r="L234" t="s">
-        <v>360</v>
-      </c>
-      <c r="M234" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="235">
+    </row>
+    <row r="235" spans="2:25" x14ac:dyDescent="0.35">
       <c r="D235" t="s">
         <v>82</v>
       </c>
       <c r="F235" t="s">
+        <v>359</v>
+      </c>
+      <c r="G235" t="s">
+        <v>360</v>
+      </c>
+      <c r="H235" t="s">
+        <v>361</v>
+      </c>
+      <c r="K235" t="s">
         <v>362</v>
       </c>
-      <c r="G235" t="s">
+      <c r="L235" t="s">
         <v>363</v>
       </c>
-      <c r="H235" t="s">
+      <c r="M235" t="s">
         <v>364</v>
       </c>
-      <c r="K235" t="s">
-        <v>365</v>
-      </c>
-      <c r="L235" t="s">
-        <v>366</v>
-      </c>
-      <c r="M235" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="236">
+    </row>
+    <row r="236" spans="2:25" x14ac:dyDescent="0.35">
       <c r="D236" t="s">
         <v>45</v>
       </c>
       <c r="F236" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I236" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="237">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="237" spans="2:25" x14ac:dyDescent="0.35">
       <c r="D237" t="s">
         <v>160</v>
       </c>
       <c r="G237" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H237" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="238">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="238" spans="2:25" x14ac:dyDescent="0.35">
       <c r="D238" t="s">
         <v>45</v>
       </c>
       <c r="F238" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I238">
         <v>1</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B239" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B240" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D241" t="s">
         <v>45</v>
       </c>
       <c r="F241" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I241" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="242">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="242" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D242" t="s">
         <v>51</v>
       </c>
       <c r="F242" t="s">
+        <v>369</v>
+      </c>
+      <c r="G242" t="s">
+        <v>371</v>
+      </c>
+      <c r="H242" t="s">
         <v>372</v>
       </c>
-      <c r="G242" t="s">
+      <c r="Q242" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D243" t="s">
+        <v>373</v>
+      </c>
+      <c r="F243" t="s">
         <v>374</v>
       </c>
-      <c r="H242" t="s">
+      <c r="G243" t="s">
         <v>375</v>
       </c>
-      <c r="Q242" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="D243" t="s">
+      <c r="H243" t="s">
         <v>376</v>
       </c>
-      <c r="F243" t="s">
+      <c r="K243" t="s">
         <v>377</v>
-      </c>
-      <c r="G243" t="s">
-        <v>378</v>
-      </c>
-      <c r="H243" t="s">
-        <v>379</v>
-      </c>
-      <c r="K243" t="s">
-        <v>380</v>
       </c>
       <c r="L243" t="s">
         <v>205</v>
@@ -4892,195 +4646,194 @@
         <v>206</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D244" t="s">
         <v>45</v>
       </c>
       <c r="F244" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="I244" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="245">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="245" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D245" t="s">
         <v>82</v>
       </c>
       <c r="F245" t="s">
+        <v>380</v>
+      </c>
+      <c r="G245" t="s">
+        <v>381</v>
+      </c>
+      <c r="H245" t="s">
+        <v>382</v>
+      </c>
+      <c r="K245" t="s">
         <v>383</v>
       </c>
-      <c r="G245" t="s">
+      <c r="L245" t="s">
         <v>384</v>
       </c>
-      <c r="H245" t="s">
+      <c r="M245" t="s">
         <v>385</v>
       </c>
-      <c r="K245" t="s">
-        <v>386</v>
-      </c>
-      <c r="L245" t="s">
-        <v>387</v>
-      </c>
-      <c r="M245" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="246">
+    </row>
+    <row r="246" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D246" t="s">
         <v>45</v>
       </c>
       <c r="F246" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="I246" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="247">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="247" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D247" t="s">
         <v>160</v>
       </c>
       <c r="G247" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H247" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="248">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="248" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B248" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B249" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B250" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D251" t="s">
         <v>110</v>
       </c>
       <c r="E251" t="s">
+        <v>390</v>
+      </c>
+      <c r="F251" t="s">
+        <v>391</v>
+      </c>
+      <c r="G251" t="s">
+        <v>392</v>
+      </c>
+      <c r="H251" t="s">
         <v>393</v>
       </c>
-      <c r="F251" t="s">
-        <v>394</v>
-      </c>
-      <c r="G251" t="s">
-        <v>395</v>
-      </c>
-      <c r="H251" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="252">
+    </row>
+    <row r="252" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B252" t="s">
         <v>60</v>
       </c>
       <c r="C252" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="253">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="253" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D253" t="s">
         <v>110</v>
       </c>
       <c r="E253" t="s">
+        <v>395</v>
+      </c>
+      <c r="F253" t="s">
+        <v>396</v>
+      </c>
+      <c r="G253" t="s">
+        <v>397</v>
+      </c>
+      <c r="H253" t="s">
         <v>398</v>
       </c>
-      <c r="F253" t="s">
-        <v>399</v>
-      </c>
-      <c r="G253" t="s">
-        <v>400</v>
-      </c>
-      <c r="H253" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="254">
+    </row>
+    <row r="254" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B254" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B255" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B256" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B257" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D258" t="s">
         <v>160</v>
       </c>
       <c r="G258" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="H258" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="259">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="259" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D259" t="s">
         <v>45</v>
       </c>
       <c r="F259" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I259">
         <v>2</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B260" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B261" t="s">
         <v>50</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="4294967293" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E160"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="16.54296875"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="13.81640625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="31.453125"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="43"/>
+    <col min="1" max="1" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="15" customFormat="1">
+    <row r="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -5088,11 +4841,11 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="2">
+      <c r="E1" s="10" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>103</v>
       </c>
@@ -5101,13 +4854,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D2" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>103</v>
       </c>
@@ -5116,13 +4869,13 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D3" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>163</v>
       </c>
@@ -5131,13 +4884,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D4" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>163</v>
       </c>
@@ -5146,43 +4899,43 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D5" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B6" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D6" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B7" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D7" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>149</v>
       </c>
@@ -5190,58 +4943,58 @@
         <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D8" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B9" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D9" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B10" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D10" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B11" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D11" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>87</v>
       </c>
@@ -5250,478 +5003,478 @@
         <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D12" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B13" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D13" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E13" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B14" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D14" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B15" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D15" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B16" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D16" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E16" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B17" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D17" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E17" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B18" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D18" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B19" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D19" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B20" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D20" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B21" t="str">
         <f>"6"</f>
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D21" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B22" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D22" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B23" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D23" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B24" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D24" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B25" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D25" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B26" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D26" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B27" t="str">
         <f>"6"</f>
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D27" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B28" t="str">
         <f>"7"</f>
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D28" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E28" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B29" t="str">
         <f>"8"</f>
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E29" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B30" t="str">
         <f>"9"</f>
         <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D30" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E30" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B31" t="str">
         <f>"10"</f>
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D31" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E31" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B32" t="str">
         <f>"11"</f>
         <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D32" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E32" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B33" t="str">
         <f>"12"</f>
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D33" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E33" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B34" t="str">
         <f>"13"</f>
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D34" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E34" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B35" t="str">
         <f>"14"</f>
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D35" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E35" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B36" t="str">
         <f>"15"</f>
         <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D36" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E36" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B37" t="str">
         <f>"16"</f>
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D37" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E37" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B38" t="str">
         <f>"17"</f>
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D38" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E38" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B39" t="str">
         <f>"18"</f>
         <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D39" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E39" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B40" t="str">
         <f>"77"</f>
         <v>77</v>
       </c>
       <c r="C40" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D40" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>186</v>
       </c>
@@ -5730,13 +5483,13 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D41" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>186</v>
       </c>
@@ -5745,13 +5498,13 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D42" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>192</v>
       </c>
@@ -5760,13 +5513,13 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D43" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>192</v>
       </c>
@@ -5775,13 +5528,13 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D44" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>192</v>
       </c>
@@ -5790,13 +5543,13 @@
         <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D45" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>131</v>
       </c>
@@ -5805,13 +5558,13 @@
         <v>99</v>
       </c>
       <c r="C46" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D46" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>140</v>
       </c>
@@ -5820,13 +5573,13 @@
         <v>99</v>
       </c>
       <c r="C47" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="D47" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>168</v>
       </c>
@@ -5835,13 +5588,13 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="D48" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>168</v>
       </c>
@@ -5850,13 +5603,13 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D49" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>111</v>
       </c>
@@ -5865,13 +5618,13 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D50" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>111</v>
       </c>
@@ -5880,13 +5633,13 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D51" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>111</v>
       </c>
@@ -5895,13 +5648,13 @@
         <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="D52" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>111</v>
       </c>
@@ -5910,13 +5663,13 @@
         <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="D53" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>173</v>
       </c>
@@ -5925,439 +5678,435 @@
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D54" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="16"/>
-    </row>
-    <row r="79">
-      <c r="B79" s="16"/>
-    </row>
-    <row r="80">
-      <c r="B80" s="16"/>
-    </row>
-    <row r="81">
-      <c r="B81" s="16"/>
-    </row>
-    <row r="82">
-      <c r="B82" s="16"/>
-    </row>
-    <row r="83">
-      <c r="B83" s="16"/>
-    </row>
-    <row r="84">
-      <c r="B84" s="16"/>
-    </row>
-    <row r="85">
-      <c r="B85" s="16"/>
-    </row>
-    <row r="86">
-      <c r="B86" s="16"/>
-    </row>
-    <row r="87">
-      <c r="B87" s="16"/>
-    </row>
-    <row r="88">
-      <c r="B88" s="16"/>
-    </row>
-    <row r="89">
-      <c r="B89" s="16"/>
-    </row>
-    <row r="90">
-      <c r="B90" s="16"/>
-    </row>
-    <row r="91">
-      <c r="B91" s="16"/>
-    </row>
-    <row r="92">
-      <c r="B92" s="16"/>
-    </row>
-    <row r="93">
-      <c r="B93" s="16"/>
-    </row>
-    <row r="94">
-      <c r="B94" s="16"/>
-    </row>
-    <row r="95">
-      <c r="B95" s="16"/>
-    </row>
-    <row r="96">
-      <c r="B96" s="16"/>
-    </row>
-    <row r="97">
-      <c r="B97" s="16"/>
-    </row>
-    <row r="98">
-      <c r="B98" s="16"/>
-    </row>
-    <row r="99">
-      <c r="B99" s="16"/>
-    </row>
-    <row r="100">
-      <c r="B100" s="16"/>
-    </row>
-    <row r="101">
-      <c r="B101" s="16"/>
-    </row>
-    <row r="102">
-      <c r="B102" s="16"/>
-    </row>
-    <row r="103">
-      <c r="B103" s="16"/>
-    </row>
-    <row r="104">
-      <c r="B104" s="16"/>
-    </row>
-    <row r="105">
-      <c r="B105" s="16"/>
-    </row>
-    <row r="106">
-      <c r="B106" s="16"/>
-    </row>
-    <row r="107">
-      <c r="B107" s="16"/>
-    </row>
-    <row r="108">
-      <c r="B108" s="16"/>
-    </row>
-    <row r="109">
-      <c r="B109" s="16"/>
-      <c r="C109" s="16"/>
-    </row>
-    <row r="110">
-      <c r="B110" s="16"/>
-      <c r="C110" s="16"/>
-    </row>
-    <row r="111">
-      <c r="B111" s="16"/>
-      <c r="C111" s="16"/>
-    </row>
-    <row r="112">
-      <c r="B112" s="16"/>
-      <c r="C112" s="16"/>
-    </row>
-    <row r="113">
-      <c r="B113" s="16"/>
-      <c r="C113" s="16"/>
-    </row>
-    <row r="114">
-      <c r="B114" s="16"/>
-      <c r="C114" s="16"/>
-    </row>
-    <row r="115">
-      <c r="B115" s="16"/>
-      <c r="C115" s="16"/>
-    </row>
-    <row r="116">
-      <c r="C116" s="16"/>
-    </row>
-    <row r="117">
-      <c r="B117" s="16"/>
-      <c r="C117" s="16"/>
-    </row>
-    <row r="118">
-      <c r="B118" s="16"/>
-      <c r="C118" s="16"/>
-    </row>
-    <row r="119">
-      <c r="B119" s="16"/>
-      <c r="C119" s="16"/>
-    </row>
-    <row r="120">
-      <c r="B120" s="16"/>
-      <c r="C120" s="16"/>
-    </row>
-    <row r="121">
-      <c r="B121" s="16"/>
-      <c r="C121" s="16"/>
-    </row>
-    <row r="122">
-      <c r="B122" s="16"/>
-      <c r="C122" s="16"/>
-    </row>
-    <row r="123">
-      <c r="B123" s="16"/>
-      <c r="C123" s="16"/>
-    </row>
-    <row r="124">
-      <c r="B124" s="16"/>
-      <c r="C124" s="16"/>
-    </row>
-    <row r="125">
-      <c r="B125" s="16"/>
-      <c r="C125" s="16"/>
-    </row>
-    <row r="126">
-      <c r="B126" s="16"/>
-      <c r="C126" s="16"/>
-    </row>
-    <row r="127">
-      <c r="B127" s="16"/>
-      <c r="C127" s="16"/>
-    </row>
-    <row r="128">
-      <c r="B128" s="16"/>
-      <c r="C128" s="16"/>
-    </row>
-    <row r="129">
-      <c r="B129" s="16"/>
-      <c r="C129" s="16"/>
-    </row>
-    <row r="130">
-      <c r="B130" s="16"/>
-      <c r="C130" s="16"/>
-    </row>
-    <row r="131">
-      <c r="B131" s="16"/>
-      <c r="C131" s="16"/>
-    </row>
-    <row r="132">
-      <c r="B132" s="16"/>
-      <c r="C132" s="16"/>
-    </row>
-    <row r="133">
-      <c r="B133" s="16"/>
-      <c r="C133" s="16"/>
-    </row>
-    <row r="134">
-      <c r="B134" s="16"/>
-      <c r="C134" s="16"/>
-    </row>
-    <row r="135">
-      <c r="B135" s="16"/>
-    </row>
-    <row r="136">
-      <c r="B136" s="16"/>
-    </row>
-    <row r="137">
-      <c r="B137" s="16"/>
-    </row>
-    <row r="138">
-      <c r="B138" s="16"/>
-    </row>
-    <row r="139">
-      <c r="B139" s="16"/>
-    </row>
-    <row r="140">
-      <c r="B140" s="16"/>
-    </row>
-    <row r="141">
-      <c r="B141" s="16"/>
-    </row>
-    <row r="143">
-      <c r="B143" s="16"/>
-    </row>
-    <row r="144">
-      <c r="B144" s="16"/>
-    </row>
-    <row r="145">
-      <c r="B145" s="16"/>
-    </row>
-    <row r="146">
-      <c r="B146" s="16"/>
-    </row>
-    <row r="147">
-      <c r="B147" s="16"/>
-    </row>
-    <row r="148">
-      <c r="B148" s="16"/>
-    </row>
-    <row r="149">
-      <c r="B149" s="16"/>
-    </row>
-    <row r="150">
-      <c r="B150" s="16"/>
-    </row>
-    <row r="151">
-      <c r="B151" s="16"/>
-    </row>
-    <row r="152">
-      <c r="B152" s="16"/>
-    </row>
-    <row r="153">
-      <c r="B153" s="16"/>
-    </row>
-    <row r="154">
-      <c r="B154" s="16"/>
-    </row>
-    <row r="155">
-      <c r="B155" s="16"/>
-    </row>
-    <row r="156">
-      <c r="B156" s="16"/>
-    </row>
-    <row r="157">
-      <c r="B157" s="16"/>
-    </row>
-    <row r="158">
-      <c r="B158" s="16"/>
-    </row>
-    <row r="159">
-      <c r="B159" s="16"/>
-    </row>
-    <row r="160">
-      <c r="B160" s="16"/>
+        <v>409</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B78" s="11"/>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B79" s="11"/>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B80" s="11"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B81" s="11"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B82" s="11"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B83" s="11"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B84" s="11"/>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B85" s="11"/>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B86" s="11"/>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B87" s="11"/>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B88" s="11"/>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B89" s="11"/>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B90" s="11"/>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B91" s="11"/>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B92" s="11"/>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B93" s="11"/>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B94" s="11"/>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B95" s="11"/>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B96" s="11"/>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B97" s="11"/>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B98" s="11"/>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B99" s="11"/>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B100" s="11"/>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B101" s="11"/>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B102" s="11"/>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B103" s="11"/>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B104" s="11"/>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B105" s="11"/>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B106" s="11"/>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B107" s="11"/>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B108" s="11"/>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B109" s="11"/>
+      <c r="C109" s="11"/>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B110" s="11"/>
+      <c r="C110" s="11"/>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B111" s="11"/>
+      <c r="C111" s="11"/>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B112" s="11"/>
+      <c r="C112" s="11"/>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B113" s="11"/>
+      <c r="C113" s="11"/>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B114" s="11"/>
+      <c r="C114" s="11"/>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B115" s="11"/>
+      <c r="C115" s="11"/>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C116" s="11"/>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B117" s="11"/>
+      <c r="C117" s="11"/>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B118" s="11"/>
+      <c r="C118" s="11"/>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B119" s="11"/>
+      <c r="C119" s="11"/>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B120" s="11"/>
+      <c r="C120" s="11"/>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B121" s="11"/>
+      <c r="C121" s="11"/>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B122" s="11"/>
+      <c r="C122" s="11"/>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B123" s="11"/>
+      <c r="C123" s="11"/>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B124" s="11"/>
+      <c r="C124" s="11"/>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B125" s="11"/>
+      <c r="C125" s="11"/>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B126" s="11"/>
+      <c r="C126" s="11"/>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B127" s="11"/>
+      <c r="C127" s="11"/>
+    </row>
+    <row r="128" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B128" s="11"/>
+      <c r="C128" s="11"/>
+    </row>
+    <row r="129" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B129" s="11"/>
+      <c r="C129" s="11"/>
+    </row>
+    <row r="130" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B130" s="11"/>
+      <c r="C130" s="11"/>
+    </row>
+    <row r="131" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B131" s="11"/>
+      <c r="C131" s="11"/>
+    </row>
+    <row r="132" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B132" s="11"/>
+      <c r="C132" s="11"/>
+    </row>
+    <row r="133" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B133" s="11"/>
+      <c r="C133" s="11"/>
+    </row>
+    <row r="134" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B134" s="11"/>
+      <c r="C134" s="11"/>
+    </row>
+    <row r="135" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B135" s="11"/>
+    </row>
+    <row r="136" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B136" s="11"/>
+    </row>
+    <row r="137" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B137" s="11"/>
+    </row>
+    <row r="138" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B138" s="11"/>
+    </row>
+    <row r="139" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B139" s="11"/>
+    </row>
+    <row r="140" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B140" s="11"/>
+    </row>
+    <row r="141" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B141" s="11"/>
+    </row>
+    <row r="143" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B143" s="11"/>
+    </row>
+    <row r="144" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B144" s="11"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B145" s="11"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B146" s="11"/>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B147" s="11"/>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B148" s="11"/>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B149" s="11"/>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B150" s="11"/>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B151" s="11"/>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B152" s="11"/>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B153" s="11"/>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B154" s="11"/>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B155" s="11"/>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B156" s="11"/>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B157" s="11"/>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B158" s="11"/>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B159" s="11"/>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B160" s="11"/>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="16.7265625"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="40.54296875"/>
+    <col min="1" max="1" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="17" t="s">
-        <v>480</v>
-      </c>
-      <c r="B1" s="17" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="15.453125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="12.1796875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="20.7265625"/>
-    <col customWidth="1" min="4" max="4" width="40.1796875"/>
+    <col min="1" max="1" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="15" customFormat="1">
+    <row r="1" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="2" ht="130.5">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C2" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="3" ht="87">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C3" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="18.81640625"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="6"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="12.81640625"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="34.1796875"/>
+    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="18" customFormat="1">
-      <c r="A1" s="18" t="s">
-        <v>491</v>
-      </c>
-      <c r="B1" s="18" t="s">
+    <row r="1" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="18" t="s">
-        <v>492</v>
-      </c>
-      <c r="D1" s="18" t="s">
+      <c r="C1" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:D124"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="13.7265625"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="23.1796875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="16.7265625"/>
+    <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
@@ -6365,15 +6114,15 @@
         <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B2" t="s">
         <v>110</v>
@@ -6382,10 +6131,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -6396,9 +6145,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B4" t="s">
         <v>82</v>
@@ -6407,7 +6156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>78</v>
       </c>
@@ -6418,7 +6167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>88</v>
       </c>
@@ -6429,7 +6178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -6440,18 +6189,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>201</v>
       </c>
@@ -6462,29 +6211,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>92</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>97</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="14" t="s">
         <v>86</v>
       </c>
       <c r="C11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>164</v>
       </c>
@@ -6495,7 +6244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>169</v>
       </c>
@@ -6506,9 +6255,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B14" t="s">
         <v>102</v>
@@ -6517,7 +6266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -6528,9 +6277,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B16" t="s">
         <v>51</v>
@@ -6539,9 +6288,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B17" t="s">
         <v>102</v>
@@ -6550,9 +6299,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B18" t="s">
         <v>102</v>
@@ -6561,7 +6310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>143</v>
       </c>
@@ -6572,7 +6321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>150</v>
       </c>
@@ -6583,9 +6332,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B21" t="s">
         <v>110</v>
@@ -6594,9 +6343,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B22" t="s">
         <v>102</v>
@@ -6605,20 +6354,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B23" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C23" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B24" t="s">
         <v>45</v>
@@ -6627,7 +6376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>125</v>
       </c>
@@ -6638,7 +6387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>154</v>
       </c>
@@ -6649,7 +6398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>157</v>
       </c>
@@ -6660,20 +6409,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>132</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="14" t="s">
         <v>86</v>
       </c>
       <c r="C28" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B29" t="s">
         <v>45</v>
@@ -6682,9 +6431,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B30" t="s">
         <v>51</v>
@@ -6693,9 +6442,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B31" t="s">
         <v>102</v>
@@ -6704,9 +6453,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B32" t="s">
         <v>102</v>
@@ -6715,9 +6464,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s">
         <v>68</v>
@@ -6726,7 +6475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>99</v>
       </c>
@@ -6737,7 +6486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>107</v>
       </c>
@@ -6748,7 +6497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>116</v>
       </c>
@@ -6759,9 +6508,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B37" t="s">
         <v>82</v>
@@ -6770,9 +6519,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B38" t="s">
         <v>45</v>
@@ -6781,9 +6530,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B39" t="s">
         <v>68</v>
@@ -6792,9 +6541,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B40" t="s">
         <v>68</v>
@@ -6803,7 +6552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>69</v>
       </c>
@@ -6814,9 +6563,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B42" t="s">
         <v>102</v>
@@ -6825,9 +6574,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B43" t="s">
         <v>102</v>
@@ -6836,20 +6585,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>368</v>
-      </c>
-      <c r="B44" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="B44" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C44" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B45" t="s">
         <v>82</v>
@@ -6858,9 +6607,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s">
         <v>82</v>
@@ -6869,18 +6618,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>134</v>
       </c>
-      <c r="B47" s="19" t="s">
+      <c r="B47" s="14" t="s">
         <v>82</v>
       </c>
       <c r="C47" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>141</v>
       </c>
@@ -6891,7 +6640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>119</v>
       </c>
@@ -6902,7 +6651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>122</v>
       </c>
@@ -6913,9 +6662,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B51" t="s">
         <v>102</v>
@@ -6924,7 +6673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>112</v>
       </c>
@@ -6935,7 +6684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>208</v>
       </c>
@@ -6946,7 +6695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -6957,7 +6706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>46</v>
       </c>
@@ -6968,7 +6717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -6979,40 +6728,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>187</v>
       </c>
-      <c r="B57" s="19" t="s">
+      <c r="B57" s="14" t="s">
         <v>110</v>
       </c>
       <c r="C57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>193</v>
       </c>
-      <c r="B58" s="19" t="s">
+      <c r="B58" s="14" t="s">
         <v>110</v>
       </c>
       <c r="C58" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>198</v>
       </c>
-      <c r="B59" s="19" t="s">
+      <c r="B59" s="14" t="s">
         <v>110</v>
       </c>
       <c r="C59" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>180</v>
       </c>
@@ -7023,7 +6772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>188</v>
       </c>
@@ -7034,7 +6783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>194</v>
       </c>
@@ -7045,9 +6794,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B63" t="s">
         <v>68</v>
@@ -7056,7 +6805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>174</v>
       </c>
@@ -7067,9 +6816,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B65" t="s">
         <v>102</v>
@@ -7078,9 +6827,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B66" t="s">
         <v>102</v>
@@ -7089,9 +6838,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B67" t="s">
         <v>102</v>
@@ -7100,9 +6849,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B68" t="s">
         <v>102</v>
@@ -7111,20 +6860,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>302</v>
-      </c>
-      <c r="B69" s="19" t="s">
-        <v>225</v>
+        <v>301</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>224</v>
       </c>
       <c r="C69" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B70" t="s">
         <v>86</v>
@@ -7133,9 +6882,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B71" t="s">
         <v>86</v>
@@ -7144,9 +6893,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B72" t="s">
         <v>86</v>
@@ -7155,9 +6904,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B73" t="s">
         <v>68</v>
@@ -7166,9 +6915,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B74" t="s">
         <v>68</v>
@@ -7177,9 +6926,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B75" t="s">
         <v>68</v>
@@ -7188,7 +6937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>213</v>
       </c>
@@ -7199,9 +6948,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B77" t="s">
         <v>102</v>
@@ -7210,65 +6959,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="19"/>
-    </row>
-    <row r="79">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B78" s="14"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>501</v>
-      </c>
-      <c r="B79" s="19" t="s">
+        <v>497</v>
+      </c>
+      <c r="B79" s="14" t="s">
         <v>102</v>
       </c>
       <c r="C79" t="b">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>503</v>
-      </c>
-      <c r="B80" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="B80" s="14" t="s">
         <v>102</v>
       </c>
       <c r="C80" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>504</v>
-      </c>
-      <c r="B81" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="B81" s="14" t="s">
         <v>102</v>
       </c>
       <c r="C81" t="b">
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>505</v>
-      </c>
-      <c r="B82" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="B82" s="14" t="s">
         <v>102</v>
       </c>
       <c r="C82" t="b">
         <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B83" t="s">
         <v>51</v>
@@ -7277,155 +7026,153 @@
         <v>0</v>
       </c>
       <c r="D83" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="19"/>
-    </row>
-    <row r="85">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B84" s="14"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>218</v>
       </c>
-      <c r="B85" s="19" t="s">
+      <c r="B85" s="14" t="s">
         <v>102</v>
       </c>
       <c r="C85" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>222</v>
-      </c>
-      <c r="B86" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B86" s="14" t="s">
         <v>102</v>
       </c>
       <c r="C86" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="19"/>
-    </row>
-    <row r="88">
-      <c r="B88" s="19"/>
-    </row>
-    <row r="89">
-      <c r="B89" s="19"/>
-    </row>
-    <row r="90">
-      <c r="B90" s="19"/>
-    </row>
-    <row r="91">
-      <c r="B91" s="19"/>
-    </row>
-    <row r="92">
-      <c r="B92" s="19"/>
-    </row>
-    <row r="93">
-      <c r="B93" s="19"/>
-    </row>
-    <row r="94">
-      <c r="B94" s="19"/>
-    </row>
-    <row r="95">
-      <c r="B95" s="19"/>
-    </row>
-    <row r="96">
-      <c r="B96" s="19"/>
-    </row>
-    <row r="97">
-      <c r="B97" s="19"/>
-    </row>
-    <row r="98">
-      <c r="B98" s="19"/>
-    </row>
-    <row r="99">
-      <c r="B99" s="19"/>
-    </row>
-    <row r="100">
-      <c r="B100" s="19"/>
-    </row>
-    <row r="101">
-      <c r="B101" s="19"/>
-    </row>
-    <row r="102">
-      <c r="B102" s="19"/>
-    </row>
-    <row r="103">
-      <c r="B103" s="19"/>
-    </row>
-    <row r="104">
-      <c r="B104" s="19"/>
-    </row>
-    <row r="105">
-      <c r="B105" s="19"/>
-    </row>
-    <row r="106">
-      <c r="B106" s="19"/>
-    </row>
-    <row r="107">
-      <c r="B107" s="19"/>
-    </row>
-    <row r="108">
-      <c r="B108" s="19"/>
-    </row>
-    <row r="109">
-      <c r="B109" s="19"/>
-    </row>
-    <row r="110">
-      <c r="B110" s="19"/>
-    </row>
-    <row r="111">
-      <c r="B111" s="19"/>
-    </row>
-    <row r="112">
-      <c r="B112" s="19"/>
-    </row>
-    <row r="113">
-      <c r="B113" s="19"/>
-    </row>
-    <row r="114">
-      <c r="B114" s="19"/>
-    </row>
-    <row r="115">
-      <c r="B115" s="19"/>
-    </row>
-    <row r="116">
-      <c r="B116" s="19"/>
-    </row>
-    <row r="117">
-      <c r="B117" s="19"/>
-    </row>
-    <row r="118">
-      <c r="B118" s="19"/>
-    </row>
-    <row r="119">
-      <c r="B119" s="19"/>
-    </row>
-    <row r="120">
-      <c r="B120" s="19"/>
-    </row>
-    <row r="121">
-      <c r="B121" s="19"/>
-    </row>
-    <row r="122">
-      <c r="B122" s="19"/>
-    </row>
-    <row r="123">
-      <c r="B123" s="19"/>
-    </row>
-    <row r="124">
-      <c r="B124" s="19"/>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B87" s="14"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B88" s="14"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B89" s="14"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B90" s="14"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B91" s="14"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B92" s="14"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B93" s="14"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B94" s="14"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B95" s="14"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B96" s="14"/>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B97" s="14"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B98" s="14"/>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B99" s="14"/>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B100" s="14"/>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B101" s="14"/>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B102" s="14"/>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B103" s="14"/>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B104" s="14"/>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B105" s="14"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B106" s="14"/>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B107" s="14"/>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B108" s="14"/>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B109" s="14"/>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B110" s="14"/>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B111" s="14"/>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B112" s="14"/>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B113" s="14"/>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B114" s="14"/>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B115" s="14"/>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B116" s="14"/>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B117" s="14"/>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B118" s="14"/>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B119" s="14"/>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B120" s="14"/>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B121" s="14"/>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B122" s="14"/>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B123" s="14"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B124" s="14"/>
     </row>
   </sheetData>
-  <sortState ref="A2:C77">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C77">
     <sortCondition ref="A2"/>
   </sortState>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
+++ b/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\MAD2_3\MADtrial\app\config\tables\MADTRIAL_INC\Forms\MADTRIAL_INC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\20250922_MAD2_3\MADtrial\app\config\tables\MADTRIAL_INC\Forms\MADTRIAL_INC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243D551D-CC65-4D4E-898A-E7CDCDD81F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD7CAF0-002C-46F6-B345-10340EADD9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1577,7 +1577,19 @@
     <t>A criança recebeu a primeia vacina do sarampo e ainda não tem idade para o segundo dose</t>
   </si>
   <si>
-    <t>data('SARVAC2') != null || data('CONSENT') == '2' || data('CARTVIS') == '2' || data('SARVAC') == '1'</t>
+    <r>
+      <t>data('SARVAC2') != null || data('CONSENT') == '2' || data('CARTVIS') == '2' |</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>| data('SARVAC') == '2'</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1587,11 +1599,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-406]General"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1631,6 +1650,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1685,28 +1711,29 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -3381,7 +3408,7 @@
       <c r="H116" t="s">
         <v>220</v>
       </c>
-      <c r="K116" t="s">
+      <c r="K116" s="15" t="s">
         <v>508</v>
       </c>
       <c r="L116" t="s">

--- a/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
+++ b/app/config/tables/MADTRIAL_INC/Forms/MADTRIAL_INC/MADTRIAL_INC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\20250922_MAD2_3\MADtrial\app\config\tables\MADTRIAL_INC\Forms\MADTRIAL_INC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\MAD\ver5\MADtrial\app\config\tables\MADTRIAL_INC\Forms\MADTRIAL_INC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD7CAF0-002C-46F6-B345-10340EADD9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E26D33E-FB19-4F34-AD84-393AB4A6383B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="549">
   <si>
     <t>setting_name</t>
   </si>
@@ -400,12 +400,6 @@
   </si>
   <si>
     <t>REGNO</t>
-  </si>
-  <si>
-    <t>Register number (triage survey)</t>
-  </si>
-  <si>
-    <t>Número de registo (ficha de triagem)</t>
   </si>
   <si>
     <t>regnons</t>
@@ -1590,6 +1584,132 @@
       </rPr>
       <t>| data('SARVAC') == '2'</t>
     </r>
+  </si>
+  <si>
+    <t>REGNO_ASSIST</t>
+  </si>
+  <si>
+    <t>Primeira número de registo (assistente)</t>
+  </si>
+  <si>
+    <t>Segundo Número de registo (nummero de triagem)</t>
+  </si>
+  <si>
+    <t>First Register number (assistant)</t>
+  </si>
+  <si>
+    <t>Second Register number (triage survey)</t>
+  </si>
+  <si>
+    <t>CICA</t>
+  </si>
+  <si>
+    <t>Horizontal measurement</t>
+  </si>
+  <si>
+    <t>Medição - Largura</t>
+  </si>
+  <si>
+    <t>Vertical measurement</t>
+  </si>
+  <si>
+    <t>Medição - Altura</t>
+  </si>
+  <si>
+    <t>selected(data('CICA'),'1')</t>
+  </si>
+  <si>
+    <t>CICAH</t>
+  </si>
+  <si>
+    <t>CICAV</t>
+  </si>
+  <si>
+    <t>evuloir</t>
+  </si>
+  <si>
+    <t>evolucao</t>
+  </si>
+  <si>
+    <t>data("evulocao") != null</t>
+  </si>
+  <si>
+    <t>Does the mother have a BCG scar?</t>
+  </si>
+  <si>
+    <t>A mãe tem cicatriz de BCG ?</t>
+  </si>
+  <si>
+    <t>Does the child have a BCG scar?</t>
+  </si>
+  <si>
+    <t>A crianca tem cicatriz de BCG ?</t>
+  </si>
+  <si>
+    <t>CICA_M</t>
+  </si>
+  <si>
+    <t>CICAH_M</t>
+  </si>
+  <si>
+    <t>CICAV_M</t>
+  </si>
+  <si>
+    <t>tipomae</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Scar</t>
+  </si>
+  <si>
+    <t>Cicatriz</t>
+  </si>
+  <si>
+    <t>No scar</t>
+  </si>
+  <si>
+    <t>Nada</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Not possible to measure</t>
+  </si>
+  <si>
+    <t>selected(data('CICA_M'),'1')</t>
+  </si>
+  <si>
+    <t>selected(data('CICA_M'),'8')</t>
+  </si>
+  <si>
+    <t>Evoluir</t>
+  </si>
+  <si>
+    <t>data('CICA')!=null</t>
+  </si>
+  <si>
+    <t>data('CICA_M')!=null</t>
+  </si>
+  <si>
+    <t>added 12-06-2026</t>
+  </si>
+  <si>
+    <t>Condição de midir não tem</t>
+  </si>
+  <si>
+    <t>data('CICAV')&gt;0 || data('CICA') != '1'</t>
+  </si>
+  <si>
+    <t>data('CICAH')&gt;0 || data('CICA')!='1'</t>
+  </si>
+  <si>
+    <t>data('CICAH_M')&gt;0|| data('CICA_M')!='1'</t>
+  </si>
+  <si>
+    <t>data('CICAV_M')&gt;0 || data('CICA_M')!='1'</t>
   </si>
 </sst>
 </file>
@@ -1660,7 +1780,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1690,6 +1810,18 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1715,7 +1847,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1734,6 +1866,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2128,7 +2262,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Y261"/>
+  <dimension ref="A1:Y285"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
@@ -2694,177 +2828,186 @@
         <v>82</v>
       </c>
       <c r="F50" t="s">
-        <v>119</v>
+        <v>507</v>
       </c>
       <c r="G50" t="s">
-        <v>120</v>
+        <v>510</v>
       </c>
       <c r="H50" t="s">
-        <v>121</v>
+        <v>508</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D51" t="s">
+        <v>82</v>
+      </c>
+      <c r="F51" t="s">
+        <v>119</v>
+      </c>
+      <c r="G51" t="s">
+        <v>511</v>
+      </c>
+      <c r="H51" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D52" t="s">
         <v>86</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E52" t="s">
         <v>87</v>
       </c>
-      <c r="F51" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B52" t="s">
+      <c r="F52" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B53" t="s">
         <v>60</v>
       </c>
-      <c r="C52" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D53" t="s">
+      <c r="C53" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D54" t="s">
         <v>45</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F54" t="s">
         <v>119</v>
       </c>
-      <c r="I53">
+      <c r="I54">
         <v>999</v>
-      </c>
-    </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B54" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
         <v>60</v>
       </c>
-      <c r="C55" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="56" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D56" t="s">
-        <v>82</v>
-      </c>
-      <c r="F56" t="s">
-        <v>125</v>
-      </c>
-      <c r="G56" t="s">
-        <v>126</v>
-      </c>
-      <c r="H56" t="s">
-        <v>127</v>
-      </c>
-      <c r="K56" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="L56" t="s">
-        <v>129</v>
-      </c>
-      <c r="M56" t="s">
-        <v>130</v>
+      <c r="C56" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D57" t="s">
+        <v>82</v>
+      </c>
+      <c r="F57" t="s">
+        <v>123</v>
+      </c>
+      <c r="G57" t="s">
+        <v>124</v>
+      </c>
+      <c r="H57" t="s">
+        <v>125</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="L57" t="s">
+        <v>127</v>
+      </c>
+      <c r="M57" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D58" t="s">
         <v>86</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E58" t="s">
+        <v>129</v>
+      </c>
+      <c r="F58" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B59" t="s">
+        <v>60</v>
+      </c>
+      <c r="C59" t="s">
         <v>131</v>
       </c>
-      <c r="F57" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="58" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B58" t="s">
-        <v>60</v>
-      </c>
-      <c r="C58" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="59" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D59" t="s">
+    </row>
+    <row r="60" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D60" t="s">
         <v>45</v>
       </c>
-      <c r="F59" t="s">
-        <v>125</v>
-      </c>
-      <c r="I59">
+      <c r="F60" t="s">
+        <v>123</v>
+      </c>
+      <c r="I60">
         <v>9999999</v>
-      </c>
-    </row>
-    <row r="60" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="61" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B62" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D62" t="s">
-        <v>82</v>
-      </c>
-      <c r="F62" t="s">
-        <v>134</v>
-      </c>
-      <c r="G62" t="s">
-        <v>135</v>
-      </c>
-      <c r="H62" t="s">
-        <v>136</v>
-      </c>
-      <c r="K62" t="s">
-        <v>137</v>
-      </c>
-      <c r="L62" t="s">
-        <v>138</v>
-      </c>
-      <c r="M62" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D63" t="s">
+        <v>82</v>
+      </c>
+      <c r="F63" t="s">
+        <v>132</v>
+      </c>
+      <c r="G63" t="s">
+        <v>133</v>
+      </c>
+      <c r="H63" t="s">
+        <v>134</v>
+      </c>
+      <c r="K63" t="s">
+        <v>135</v>
+      </c>
+      <c r="L63" t="s">
+        <v>136</v>
+      </c>
+      <c r="M63" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D64" t="s">
         <v>86</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E64" t="s">
+        <v>138</v>
+      </c>
+      <c r="F64" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B65" t="s">
+        <v>60</v>
+      </c>
+      <c r="C65" t="s">
         <v>140</v>
       </c>
-      <c r="F63" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B64" t="s">
-        <v>60</v>
-      </c>
-      <c r="C64" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D65" t="s">
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D66" t="s">
         <v>45</v>
       </c>
-      <c r="F65" t="s">
-        <v>134</v>
-      </c>
-      <c r="I65">
+      <c r="F66" t="s">
+        <v>132</v>
+      </c>
+      <c r="I66">
         <v>999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B66" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.35">
@@ -2874,95 +3017,86 @@
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D70" t="s">
-        <v>51</v>
-      </c>
-      <c r="F70" t="s">
-        <v>143</v>
-      </c>
-      <c r="G70" t="s">
-        <v>144</v>
-      </c>
-      <c r="H70" t="s">
-        <v>145</v>
-      </c>
-      <c r="K70" t="s">
-        <v>146</v>
-      </c>
-      <c r="L70" t="s">
-        <v>147</v>
-      </c>
-      <c r="M70" t="s">
-        <v>148</v>
-      </c>
-      <c r="R70" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="71" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D71" t="s">
+        <v>51</v>
+      </c>
+      <c r="F71" t="s">
+        <v>141</v>
+      </c>
+      <c r="G71" t="s">
+        <v>142</v>
+      </c>
+      <c r="H71" t="s">
+        <v>143</v>
+      </c>
+      <c r="K71" t="s">
+        <v>144</v>
+      </c>
+      <c r="L71" t="s">
+        <v>145</v>
+      </c>
+      <c r="M71" t="s">
+        <v>146</v>
+      </c>
+      <c r="R71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D72" t="s">
         <v>86</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E72" t="s">
+        <v>147</v>
+      </c>
+      <c r="F72" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
+        <v>60</v>
+      </c>
+      <c r="C73" t="s">
         <v>149</v>
       </c>
-      <c r="F71" t="s">
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D74" t="s">
+        <v>45</v>
+      </c>
+      <c r="F74" t="s">
+        <v>141</v>
+      </c>
+      <c r="I74" s="6" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B72" t="s">
-        <v>60</v>
-      </c>
-      <c r="C72" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D73" t="s">
-        <v>45</v>
-      </c>
-      <c r="F73" t="s">
-        <v>143</v>
-      </c>
-      <c r="I73" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B74" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="75" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B76" t="s">
         <v>60</v>
       </c>
-      <c r="C75" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D76" t="s">
-        <v>82</v>
-      </c>
-      <c r="F76" t="s">
-        <v>154</v>
-      </c>
-      <c r="G76" t="s">
-        <v>155</v>
-      </c>
-      <c r="H76" t="s">
-        <v>156</v>
+      <c r="C76" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="77" spans="2:18" x14ac:dyDescent="0.35">
@@ -2970,123 +3104,132 @@
         <v>82</v>
       </c>
       <c r="F77" t="s">
+        <v>152</v>
+      </c>
+      <c r="G77" t="s">
+        <v>153</v>
+      </c>
+      <c r="H77" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="78" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D78" t="s">
+        <v>82</v>
+      </c>
+      <c r="F78" t="s">
+        <v>155</v>
+      </c>
+      <c r="G78" t="s">
+        <v>156</v>
+      </c>
+      <c r="H78" t="s">
         <v>157</v>
       </c>
-      <c r="G77" t="s">
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B79" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="80" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D80" t="s">
         <v>158</v>
       </c>
-      <c r="H77" t="s">
+      <c r="G80" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="78" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B78" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D79" t="s">
+      <c r="H80" t="s">
         <v>160</v>
-      </c>
-      <c r="G79" t="s">
-        <v>161</v>
-      </c>
-      <c r="H79" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B80" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="81" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="82" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B82" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="82" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D82" t="s">
+    <row r="83" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D83" t="s">
         <v>102</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E83" t="s">
+        <v>161</v>
+      </c>
+      <c r="F83" t="s">
+        <v>162</v>
+      </c>
+      <c r="G83" t="s">
         <v>163</v>
       </c>
-      <c r="F82" t="s">
+      <c r="H83" t="s">
         <v>164</v>
       </c>
-      <c r="G82" t="s">
+      <c r="R83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B84" t="s">
+        <v>60</v>
+      </c>
+      <c r="C84" t="s">
         <v>165</v>
       </c>
-      <c r="H82" t="s">
+    </row>
+    <row r="85" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D85" t="s">
+        <v>102</v>
+      </c>
+      <c r="E85" t="s">
         <v>166</v>
       </c>
-      <c r="R82" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B83" t="s">
+      <c r="F85" t="s">
+        <v>167</v>
+      </c>
+      <c r="G85" t="s">
+        <v>168</v>
+      </c>
+      <c r="H85" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="86" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B86" t="s">
         <v>60</v>
       </c>
-      <c r="C83" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="84" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D84" t="s">
+      <c r="C86" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="87" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="D87" t="s">
         <v>102</v>
       </c>
-      <c r="E84" t="s">
-        <v>168</v>
-      </c>
-      <c r="F84" t="s">
-        <v>169</v>
-      </c>
-      <c r="G84" t="s">
-        <v>170</v>
-      </c>
-      <c r="H84" t="s">
+      <c r="E87" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="85" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B85" t="s">
-        <v>60</v>
-      </c>
-      <c r="C85" t="s">
+      <c r="F87" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="86" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D86" t="s">
-        <v>102</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="G87" t="s">
         <v>173</v>
       </c>
-      <c r="F86" t="s">
+      <c r="H87" t="s">
         <v>174</v>
       </c>
-      <c r="G86" t="s">
+      <c r="K87" t="s">
         <v>175</v>
       </c>
-      <c r="H86" t="s">
+      <c r="L87" t="s">
         <v>176</v>
       </c>
-      <c r="K86" t="s">
+      <c r="M87" t="s">
         <v>177</v>
-      </c>
-      <c r="L86" t="s">
-        <v>178</v>
-      </c>
-      <c r="M86" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="87" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="B87" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="88" spans="2:18" x14ac:dyDescent="0.35">
@@ -3096,1745 +3239,1994 @@
     </row>
     <row r="89" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="90" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
-        <v>60</v>
-      </c>
-      <c r="C90" t="s">
-        <v>167</v>
+        <v>54</v>
       </c>
     </row>
     <row r="91" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
+        <v>60</v>
+      </c>
+      <c r="C91" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="92" spans="2:18" x14ac:dyDescent="0.35">
+      <c r="B92" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="92" spans="2:18" x14ac:dyDescent="0.35">
-      <c r="D92" t="s">
-        <v>82</v>
-      </c>
-      <c r="F92" t="s">
-        <v>180</v>
-      </c>
-      <c r="G92" t="s">
-        <v>181</v>
-      </c>
-      <c r="H92" t="s">
-        <v>182</v>
-      </c>
-      <c r="K92" t="s">
-        <v>183</v>
-      </c>
-      <c r="L92" t="s">
-        <v>184</v>
-      </c>
-      <c r="M92" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="93" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D93" t="s">
-        <v>110</v>
-      </c>
-      <c r="E93" t="s">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="F93" t="s">
-        <v>187</v>
+        <v>178</v>
+      </c>
+      <c r="G93" t="s">
+        <v>179</v>
+      </c>
+      <c r="H93" t="s">
+        <v>180</v>
+      </c>
+      <c r="K93" t="s">
+        <v>181</v>
+      </c>
+      <c r="L93" t="s">
+        <v>182</v>
+      </c>
+      <c r="M93" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="94" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D94" t="s">
-        <v>82</v>
+        <v>110</v>
+      </c>
+      <c r="E94" t="s">
+        <v>184</v>
       </c>
       <c r="F94" t="s">
-        <v>188</v>
-      </c>
-      <c r="G94" t="s">
-        <v>189</v>
-      </c>
-      <c r="H94" t="s">
-        <v>190</v>
-      </c>
-      <c r="K94" t="s">
-        <v>191</v>
-      </c>
-      <c r="L94" t="s">
-        <v>184</v>
-      </c>
-      <c r="M94" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D95" t="s">
-        <v>110</v>
-      </c>
-      <c r="E95" t="s">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="F95" t="s">
-        <v>193</v>
+        <v>186</v>
+      </c>
+      <c r="G95" t="s">
+        <v>187</v>
+      </c>
+      <c r="H95" t="s">
+        <v>188</v>
+      </c>
+      <c r="K95" t="s">
+        <v>189</v>
+      </c>
+      <c r="L95" t="s">
+        <v>182</v>
+      </c>
+      <c r="M95" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="96" spans="2:18" x14ac:dyDescent="0.35">
       <c r="D96" t="s">
-        <v>82</v>
+        <v>110</v>
+      </c>
+      <c r="E96" t="s">
+        <v>190</v>
       </c>
       <c r="F96" t="s">
-        <v>194</v>
-      </c>
-      <c r="G96" t="s">
-        <v>195</v>
-      </c>
-      <c r="H96" t="s">
-        <v>196</v>
-      </c>
-      <c r="K96" t="s">
-        <v>197</v>
-      </c>
-      <c r="L96" t="s">
-        <v>184</v>
-      </c>
-      <c r="M96" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D97" t="s">
+        <v>82</v>
+      </c>
+      <c r="F97" t="s">
+        <v>192</v>
+      </c>
+      <c r="G97" t="s">
+        <v>193</v>
+      </c>
+      <c r="H97" t="s">
+        <v>194</v>
+      </c>
+      <c r="K97" t="s">
+        <v>195</v>
+      </c>
+      <c r="L97" t="s">
+        <v>182</v>
+      </c>
+      <c r="M97" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="98" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D98" t="s">
         <v>110</v>
       </c>
-      <c r="E97" t="s">
-        <v>192</v>
-      </c>
-      <c r="F97" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B98" t="s">
+      <c r="E98" t="s">
+        <v>190</v>
+      </c>
+      <c r="F98" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="99" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B99" t="s">
         <v>60</v>
       </c>
-      <c r="C98" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D99" t="s">
+      <c r="C99" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="100" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D100" t="s">
         <v>45</v>
       </c>
-      <c r="F99" t="s">
-        <v>188</v>
-      </c>
-      <c r="I99">
+      <c r="F100" t="s">
+        <v>186</v>
+      </c>
+      <c r="I100">
         <v>999999999</v>
-      </c>
-    </row>
-    <row r="100" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B100" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="101" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="102" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B102" t="s">
         <v>60</v>
       </c>
-      <c r="C101" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="102" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D102" t="s">
+      <c r="C102" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="103" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D103" t="s">
         <v>45</v>
       </c>
-      <c r="F102" t="s">
-        <v>194</v>
-      </c>
-      <c r="I102">
+      <c r="F103" t="s">
+        <v>192</v>
+      </c>
+      <c r="I103">
         <v>999999999</v>
-      </c>
-    </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B103" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="104" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="105" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B105" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="106" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B106" t="s">
+    <row r="107" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B107" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D107" t="s">
+    <row r="108" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D108" t="s">
         <v>102</v>
       </c>
-      <c r="E107" t="s">
-        <v>163</v>
-      </c>
-      <c r="F107" t="s">
+      <c r="E108" t="s">
+        <v>161</v>
+      </c>
+      <c r="F108" t="s">
+        <v>199</v>
+      </c>
+      <c r="G108" t="s">
+        <v>200</v>
+      </c>
+      <c r="H108" t="s">
         <v>201</v>
       </c>
-      <c r="G107" t="s">
+      <c r="K108" t="s">
         <v>202</v>
       </c>
-      <c r="H107" t="s">
+      <c r="L108" t="s">
         <v>203</v>
       </c>
-      <c r="K107" t="s">
+      <c r="M108" t="s">
         <v>204</v>
       </c>
-      <c r="L107" t="s">
+    </row>
+    <row r="109" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B109" t="s">
+        <v>60</v>
+      </c>
+      <c r="C109" t="s">
         <v>205</v>
       </c>
-      <c r="M107" t="s">
+    </row>
+    <row r="110" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D110" t="s">
+        <v>102</v>
+      </c>
+      <c r="E110" t="s">
+        <v>161</v>
+      </c>
+      <c r="F110" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="108" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B108" t="s">
-        <v>60</v>
-      </c>
-      <c r="C108" t="s">
+      <c r="G110" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D109" t="s">
-        <v>102</v>
-      </c>
-      <c r="E109" t="s">
-        <v>163</v>
-      </c>
-      <c r="F109" t="s">
+      <c r="H110" t="s">
         <v>208</v>
       </c>
-      <c r="G109" t="s">
+      <c r="K110" t="s">
         <v>209</v>
       </c>
-      <c r="H109" t="s">
-        <v>210</v>
-      </c>
-      <c r="K109" t="s">
-        <v>211</v>
-      </c>
-      <c r="L109" t="s">
-        <v>205</v>
-      </c>
-      <c r="M109" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="110" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B110" t="s">
-        <v>50</v>
+      <c r="L110" t="s">
+        <v>203</v>
+      </c>
+      <c r="M110" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="111" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B111" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="112" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B112" t="s">
         <v>60</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C112" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="113" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D113" t="s">
+        <v>102</v>
+      </c>
+      <c r="E113" t="s">
+        <v>161</v>
+      </c>
+      <c r="F113" t="s">
+        <v>211</v>
+      </c>
+      <c r="G113" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="112" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D112" t="s">
+      <c r="H113" t="s">
+        <v>213</v>
+      </c>
+      <c r="K113" t="s">
+        <v>214</v>
+      </c>
+      <c r="L113" t="s">
+        <v>203</v>
+      </c>
+      <c r="M113" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="114" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B114" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="115" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B115" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="116" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B116" t="s">
+        <v>60</v>
+      </c>
+      <c r="C116" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="117" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D117" t="s">
         <v>102</v>
       </c>
-      <c r="E112" t="s">
-        <v>163</v>
-      </c>
-      <c r="F112" t="s">
-        <v>213</v>
-      </c>
-      <c r="G112" t="s">
+      <c r="E117" t="s">
+        <v>161</v>
+      </c>
+      <c r="F117" t="s">
+        <v>216</v>
+      </c>
+      <c r="G117" t="s">
+        <v>217</v>
+      </c>
+      <c r="H117" t="s">
+        <v>218</v>
+      </c>
+      <c r="K117" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="L117" t="s">
+        <v>203</v>
+      </c>
+      <c r="M117" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="118" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B118" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="120" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B120" t="s">
+        <v>60</v>
+      </c>
+      <c r="C120" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="121" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D121" t="s">
+        <v>102</v>
+      </c>
+      <c r="E121" t="s">
+        <v>161</v>
+      </c>
+      <c r="F121" t="s">
+        <v>219</v>
+      </c>
+      <c r="G121" t="s">
+        <v>220</v>
+      </c>
+      <c r="H121" t="s">
+        <v>221</v>
+      </c>
+      <c r="K121" t="s">
         <v>214</v>
       </c>
-      <c r="H112" t="s">
-        <v>215</v>
-      </c>
-      <c r="K112" t="s">
-        <v>216</v>
-      </c>
-      <c r="L112" t="s">
-        <v>205</v>
-      </c>
-      <c r="M112" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="113" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B113" t="s">
+      <c r="L121" t="s">
+        <v>203</v>
+      </c>
+      <c r="M121" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="122" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B122" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="114" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B114" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="115" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B115" t="s">
-        <v>60</v>
-      </c>
-      <c r="C115" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="116" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D116" t="s">
-        <v>102</v>
-      </c>
-      <c r="E116" t="s">
-        <v>163</v>
-      </c>
-      <c r="F116" t="s">
-        <v>218</v>
-      </c>
-      <c r="G116" t="s">
-        <v>219</v>
-      </c>
-      <c r="H116" t="s">
-        <v>220</v>
-      </c>
-      <c r="K116" s="15" t="s">
-        <v>508</v>
-      </c>
-      <c r="L116" t="s">
-        <v>205</v>
-      </c>
-      <c r="M116" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="117" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B117" t="s">
+    <row r="123" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B123" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="119" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B119" t="s">
-        <v>60</v>
-      </c>
-      <c r="C119" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="120" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D120" t="s">
-        <v>102</v>
-      </c>
-      <c r="E120" t="s">
-        <v>163</v>
-      </c>
-      <c r="F120" t="s">
-        <v>221</v>
-      </c>
-      <c r="G120" t="s">
-        <v>222</v>
-      </c>
-      <c r="H120" t="s">
-        <v>223</v>
-      </c>
-      <c r="K120" t="s">
-        <v>216</v>
-      </c>
-      <c r="L120" t="s">
-        <v>205</v>
-      </c>
-      <c r="M120" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="121" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B121" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="122" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B122" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="123" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B123" s="7"/>
-    </row>
     <row r="124" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B124" t="s">
-        <v>54</v>
-      </c>
+      <c r="B124" s="7"/>
     </row>
     <row r="125" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="126" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B126" t="s">
         <v>60</v>
       </c>
-      <c r="C125" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="126" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="D126" t="s">
+      <c r="C126" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="127" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D127" t="s">
+        <v>222</v>
+      </c>
+      <c r="F127" t="s">
+        <v>223</v>
+      </c>
+      <c r="G127" t="s">
         <v>224</v>
       </c>
-      <c r="F126" t="s">
+      <c r="H127" t="s">
         <v>225</v>
-      </c>
-      <c r="G126" t="s">
-        <v>226</v>
-      </c>
-      <c r="H126" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="127" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B127" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="128" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="129" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B129" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="129" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="D129" t="s">
-        <v>68</v>
-      </c>
-      <c r="F129" t="s">
-        <v>228</v>
-      </c>
-      <c r="G129" t="s">
-        <v>229</v>
-      </c>
-      <c r="H129" t="s">
-        <v>230</v>
-      </c>
-      <c r="K129" t="s">
-        <v>231</v>
-      </c>
-      <c r="L129" t="s">
-        <v>232</v>
-      </c>
-      <c r="M129" t="s">
-        <v>233</v>
-      </c>
-      <c r="N129" t="s">
-        <v>234</v>
-      </c>
-      <c r="O129" t="s">
-        <v>235</v>
-      </c>
-      <c r="P129" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="130" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D130" t="s">
+        <v>68</v>
+      </c>
+      <c r="F130" t="s">
+        <v>226</v>
+      </c>
+      <c r="G130" t="s">
+        <v>227</v>
+      </c>
+      <c r="H130" t="s">
+        <v>228</v>
+      </c>
+      <c r="K130" t="s">
+        <v>229</v>
+      </c>
+      <c r="L130" t="s">
+        <v>230</v>
+      </c>
+      <c r="M130" t="s">
+        <v>231</v>
+      </c>
+      <c r="N130" t="s">
+        <v>232</v>
+      </c>
+      <c r="O130" t="s">
+        <v>233</v>
+      </c>
+      <c r="P130" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="131" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="D131" t="s">
         <v>82</v>
       </c>
-      <c r="F130" t="s">
+      <c r="F131" t="s">
+        <v>234</v>
+      </c>
+      <c r="G131" t="s">
+        <v>235</v>
+      </c>
+      <c r="H131" t="s">
         <v>236</v>
       </c>
-      <c r="G130" t="s">
+      <c r="K131" t="s">
         <v>237</v>
       </c>
-      <c r="H130" t="s">
+      <c r="L131" t="s">
         <v>238</v>
       </c>
-      <c r="K130" t="s">
+      <c r="M131" t="s">
         <v>239</v>
-      </c>
-      <c r="L130" t="s">
-        <v>240</v>
-      </c>
-      <c r="M130" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="131" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B131" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="132" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="133" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B133" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="133" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="D133" t="s">
+    <row r="134" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="D134" t="s">
         <v>102</v>
       </c>
-      <c r="E133" t="s">
-        <v>242</v>
-      </c>
-      <c r="F133" t="s">
-        <v>243</v>
-      </c>
-      <c r="G133" t="s">
-        <v>244</v>
-      </c>
-      <c r="H133" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="134" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B134" t="s">
+      <c r="E134" t="s">
+        <v>249</v>
+      </c>
+      <c r="F134" t="s">
+        <v>512</v>
+      </c>
+      <c r="G134" t="s">
+        <v>525</v>
+      </c>
+      <c r="H134" t="s">
+        <v>526</v>
+      </c>
+      <c r="K134" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="135" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B135" t="s">
         <v>60</v>
       </c>
-      <c r="C134" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="135" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="D135" t="s">
-        <v>51</v>
-      </c>
-      <c r="F135" t="s">
-        <v>247</v>
-      </c>
-      <c r="G135" t="s">
-        <v>248</v>
-      </c>
-      <c r="H135" t="s">
-        <v>249</v>
-      </c>
-      <c r="K135" t="s">
-        <v>250</v>
-      </c>
-      <c r="L135" t="s">
-        <v>147</v>
-      </c>
-      <c r="M135" t="s">
-        <v>148</v>
-      </c>
+      <c r="C135" t="s">
+        <v>517</v>
+      </c>
+      <c r="I135" s="16"/>
     </row>
     <row r="136" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B136" t="s">
-        <v>50</v>
+      <c r="D136" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F136" t="s">
+        <v>518</v>
+      </c>
+      <c r="G136" t="s">
+        <v>513</v>
+      </c>
+      <c r="H136" t="s">
+        <v>514</v>
+      </c>
+      <c r="K136" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="137" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B137" t="s">
-        <v>54</v>
+      <c r="D137" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F137" t="s">
+        <v>519</v>
+      </c>
+      <c r="G137" t="s">
+        <v>515</v>
+      </c>
+      <c r="H137" t="s">
+        <v>516</v>
+      </c>
+      <c r="K137" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="138" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B138" t="s">
-        <v>41</v>
-      </c>
+      <c r="D138" t="s">
+        <v>86</v>
+      </c>
+      <c r="E138" t="s">
+        <v>520</v>
+      </c>
+      <c r="F138" t="s">
+        <v>521</v>
+      </c>
+      <c r="I138" s="16"/>
     </row>
     <row r="139" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="D139" t="s">
-        <v>102</v>
-      </c>
-      <c r="E139" t="s">
-        <v>251</v>
-      </c>
-      <c r="F139" t="s">
-        <v>252</v>
-      </c>
-      <c r="G139" t="s">
-        <v>253</v>
-      </c>
-      <c r="H139" t="s">
-        <v>254</v>
-      </c>
+      <c r="B139" t="s">
+        <v>60</v>
+      </c>
+      <c r="C139" t="s">
+        <v>522</v>
+      </c>
+      <c r="I139" s="16"/>
     </row>
     <row r="140" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D140" t="s">
-        <v>102</v>
-      </c>
-      <c r="E140" t="s">
-        <v>251</v>
+        <v>45</v>
       </c>
       <c r="F140" t="s">
-        <v>255</v>
-      </c>
-      <c r="G140" t="s">
-        <v>256</v>
-      </c>
-      <c r="H140" t="s">
-        <v>257</v>
+        <v>518</v>
+      </c>
+      <c r="I140" s="16">
+        <v>88</v>
       </c>
     </row>
     <row r="141" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D141" t="s">
+        <v>45</v>
+      </c>
+      <c r="F141" t="s">
+        <v>519</v>
+      </c>
+      <c r="I141" s="16">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="142" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B142" t="s">
+        <v>50</v>
+      </c>
+      <c r="I142" s="16"/>
+    </row>
+    <row r="143" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B143" t="s">
+        <v>50</v>
+      </c>
+      <c r="I143" s="16"/>
+    </row>
+    <row r="144" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B144" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="145" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B145" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="146" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D146" t="s">
         <v>102</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E146" t="s">
+        <v>530</v>
+      </c>
+      <c r="F146" t="s">
+        <v>527</v>
+      </c>
+      <c r="G146" t="s">
+        <v>523</v>
+      </c>
+      <c r="H146" t="s">
+        <v>524</v>
+      </c>
+      <c r="K146" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="147" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B147" t="s">
+        <v>60</v>
+      </c>
+      <c r="C147" t="s">
+        <v>538</v>
+      </c>
+      <c r="I147" s="16"/>
+    </row>
+    <row r="148" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D148" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F148" t="s">
+        <v>528</v>
+      </c>
+      <c r="G148" t="s">
+        <v>513</v>
+      </c>
+      <c r="H148" t="s">
+        <v>514</v>
+      </c>
+      <c r="K148" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="149" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D149" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F149" t="s">
+        <v>529</v>
+      </c>
+      <c r="G149" t="s">
+        <v>515</v>
+      </c>
+      <c r="H149" t="s">
+        <v>516</v>
+      </c>
+      <c r="K149" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="150" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B150" t="s">
+        <v>60</v>
+      </c>
+      <c r="C150" t="s">
+        <v>539</v>
+      </c>
+      <c r="I150" s="16"/>
+    </row>
+    <row r="151" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D151" t="s">
+        <v>45</v>
+      </c>
+      <c r="F151" t="s">
+        <v>528</v>
+      </c>
+      <c r="I151" s="16">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="152" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D152" t="s">
+        <v>45</v>
+      </c>
+      <c r="F152" t="s">
+        <v>529</v>
+      </c>
+      <c r="I152" s="16">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="153" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B153" t="s">
+        <v>50</v>
+      </c>
+      <c r="I153" s="16"/>
+    </row>
+    <row r="154" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B154" t="s">
+        <v>50</v>
+      </c>
+      <c r="I154" s="16"/>
+    </row>
+    <row r="155" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B155" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="156" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B156" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="157" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D157" t="s">
+        <v>102</v>
+      </c>
+      <c r="E157" t="s">
+        <v>240</v>
+      </c>
+      <c r="F157" t="s">
+        <v>241</v>
+      </c>
+      <c r="G157" t="s">
+        <v>242</v>
+      </c>
+      <c r="H157" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="158" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B158" t="s">
+        <v>60</v>
+      </c>
+      <c r="C158" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="159" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D159" t="s">
+        <v>51</v>
+      </c>
+      <c r="F159" t="s">
+        <v>245</v>
+      </c>
+      <c r="G159" t="s">
+        <v>246</v>
+      </c>
+      <c r="H159" t="s">
+        <v>247</v>
+      </c>
+      <c r="K159" t="s">
+        <v>248</v>
+      </c>
+      <c r="L159" t="s">
+        <v>145</v>
+      </c>
+      <c r="M159" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="160" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B160" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="161" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B161" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="162" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B162" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="163" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D163" t="s">
+        <v>102</v>
+      </c>
+      <c r="E163" t="s">
+        <v>249</v>
+      </c>
+      <c r="F163" t="s">
+        <v>250</v>
+      </c>
+      <c r="G163" t="s">
         <v>251</v>
       </c>
-      <c r="F141" t="s">
+      <c r="H163" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="164" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D164" t="s">
+        <v>102</v>
+      </c>
+      <c r="E164" t="s">
+        <v>249</v>
+      </c>
+      <c r="F164" t="s">
+        <v>253</v>
+      </c>
+      <c r="G164" t="s">
+        <v>254</v>
+      </c>
+      <c r="H164" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="165" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D165" t="s">
+        <v>102</v>
+      </c>
+      <c r="E165" t="s">
+        <v>249</v>
+      </c>
+      <c r="F165" t="s">
+        <v>256</v>
+      </c>
+      <c r="G165" t="s">
+        <v>257</v>
+      </c>
+      <c r="H165" t="s">
         <v>258</v>
       </c>
-      <c r="G141" t="s">
+    </row>
+    <row r="166" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B166" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C166" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="H141" t="s">
+      <c r="D166" s="8"/>
+      <c r="E166" s="8"/>
+      <c r="F166" s="8"/>
+      <c r="G166" s="8"/>
+      <c r="H166" s="8"/>
+      <c r="I166" s="8"/>
+    </row>
+    <row r="167" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B167" s="8"/>
+      <c r="C167" s="8"/>
+      <c r="D167" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E167" s="8"/>
+      <c r="F167" s="8" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="142" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B142" s="8" t="s">
+      <c r="G167" s="8"/>
+      <c r="H167" s="8"/>
+      <c r="I167" s="8" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="168" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B168" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C168" s="8"/>
+      <c r="D168" s="8"/>
+      <c r="E168" s="8"/>
+      <c r="F168" s="8"/>
+      <c r="G168" s="8"/>
+      <c r="H168" s="8"/>
+      <c r="I168" s="8"/>
+    </row>
+    <row r="169" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B169" s="8"/>
+      <c r="C169" s="8"/>
+      <c r="D169" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E169" s="8"/>
+      <c r="F169" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="G169" s="8"/>
+      <c r="H169" s="8"/>
+      <c r="I169" s="8" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="170" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B170" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C170" s="8"/>
+      <c r="D170" s="8"/>
+      <c r="E170" s="8"/>
+      <c r="F170" s="8"/>
+      <c r="G170" s="8"/>
+      <c r="H170" s="8"/>
+      <c r="I170" s="8"/>
+    </row>
+    <row r="171" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B171" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="172" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B172" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="173" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D173" t="s">
+        <v>102</v>
+      </c>
+      <c r="E173" t="s">
+        <v>249</v>
+      </c>
+      <c r="F173" t="s">
+        <v>263</v>
+      </c>
+      <c r="G173" t="s">
+        <v>264</v>
+      </c>
+      <c r="H173" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="174" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D174" t="s">
+        <v>102</v>
+      </c>
+      <c r="E174" t="s">
+        <v>249</v>
+      </c>
+      <c r="F174" t="s">
+        <v>266</v>
+      </c>
+      <c r="G174" t="s">
+        <v>267</v>
+      </c>
+      <c r="H174" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="175" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D175" t="s">
+        <v>102</v>
+      </c>
+      <c r="E175" t="s">
+        <v>249</v>
+      </c>
+      <c r="F175" t="s">
+        <v>269</v>
+      </c>
+      <c r="G175" t="s">
+        <v>270</v>
+      </c>
+      <c r="H175" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="176" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B176" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="177" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B177" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="178" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D178" t="s">
+        <v>102</v>
+      </c>
+      <c r="E178" t="s">
+        <v>249</v>
+      </c>
+      <c r="F178" t="s">
+        <v>272</v>
+      </c>
+      <c r="G178" t="s">
+        <v>273</v>
+      </c>
+      <c r="H178" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="179" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D179" t="s">
+        <v>68</v>
+      </c>
+      <c r="F179" t="s">
+        <v>275</v>
+      </c>
+      <c r="G179" t="s">
+        <v>276</v>
+      </c>
+      <c r="H179" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="180" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B180" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="181" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B181" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="182" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D182" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E182" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F182" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="G182" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="H182" s="9" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="183" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B183" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C142" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="D142" s="8"/>
-      <c r="E142" s="8"/>
-      <c r="F142" s="8"/>
-      <c r="G142" s="8"/>
-      <c r="H142" s="8"/>
-      <c r="I142" s="8"/>
-    </row>
-    <row r="143" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B143" s="8"/>
-      <c r="C143" s="8"/>
-      <c r="D143" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E143" s="8"/>
-      <c r="F143" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="G143" s="8"/>
-      <c r="H143" s="8"/>
-      <c r="I143" s="8" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="144" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B144" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C144" s="8"/>
-      <c r="D144" s="8"/>
-      <c r="E144" s="8"/>
-      <c r="F144" s="8"/>
-      <c r="G144" s="8"/>
-      <c r="H144" s="8"/>
-      <c r="I144" s="8"/>
-    </row>
-    <row r="145" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B145" s="8"/>
-      <c r="C145" s="8"/>
-      <c r="D145" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E145" s="8"/>
-      <c r="F145" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="G145" s="8"/>
-      <c r="H145" s="8"/>
-      <c r="I145" s="8" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="146" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B146" s="8" t="s">
+      <c r="C183" s="9" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="184" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D184" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E184" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="F184" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="G184" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="H184" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="185" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B185" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C185" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="186" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D186" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F186" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="G186" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="H186" s="9" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="187" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B187" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C146" s="8"/>
-      <c r="D146" s="8"/>
-      <c r="E146" s="8"/>
-      <c r="F146" s="8"/>
-      <c r="G146" s="8"/>
-      <c r="H146" s="8"/>
-      <c r="I146" s="8"/>
-    </row>
-    <row r="147" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B147" t="s">
+    </row>
+    <row r="188" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B188" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="189" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B189" s="9" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="148" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B148" t="s">
+    <row r="190" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B190" s="9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="149" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D149" t="s">
+    <row r="191" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D191" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E149" t="s">
-        <v>251</v>
-      </c>
-      <c r="F149" t="s">
-        <v>265</v>
-      </c>
-      <c r="G149" t="s">
-        <v>266</v>
-      </c>
-      <c r="H149" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="150" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D150" t="s">
+      <c r="E191" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="G191" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="H191" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="192" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B192" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="193" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D193" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E193" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="G193" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="H193" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="194" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B194" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="195" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="D195" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="G195" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="H195" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="196" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B196" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="197" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B197" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="198" spans="2:13" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B198" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="199" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B199" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="200" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D200" t="s">
+        <v>222</v>
+      </c>
+      <c r="F200" t="s">
+        <v>299</v>
+      </c>
+      <c r="G200" t="s">
+        <v>300</v>
+      </c>
+      <c r="H200" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="201" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B201" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="202" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B202" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="203" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D203" t="s">
         <v>102</v>
       </c>
-      <c r="E150" t="s">
-        <v>251</v>
-      </c>
-      <c r="F150" t="s">
-        <v>268</v>
-      </c>
-      <c r="G150" t="s">
-        <v>269</v>
-      </c>
-      <c r="H150" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="151" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D151" t="s">
+      <c r="E203" t="s">
+        <v>161</v>
+      </c>
+      <c r="F203" t="s">
+        <v>302</v>
+      </c>
+      <c r="G203" t="s">
+        <v>303</v>
+      </c>
+      <c r="H203" t="s">
+        <v>304</v>
+      </c>
+      <c r="K203" t="s">
+        <v>305</v>
+      </c>
+      <c r="L203" t="s">
+        <v>203</v>
+      </c>
+      <c r="M203" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="204" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B204" t="s">
+        <v>60</v>
+      </c>
+      <c r="C204" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="205" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D205" t="s">
+        <v>68</v>
+      </c>
+      <c r="F205" t="s">
+        <v>307</v>
+      </c>
+      <c r="G205" t="s">
+        <v>308</v>
+      </c>
+      <c r="H205" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="206" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B206" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="207" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="D207" t="s">
         <v>102</v>
       </c>
-      <c r="E151" t="s">
-        <v>251</v>
-      </c>
-      <c r="F151" t="s">
-        <v>271</v>
-      </c>
-      <c r="G151" t="s">
-        <v>272</v>
-      </c>
-      <c r="H151" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="152" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B152" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="153" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B153" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="154" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D154" t="s">
-        <v>102</v>
-      </c>
-      <c r="E154" t="s">
-        <v>251</v>
-      </c>
-      <c r="F154" t="s">
-        <v>274</v>
-      </c>
-      <c r="G154" t="s">
-        <v>275</v>
-      </c>
-      <c r="H154" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="155" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D155" t="s">
-        <v>68</v>
-      </c>
-      <c r="F155" t="s">
-        <v>277</v>
-      </c>
-      <c r="G155" t="s">
-        <v>278</v>
-      </c>
-      <c r="H155" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="156" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B156" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="157" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B157" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="158" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="D158" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E158" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="F158" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="G158" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="H158" s="9" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="159" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B159" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C159" s="9" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="160" spans="2:9" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="D160" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E160" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="F160" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="G160" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="H160" s="9" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="161" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B161" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C161" s="9" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="162" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="D162" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F162" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="G162" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="H162" s="9" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="163" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B163" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="164" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B164" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="165" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B165" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="166" spans="2:8" s="9" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B166" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="167" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="D167" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E167" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="F167" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="G167" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="H167" s="4" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="168" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B168" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="169" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="D169" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E169" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="F169" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="G169" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="H169" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="170" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B170" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="171" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="D171" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F171" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="G171" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="H171" s="4" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="172" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B172" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="173" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B173" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="174" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B174" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="175" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B175" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="176" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="D176" t="s">
-        <v>224</v>
-      </c>
-      <c r="F176" t="s">
-        <v>301</v>
-      </c>
-      <c r="G176" t="s">
-        <v>302</v>
-      </c>
-      <c r="H176" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="177" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B177" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="178" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B178" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="179" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="D179" t="s">
-        <v>102</v>
-      </c>
-      <c r="E179" t="s">
-        <v>163</v>
-      </c>
-      <c r="F179" t="s">
-        <v>304</v>
-      </c>
-      <c r="G179" t="s">
-        <v>305</v>
-      </c>
-      <c r="H179" t="s">
-        <v>306</v>
-      </c>
-      <c r="K179" t="s">
-        <v>307</v>
-      </c>
-      <c r="L179" t="s">
-        <v>205</v>
-      </c>
-      <c r="M179" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="180" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B180" t="s">
-        <v>60</v>
-      </c>
-      <c r="C180" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="181" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="D181" t="s">
-        <v>68</v>
-      </c>
-      <c r="F181" t="s">
-        <v>309</v>
-      </c>
-      <c r="G181" t="s">
+      <c r="E207" t="s">
+        <v>161</v>
+      </c>
+      <c r="F207" t="s">
         <v>310</v>
       </c>
-      <c r="H181" t="s">
+      <c r="G207" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="182" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B182" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="183" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="D183" t="s">
-        <v>102</v>
-      </c>
-      <c r="E183" t="s">
-        <v>163</v>
-      </c>
-      <c r="F183" t="s">
+      <c r="H207" t="s">
         <v>312</v>
       </c>
-      <c r="G183" t="s">
+      <c r="K207" t="s">
         <v>313</v>
       </c>
-      <c r="H183" t="s">
-        <v>314</v>
-      </c>
-      <c r="K183" t="s">
-        <v>315</v>
-      </c>
-      <c r="L183" t="s">
-        <v>205</v>
-      </c>
-      <c r="M183" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="184" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B184" t="s">
-        <v>60</v>
-      </c>
-      <c r="C184" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="185" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="D185" t="s">
-        <v>68</v>
-      </c>
-      <c r="F185" t="s">
-        <v>317</v>
-      </c>
-      <c r="G185" t="s">
-        <v>310</v>
-      </c>
-      <c r="H185" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="186" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B186" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="187" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="D187" t="s">
-        <v>102</v>
-      </c>
-      <c r="E187" t="s">
-        <v>251</v>
-      </c>
-      <c r="F187" t="s">
-        <v>318</v>
-      </c>
-      <c r="G187" t="s">
-        <v>319</v>
-      </c>
-      <c r="H187" t="s">
-        <v>320</v>
-      </c>
-      <c r="K187" t="s">
-        <v>321</v>
-      </c>
-      <c r="L187" t="s">
-        <v>205</v>
-      </c>
-      <c r="M187" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="188" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B188" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="189" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B189" t="s">
-        <v>60</v>
-      </c>
-      <c r="C189" t="s">
-        <v>322</v>
-      </c>
-      <c r="S189" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="190" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B190" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="191" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="D191" t="s">
-        <v>45</v>
-      </c>
-      <c r="F191" t="s">
-        <v>324</v>
-      </c>
-      <c r="I191">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="192" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="D192" t="s">
-        <v>160</v>
-      </c>
-      <c r="G192" t="s">
-        <v>325</v>
-      </c>
-      <c r="H192" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="193" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B193" t="s">
-        <v>60</v>
-      </c>
-      <c r="C193" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="194" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="D194" t="s">
-        <v>160</v>
-      </c>
-      <c r="G194" t="s">
-        <v>327</v>
-      </c>
-      <c r="H194" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="195" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B195" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="196" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B196" t="s">
-        <v>60</v>
-      </c>
-      <c r="C196" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="197" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="D197" t="s">
-        <v>160</v>
-      </c>
-      <c r="G197" t="s">
-        <v>329</v>
-      </c>
-      <c r="H197" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="198" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B198" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="199" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B199" t="s">
-        <v>60</v>
-      </c>
-      <c r="C199" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="200" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="D200" t="s">
-        <v>160</v>
-      </c>
-      <c r="G200" t="s">
-        <v>332</v>
-      </c>
-      <c r="H200" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="201" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B201" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="202" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B202" t="s">
-        <v>60</v>
-      </c>
-      <c r="C202" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="203" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="D203" t="s">
-        <v>160</v>
-      </c>
-      <c r="G203" t="s">
-        <v>335</v>
-      </c>
-      <c r="H203" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="204" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B204" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="205" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B205" t="s">
-        <v>60</v>
-      </c>
-      <c r="C205" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="206" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="D206" t="s">
-        <v>160</v>
-      </c>
-      <c r="G206" t="s">
-        <v>338</v>
-      </c>
-      <c r="H206" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="207" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B207" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="208" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="L207" t="s">
+        <v>203</v>
+      </c>
+      <c r="M207" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="208" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B208" t="s">
         <v>60</v>
       </c>
       <c r="C208" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="209" spans="2:20" x14ac:dyDescent="0.35">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="209" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D209" t="s">
-        <v>160</v>
+        <v>68</v>
+      </c>
+      <c r="F209" t="s">
+        <v>315</v>
       </c>
       <c r="G209" t="s">
-        <v>341</v>
+        <v>308</v>
       </c>
       <c r="H209" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="210" spans="2:20" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="210" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B210" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="211" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B211" t="s">
+    <row r="211" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="D211" t="s">
+        <v>102</v>
+      </c>
+      <c r="E211" t="s">
+        <v>249</v>
+      </c>
+      <c r="F211" t="s">
+        <v>316</v>
+      </c>
+      <c r="G211" t="s">
+        <v>317</v>
+      </c>
+      <c r="H211" t="s">
+        <v>318</v>
+      </c>
+      <c r="K211" t="s">
+        <v>319</v>
+      </c>
+      <c r="L211" t="s">
+        <v>203</v>
+      </c>
+      <c r="M211" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="212" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B212" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="213" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B213" t="s">
         <v>60</v>
       </c>
-      <c r="C211" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="212" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="D212" t="s">
-        <v>160</v>
-      </c>
-      <c r="G212" t="s">
-        <v>344</v>
-      </c>
-      <c r="H212" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="213" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B213" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="214" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="C213" t="s">
+        <v>320</v>
+      </c>
+      <c r="S213" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="214" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B214" t="s">
-        <v>60</v>
-      </c>
-      <c r="C214" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="215" spans="2:20" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="215" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D215" t="s">
-        <v>160</v>
-      </c>
-      <c r="G215" t="s">
-        <v>346</v>
-      </c>
-      <c r="H215" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="216" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B216" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="217" spans="2:20" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="F215" t="s">
+        <v>322</v>
+      </c>
+      <c r="I215">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="D216" t="s">
+        <v>158</v>
+      </c>
+      <c r="G216" t="s">
+        <v>323</v>
+      </c>
+      <c r="H216" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="217" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B217" t="s">
         <v>60</v>
       </c>
       <c r="C217" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="218" spans="2:20" x14ac:dyDescent="0.35">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="218" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D218" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G218" t="s">
-        <v>349</v>
+        <v>325</v>
       </c>
       <c r="H218" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="219" spans="2:20" x14ac:dyDescent="0.35">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="219" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B219" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="221" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B221" t="s">
+    <row r="220" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B220" t="s">
         <v>60</v>
       </c>
-      <c r="C221" t="s">
+      <c r="C220" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="221" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="D221" t="s">
+        <v>158</v>
+      </c>
+      <c r="G221" t="s">
+        <v>327</v>
+      </c>
+      <c r="H221" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="222" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B222" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="223" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="B223" t="s">
+        <v>60</v>
+      </c>
+      <c r="C223" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="224" spans="2:19" x14ac:dyDescent="0.35">
+      <c r="D224" t="s">
+        <v>158</v>
+      </c>
+      <c r="G224" t="s">
+        <v>330</v>
+      </c>
+      <c r="H224" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="225" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B225" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="226" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B226" t="s">
+        <v>60</v>
+      </c>
+      <c r="C226" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="227" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D227" t="s">
+        <v>158</v>
+      </c>
+      <c r="G227" t="s">
+        <v>333</v>
+      </c>
+      <c r="H227" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="228" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B228" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="229" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B229" t="s">
+        <v>60</v>
+      </c>
+      <c r="C229" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="230" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D230" t="s">
+        <v>158</v>
+      </c>
+      <c r="G230" t="s">
+        <v>336</v>
+      </c>
+      <c r="H230" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="231" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B231" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="232" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B232" t="s">
+        <v>60</v>
+      </c>
+      <c r="C232" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="233" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D233" t="s">
+        <v>158</v>
+      </c>
+      <c r="G233" t="s">
+        <v>339</v>
+      </c>
+      <c r="H233" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="234" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B234" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="235" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B235" t="s">
+        <v>60</v>
+      </c>
+      <c r="C235" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="236" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D236" t="s">
+        <v>158</v>
+      </c>
+      <c r="G236" t="s">
+        <v>342</v>
+      </c>
+      <c r="H236" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="237" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B237" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="238" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B238" t="s">
+        <v>60</v>
+      </c>
+      <c r="C238" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="239" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="D239" t="s">
+        <v>158</v>
+      </c>
+      <c r="G239" t="s">
+        <v>344</v>
+      </c>
+      <c r="H239" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="240" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B240" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="241" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B241" t="s">
+        <v>60</v>
+      </c>
+      <c r="C241" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="242" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="D242" t="s">
+        <v>158</v>
+      </c>
+      <c r="G242" t="s">
+        <v>347</v>
+      </c>
+      <c r="H242" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="243" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B243" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="245" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B245" t="s">
+        <v>60</v>
+      </c>
+      <c r="C245" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="246" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="D246" t="s">
+        <v>158</v>
+      </c>
+      <c r="G246" t="s">
+        <v>159</v>
+      </c>
+      <c r="H246" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="247" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B247" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="248" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B248" t="s">
+        <v>60</v>
+      </c>
+      <c r="C248" t="s">
+        <v>504</v>
+      </c>
+      <c r="S248" t="s">
+        <v>60</v>
+      </c>
+      <c r="T248" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="249" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="C249" s="2"/>
+      <c r="D249" t="s">
+        <v>158</v>
+      </c>
+      <c r="G249" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="222" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="D222" t="s">
-        <v>160</v>
-      </c>
-      <c r="G222" t="s">
-        <v>161</v>
-      </c>
-      <c r="H222" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="223" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B223" t="s">
+      <c r="H249" t="s">
+        <v>505</v>
+      </c>
+      <c r="U249" t="s">
+        <v>158</v>
+      </c>
+      <c r="X249" t="s">
+        <v>349</v>
+      </c>
+      <c r="Y249" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="250" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B250" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="224" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B224" t="s">
-        <v>60</v>
-      </c>
-      <c r="C224" t="s">
-        <v>506</v>
-      </c>
-      <c r="S224" t="s">
-        <v>60</v>
-      </c>
-      <c r="T224" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="225" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="C225" s="2"/>
-      <c r="D225" t="s">
-        <v>160</v>
-      </c>
-      <c r="G225" t="s">
-        <v>505</v>
-      </c>
-      <c r="H225" t="s">
-        <v>507</v>
-      </c>
-      <c r="U225" t="s">
-        <v>160</v>
-      </c>
-      <c r="X225" t="s">
-        <v>351</v>
-      </c>
-      <c r="Y225" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="226" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B226" t="s">
+      <c r="S250" t="s">
         <v>50</v>
       </c>
-      <c r="S226" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="231" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B231" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="232" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B232" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="233" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B233" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="234" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="D234" t="s">
-        <v>82</v>
-      </c>
-      <c r="F234" t="s">
-        <v>353</v>
-      </c>
-      <c r="G234" t="s">
-        <v>354</v>
-      </c>
-      <c r="H234" t="s">
-        <v>355</v>
-      </c>
-      <c r="K234" t="s">
-        <v>356</v>
-      </c>
-      <c r="L234" t="s">
-        <v>357</v>
-      </c>
-      <c r="M234" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="235" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="D235" t="s">
-        <v>82</v>
-      </c>
-      <c r="F235" t="s">
-        <v>359</v>
-      </c>
-      <c r="G235" t="s">
-        <v>360</v>
-      </c>
-      <c r="H235" t="s">
-        <v>361</v>
-      </c>
-      <c r="K235" t="s">
-        <v>362</v>
-      </c>
-      <c r="L235" t="s">
-        <v>363</v>
-      </c>
-      <c r="M235" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="236" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="D236" t="s">
-        <v>45</v>
-      </c>
-      <c r="F236" t="s">
-        <v>365</v>
-      </c>
-      <c r="I236" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="237" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="D237" t="s">
-        <v>160</v>
-      </c>
-      <c r="G237" t="s">
-        <v>367</v>
-      </c>
-      <c r="H237" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="238" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="D238" t="s">
-        <v>45</v>
-      </c>
-      <c r="F238" t="s">
-        <v>324</v>
-      </c>
-      <c r="I238">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="239" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B239" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="240" spans="2:25" x14ac:dyDescent="0.35">
-      <c r="B240" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="241" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D241" t="s">
-        <v>45</v>
-      </c>
-      <c r="F241" t="s">
-        <v>369</v>
-      </c>
-      <c r="I241" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="242" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D242" t="s">
-        <v>51</v>
-      </c>
-      <c r="F242" t="s">
-        <v>369</v>
-      </c>
-      <c r="G242" t="s">
-        <v>371</v>
-      </c>
-      <c r="H242" t="s">
-        <v>372</v>
-      </c>
-      <c r="Q242" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D243" t="s">
-        <v>373</v>
-      </c>
-      <c r="F243" t="s">
-        <v>374</v>
-      </c>
-      <c r="G243" t="s">
-        <v>375</v>
-      </c>
-      <c r="H243" t="s">
-        <v>376</v>
-      </c>
-      <c r="K243" t="s">
-        <v>377</v>
-      </c>
-      <c r="L243" t="s">
-        <v>205</v>
-      </c>
-      <c r="M243" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="244" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D244" t="s">
-        <v>45</v>
-      </c>
-      <c r="F244" t="s">
-        <v>378</v>
-      </c>
-      <c r="I244" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="245" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D245" t="s">
-        <v>82</v>
-      </c>
-      <c r="F245" t="s">
-        <v>380</v>
-      </c>
-      <c r="G245" t="s">
-        <v>381</v>
-      </c>
-      <c r="H245" t="s">
-        <v>382</v>
-      </c>
-      <c r="K245" t="s">
-        <v>383</v>
-      </c>
-      <c r="L245" t="s">
-        <v>384</v>
-      </c>
-      <c r="M245" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="246" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D246" t="s">
-        <v>45</v>
-      </c>
-      <c r="F246" t="s">
-        <v>386</v>
-      </c>
-      <c r="I246" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="247" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D247" t="s">
-        <v>160</v>
-      </c>
-      <c r="G247" t="s">
-        <v>388</v>
-      </c>
-      <c r="H247" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="248" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B248" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="249" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B249" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="250" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B250" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="251" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D251" t="s">
-        <v>110</v>
-      </c>
-      <c r="E251" t="s">
-        <v>390</v>
-      </c>
-      <c r="F251" t="s">
-        <v>391</v>
-      </c>
-      <c r="G251" t="s">
-        <v>392</v>
-      </c>
-      <c r="H251" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="252" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B252" t="s">
-        <v>60</v>
-      </c>
-      <c r="C252" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="253" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="D253" t="s">
-        <v>110</v>
-      </c>
-      <c r="E253" t="s">
-        <v>395</v>
-      </c>
-      <c r="F253" t="s">
-        <v>396</v>
-      </c>
-      <c r="G253" t="s">
-        <v>397</v>
-      </c>
-      <c r="H253" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="254" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B254" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="255" spans="2:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="255" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B255" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="256" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="256" spans="2:25" x14ac:dyDescent="0.35">
       <c r="B256" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="257" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="257" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B257" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="258" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="258" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D258" t="s">
-        <v>160</v>
+        <v>82</v>
+      </c>
+      <c r="F258" t="s">
+        <v>351</v>
       </c>
       <c r="G258" t="s">
-        <v>399</v>
+        <v>352</v>
       </c>
       <c r="H258" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="259" spans="2:9" x14ac:dyDescent="0.35">
+        <v>353</v>
+      </c>
+      <c r="K258" t="s">
+        <v>354</v>
+      </c>
+      <c r="L258" t="s">
+        <v>355</v>
+      </c>
+      <c r="M258" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="259" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D259" t="s">
+        <v>82</v>
+      </c>
+      <c r="F259" t="s">
+        <v>357</v>
+      </c>
+      <c r="G259" t="s">
+        <v>358</v>
+      </c>
+      <c r="H259" t="s">
+        <v>359</v>
+      </c>
+      <c r="K259" t="s">
+        <v>360</v>
+      </c>
+      <c r="L259" t="s">
+        <v>361</v>
+      </c>
+      <c r="M259" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="260" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D260" t="s">
         <v>45</v>
       </c>
-      <c r="F259" t="s">
-        <v>324</v>
-      </c>
-      <c r="I259">
+      <c r="F260" t="s">
+        <v>363</v>
+      </c>
+      <c r="I260" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="261" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D261" t="s">
+        <v>158</v>
+      </c>
+      <c r="G261" t="s">
+        <v>365</v>
+      </c>
+      <c r="H261" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="262" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D262" t="s">
+        <v>45</v>
+      </c>
+      <c r="F262" t="s">
+        <v>322</v>
+      </c>
+      <c r="I262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B263" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="264" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B264" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="265" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D265" t="s">
+        <v>45</v>
+      </c>
+      <c r="F265" t="s">
+        <v>367</v>
+      </c>
+      <c r="I265" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="266" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D266" t="s">
+        <v>51</v>
+      </c>
+      <c r="F266" t="s">
+        <v>367</v>
+      </c>
+      <c r="G266" t="s">
+        <v>369</v>
+      </c>
+      <c r="H266" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q266" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D267" t="s">
+        <v>371</v>
+      </c>
+      <c r="F267" t="s">
+        <v>372</v>
+      </c>
+      <c r="G267" t="s">
+        <v>373</v>
+      </c>
+      <c r="H267" t="s">
+        <v>374</v>
+      </c>
+      <c r="K267" t="s">
+        <v>375</v>
+      </c>
+      <c r="L267" t="s">
+        <v>203</v>
+      </c>
+      <c r="M267" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="268" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D268" t="s">
+        <v>45</v>
+      </c>
+      <c r="F268" t="s">
+        <v>376</v>
+      </c>
+      <c r="I268" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="269" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D269" t="s">
+        <v>82</v>
+      </c>
+      <c r="F269" t="s">
+        <v>378</v>
+      </c>
+      <c r="G269" t="s">
+        <v>379</v>
+      </c>
+      <c r="H269" t="s">
+        <v>380</v>
+      </c>
+      <c r="K269" t="s">
+        <v>381</v>
+      </c>
+      <c r="L269" t="s">
+        <v>382</v>
+      </c>
+      <c r="M269" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="270" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D270" t="s">
+        <v>45</v>
+      </c>
+      <c r="F270" t="s">
+        <v>384</v>
+      </c>
+      <c r="I270" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="271" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="D271" t="s">
+        <v>158</v>
+      </c>
+      <c r="G271" t="s">
+        <v>386</v>
+      </c>
+      <c r="H271" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="272" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B272" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="273" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B273" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="274" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B274" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="275" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D275" t="s">
+        <v>110</v>
+      </c>
+      <c r="E275" t="s">
+        <v>388</v>
+      </c>
+      <c r="F275" t="s">
+        <v>389</v>
+      </c>
+      <c r="G275" t="s">
+        <v>390</v>
+      </c>
+      <c r="H275" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="276" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B276" t="s">
+        <v>60</v>
+      </c>
+      <c r="C276" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="277" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D277" t="s">
+        <v>110</v>
+      </c>
+      <c r="E277" t="s">
+        <v>393</v>
+      </c>
+      <c r="F277" t="s">
+        <v>394</v>
+      </c>
+      <c r="G277" t="s">
+        <v>395</v>
+      </c>
+      <c r="H277" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="278" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B278" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="279" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B279" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="280" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B280" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="281" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B281" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="282" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D282" t="s">
+        <v>158</v>
+      </c>
+      <c r="G282" t="s">
+        <v>397</v>
+      </c>
+      <c r="H282" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="283" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D283" t="s">
+        <v>45</v>
+      </c>
+      <c r="F283" t="s">
+        <v>322</v>
+      </c>
+      <c r="I283">
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B260" t="s">
+    <row r="284" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B284" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="261" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B261" t="s">
+    <row r="285" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B285" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4857,10 +5249,10 @@
   <sheetData>
     <row r="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4869,7 +5261,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -4881,10 +5273,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -4896,129 +5288,129 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B4" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B5" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B6" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B7" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D7" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B8" t="s">
         <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B9" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D9" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B10" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D10" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B11" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -5030,610 +5422,610 @@
         <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D12" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B13" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D13" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E13" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B14" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D14" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B15" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D15" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B16" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D16" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E16" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B17" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D17" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E17" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B18" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D18" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B19" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D19" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B20" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D20" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B21" t="str">
         <f>"6"</f>
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D21" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B22" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D22" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B23" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D23" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B24" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D24" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B25" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D25" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B26" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D26" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B27" t="str">
         <f>"6"</f>
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D27" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B28" t="str">
         <f>"7"</f>
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D28" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E28" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B29" t="str">
         <f>"8"</f>
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D29" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E29" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B30" t="str">
         <f>"9"</f>
         <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D30" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E30" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B31" t="str">
         <f>"10"</f>
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D31" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E31" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B32" t="str">
         <f>"11"</f>
         <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D32" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E32" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B33" t="str">
         <f>"12"</f>
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D33" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E33" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B34" t="str">
         <f>"13"</f>
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D34" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E34" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B35" t="str">
         <f>"14"</f>
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D35" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E35" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B36" t="str">
         <f>"15"</f>
         <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D36" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E36" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B37" t="str">
         <f>"16"</f>
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D37" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E37" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B38" t="str">
         <f>"17"</f>
         <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D38" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E38" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B39" t="str">
         <f>"18"</f>
         <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D39" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E39" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B40" t="str">
         <f>"77"</f>
         <v>77</v>
       </c>
       <c r="C40" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D40" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B41" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D41" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B42" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D42" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B43" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D43" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B44" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D44" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B45" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D45" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" ref="B46:B47" si="0">"99"</f>
         <v>99</v>
       </c>
       <c r="C46" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D46" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="0"/>
         <v>99</v>
       </c>
       <c r="C47" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D47" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B48" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D48" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B49" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D49" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -5645,10 +6037,10 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D50" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -5660,10 +6052,10 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D51" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -5675,10 +6067,10 @@
         <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D52" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -5690,25 +6082,82 @@
         <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D53" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B54" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D54" t="s">
-        <v>409</v>
+        <v>407</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>530</v>
+      </c>
+      <c r="B55" t="s">
+        <v>531</v>
+      </c>
+      <c r="C55" t="s">
+        <v>532</v>
+      </c>
+      <c r="D55" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>530</v>
+      </c>
+      <c r="B56" t="str">
+        <f>"2"</f>
+        <v>2</v>
+      </c>
+      <c r="C56" t="s">
+        <v>534</v>
+      </c>
+      <c r="D56" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>530</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="C57" t="s">
+        <v>537</v>
+      </c>
+      <c r="D57" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>520</v>
+      </c>
+      <c r="B58" t="s">
+        <v>531</v>
+      </c>
+      <c r="C58" t="s">
+        <v>540</v>
+      </c>
+      <c r="D58" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="78" spans="2:2" x14ac:dyDescent="0.35">
@@ -5999,7 +6448,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>29</v>
@@ -6007,10 +6456,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -6032,16 +6481,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
@@ -6049,13 +6498,13 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="C2" t="s">
-        <v>484</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="87" x14ac:dyDescent="0.35">
@@ -6063,13 +6512,13 @@
         <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -6091,13 +6540,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>24</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>40</v>
@@ -6108,13 +6557,13 @@
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -6125,7 +6574,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
@@ -6133,7 +6582,7 @@
     <col min="3" max="3" width="16.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
@@ -6141,15 +6590,15 @@
         <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B2" t="s">
         <v>110</v>
@@ -6158,10 +6607,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -6172,9 +6621,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B4" t="s">
         <v>82</v>
@@ -6183,7 +6632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>78</v>
       </c>
@@ -6194,7 +6643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>88</v>
       </c>
@@ -6205,7 +6654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -6216,20 +6665,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B9" t="s">
         <v>102</v>
@@ -6238,97 +6687,115 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>512</v>
+      </c>
+      <c r="B10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>527</v>
+      </c>
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>518</v>
+      </c>
+      <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>528</v>
+      </c>
+      <c r="B13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>519</v>
+      </c>
+      <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>529</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>92</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B16" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="C16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>97</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B17" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="C11" t="b">
+      <c r="C17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>164</v>
-      </c>
-      <c r="B12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>169</v>
-      </c>
-      <c r="B13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>274</v>
-      </c>
-      <c r="B14" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>369</v>
-      </c>
-      <c r="B16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>255</v>
-      </c>
-      <c r="B17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>271</v>
+        <v>162</v>
       </c>
       <c r="B18" t="s">
         <v>102</v>
@@ -6337,155 +6804,158 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="B19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>272</v>
+      </c>
+      <c r="B20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" t="s">
         <v>51</v>
       </c>
-      <c r="C19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>150</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>367</v>
+      </c>
+      <c r="B22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>253</v>
+      </c>
+      <c r="B23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>269</v>
+      </c>
+      <c r="B24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" t="s">
         <v>86</v>
       </c>
-      <c r="C20" t="b">
+      <c r="C26" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>391</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>389</v>
+      </c>
+      <c r="B27" t="s">
         <v>110</v>
       </c>
-      <c r="C21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>252</v>
-      </c>
-      <c r="B22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>374</v>
-      </c>
-      <c r="B23" t="s">
-        <v>373</v>
-      </c>
-      <c r="C23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>378</v>
-      </c>
-      <c r="B24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>125</v>
-      </c>
-      <c r="B25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>154</v>
-      </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>157</v>
-      </c>
-      <c r="B27" t="s">
-        <v>82</v>
-      </c>
       <c r="C27" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>132</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>86</v>
+        <v>521</v>
+      </c>
+      <c r="B28" t="s">
+        <v>68</v>
       </c>
       <c r="C28" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E28" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>324</v>
+        <v>250</v>
       </c>
       <c r="B29" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>372</v>
+      </c>
+      <c r="B30" t="s">
+        <v>371</v>
+      </c>
+      <c r="C30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>376</v>
+      </c>
+      <c r="B31" t="s">
         <v>45</v>
       </c>
-      <c r="C29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>247</v>
-      </c>
-      <c r="B30" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>318</v>
-      </c>
-      <c r="B31" t="s">
-        <v>102</v>
-      </c>
       <c r="C31" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>243</v>
+        <v>123</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
@@ -6493,10 +6963,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>317</v>
+        <v>152</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C33" t="b">
         <v>0</v>
@@ -6504,10 +6974,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C34" t="b">
         <v>0</v>
@@ -6515,21 +6985,21 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>107</v>
-      </c>
-      <c r="B35" t="s">
-        <v>68</v>
+        <v>130</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>86</v>
       </c>
       <c r="C35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>116</v>
+        <v>322</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="C36" t="b">
         <v>0</v>
@@ -6537,10 +7007,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>380</v>
+        <v>245</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="C37" t="b">
         <v>0</v>
@@ -6548,10 +7018,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>386</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="C38" t="b">
         <v>0</v>
@@ -6559,10 +7029,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="C39" t="b">
         <v>0</v>
@@ -6570,7 +7040,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>277</v>
+        <v>315</v>
       </c>
       <c r="B40" t="s">
         <v>68</v>
@@ -6581,7 +7051,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="B41" t="s">
         <v>68</v>
@@ -6592,10 +7062,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>312</v>
+        <v>107</v>
       </c>
       <c r="B42" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="C42" t="b">
         <v>0</v>
@@ -6603,10 +7073,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>304</v>
+        <v>116</v>
       </c>
       <c r="B43" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="C43" t="b">
         <v>0</v>
@@ -6614,10 +7084,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>365</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>68</v>
+        <v>378</v>
+      </c>
+      <c r="B44" t="s">
+        <v>82</v>
       </c>
       <c r="C44" t="b">
         <v>0</v>
@@ -6625,10 +7095,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>353</v>
+        <v>384</v>
       </c>
       <c r="B45" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="C45" t="b">
         <v>0</v>
@@ -6636,10 +7106,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>359</v>
+        <v>307</v>
       </c>
       <c r="B46" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C46" t="b">
         <v>0</v>
@@ -6647,10 +7117,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>134</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>82</v>
+        <v>275</v>
+      </c>
+      <c r="B47" t="s">
+        <v>68</v>
       </c>
       <c r="C47" t="b">
         <v>0</v>
@@ -6658,21 +7128,21 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
       <c r="B48" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>119</v>
+        <v>310</v>
       </c>
       <c r="B49" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C49" t="b">
         <v>0</v>
@@ -6680,21 +7150,21 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>122</v>
+        <v>302</v>
       </c>
       <c r="B50" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>265</v>
-      </c>
-      <c r="B51" t="s">
-        <v>102</v>
+        <v>363</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>68</v>
       </c>
       <c r="C51" t="b">
         <v>0</v>
@@ -6702,10 +7172,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>112</v>
+        <v>351</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="C52" t="b">
         <v>0</v>
@@ -6713,10 +7183,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>208</v>
+        <v>357</v>
       </c>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="C53" t="b">
         <v>0</v>
@@ -6724,10 +7194,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>104</v>
-      </c>
-      <c r="B54" t="s">
-        <v>102</v>
+        <v>132</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>82</v>
       </c>
       <c r="C54" t="b">
         <v>0</v>
@@ -6735,21 +7205,21 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>46</v>
+        <v>139</v>
       </c>
       <c r="B55" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="C55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>119</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C56" t="b">
         <v>0</v>
@@ -6757,21 +7227,21 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>187</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>110</v>
+        <v>120</v>
+      </c>
+      <c r="B57" t="s">
+        <v>86</v>
       </c>
       <c r="C57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>193</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>110</v>
+        <v>263</v>
+      </c>
+      <c r="B58" t="s">
+        <v>102</v>
       </c>
       <c r="C58" t="b">
         <v>0</v>
@@ -6779,9 +7249,9 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>198</v>
-      </c>
-      <c r="B59" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B59" t="s">
         <v>110</v>
       </c>
       <c r="C59" t="b">
@@ -6790,10 +7260,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="B60" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C60" t="b">
         <v>0</v>
@@ -6801,10 +7271,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>188</v>
+        <v>104</v>
       </c>
       <c r="B61" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C61" t="b">
         <v>0</v>
@@ -6812,10 +7282,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>194</v>
+        <v>46</v>
       </c>
       <c r="B62" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="C62" t="b">
         <v>0</v>
@@ -6823,10 +7293,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>228</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C63" t="b">
         <v>0</v>
@@ -6834,276 +7304,343 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>174</v>
-      </c>
-      <c r="B64" t="s">
+        <v>185</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>191</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>196</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>178</v>
+      </c>
+      <c r="B67" t="s">
+        <v>82</v>
+      </c>
+      <c r="C67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>186</v>
+      </c>
+      <c r="B68" t="s">
+        <v>82</v>
+      </c>
+      <c r="C68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>192</v>
+      </c>
+      <c r="B69" t="s">
+        <v>82</v>
+      </c>
+      <c r="C69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>226</v>
+      </c>
+      <c r="B70" t="s">
+        <v>68</v>
+      </c>
+      <c r="C70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>172</v>
+      </c>
+      <c r="B71" t="s">
         <v>102</v>
       </c>
-      <c r="C64" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>268</v>
-      </c>
-      <c r="B65" t="s">
+      <c r="C71" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>266</v>
+      </c>
+      <c r="B72" t="s">
         <v>102</v>
       </c>
-      <c r="C65" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+      <c r="C72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>492</v>
+      </c>
+      <c r="B73" t="s">
+        <v>102</v>
+      </c>
+      <c r="C73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>278</v>
+      </c>
+      <c r="B74" t="s">
+        <v>102</v>
+      </c>
+      <c r="C74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>290</v>
+      </c>
+      <c r="B75" t="s">
+        <v>102</v>
+      </c>
+      <c r="C75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>299</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="C76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>493</v>
+      </c>
+      <c r="B77" t="s">
+        <v>86</v>
+      </c>
+      <c r="C77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>283</v>
+      </c>
+      <c r="B78" t="s">
+        <v>86</v>
+      </c>
+      <c r="C78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>294</v>
+      </c>
+      <c r="B79" t="s">
+        <v>86</v>
+      </c>
+      <c r="C79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>494</v>
       </c>
-      <c r="B66" t="s">
-        <v>102</v>
-      </c>
-      <c r="C66" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>280</v>
-      </c>
-      <c r="B67" t="s">
-        <v>102</v>
-      </c>
-      <c r="C67" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>292</v>
-      </c>
-      <c r="B68" t="s">
-        <v>102</v>
-      </c>
-      <c r="C68" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>301</v>
-      </c>
-      <c r="B69" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="C69" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>495</v>
-      </c>
-      <c r="B70" t="s">
-        <v>86</v>
-      </c>
-      <c r="C70" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>285</v>
-      </c>
-      <c r="B71" t="s">
-        <v>86</v>
-      </c>
-      <c r="C71" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>296</v>
-      </c>
-      <c r="B72" t="s">
-        <v>86</v>
-      </c>
-      <c r="C72" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>496</v>
-      </c>
-      <c r="B73" t="s">
+      <c r="B80" t="s">
         <v>68</v>
       </c>
-      <c r="C73" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>289</v>
-      </c>
-      <c r="B74" t="s">
-        <v>68</v>
-      </c>
-      <c r="C74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>300</v>
-      </c>
-      <c r="B75" t="s">
-        <v>68</v>
-      </c>
-      <c r="C75" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>213</v>
-      </c>
-      <c r="B76" t="s">
-        <v>102</v>
-      </c>
-      <c r="C76" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>258</v>
-      </c>
-      <c r="B77" t="s">
-        <v>102</v>
-      </c>
-      <c r="C77" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B78" s="14"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>497</v>
-      </c>
-      <c r="B79" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="C79" t="b">
-        <v>1</v>
-      </c>
-      <c r="D79" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>499</v>
-      </c>
-      <c r="B80" s="14" t="s">
-        <v>102</v>
-      </c>
       <c r="C80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>500</v>
-      </c>
-      <c r="B81" s="14" t="s">
-        <v>102</v>
+        <v>287</v>
+      </c>
+      <c r="B81" t="s">
+        <v>68</v>
       </c>
       <c r="C81" t="b">
-        <v>1</v>
-      </c>
-      <c r="D81" t="s">
-        <v>434</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>501</v>
-      </c>
-      <c r="B82" s="14" t="s">
-        <v>102</v>
+        <v>298</v>
+      </c>
+      <c r="B82" t="s">
+        <v>68</v>
       </c>
       <c r="C82" t="b">
-        <v>1</v>
-      </c>
-      <c r="D82" t="s">
-        <v>434</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>262</v>
+        <v>211</v>
       </c>
       <c r="B83" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="C83" t="b">
         <v>0</v>
       </c>
-      <c r="D83" t="s">
-        <v>434</v>
-      </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B84" s="14"/>
+      <c r="A84" t="s">
+        <v>256</v>
+      </c>
+      <c r="B84" t="s">
+        <v>102</v>
+      </c>
+      <c r="C84" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>218</v>
-      </c>
-      <c r="B85" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="C85" t="b">
-        <v>0</v>
-      </c>
+      <c r="B85" s="14"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>221</v>
+        <v>495</v>
       </c>
       <c r="B86" s="14" t="s">
         <v>102</v>
       </c>
       <c r="C86" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D86" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B87" s="14"/>
+      <c r="A87" t="s">
+        <v>497</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C87" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B88" s="14"/>
+      <c r="A88" t="s">
+        <v>498</v>
+      </c>
+      <c r="B88" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C88" t="b">
+        <v>1</v>
+      </c>
+      <c r="D88" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B89" s="14"/>
+      <c r="A89" t="s">
+        <v>499</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C89" t="b">
+        <v>1</v>
+      </c>
+      <c r="D89" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B90" s="14"/>
+      <c r="A90" t="s">
+        <v>260</v>
+      </c>
+      <c r="B90" t="s">
+        <v>51</v>
+      </c>
+      <c r="C90" t="b">
+        <v>0</v>
+      </c>
+      <c r="D90" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B91" s="14"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B92" s="14"/>
+      <c r="A92" t="s">
+        <v>216</v>
+      </c>
+      <c r="B92" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C92" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B93" s="14"/>
+      <c r="A93" t="s">
+        <v>219</v>
+      </c>
+      <c r="B93" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C93" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B94" s="14"/>
+      <c r="A94" t="s">
+        <v>507</v>
+      </c>
+      <c r="B94" t="s">
+        <v>82</v>
+      </c>
+      <c r="C94" t="b">
+        <v>0</v>
+      </c>
+      <c r="D94" t="s">
+        <v>543</v>
+      </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B95" s="14"/>
@@ -7195,8 +7732,29 @@
     <row r="124" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B124" s="14"/>
     </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B125" s="14"/>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B126" s="14"/>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B127" s="14"/>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B128" s="14"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B129" s="14"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B130" s="14"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B131" s="14"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C77">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C84">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
